--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,15 +49,27 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.09.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>BALSU</x:t>
   </x:si>
   <x:si>
     <x:t>07.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
@@ -215,9 +227,6 @@
   </x:si>
   <x:si>
     <x:t>12.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.09.2026</x:t>
   </x:si>
   <x:si>
     <x:t>KLSYN</x:t>
@@ -1360,7 +1369,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K173"/>
+  <x:dimension ref="A1:K175"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1409,22 +1418,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>100000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>8.73</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1441,10 +1450,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>96033600</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>650000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>13</x:v>
@@ -1456,7 +1465,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>4.88</x:v>
+        <x:v>57.4</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>0</x:v>
@@ -1473,22 +1482,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>36000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>6.45</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1501,32 +1510,29 @@
       <x:c r="B5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C5" s="0">
-        <x:v>500000</x:v>
+      <x:c r="C5" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>15000000</x:v>
+        <x:v>96033600</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>4367500</x:v>
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>9</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="J5" s="0">
-        <x:v>8.74</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
@@ -1536,67 +1542,64 @@
       <x:c r="B6" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C6" s="0">
-        <x:v>100000</x:v>
+      <x:c r="C6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>13500000</x:v>
+        <x:v>36000000</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>2503000</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>25.36</x:v>
+        <x:v>6.27</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>25.03</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="C7" s="0">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E7" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F7" s="0">
+        <x:v>4367500</x:v>
+      </x:c>
+      <x:c r="G7" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H7" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I7" s="0">
+        <x:v>8.82</x:v>
+      </x:c>
+      <x:c r="J7" s="0">
+        <x:v>8.74</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>20746859</x:v>
-      </x:c>
-      <x:c r="D7" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E7" s="0">
-        <x:v>210000000</x:v>
-      </x:c>
-      <x:c r="F7" s="0">
-        <x:v>145013995</x:v>
-      </x:c>
-      <x:c r="G7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="0">
-        <x:v>3.7</x:v>
-      </x:c>
-      <x:c r="I7" s="0">
-        <x:v>6.9</x:v>
-      </x:c>
-      <x:c r="J7" s="0">
-        <x:v>6.99</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -1604,69 +1607,69 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>11397816</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>15000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>269900283</x:v>
+        <x:v>2503000</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>20.84</x:v>
+        <x:v>23.62</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>23.68</x:v>
+        <x:v>25.03</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="C9" s="0">
-        <x:v>1000000</x:v>
+        <x:v>20746859</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>50000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>500000000</x:v>
+        <x:v>210000000</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>8385000</x:v>
+        <x:v>145013995</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0.04</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>7.06</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>8.39</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1674,80 +1677,80 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>2300000</x:v>
+        <x:v>11397816</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>12000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>12000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1739216</x:v>
+        <x:v>269900283</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>3.83</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>14.19</x:v>
+        <x:v>19.1</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>0.76</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D11" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E11" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F11" s="0">
+        <x:v>8385000</x:v>
+      </x:c>
+      <x:c r="G11" s="0">
+        <x:v>2.05</x:v>
+      </x:c>
+      <x:c r="H11" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I11" s="0">
+        <x:v>6.8</x:v>
+      </x:c>
+      <x:c r="J11" s="0">
+        <x:v>8.39</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>4790000</x:v>
-      </x:c>
-      <x:c r="D11" s="0">
-        <x:v>12000000</x:v>
-      </x:c>
-      <x:c r="E11" s="0">
-        <x:v>12000000</x:v>
-      </x:c>
-      <x:c r="F11" s="0">
-        <x:v>7029498</x:v>
-      </x:c>
-      <x:c r="G11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="0">
-        <x:v>7.98</x:v>
-      </x:c>
-      <x:c r="I11" s="0">
-        <x:v>4.77</x:v>
-      </x:c>
-      <x:c r="J11" s="0">
-        <x:v>1.47</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="C12" s="0">
-        <x:v>4850000</x:v>
+        <x:v>2300000</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>12000000</x:v>
@@ -1756,19 +1759,19 @@
         <x:v>12000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3543837</x:v>
+        <x:v>1739216</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>8.08</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>14.4</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>34</x:v>
@@ -1779,34 +1782,34 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>4790000</x:v>
+      </x:c>
+      <x:c r="D13" s="0">
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="E13" s="0">
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="F13" s="0">
+        <x:v>7029498</x:v>
+      </x:c>
+      <x:c r="G13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="0">
+        <x:v>7.98</x:v>
+      </x:c>
+      <x:c r="I13" s="0">
+        <x:v>4.69</x:v>
+      </x:c>
+      <x:c r="J13" s="0">
+        <x:v>1.47</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>61493</x:v>
-      </x:c>
-      <x:c r="D13" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E13" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F13" s="0">
-        <x:v>3995647</x:v>
-      </x:c>
-      <x:c r="G13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="I13" s="0">
-        <x:v>66.1</x:v>
-      </x:c>
-      <x:c r="J13" s="0">
-        <x:v>64.98</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
@@ -1814,34 +1817,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>4850000</x:v>
+      </x:c>
+      <x:c r="D14" s="0">
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="E14" s="0">
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="F14" s="0">
+        <x:v>3543837</x:v>
+      </x:c>
+      <x:c r="G14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="0">
+        <x:v>8.08</x:v>
+      </x:c>
+      <x:c r="I14" s="0">
+        <x:v>13.8</x:v>
+      </x:c>
+      <x:c r="J14" s="0">
+        <x:v>0.73</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>20000000</x:v>
-      </x:c>
-      <x:c r="D14" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="E14" s="0">
-        <x:v>750000000</x:v>
-      </x:c>
-      <x:c r="F14" s="0">
-        <x:v>26500000</x:v>
-      </x:c>
-      <x:c r="G14" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="0">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="I14" s="0">
-        <x:v>1.34</x:v>
-      </x:c>
-      <x:c r="J14" s="0">
-        <x:v>1.33</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1851,29 +1854,32 @@
       <x:c r="B15" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C15" s="0">
+        <x:v>61493</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>150000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>33000000</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F15" s="0">
+        <x:v>3995647</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>0</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>128.7</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>0</x:v>
+        <x:v>64.98</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1881,34 +1887,34 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>100000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>50000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>500000000</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>613000</x:v>
+        <x:v>26500000</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>5.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>5.41</x:v>
+        <x:v>1.32</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>6.13</x:v>
+        <x:v>1.33</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1918,64 +1924,61 @@
       <x:c r="B17" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C17" s="0">
-        <x:v>10366031</x:v>
+      <x:c r="C17" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>25000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>240000000</x:v>
-      </x:c>
-      <x:c r="F17" s="0">
-        <x:v>102614742</x:v>
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>10.2</x:v>
+        <x:v>125.2</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>9.9</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>1800452</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>15000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>150000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>17447883</x:v>
+        <x:v>613000</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>3</x:v>
+        <x:v>5.26</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>9</x:v>
+        <x:v>5.28</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>9.69</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
         <x:v>46</x:v>
@@ -1988,96 +1991,99 @@
       <x:c r="B19" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C19" s="0">
+        <x:v>10366031</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>13409218</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F19" s="0">
+        <x:v>102614742</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>9.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>18.29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>0</x:v>
+        <x:v>9.9</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C20" s="0">
+        <x:v>1800452</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>55000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F20" s="0">
+        <x:v>17447883</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>5.09</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>0</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>1.67</x:v>
+        <x:v>8.82</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>0</x:v>
+        <x:v>9.69</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>200000</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>25000000</x:v>
+        <x:v>13409218</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>415500000</x:v>
-      </x:c>
-      <x:c r="F21" s="0">
-        <x:v>3174011</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>17.13</x:v>
+        <x:v>18.25</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>15.87</x:v>
-      </x:c>
-      <x:c r="K21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -2085,69 +2091,66 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>5017182</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>40000000</x:v>
+        <x:v>55000000</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F22" s="0">
-        <x:v>95092049</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>17.89</x:v>
+        <x:v>1.63</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>18.95</x:v>
-      </x:c>
-      <x:c r="K22" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B23" s="0" t="s">
+      <x:c r="C23" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D23" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="E23" s="0">
+        <x:v>415500000</x:v>
+      </x:c>
+      <x:c r="F23" s="0">
+        <x:v>3174011</x:v>
+      </x:c>
+      <x:c r="G23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I23" s="0">
+        <x:v>16.72</x:v>
+      </x:c>
+      <x:c r="J23" s="0">
+        <x:v>15.87</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>11393782</x:v>
-      </x:c>
-      <x:c r="D23" s="0">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="E23" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F23" s="0">
-        <x:v>39811519</x:v>
-      </x:c>
-      <x:c r="G23" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="0">
-        <x:v>0.65</x:v>
-      </x:c>
-      <x:c r="I23" s="0">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="J23" s="0">
-        <x:v>3.49</x:v>
-      </x:c>
-      <x:c r="K23" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -2158,31 +2161,31 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>2500000</x:v>
+        <x:v>6067182</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>2500000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>950421206</x:v>
+        <x:v>114062870</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>434.75</x:v>
+        <x:v>17.45</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>380.17</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -2190,328 +2193,331 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>179529</x:v>
+        <x:v>12760028</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>230000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>15000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>12528563</x:v>
+        <x:v>45251910</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>1.66</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>1.29</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>69.25</x:v>
+        <x:v>4.07</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>69.79</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>2501710</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>450000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>97116052</x:v>
+        <x:v>950421206</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>36.2</x:v>
+        <x:v>429.75</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>38.82</x:v>
+        <x:v>380.17</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="C27" s="0">
-        <x:v>57675584</x:v>
+        <x:v>181529</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>85125000</x:v>
+        <x:v>230000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>5000000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>2781852532</x:v>
+        <x:v>12667063</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>1.8</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>53.65</x:v>
+        <x:v>69.25</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>48.23</x:v>
+        <x:v>69.78</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="C28" s="0">
-        <x:v>49697313</x:v>
+        <x:v>2501710</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>25000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>450000000</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1701868254</x:v>
+        <x:v>97116052</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>1.68</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>36</x:v>
+        <x:v>35.86</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>34.24</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>57675584</x:v>
+      </x:c>
+      <x:c r="D29" s="0">
+        <x:v>85125000</x:v>
+      </x:c>
+      <x:c r="E29" s="0">
+        <x:v>5000000000</x:v>
+      </x:c>
+      <x:c r="F29" s="0">
+        <x:v>2781852532</x:v>
+      </x:c>
+      <x:c r="G29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="0">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="I29" s="0">
+        <x:v>52.25</x:v>
+      </x:c>
+      <x:c r="J29" s="0">
+        <x:v>48.23</x:v>
+      </x:c>
+      <x:c r="K29" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>324474</x:v>
-      </x:c>
-      <x:c r="D29" s="0">
-        <x:v>3000000</x:v>
-      </x:c>
-      <x:c r="E29" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F29" s="0">
-        <x:v>1781383</x:v>
-      </x:c>
-      <x:c r="G29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="0">
-        <x:v>0.08</x:v>
-      </x:c>
-      <x:c r="I29" s="0">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J29" s="0">
-        <x:v>5.49</x:v>
-      </x:c>
-      <x:c r="K29" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>7999148</x:v>
+        <x:v>49697313</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>15000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>300000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>168715651</x:v>
+        <x:v>1701868254</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2.11</x:v>
+        <x:v>1.68</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>24.72</x:v>
+        <x:v>35.14</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>21.09</x:v>
+        <x:v>34.24</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>201000</x:v>
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>21739600</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>350000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2071755</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>10.1</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>10.31</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C32" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1500000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F32" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F32" s="0">
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>9.15</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>0</x:v>
+        <x:v>21.09</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B33" s="0" t="s">
+      <x:c r="C33" s="0">
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="D33" s="0">
+        <x:v>21739600</x:v>
+      </x:c>
+      <x:c r="E33" s="0">
+        <x:v>350000000</x:v>
+      </x:c>
+      <x:c r="F33" s="0">
+        <x:v>2071755</x:v>
+      </x:c>
+      <x:c r="G33" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H33" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I33" s="0">
+        <x:v>9.96</x:v>
+      </x:c>
+      <x:c r="J33" s="0">
+        <x:v>10.31</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>1900000</x:v>
-      </x:c>
-      <x:c r="D33" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E33" s="0">
-        <x:v>65000000</x:v>
-      </x:c>
-      <x:c r="F33" s="0">
-        <x:v>14177000</x:v>
-      </x:c>
-      <x:c r="G33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H33" s="0">
-        <x:v>0.35</x:v>
-      </x:c>
-      <x:c r="I33" s="0">
-        <x:v>8.67</x:v>
-      </x:c>
-      <x:c r="J33" s="0">
-        <x:v>7.46</x:v>
-      </x:c>
-      <x:c r="K33" s="0" t="s">
-        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>26398084</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>13</x:v>
@@ -2523,7 +2529,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>178</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>0</x:v>
@@ -2531,690 +2537,687 @@
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>1900000</x:v>
+      </x:c>
+      <x:c r="D35" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E35" s="0">
+        <x:v>65000000</x:v>
+      </x:c>
+      <x:c r="F35" s="0">
+        <x:v>14177000</x:v>
+      </x:c>
+      <x:c r="G35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="0">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I35" s="0">
+        <x:v>8.55</x:v>
+      </x:c>
+      <x:c r="J35" s="0">
+        <x:v>7.46</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E35" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F35" s="0">
-        <x:v>127481195</x:v>
-      </x:c>
-      <x:c r="G35" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="0">
-        <x:v>0.82</x:v>
-      </x:c>
-      <x:c r="I35" s="0">
-        <x:v>20.06</x:v>
-      </x:c>
-      <x:c r="J35" s="0">
-        <x:v>7.13</x:v>
-      </x:c>
-      <x:c r="K35" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>970810</x:v>
+      <x:c r="C36" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>7300000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>225000000</x:v>
-      </x:c>
-      <x:c r="F36" s="0">
-        <x:v>28043898</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>22.98</x:v>
+        <x:v>160.2</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>28.89</x:v>
-      </x:c>
-      <x:c r="K36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>1001579</x:v>
-      </x:c>
-      <x:c r="D37" s="0">
-        <x:v>10000000</x:v>
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>15106723</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.56</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>9.33</x:v>
+        <x:v>20.3</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>15.08</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>970810</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>40000000</x:v>
+        <x:v>7300000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>225000000</x:v>
+      </x:c>
+      <x:c r="F38" s="0">
+        <x:v>28043898</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>4.48</x:v>
+        <x:v>22.66</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>0</x:v>
+        <x:v>28.89</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>1001579</x:v>
+      </x:c>
+      <x:c r="D39" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E39" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F39" s="0">
+        <x:v>15106723</x:v>
+      </x:c>
+      <x:c r="G39" s="0">
+        <x:v>2.56</x:v>
+      </x:c>
+      <x:c r="H39" s="0">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="I39" s="0">
+        <x:v>9.07</x:v>
+      </x:c>
+      <x:c r="J39" s="0">
+        <x:v>15.08</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>2097370</x:v>
-      </x:c>
-      <x:c r="D39" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E39" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F39" s="0">
-        <x:v>48772185</x:v>
-      </x:c>
-      <x:c r="G39" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H39" s="0">
-        <x:v>2.78</x:v>
-      </x:c>
-      <x:c r="I39" s="0">
-        <x:v>20.72</x:v>
-      </x:c>
-      <x:c r="J39" s="0">
-        <x:v>23.25</x:v>
-      </x:c>
-      <x:c r="K39" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>28952670</x:v>
+      <x:c r="C40" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>80000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F40" s="0">
-        <x:v>810882777</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>1.11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>40.54</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="J40" s="0">
-        <x:v>28.01</x:v>
-      </x:c>
-      <x:c r="K40" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="C41" s="0">
-        <x:v>7024156</x:v>
+        <x:v>2097370</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>80000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>93719334</x:v>
+        <x:v>48772185</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>0.78</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>11.42</x:v>
+        <x:v>21.14</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>13.34</x:v>
+        <x:v>23.25</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="C42" s="0">
-        <x:v>3500000</x:v>
+        <x:v>28964237</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>49400000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>137144284</x:v>
+        <x:v>811351010</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>0.71</x:v>
+        <x:v>1.11</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>37.4</x:v>
+        <x:v>40.78</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>39.18</x:v>
+        <x:v>28.01</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="C43" s="0">
-        <x:v>3753472</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>6000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>432000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>224929072</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>0.91</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>61.7</x:v>
+        <x:v>11.06</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>59.93</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>3189049</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>4000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>400000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>154328962</x:v>
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>3.74</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>5.65</x:v>
+        <x:v>38.52</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>48.39</x:v>
+        <x:v>39.18</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>3753472</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>35000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>432000000</x:v>
+      </x:c>
+      <x:c r="F45" s="0">
+        <x:v>224929072</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>0</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>3.91</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>0</x:v>
+        <x:v>59.93</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>3540000</x:v>
+        <x:v>3189049</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>10000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>159604563</x:v>
+        <x:v>154328962</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>21.58</x:v>
+        <x:v>5.44</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>45.09</x:v>
+        <x:v>48.39</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C47" s="0">
-        <x:v>17973248</x:v>
+      <x:c r="C47" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D47" s="0">
         <x:v>35000000</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F47" s="0">
-        <x:v>157359225</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>4.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>9.16</x:v>
+        <x:v>3.72</x:v>
       </x:c>
       <x:c r="J47" s="0">
-        <x:v>8.76</x:v>
-      </x:c>
-      <x:c r="K47" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="C48" s="0">
-        <x:v>236122</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1700000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>110000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>14609667</x:v>
+        <x:v>163043763</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>71.6</x:v>
+        <x:v>22.28</x:v>
       </x:c>
       <x:c r="J48" s="0">
-        <x:v>61.87</x:v>
+        <x:v>44.07</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>1000000</x:v>
+        <x:v>18183248</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>35000000</x:v>
+      </x:c>
+      <x:c r="E49" s="0">
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>21055375</x:v>
+        <x:v>159279425</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>0.29</x:v>
+        <x:v>4.55</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>17.9</x:v>
+        <x:v>8.96</x:v>
       </x:c>
       <x:c r="J49" s="0">
-        <x:v>21.06</x:v>
+        <x:v>8.76</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>236122</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2000000</x:v>
+        <x:v>1700000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F50" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>110000000</x:v>
+      </x:c>
+      <x:c r="F50" s="0">
+        <x:v>14609667</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>0</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>5.65</x:v>
+        <x:v>70.4</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>0</x:v>
+        <x:v>61.87</x:v>
+      </x:c>
+      <x:c r="K50" s="0" t="s">
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
+      <x:c r="C51" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>21055375</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
+        <x:v>17.87</x:v>
+      </x:c>
+      <x:c r="J51" s="0">
+        <x:v>21.06</x:v>
+      </x:c>
+      <x:c r="K51" s="0" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>104895788</x:v>
-      </x:c>
-      <x:c r="D51" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="E51" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F51" s="0">
-        <x:v>1026744716</x:v>
-      </x:c>
-      <x:c r="G51" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H51" s="0">
-        <x:v>1.17</x:v>
-      </x:c>
-      <x:c r="I51" s="0">
-        <x:v>12.18</x:v>
-      </x:c>
-      <x:c r="J51" s="0">
-        <x:v>9.79</x:v>
-      </x:c>
-      <x:c r="K51" s="0" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="C52" s="0">
-        <x:v>16445115</x:v>
+      <x:c r="C52" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>25000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F52" s="0">
-        <x:v>393919718</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>3.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>43.54</x:v>
+        <x:v>5.44</x:v>
       </x:c>
       <x:c r="J52" s="0">
-        <x:v>23.95</x:v>
-      </x:c>
-      <x:c r="K52" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>1110000</x:v>
+        <x:v>105404634</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>1100000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>587039028</x:v>
+        <x:v>1032884452</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>0.09</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>434.75</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="J53" s="0">
-        <x:v>528.86</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>24398659</x:v>
+        <x:v>16445115</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>40000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>850000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>590270273</x:v>
+        <x:v>393919718</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>0.94</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>40.54</x:v>
+        <x:v>44.5</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>24.19</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
         <x:v>127</x:v>
@@ -3222,69 +3225,69 @@
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>46563878</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>50000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>500007798</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>12.18</x:v>
+        <x:v>429.75</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>10.74</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>6611571</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>9000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>240000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>39750803</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>0.69</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>6.45</x:v>
+        <x:v>40.78</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>6.01</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
         <x:v>130</x:v>
@@ -3292,311 +3295,314 @@
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C57" s="0">
+        <x:v>46563878</x:v>
+      </x:c>
+      <x:c r="D57" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E57" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F57" s="0">
+        <x:v>500007798</x:v>
+      </x:c>
+      <x:c r="G57" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H57" s="0">
+        <x:v>0.52</x:v>
+      </x:c>
+      <x:c r="I57" s="0">
+        <x:v>12.4</x:v>
+      </x:c>
+      <x:c r="J57" s="0">
+        <x:v>10.74</x:v>
+      </x:c>
+      <x:c r="K57" s="0" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C57" s="0">
-        <x:v>2596120</x:v>
-      </x:c>
-      <x:c r="D57" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E57" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F57" s="0">
-        <x:v>66065196</x:v>
-      </x:c>
-      <x:c r="G57" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H57" s="0">
-        <x:v>1.36</x:v>
-      </x:c>
-      <x:c r="I57" s="0">
-        <x:v>18.96</x:v>
-      </x:c>
-      <x:c r="J57" s="0">
-        <x:v>25.45</x:v>
-      </x:c>
-      <x:c r="K57" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C58" s="0">
+        <x:v>6611571</x:v>
+      </x:c>
+      <x:c r="D58" s="0">
+        <x:v>9000000</x:v>
+      </x:c>
+      <x:c r="E58" s="0">
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F58" s="0">
+        <x:v>39750803</x:v>
+      </x:c>
+      <x:c r="G58" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58" s="0">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I58" s="0">
+        <x:v>6.27</x:v>
+      </x:c>
+      <x:c r="J58" s="0">
+        <x:v>6.01</x:v>
+      </x:c>
+      <x:c r="K58" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C58" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="D58" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E58" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F58" s="0">
-        <x:v>4455000</x:v>
-      </x:c>
-      <x:c r="G58" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H58" s="0">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="I58" s="0">
-        <x:v>3.99</x:v>
-      </x:c>
-      <x:c r="J58" s="0">
-        <x:v>4.46</x:v>
-      </x:c>
-      <x:c r="K58" s="0" t="s">
-        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>200000</x:v>
+        <x:v>2596120</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>13760000</x:v>
-      </x:c>
-      <x:c r="E59" s="0">
-        <x:v>300000000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F59" s="0">
-        <x:v>2564000</x:v>
+        <x:v>66065196</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1.36</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>6.9</x:v>
+        <x:v>18.4</x:v>
       </x:c>
       <x:c r="J59" s="0">
-        <x:v>12.82</x:v>
+        <x:v>25.45</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C60" s="0">
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D60" s="0">
         <x:v>30000000</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F60" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>400000000</x:v>
+      </x:c>
+      <x:c r="F60" s="0">
+        <x:v>4455000</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>30.22</x:v>
+        <x:v>3.93</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>0</x:v>
+        <x:v>4.46</x:v>
+      </x:c>
+      <x:c r="K60" s="0" t="s">
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D61" s="0">
+        <x:v>13760000</x:v>
+      </x:c>
+      <x:c r="E61" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F61" s="0">
+        <x:v>2564000</x:v>
+      </x:c>
+      <x:c r="G61" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I61" s="0">
+        <x:v>6.9</x:v>
+      </x:c>
+      <x:c r="J61" s="0">
+        <x:v>12.82</x:v>
+      </x:c>
+      <x:c r="K61" s="0" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C61" s="0">
-        <x:v>5831653</x:v>
-      </x:c>
-      <x:c r="D61" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E61" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F61" s="0">
-        <x:v>304086107</x:v>
-      </x:c>
-      <x:c r="G61" s="0">
-        <x:v>2.96</x:v>
-      </x:c>
-      <x:c r="H61" s="0">
-        <x:v>0.83</x:v>
-      </x:c>
-      <x:c r="I61" s="0">
-        <x:v>2.98</x:v>
-      </x:c>
-      <x:c r="J61" s="0">
-        <x:v>52.14</x:v>
-      </x:c>
-      <x:c r="K61" s="0" t="s">
-        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C62" s="0">
-        <x:v>14512000</x:v>
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D62" s="0">
-        <x:v>79451200</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E62" s="0">
         <x:v>1000000000</x:v>
       </x:c>
-      <x:c r="F62" s="0">
-        <x:v>575005862</x:v>
+      <x:c r="F62" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>1.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>37.5</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>39.62</x:v>
-      </x:c>
-      <x:c r="K62" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>3799828</x:v>
+        <x:v>5831653</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>3000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>300000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>177844244</x:v>
+        <x:v>304086107</x:v>
       </x:c>
       <x:c r="G63" s="0">
-        <x:v>3.75</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>0.95</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>23</x:v>
+        <x:v>2.84</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>46.8</x:v>
+        <x:v>52.14</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C64" s="0">
+        <x:v>14512000</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>15000000</x:v>
+        <x:v>79451200</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F64" s="0">
+        <x:v>575005862</x:v>
       </x:c>
       <x:c r="G64" s="0">
-        <x:v>5.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>25.36</x:v>
+        <x:v>37.52</x:v>
       </x:c>
       <x:c r="J64" s="0">
-        <x:v>0</x:v>
+        <x:v>39.62</x:v>
+      </x:c>
+      <x:c r="K64" s="0" t="s">
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>8337681</x:v>
+        <x:v>3799828</x:v>
       </x:c>
       <x:c r="D65" s="0">
-        <x:v>6500000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>100000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F65" s="0">
-        <x:v>37235183</x:v>
+        <x:v>177844244</x:v>
       </x:c>
       <x:c r="G65" s="0">
-        <x:v>1.43</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>3.78</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>4.47</x:v>
+        <x:v>46.8</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
@@ -3604,28 +3610,28 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>9275000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>950000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G66" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H66" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>38.94</x:v>
+        <x:v>24.98</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>0</x:v>
@@ -3633,66 +3639,66 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
       <x:c r="C67" s="0">
-        <x:v>1364000</x:v>
+        <x:v>8337681</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>23460000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>9000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>409075556</x:v>
+        <x:v>37235183</x:v>
       </x:c>
       <x:c r="G67" s="0">
-        <x:v>1.7</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>300.25</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>299.91</x:v>
+        <x:v>4.47</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>380000000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>950000000</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G68" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>20.92</x:v>
+        <x:v>37.84</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>0</x:v>
@@ -3700,287 +3706,284 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C69" s="0">
+        <x:v>1364000</x:v>
+      </x:c>
+      <x:c r="D69" s="0">
+        <x:v>23460000</x:v>
+      </x:c>
+      <x:c r="E69" s="0">
+        <x:v>9000000000</x:v>
+      </x:c>
+      <x:c r="F69" s="0">
+        <x:v>409075556</x:v>
+      </x:c>
+      <x:c r="G69" s="0">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H69" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I69" s="0">
+        <x:v>295.5</x:v>
+      </x:c>
+      <x:c r="J69" s="0">
+        <x:v>299.91</x:v>
+      </x:c>
+      <x:c r="K69" s="0" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C69" s="0">
-        <x:v>507440</x:v>
-      </x:c>
-      <x:c r="D69" s="0">
-        <x:v>2500000</x:v>
-      </x:c>
-      <x:c r="E69" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F69" s="0">
-        <x:v>42117724</x:v>
-      </x:c>
-      <x:c r="G69" s="0">
-        <x:v>2.67</x:v>
-      </x:c>
-      <x:c r="H69" s="0">
-        <x:v>0.54</x:v>
-      </x:c>
-      <x:c r="I69" s="0">
-        <x:v>277.75</x:v>
-      </x:c>
-      <x:c r="J69" s="0">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K69" s="0" t="s">
-        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C70" s="0">
-        <x:v>2000000</x:v>
+      <x:c r="C70" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>2000000</x:v>
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F70" s="0">
-        <x:v>81947000</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G70" s="0">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>34.38</x:v>
+        <x:v>20.58</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>40.97</x:v>
-      </x:c>
-      <x:c r="K70" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>9854768</x:v>
+        <x:v>507440</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F71" s="0">
-        <x:v>233360906</x:v>
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G71" s="0">
-        <x:v>0.63</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0.62</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>20.84</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>23.68</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>324474</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D72" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>30000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F72" s="0">
-        <x:v>1781383</x:v>
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>0.08</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>17</x:v>
+        <x:v>34.32</x:v>
       </x:c>
       <x:c r="J72" s="0">
-        <x:v>5.49</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F73" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C73" s="0">
+        <x:v>9854768</x:v>
+      </x:c>
+      <x:c r="D73" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E73" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F73" s="0">
+        <x:v>233360906</x:v>
       </x:c>
       <x:c r="G73" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>0</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>17.13</x:v>
+        <x:v>19.1</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>0</x:v>
+        <x:v>23.68</x:v>
+      </x:c>
+      <x:c r="K73" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C74" s="0">
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>100000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="F74" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F74" s="0">
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G74" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>5.46</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K74" s="0" t="s">
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>13000000</x:v>
+      <x:c r="C75" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E75" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F75" s="0">
-        <x:v>85838440</x:v>
+      <x:c r="E75" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>6.54</x:v>
+        <x:v>16.72</x:v>
       </x:c>
       <x:c r="J75" s="0">
-        <x:v>6.6</x:v>
-      </x:c>
-      <x:c r="K75" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C76" s="0">
-        <x:v>174500000</x:v>
-      </x:c>
-      <x:c r="D76" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D76" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F76" s="0">
-        <x:v>694527000</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>2.82</x:v>
+        <x:v>5.41</x:v>
       </x:c>
       <x:c r="J76" s="0">
-        <x:v>3.98</x:v>
-      </x:c>
-      <x:c r="K76" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>635229</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>13</x:v>
@@ -3989,570 +3992,573 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F77" s="0">
-        <x:v>11323561</x:v>
+        <x:v>85838440</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>0.33</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>18.96</x:v>
+        <x:v>6.36</x:v>
       </x:c>
       <x:c r="J77" s="0">
-        <x:v>17.83</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C78" s="0">
+        <x:v>174500000</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E78" s="0">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F78" s="0">
+        <x:v>694527000</x:v>
+      </x:c>
+      <x:c r="G78" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H78" s="0">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="I78" s="0">
+        <x:v>2.94</x:v>
+      </x:c>
+      <x:c r="J78" s="0">
+        <x:v>3.98</x:v>
+      </x:c>
+      <x:c r="K78" s="0" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="C78" s="0">
-        <x:v>130000</x:v>
-      </x:c>
-      <x:c r="D78" s="0">
-        <x:v>3500000</x:v>
-      </x:c>
-      <x:c r="E78" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F78" s="0">
-        <x:v>4947800</x:v>
-      </x:c>
-      <x:c r="G78" s="0">
-        <x:v>1.6</x:v>
-      </x:c>
-      <x:c r="H78" s="0">
-        <x:v>0.03</x:v>
-      </x:c>
-      <x:c r="I78" s="0">
-        <x:v>31.38</x:v>
-      </x:c>
-      <x:c r="J78" s="0">
-        <x:v>38.06</x:v>
-      </x:c>
-      <x:c r="K78" s="0" t="s">
-        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C79" s="0">
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E79" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F79" s="0">
+        <x:v>11323561</x:v>
+      </x:c>
+      <x:c r="G79" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H79" s="0">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="I79" s="0">
+        <x:v>18.4</x:v>
+      </x:c>
+      <x:c r="J79" s="0">
+        <x:v>17.83</x:v>
+      </x:c>
+      <x:c r="K79" s="0" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D79" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E79" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F79" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G79" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H79" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I79" s="0">
-        <x:v>223.8</x:v>
-      </x:c>
-      <x:c r="J79" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
       <x:c r="C80" s="0">
-        <x:v>447761</x:v>
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D80" s="0">
-        <x:v>3000000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>120000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>18415143</x:v>
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G80" s="0">
-        <x:v>0</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>33.74</x:v>
+        <x:v>31.78</x:v>
       </x:c>
       <x:c r="J80" s="0">
-        <x:v>41.13</x:v>
+        <x:v>38.06</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="C81" s="0">
-        <x:v>200000</x:v>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>2000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F81" s="0">
-        <x:v>4022593</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>1.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>4.41</x:v>
+        <x:v>221.9</x:v>
       </x:c>
       <x:c r="J81" s="0">
-        <x:v>20.11</x:v>
-      </x:c>
-      <x:c r="K81" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>946718</x:v>
+        <x:v>447761</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>20000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>500000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F82" s="0">
-        <x:v>37333519</x:v>
+        <x:v>18415143</x:v>
       </x:c>
       <x:c r="G82" s="0">
-        <x:v>7.55</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>46.88</x:v>
+        <x:v>33.6</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>39.43</x:v>
+        <x:v>41.13</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D83" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C83" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D83" s="0">
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E83" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F83" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F83" s="0">
+        <x:v>4022593</x:v>
       </x:c>
       <x:c r="G83" s="0">
-        <x:v>0</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>0</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>19.32</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="J83" s="0">
-        <x:v>0</x:v>
+        <x:v>20.11</x:v>
+      </x:c>
+      <x:c r="K83" s="0" t="s">
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>188</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>3043115</x:v>
+        <x:v>946718</x:v>
       </x:c>
       <x:c r="D84" s="0">
-        <x:v>50000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>49736990</x:v>
+        <x:v>37333519</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>0</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>21.88</x:v>
+        <x:v>43.6</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>16.34</x:v>
+        <x:v>39.43</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="C85" s="0">
-        <x:v>2382736</x:v>
+      <x:c r="C85" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F85" s="0">
-        <x:v>92635231</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>72.65</x:v>
+        <x:v>18.36</x:v>
       </x:c>
       <x:c r="J85" s="0">
-        <x:v>38.88</x:v>
-      </x:c>
-      <x:c r="K85" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C86" s="0">
+        <x:v>3043115</x:v>
       </x:c>
       <x:c r="D86" s="0">
-        <x:v>4191000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>160000000</x:v>
-      </x:c>
-      <x:c r="F86" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F86" s="0">
+        <x:v>49736990</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>53</x:v>
+        <x:v>21.74</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>0</x:v>
+        <x:v>16.34</x:v>
+      </x:c>
+      <x:c r="K86" s="0" t="s">
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="B87" s="0" t="s">
+      <x:c r="C87" s="0">
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E87" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F87" s="0">
+        <x:v>92635231</x:v>
+      </x:c>
+      <x:c r="G87" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H87" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I87" s="0">
+        <x:v>72.7</x:v>
+      </x:c>
+      <x:c r="J87" s="0">
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="K87" s="0" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="C87" s="0">
-        <x:v>4650000</x:v>
-      </x:c>
-      <x:c r="D87" s="0">
-        <x:v>75000000</x:v>
-      </x:c>
-      <x:c r="E87" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F87" s="0">
-        <x:v>49978950</x:v>
-      </x:c>
-      <x:c r="G87" s="0">
-        <x:v>1.67</x:v>
-      </x:c>
-      <x:c r="H87" s="0">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="I87" s="0">
-        <x:v>12.05</x:v>
-      </x:c>
-      <x:c r="J87" s="0">
-        <x:v>10.75</x:v>
-      </x:c>
-      <x:c r="K87" s="0" t="s">
-        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C88" s="0">
-        <x:v>806343</x:v>
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D88" s="0">
-        <x:v>1862500</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>75000000</x:v>
-      </x:c>
-      <x:c r="F88" s="0">
-        <x:v>30363861</x:v>
+        <x:v>160000000</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>34.68</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>37.66</x:v>
-      </x:c>
-      <x:c r="K88" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>199</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>310000</x:v>
+        <x:v>4650000</x:v>
       </x:c>
       <x:c r="D89" s="0">
-        <x:v>5000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="E89" s="0">
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F89" s="0">
-        <x:v>49980500</x:v>
+        <x:v>49978950</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>0</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>12.05</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>161.23</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>2000000</x:v>
+        <x:v>806343</x:v>
       </x:c>
       <x:c r="D90" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>100000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F90" s="0">
-        <x:v>31366572</x:v>
+        <x:v>30363861</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>0.4</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>9</x:v>
+        <x:v>34.54</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>15.68</x:v>
+        <x:v>37.66</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C91" s="0">
+        <x:v>310000</x:v>
+      </x:c>
+      <x:c r="D91" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E91" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F91" s="0">
+        <x:v>49980500</x:v>
+      </x:c>
+      <x:c r="G91" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H91" s="0">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="I91" s="0">
+        <x:v>11.7</x:v>
+      </x:c>
+      <x:c r="J91" s="0">
+        <x:v>161.23</x:v>
+      </x:c>
+      <x:c r="K91" s="0" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C91" s="0">
-        <x:v>1250000</x:v>
-      </x:c>
-      <x:c r="D91" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="E91" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F91" s="0">
-        <x:v>11187500</x:v>
-      </x:c>
-      <x:c r="G91" s="0">
-        <x:v>2.08</x:v>
-      </x:c>
-      <x:c r="H91" s="0">
-        <x:v>0.05</x:v>
-      </x:c>
-      <x:c r="I91" s="0">
-        <x:v>1.94</x:v>
-      </x:c>
-      <x:c r="J91" s="0">
-        <x:v>8.95</x:v>
-      </x:c>
-      <x:c r="K91" s="0" t="s">
-        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C92" s="0">
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D92" s="0">
-        <x:v>6950000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F92" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F92" s="0">
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.89</x:v>
+        <x:v>8.82</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>0</x:v>
+        <x:v>15.68</x:v>
+      </x:c>
+      <x:c r="K92" s="0" t="s">
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="C93" s="0">
-        <x:v>12500000</x:v>
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>12500000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>60000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>61582393</x:v>
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>5</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>2.07</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>4.93</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -4560,66 +4566,66 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="C94" s="0">
-        <x:v>2093944</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>220000000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>8500000000</x:v>
-      </x:c>
-      <x:c r="F94" s="0">
-        <x:v>200139168</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>103.7</x:v>
+        <x:v>3.58</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>95.58</x:v>
-      </x:c>
-      <x:c r="K94" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C95" s="0">
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D95" s="0">
-        <x:v>150000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="F95" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>60000000</x:v>
+      </x:c>
+      <x:c r="F95" s="0">
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>50</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>0</x:v>
+        <x:v>4.93</x:v>
+      </x:c>
+      <x:c r="K95" s="0" t="s">
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
@@ -4627,279 +4633,276 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>51245979</x:v>
+        <x:v>2093944</x:v>
       </x:c>
       <x:c r="D96" s="0">
-        <x:v>85000000</x:v>
+        <x:v>220000000</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>200000000</x:v>
+        <x:v>8500000000</x:v>
       </x:c>
       <x:c r="F96" s="0">
-        <x:v>125342407</x:v>
+        <x:v>200139168</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>2.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>1.31</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>2.87</x:v>
+        <x:v>102.4</x:v>
       </x:c>
       <x:c r="J96" s="0">
-        <x:v>2.45</x:v>
+        <x:v>95.58</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="C97" s="0">
-        <x:v>1584837</x:v>
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>2500000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F97" s="0">
-        <x:v>92450176</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>66.1</x:v>
+        <x:v>47.08</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>58.33</x:v>
-      </x:c>
-      <x:c r="K97" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>7999148</x:v>
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>11000000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E98" s="0">
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F98" s="0">
-        <x:v>168715651</x:v>
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>0</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>2.11</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>24.72</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>21.09</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>14000000</x:v>
+        <x:v>1584837</x:v>
       </x:c>
       <x:c r="D99" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>200000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F99" s="0">
-        <x:v>236130680</x:v>
+        <x:v>92450176</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>1.17</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>25.42</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>16.87</x:v>
+        <x:v>58.33</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>1700005</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D100" s="0">
-        <x:v>95000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>1425000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F100" s="0">
-        <x:v>20390731</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>0.18</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>5.41</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="J100" s="0">
-        <x:v>11.99</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>6000000</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>6000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F101" s="0">
-        <x:v>132286928</x:v>
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>0.16</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>16.48</x:v>
+        <x:v>24.58</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>22.05</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>1675000</x:v>
+        <x:v>1700005</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>9000000</x:v>
+        <x:v>95000000</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1425000000</x:v>
       </x:c>
       <x:c r="F102" s="0">
-        <x:v>114158717</x:v>
+        <x:v>20390731</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>7.81</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>80.6</x:v>
+        <x:v>5.28</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>68.15</x:v>
+        <x:v>11.99</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C103" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="D103" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E103" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F103" s="0">
+        <x:v>132286928</x:v>
+      </x:c>
+      <x:c r="G103" s="0">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="H103" s="0">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="I103" s="0">
+        <x:v>15.32</x:v>
+      </x:c>
+      <x:c r="J103" s="0">
+        <x:v>22.05</x:v>
+      </x:c>
+      <x:c r="K103" s="0" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="C103" s="0">
-        <x:v>1824868</x:v>
-      </x:c>
-      <x:c r="D103" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E103" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F103" s="0">
-        <x:v>64572720</x:v>
-      </x:c>
-      <x:c r="G103" s="0">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="H103" s="0">
-        <x:v>0.68</x:v>
-      </x:c>
-      <x:c r="I103" s="0">
-        <x:v>31.82</x:v>
-      </x:c>
-      <x:c r="J103" s="0">
-        <x:v>35.38</x:v>
-      </x:c>
-      <x:c r="K103" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
@@ -4907,66 +4910,69 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="C104" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C104" s="0">
+        <x:v>1675000</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>50000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E104" s="0">
         <x:v>500000000</x:v>
       </x:c>
-      <x:c r="F104" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F104" s="0">
+        <x:v>114158717</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>5</x:v>
+        <x:v>7.81</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>0</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>6.77</x:v>
+        <x:v>81.65</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>0</x:v>
+        <x:v>68.15</x:v>
+      </x:c>
+      <x:c r="K104" s="0" t="s">
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1824868</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>30000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F105" s="0">
-        <x:v>19787700</x:v>
+        <x:v>64572720</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>0.67</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>9.08</x:v>
+        <x:v>30.38</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>19.79</x:v>
+        <x:v>35.38</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
@@ -4974,34 +4980,31 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="C106" s="0">
-        <x:v>98551</x:v>
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D106" s="0">
-        <x:v>6500000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0">
-        <x:v>1295684</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>10.62</x:v>
+        <x:v>6.55</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>13.15</x:v>
-      </x:c>
-      <x:c r="K106" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -5009,31 +5012,31 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>6049315</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>15000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>150000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F107" s="0">
-        <x:v>66439559</x:v>
+        <x:v>19787700</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>0</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>11.26</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>10.98</x:v>
+        <x:v>19.79</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
         <x:v>222</x:v>
@@ -5041,212 +5044,212 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>37225000</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D108" s="0">
-        <x:v>12000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>150000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F108" s="0">
-        <x:v>149982056</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>8.99</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>3.45</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>1.67</x:v>
+        <x:v>10.59</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>4.03</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6049315</x:v>
       </x:c>
       <x:c r="D109" s="0">
-        <x:v>1000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>350000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F109" s="0">
-        <x:v>284578907</x:v>
+        <x:v>66439559</x:v>
       </x:c>
       <x:c r="G109" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>228.8</x:v>
+        <x:v>11.26</x:v>
       </x:c>
       <x:c r="J109" s="0">
-        <x:v>284.58</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>600000</x:v>
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>600000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>25000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F110" s="0">
-        <x:v>22814140</x:v>
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>0</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>0.15</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>5.83</x:v>
+        <x:v>1.63</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>38.02</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C111" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D111" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E111" s="0">
+        <x:v>350000000</x:v>
+      </x:c>
+      <x:c r="F111" s="0">
+        <x:v>284578907</x:v>
+      </x:c>
+      <x:c r="G111" s="0">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H111" s="0">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I111" s="0">
+        <x:v>234.7</x:v>
+      </x:c>
+      <x:c r="J111" s="0">
+        <x:v>284.58</x:v>
+      </x:c>
+      <x:c r="K111" s="0" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="C111" s="0">
-        <x:v>11703083</x:v>
-      </x:c>
-      <x:c r="D111" s="0">
-        <x:v>16000000</x:v>
-      </x:c>
-      <x:c r="E111" s="0">
-        <x:v>720000000</x:v>
-      </x:c>
-      <x:c r="F111" s="0">
-        <x:v>978644023</x:v>
-      </x:c>
-      <x:c r="G111" s="0">
-        <x:v>10.16</x:v>
-      </x:c>
-      <x:c r="H111" s="0">
-        <x:v>1.67</x:v>
-      </x:c>
-      <x:c r="I111" s="0">
-        <x:v>205.6</x:v>
-      </x:c>
-      <x:c r="J111" s="0">
-        <x:v>83.62</x:v>
-      </x:c>
-      <x:c r="K111" s="0" t="s">
-        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C112" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="D112" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="E112" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="F112" s="0">
+        <x:v>22814140</x:v>
+      </x:c>
+      <x:c r="G112" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H112" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="I112" s="0">
+        <x:v>5.9</x:v>
+      </x:c>
+      <x:c r="J112" s="0">
+        <x:v>38.02</x:v>
+      </x:c>
+      <x:c r="K112" s="0" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="C112" s="0">
-        <x:v>5100000</x:v>
-      </x:c>
-      <x:c r="D112" s="0">
-        <x:v>9000000</x:v>
-      </x:c>
-      <x:c r="E112" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F112" s="0">
-        <x:v>90022686</x:v>
-      </x:c>
-      <x:c r="G112" s="0">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="H112" s="0">
-        <x:v>4.31</x:v>
-      </x:c>
-      <x:c r="I112" s="0">
-        <x:v>31.4</x:v>
-      </x:c>
-      <x:c r="J112" s="0">
-        <x:v>17.65</x:v>
-      </x:c>
-      <x:c r="K112" s="0" t="s">
-        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C113" s="0">
+        <x:v>11703083</x:v>
+      </x:c>
+      <x:c r="D113" s="0">
+        <x:v>16000000</x:v>
+      </x:c>
+      <x:c r="E113" s="0">
+        <x:v>720000000</x:v>
+      </x:c>
+      <x:c r="F113" s="0">
+        <x:v>978644023</x:v>
+      </x:c>
+      <x:c r="G113" s="0">
+        <x:v>10.16</x:v>
+      </x:c>
+      <x:c r="H113" s="0">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="I113" s="0">
+        <x:v>215.8</x:v>
+      </x:c>
+      <x:c r="J113" s="0">
+        <x:v>83.62</x:v>
+      </x:c>
+      <x:c r="K113" s="0" t="s">
         <x:v>231</x:v>
-      </x:c>
-      <x:c r="C113" s="0">
-        <x:v>3228679</x:v>
-      </x:c>
-      <x:c r="D113" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E113" s="0">
-        <x:v>175000000</x:v>
-      </x:c>
-      <x:c r="F113" s="0">
-        <x:v>51395842</x:v>
-      </x:c>
-      <x:c r="G113" s="0">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="H113" s="0">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="I113" s="0">
-        <x:v>8.73</x:v>
-      </x:c>
-      <x:c r="J113" s="0">
-        <x:v>15.92</x:v>
-      </x:c>
-      <x:c r="K113" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
@@ -5254,31 +5257,31 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>150000</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>6000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>240000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F114" s="0">
-        <x:v>6145450</x:v>
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>0</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>0.02</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>5.39</x:v>
+        <x:v>30.48</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>40.97</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
         <x:v>233</x:v>
@@ -5286,34 +5289,37 @@
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C115" s="0">
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F115" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>175000000</x:v>
+      </x:c>
+      <x:c r="F115" s="0">
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>11.6</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="J115" s="0">
-        <x:v>0</x:v>
+        <x:v>15.92</x:v>
+      </x:c>
+      <x:c r="K115" s="0" t="s">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
@@ -5321,311 +5327,311 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>366107</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>1200000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>30000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F116" s="0">
-        <x:v>6010300</x:v>
+        <x:v>6145450</x:v>
       </x:c>
       <x:c r="G116" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>14.62</x:v>
+        <x:v>5.26</x:v>
       </x:c>
       <x:c r="J116" s="0">
-        <x:v>16.42</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C117" s="0">
-        <x:v>120000</x:v>
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>26398084</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F117" s="0">
-        <x:v>3830160</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F117" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>178</x:v>
+        <x:v>11.06</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>31.92</x:v>
-      </x:c>
-      <x:c r="K117" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>13050000</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>13050000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>1305000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F118" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G118" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>3.13</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>117.4</x:v>
+        <x:v>14.26</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>94.36</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
       <x:c r="C119" s="0">
-        <x:v>36605658</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D119" s="0">
+        <x:v>26398084</x:v>
+      </x:c>
+      <x:c r="E119" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="E119" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
       <x:c r="F119" s="0">
-        <x:v>174340918</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G119" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>3.66</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>4.65</x:v>
+        <x:v>160.2</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>4.76</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>1000000</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="D120" s="0">
-        <x:v>4000000</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>1305000000</x:v>
       </x:c>
       <x:c r="F120" s="0">
-        <x:v>429817200</x:v>
+        <x:v>1231340857</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>0.08</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>434.75</x:v>
+        <x:v>113.2</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>429.82</x:v>
+        <x:v>94.36</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>300000</x:v>
+        <x:v>36605658</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>60000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>171000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>791000</x:v>
+        <x:v>174340918</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>0.05</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>3</x:v>
+        <x:v>4.71</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>2.64</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>2175097</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>15000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>175000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>17901652</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>13.69</x:v>
+        <x:v>429.75</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>8.23</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C123" s="0">
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>50000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F123" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>171000000</x:v>
+      </x:c>
+      <x:c r="F123" s="0">
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>2.76</x:v>
+        <x:v>3.04</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>0</x:v>
+        <x:v>2.64</x:v>
+      </x:c>
+      <x:c r="K123" s="0" t="s">
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>43000</x:v>
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>200000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>5000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>1024885</x:v>
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>0.43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0.09</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>27.46</x:v>
+        <x:v>14.15</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>23.83</x:v>
+        <x:v>8.23</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -5633,372 +5639,372 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C125" s="0">
-        <x:v>9937037</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>11000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F125" s="0">
-        <x:v>50001023</x:v>
+        <x:v>152000000</x:v>
+      </x:c>
+      <x:c r="F125" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G125" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>0.53</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>2.31</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J125" s="0">
-        <x:v>5.03</x:v>
-      </x:c>
-      <x:c r="K125" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C126" s="0">
+        <x:v>43000</x:v>
+      </x:c>
+      <x:c r="D126" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="E126" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="F126" s="0">
+        <x:v>1024885</x:v>
+      </x:c>
+      <x:c r="G126" s="0">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="H126" s="0">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="I126" s="0">
+        <x:v>26.66</x:v>
+      </x:c>
+      <x:c r="J126" s="0">
+        <x:v>23.83</x:v>
+      </x:c>
+      <x:c r="K126" s="0" t="s">
         <x:v>247</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D126" s="0">
-        <x:v>5500000</x:v>
-      </x:c>
-      <x:c r="E126" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F126" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G126" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H126" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I126" s="0">
-        <x:v>2.65</x:v>
-      </x:c>
-      <x:c r="J126" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>13064888</x:v>
+        <x:v>9937037</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>30000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>600000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F127" s="0">
-        <x:v>268254173</x:v>
+        <x:v>50001023</x:v>
       </x:c>
       <x:c r="G127" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>40.54</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>20.53</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C128" s="0">
-        <x:v>111673026</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>150000000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F128" s="0">
-        <x:v>500005947</x:v>
+        <x:v>139000000</x:v>
+      </x:c>
+      <x:c r="F128" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>12.18</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>4.48</x:v>
-      </x:c>
-      <x:c r="K128" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D129" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C129" s="0">
+        <x:v>13064888</x:v>
+      </x:c>
+      <x:c r="D129" s="0">
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F129" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F129" s="0">
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>3.65</x:v>
+        <x:v>40.78</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>0</x:v>
+        <x:v>20.53</x:v>
+      </x:c>
+      <x:c r="K129" s="0" t="s">
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C130" s="0">
+        <x:v>111673026</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>19600000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>92000000</x:v>
-      </x:c>
-      <x:c r="F130" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F130" s="0">
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>0</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>7</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>0</x:v>
+        <x:v>4.48</x:v>
+      </x:c>
+      <x:c r="K130" s="0" t="s">
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C131" s="0">
-        <x:v>1100000</x:v>
-      </x:c>
-      <x:c r="D131" s="0">
-        <x:v>2000000</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F131" s="0">
-        <x:v>56064346</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F131" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>183.7</x:v>
+        <x:v>3.62</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>50.97</x:v>
-      </x:c>
-      <x:c r="K131" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C132" s="0">
-        <x:v>6598092</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D132" s="0">
-        <x:v>11160000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F132" s="0">
-        <x:v>72091269</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F132" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>5.91</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>17.13</x:v>
+        <x:v>6.85</x:v>
       </x:c>
       <x:c r="J132" s="0">
-        <x:v>10.93</x:v>
-      </x:c>
-      <x:c r="K132" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>1590000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D133" s="0">
-        <x:v>2160000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>35000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F133" s="0">
-        <x:v>60641600</x:v>
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>0.91</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>37.02</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J133" s="0">
-        <x:v>38.14</x:v>
+        <x:v>50.97</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>1989802</x:v>
+        <x:v>6598092</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>5000000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>250000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F134" s="0">
-        <x:v>78711752</x:v>
+        <x:v>72091269</x:v>
       </x:c>
       <x:c r="G134" s="0">
-        <x:v>2.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>1.17</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>141</x:v>
+        <x:v>16.72</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>39.56</x:v>
+        <x:v>10.93</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C135" s="0">
+        <x:v>1590000</x:v>
+      </x:c>
+      <x:c r="D135" s="0">
+        <x:v>2160000</x:v>
+      </x:c>
+      <x:c r="E135" s="0">
+        <x:v>35000000</x:v>
+      </x:c>
+      <x:c r="F135" s="0">
+        <x:v>60641600</x:v>
+      </x:c>
+      <x:c r="G135" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H135" s="0">
+        <x:v>0.91</x:v>
+      </x:c>
+      <x:c r="I135" s="0">
+        <x:v>36.26</x:v>
+      </x:c>
+      <x:c r="J135" s="0">
+        <x:v>38.14</x:v>
+      </x:c>
+      <x:c r="K135" s="0" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D135" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="E135" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F135" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G135" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H135" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I135" s="0">
-        <x:v>549.5</x:v>
-      </x:c>
-      <x:c r="J135" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
@@ -6006,69 +6012,66 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>300000</x:v>
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>67500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>326000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F136" s="0">
-        <x:v>1369300</x:v>
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G136" s="0">
-        <x:v>10</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>7.15</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>4.56</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="C137" s="0">
-        <x:v>76908759</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>12000000000</x:v>
-      </x:c>
-      <x:c r="F137" s="0">
-        <x:v>1979731803</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F137" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>38.08</x:v>
+        <x:v>543.5</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>25.74</x:v>
-      </x:c>
-      <x:c r="K137" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
@@ -6076,34 +6079,34 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>8291656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>11000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>200000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F138" s="0">
-        <x:v>126004459</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>16.61</x:v>
+        <x:v>7.01</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>15.2</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
@@ -6111,34 +6114,34 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C139" s="0">
+        <x:v>76908759</x:v>
+      </x:c>
+      <x:c r="D139" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="E139" s="0">
+        <x:v>12000000000</x:v>
+      </x:c>
+      <x:c r="F139" s="0">
+        <x:v>1979731803</x:v>
+      </x:c>
+      <x:c r="G139" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H139" s="0">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="I139" s="0">
+        <x:v>35.74</x:v>
+      </x:c>
+      <x:c r="J139" s="0">
+        <x:v>25.74</x:v>
+      </x:c>
+      <x:c r="K139" s="0" t="s">
         <x:v>263</x:v>
-      </x:c>
-      <x:c r="C139" s="0">
-        <x:v>2975773</x:v>
-      </x:c>
-      <x:c r="D139" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="E139" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F139" s="0">
-        <x:v>44771095</x:v>
-      </x:c>
-      <x:c r="G139" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H139" s="0">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="I139" s="0">
-        <x:v>24.28</x:v>
-      </x:c>
-      <x:c r="J139" s="0">
-        <x:v>15.05</x:v>
-      </x:c>
-      <x:c r="K139" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
@@ -6146,270 +6149,276 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>10994323</x:v>
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D140" s="0">
-        <x:v>21600000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>183002238</x:v>
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G140" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>5.09</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>13.59</x:v>
+        <x:v>16.23</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>16.65</x:v>
+        <x:v>15.2</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>36870641</x:v>
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>195000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F141" s="0">
-        <x:v>416172590</x:v>
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G141" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>1.89</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>16.7</x:v>
+        <x:v>23.42</x:v>
       </x:c>
       <x:c r="J141" s="0">
-        <x:v>11.29</x:v>
+        <x:v>15.05</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>268</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>5100000</x:v>
+        <x:v>10994323</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>20000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>700000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F142" s="0">
-        <x:v>155318227</x:v>
+        <x:v>183002238</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>6.81</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>0.93</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>59.9</x:v>
+        <x:v>13.52</x:v>
       </x:c>
       <x:c r="J142" s="0">
-        <x:v>30.45</x:v>
+        <x:v>16.65</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="C143" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C143" s="0">
+        <x:v>36870641</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>300000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>700000000</x:v>
-      </x:c>
-      <x:c r="F143" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2500000000</x:v>
+      </x:c>
+      <x:c r="F143" s="0">
+        <x:v>416172590</x:v>
       </x:c>
       <x:c r="G143" s="0">
-        <x:v>6.67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>0</x:v>
+        <x:v>1.89</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>2.04</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>0</x:v>
+        <x:v>11.29</x:v>
+      </x:c>
+      <x:c r="K143" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C144" s="0">
+        <x:v>5100000</x:v>
+      </x:c>
+      <x:c r="D144" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="E144" s="0">
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F144" s="0">
+        <x:v>155318227</x:v>
+      </x:c>
+      <x:c r="G144" s="0">
+        <x:v>6.81</x:v>
+      </x:c>
+      <x:c r="H144" s="0">
+        <x:v>0.93</x:v>
+      </x:c>
+      <x:c r="I144" s="0">
+        <x:v>59.25</x:v>
+      </x:c>
+      <x:c r="J144" s="0">
+        <x:v>30.45</x:v>
+      </x:c>
+      <x:c r="K144" s="0" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="C144" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="D144" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E144" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F144" s="0">
-        <x:v>39090077</x:v>
-      </x:c>
-      <x:c r="G144" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H144" s="0">
-        <x:v>0.21</x:v>
-      </x:c>
-      <x:c r="I144" s="0">
-        <x:v>10.2</x:v>
-      </x:c>
-      <x:c r="J144" s="0">
-        <x:v>7.82</x:v>
-      </x:c>
-      <x:c r="K144" s="0" t="s">
-        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="C145" s="0">
-        <x:v>905991</x:v>
+      <x:c r="C145" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>21000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F145" s="0">
-        <x:v>17447317</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F145" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G145" s="0">
-        <x:v>3</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>16.67</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>19.26</x:v>
-      </x:c>
-      <x:c r="K145" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="C146" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="D146" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E146" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F146" s="0">
+        <x:v>39090077</x:v>
+      </x:c>
+      <x:c r="G146" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H146" s="0">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="I146" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J146" s="0">
+        <x:v>7.82</x:v>
+      </x:c>
+      <x:c r="K146" s="0" t="s">
         <x:v>277</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D146" s="0">
-        <x:v>11700000</x:v>
-      </x:c>
-      <x:c r="E146" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F146" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G146" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H146" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I146" s="0">
-        <x:v>40.82</x:v>
-      </x:c>
-      <x:c r="J146" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C147" s="0">
+        <x:v>905991</x:v>
       </x:c>
       <x:c r="D147" s="0">
-        <x:v>1000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F147" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F147" s="0">
+        <x:v>17447317</x:v>
       </x:c>
       <x:c r="G147" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>0</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>549.5</x:v>
+        <x:v>16.3</x:v>
       </x:c>
       <x:c r="J147" s="0">
-        <x:v>0</x:v>
+        <x:v>19.26</x:v>
+      </x:c>
+      <x:c r="K147" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
@@ -6419,904 +6428,968 @@
       <x:c r="B148" s="0" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="C148" s="0">
-        <x:v>53584</x:v>
+      <x:c r="C148" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D148" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>640000000</x:v>
-      </x:c>
-      <x:c r="F148" s="0">
-        <x:v>8271098</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F148" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>254</x:v>
+        <x:v>39.68</x:v>
       </x:c>
       <x:c r="J148" s="0">
-        <x:v>154.36</x:v>
-      </x:c>
-      <x:c r="K148" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="C149" s="0">
-        <x:v>7550000</x:v>
+      <x:c r="C149" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D149" s="0">
-        <x:v>30000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F149" s="0">
-        <x:v>111777791</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F149" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G149" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>14.2</x:v>
+        <x:v>543.5</x:v>
       </x:c>
       <x:c r="J149" s="0">
-        <x:v>14.81</x:v>
-      </x:c>
-      <x:c r="K149" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>2097716</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>10112561</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>120000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F150" s="0">
-        <x:v>28985167</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G150" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>1.22</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="J150" s="0">
-        <x:v>13.82</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C151" s="0">
+        <x:v>7550000</x:v>
+      </x:c>
+      <x:c r="D151" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="E151" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F151" s="0">
+        <x:v>111777791</x:v>
+      </x:c>
+      <x:c r="G151" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H151" s="0">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="I151" s="0">
+        <x:v>14.23</x:v>
+      </x:c>
+      <x:c r="J151" s="0">
+        <x:v>14.81</x:v>
+      </x:c>
+      <x:c r="K151" s="0" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="C151" s="0">
-        <x:v>5185302</x:v>
-      </x:c>
-      <x:c r="D151" s="0">
-        <x:v>57000000</x:v>
-      </x:c>
-      <x:c r="E151" s="0">
-        <x:v>513000000</x:v>
-      </x:c>
-      <x:c r="F151" s="0">
-        <x:v>37061183</x:v>
-      </x:c>
-      <x:c r="G151" s="0">
-        <x:v>5.7</x:v>
-      </x:c>
-      <x:c r="H151" s="0">
-        <x:v>0.26</x:v>
-      </x:c>
-      <x:c r="I151" s="0">
-        <x:v>5.65</x:v>
-      </x:c>
-      <x:c r="J151" s="0">
-        <x:v>7.15</x:v>
-      </x:c>
-      <x:c r="K151" s="0" t="s">
-        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>290</x:v>
-      </x:c>
       <x:c r="C152" s="0">
-        <x:v>669111</x:v>
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D152" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>260000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F152" s="0">
-        <x:v>151220429</x:v>
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G152" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>781</x:v>
+        <x:v>1.19</x:v>
       </x:c>
       <x:c r="J152" s="0">
-        <x:v>226</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>38840</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>1000000</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>270000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F153" s="0">
-        <x:v>9431791</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G153" s="0">
-        <x:v>0</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>549.5</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="J153" s="0">
-        <x:v>242.84</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K153" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>2250000</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D154" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>300000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F154" s="0">
-        <x:v>31750000</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G154" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>14.2</x:v>
+        <x:v>777.5</x:v>
       </x:c>
       <x:c r="J154" s="0">
-        <x:v>14.11</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>293</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>1500000</x:v>
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D155" s="0">
-        <x:v>10112561</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>175000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F155" s="0">
-        <x:v>21870885</x:v>
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G155" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>1.22</x:v>
+        <x:v>543.5</x:v>
       </x:c>
       <x:c r="J155" s="0">
-        <x:v>14.58</x:v>
+        <x:v>242.84</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="B156" s="0" t="s">
+      <x:c r="C156" s="0">
+        <x:v>2250000</x:v>
+      </x:c>
+      <x:c r="D156" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="E156" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F156" s="0">
+        <x:v>31750000</x:v>
+      </x:c>
+      <x:c r="G156" s="0">
+        <x:v>4.98</x:v>
+      </x:c>
+      <x:c r="H156" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I156" s="0">
+        <x:v>14.23</x:v>
+      </x:c>
+      <x:c r="J156" s="0">
+        <x:v>14.11</x:v>
+      </x:c>
+      <x:c r="K156" s="0" t="s">
         <x:v>295</x:v>
-      </x:c>
-      <x:c r="C156" s="0">
-        <x:v>1430040</x:v>
-      </x:c>
-      <x:c r="D156" s="0">
-        <x:v>8299326</x:v>
-      </x:c>
-      <x:c r="E156" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F156" s="0">
-        <x:v>198303629</x:v>
-      </x:c>
-      <x:c r="G156" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H156" s="0">
-        <x:v>1.51</x:v>
-      </x:c>
-      <x:c r="I156" s="0">
-        <x:v>140.9</x:v>
-      </x:c>
-      <x:c r="J156" s="0">
-        <x:v>138.67</x:v>
-      </x:c>
-      <x:c r="K156" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C157" s="0">
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D157" s="0">
-        <x:v>2500000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F157" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>175000000</x:v>
+      </x:c>
+      <x:c r="F157" s="0">
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G157" s="0">
-        <x:v>2.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>0</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>277.75</x:v>
+        <x:v>1.19</x:v>
       </x:c>
       <x:c r="J157" s="0">
-        <x:v>0</x:v>
+        <x:v>14.58</x:v>
+      </x:c>
+      <x:c r="K157" s="0" t="s">
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>845945</x:v>
+        <x:v>1430040</x:v>
       </x:c>
       <x:c r="D158" s="0">
-        <x:v>15000000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>250000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F158" s="0">
-        <x:v>10058606</x:v>
+        <x:v>198303629</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>3.78</x:v>
+        <x:v>139.5</x:v>
       </x:c>
       <x:c r="J158" s="0">
-        <x:v>11.89</x:v>
+        <x:v>138.67</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="C159" s="0">
-        <x:v>21446</x:v>
+      <x:c r="C159" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D159" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F159" s="0">
-        <x:v>2015907</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F159" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G159" s="0">
-        <x:v>0</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>44.78</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="J159" s="0">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="K159" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>301</x:v>
-      </x:c>
       <x:c r="C160" s="0">
-        <x:v>850000</x:v>
+        <x:v>845945</x:v>
       </x:c>
       <x:c r="D160" s="0">
-        <x:v>4250000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>40000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F160" s="0">
-        <x:v>6548328</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G160" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>1</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>6.94</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="J160" s="0">
-        <x:v>7.7</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="C161" s="0">
-        <x:v>15000000</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D161" s="0">
-        <x:v>300000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>600000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F161" s="0">
-        <x:v>23990000</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>0.22</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>3.12</x:v>
+        <x:v>43.2</x:v>
       </x:c>
       <x:c r="J161" s="0">
-        <x:v>1.6</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K161" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>6397124</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D162" s="0">
-        <x:v>35300000</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>1046645000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F162" s="0">
-        <x:v>122892213</x:v>
+        <x:v>6548328</x:v>
       </x:c>
       <x:c r="G162" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>0.21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>4.06</x:v>
+        <x:v>6.89</x:v>
       </x:c>
       <x:c r="J162" s="0">
-        <x:v>19.21</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>17495257</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="D163" s="0">
-        <x:v>17500000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>525000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F163" s="0">
-        <x:v>409385433</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>5</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>17.9</x:v>
+        <x:v>3.07</x:v>
       </x:c>
       <x:c r="J163" s="0">
-        <x:v>23.4</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="C164" s="0">
+        <x:v>6397124</x:v>
+      </x:c>
+      <x:c r="D164" s="0">
+        <x:v>35300000</x:v>
+      </x:c>
+      <x:c r="E164" s="0">
+        <x:v>1046645000</x:v>
+      </x:c>
+      <x:c r="F164" s="0">
+        <x:v>122892213</x:v>
+      </x:c>
+      <x:c r="G164" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H164" s="0">
+        <x:v>0.21</x:v>
+      </x:c>
+      <x:c r="I164" s="0">
+        <x:v>3.94</x:v>
+      </x:c>
+      <x:c r="J164" s="0">
+        <x:v>19.21</x:v>
+      </x:c>
+      <x:c r="K164" s="0" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="C164" s="0">
-        <x:v>9350000</x:v>
-      </x:c>
-      <x:c r="D164" s="0">
-        <x:v>14710247</x:v>
-      </x:c>
-      <x:c r="E164" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F164" s="0">
-        <x:v>69547091</x:v>
-      </x:c>
-      <x:c r="G164" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H164" s="0">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="I164" s="0">
-        <x:v>2.3</x:v>
-      </x:c>
-      <x:c r="J164" s="0">
-        <x:v>7.44</x:v>
-      </x:c>
-      <x:c r="K164" s="0" t="s">
-        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D165" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>17495257</x:v>
+      </x:c>
+      <x:c r="D165" s="0">
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>100000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F165" s="0">
-        <x:v>75911475</x:v>
+        <x:v>409385433</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>0.37</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>23</x:v>
+        <x:v>17.87</x:v>
       </x:c>
       <x:c r="J165" s="0">
-        <x:v>51.7</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="C166" s="0">
+        <x:v>9350000</x:v>
+      </x:c>
+      <x:c r="D166" s="0">
+        <x:v>14710247</x:v>
+      </x:c>
+      <x:c r="E166" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F166" s="0">
+        <x:v>69547091</x:v>
+      </x:c>
+      <x:c r="G166" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H166" s="0">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="I166" s="0">
+        <x:v>2.25</x:v>
+      </x:c>
+      <x:c r="J166" s="0">
+        <x:v>7.44</x:v>
+      </x:c>
+      <x:c r="K166" s="0" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="C166" s="0">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="D166" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E166" s="0">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="F166" s="0">
-        <x:v>13401783</x:v>
-      </x:c>
-      <x:c r="G166" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H166" s="0">
-        <x:v>0.08</x:v>
-      </x:c>
-      <x:c r="I166" s="0">
-        <x:v>2.31</x:v>
-      </x:c>
-      <x:c r="J166" s="0">
-        <x:v>26.8</x:v>
-      </x:c>
-      <x:c r="K166" s="0" t="s">
-        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="C167" s="0">
+        <x:v>1468255</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E167" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F167" s="0">
+        <x:v>75911475</x:v>
+      </x:c>
+      <x:c r="G167" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H167" s="0">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="I167" s="0">
+        <x:v>22.74</x:v>
+      </x:c>
+      <x:c r="J167" s="0">
+        <x:v>51.7</x:v>
+      </x:c>
+      <x:c r="K167" s="0" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="C167" s="0">
-        <x:v>725000</x:v>
-      </x:c>
-      <x:c r="D167" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E167" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F167" s="0">
-        <x:v>48539975</x:v>
-      </x:c>
-      <x:c r="G167" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H167" s="0">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="I167" s="0">
-        <x:v>38.94</x:v>
-      </x:c>
-      <x:c r="J167" s="0">
-        <x:v>66.95</x:v>
-      </x:c>
-      <x:c r="K167" s="0" t="s">
-        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>319</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>1060056</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D168" s="0">
-        <x:v>7000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>250000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F168" s="0">
-        <x:v>60762934</x:v>
+        <x:v>13401783</x:v>
       </x:c>
       <x:c r="G168" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>0.44</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>223.8</x:v>
+        <x:v>2.23</x:v>
       </x:c>
       <x:c r="J168" s="0">
-        <x:v>57.32</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="C169" s="0">
+        <x:v>725000</x:v>
+      </x:c>
+      <x:c r="D169" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E169" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F169" s="0">
+        <x:v>48539975</x:v>
+      </x:c>
+      <x:c r="G169" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H169" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="I169" s="0">
+        <x:v>37.84</x:v>
+      </x:c>
+      <x:c r="J169" s="0">
+        <x:v>66.95</x:v>
+      </x:c>
+      <x:c r="K169" s="0" t="s">
         <x:v>321</x:v>
-      </x:c>
-      <x:c r="C169" s="0">
-        <x:v>132750000</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E169" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F169" s="0">
-        <x:v>565141750</x:v>
-      </x:c>
-      <x:c r="G169" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H169" s="0">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="I169" s="0">
-        <x:v>2.82</x:v>
-      </x:c>
-      <x:c r="J169" s="0">
-        <x:v>4.26</x:v>
-      </x:c>
-      <x:c r="K169" s="0" t="s">
-        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="B170" s="0" t="s">
+      <x:c r="C170" s="0">
+        <x:v>1060056</x:v>
+      </x:c>
+      <x:c r="D170" s="0">
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="E170" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F170" s="0">
+        <x:v>60762934</x:v>
+      </x:c>
+      <x:c r="G170" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H170" s="0">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I170" s="0">
+        <x:v>221.9</x:v>
+      </x:c>
+      <x:c r="J170" s="0">
+        <x:v>57.32</x:v>
+      </x:c>
+      <x:c r="K170" s="0" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="C170" s="0">
-        <x:v>373000</x:v>
-      </x:c>
-      <x:c r="D170" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="E170" s="0">
-        <x:v>75000000</x:v>
-      </x:c>
-      <x:c r="F170" s="0">
-        <x:v>23786370</x:v>
-      </x:c>
-      <x:c r="G170" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H170" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="I170" s="0">
-        <x:v>8.35</x:v>
-      </x:c>
-      <x:c r="J170" s="0">
-        <x:v>63.77</x:v>
-      </x:c>
-      <x:c r="K170" s="0" t="s">
-        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="D171" s="0">
-        <x:v>10000000</x:v>
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>140000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F171" s="0">
-        <x:v>133271568</x:v>
+        <x:v>565141750</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>10.46</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="J171" s="0">
-        <x:v>13.33</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>66142950</x:v>
+        <x:v>373000</x:v>
       </x:c>
       <x:c r="D172" s="0">
-        <x:v>105000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>650000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F172" s="0">
-        <x:v>384952260</x:v>
+        <x:v>23786370</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>2.71</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>7.06</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J172" s="0">
-        <x:v>5.82</x:v>
+        <x:v>63.77</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C173" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="D173" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E173" s="0">
+        <x:v>140000000</x:v>
+      </x:c>
+      <x:c r="F173" s="0">
+        <x:v>133271568</x:v>
+      </x:c>
+      <x:c r="G173" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H173" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I173" s="0">
+        <x:v>10.5</x:v>
+      </x:c>
+      <x:c r="J173" s="0">
+        <x:v>13.33</x:v>
+      </x:c>
+      <x:c r="K173" s="0" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="B173" s="0" t="s">
+    </x:row>
+    <x:row r="174" spans="1:11">
+      <x:c r="A174" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="C173" s="0">
+      <x:c r="C174" s="0">
+        <x:v>66142950</x:v>
+      </x:c>
+      <x:c r="D174" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="E174" s="0">
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F174" s="0">
+        <x:v>384952260</x:v>
+      </x:c>
+      <x:c r="G174" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H174" s="0">
+        <x:v>2.71</x:v>
+      </x:c>
+      <x:c r="I174" s="0">
+        <x:v>6.8</x:v>
+      </x:c>
+      <x:c r="J174" s="0">
+        <x:v>5.82</x:v>
+      </x:c>
+      <x:c r="K174" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:11">
+      <x:c r="A175" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C175" s="0">
         <x:v>3081843</x:v>
       </x:c>
-      <x:c r="D173" s="0">
+      <x:c r="D175" s="0">
         <x:v>5000000</x:v>
       </x:c>
-      <x:c r="E173" s="0">
+      <x:c r="E175" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F173" s="0">
+      <x:c r="F175" s="0">
         <x:v>43986444</x:v>
       </x:c>
-      <x:c r="G173" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H173" s="0">
+      <x:c r="G175" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H175" s="0">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="I173" s="0">
-        <x:v>5.67</x:v>
-      </x:c>
-      <x:c r="J173" s="0">
+      <x:c r="I175" s="0">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="J175" s="0">
         <x:v>14.27</x:v>
       </x:c>
-      <x:c r="K173" s="0" t="s">
-        <x:v>273</x:v>
+      <x:c r="K175" s="0" t="s">
+        <x:v>276</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -55,6 +55,9 @@
     <x:t>14.09.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
     <x:t/>
   </x:si>
   <x:si>
@@ -94,57 +97,57 @@
     <x:t>01.09.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.03.2020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.03.2020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.08.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>10.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23.03.2020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.03.2020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.08.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>OTTO</x:t>
   </x:si>
   <x:si>
@@ -710,9 +713,6 @@
   </x:si>
   <x:si>
     <x:t>11.07.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
   </x:si>
   <x:si>
     <x:t>17.11.2025</x:t>
@@ -1369,7 +1369,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K175"/>
+  <x:dimension ref="A1:K176"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1414,8 +1414,8 @@
       <x:c r="B2" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C2" s="0">
+        <x:v>14092</x:v>
       </x:c>
       <x:c r="D2" s="0">
         <x:v>1000000</x:v>
@@ -1423,49 +1423,52 @@
       <x:c r="E2" s="0">
         <x:v>300000000</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F2" s="0">
+        <x:v>4152925</x:v>
       </x:c>
       <x:c r="G2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>0</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>295</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="J2" s="0">
-        <x:v>0</x:v>
+        <x:v>294.7</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>20000000</x:v>
+        <x:v>2850000</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>0</x:v>
+        <x:v>2.41</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>57.4</x:v>
+        <x:v>29.76</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>0</x:v>
@@ -1473,31 +1476,31 @@
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>10000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>8.21</x:v>
+        <x:v>54.85</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1505,31 +1508,31 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>96033600</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>650000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>4.4</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1537,255 +1540,255 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C6" s="0">
+        <x:v>12450000</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>36000000</x:v>
+        <x:v>96033600</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>60880500</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>6.27</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>0</x:v>
+        <x:v>4.89</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>500000</x:v>
+      <x:c r="C7" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>15000000</x:v>
+        <x:v>36000000</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F7" s="0">
-        <x:v>4367500</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>8.82</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>8.74</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="C8" s="0">
-        <x:v>100000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>13500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>400000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>2503000</x:v>
+        <x:v>4367500</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>23.62</x:v>
+        <x:v>8.64</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>25.03</x:v>
+        <x:v>8.74</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>20746859</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>30000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>210000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>145013995</x:v>
+        <x:v>8213000</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>3.7</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>6.9</x:v>
+        <x:v>22.36</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>6.99</x:v>
+        <x:v>23.47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>11397816</x:v>
+        <x:v>20746859</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>15000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>210000000</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>269900283</x:v>
+        <x:v>145013995</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>0.71</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>19.1</x:v>
+        <x:v>6.87</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>23.68</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11397816</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>50000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>8385000</x:v>
+        <x:v>269900283</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.05</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>6.8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>8.39</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>2300000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>12000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>12000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>1739216</x:v>
+        <x:v>8385000</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>3.83</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>14.4</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>0.76</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>4790000</x:v>
+        <x:v>2300000</x:v>
       </x:c>
       <x:c r="D13" s="0">
         <x:v>12000000</x:v>
@@ -1794,33 +1797,33 @@
         <x:v>12000000</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>7029498</x:v>
+        <x:v>1739216</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>7.98</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>4.69</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>1.47</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>4850000</x:v>
+        <x:v>4790000</x:v>
       </x:c>
       <x:c r="D14" s="0">
         <x:v>12000000</x:v>
@@ -1829,226 +1832,226 @@
         <x:v>12000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>3543837</x:v>
+        <x:v>7029498</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>8.08</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>13.8</x:v>
+        <x:v>4.61</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>0.73</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>61493</x:v>
+        <x:v>4850000</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>2000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>250000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>3995647</x:v>
+        <x:v>3543837</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>0.04</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>66</x:v>
+        <x:v>12.79</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>64.98</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>20000000</x:v>
+        <x:v>61493</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>750000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>26500000</x:v>
+        <x:v>3995647</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>1.32</x:v>
+        <x:v>64.55</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>1.33</x:v>
+        <x:v>64.98</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="D17" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="E17" s="0">
+        <x:v>750000000</x:v>
+      </x:c>
+      <x:c r="F17" s="0">
+        <x:v>26500000</x:v>
+      </x:c>
+      <x:c r="G17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I17" s="0">
+        <x:v>1.29</x:v>
+      </x:c>
+      <x:c r="J17" s="0">
+        <x:v>1.33</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D17" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="E17" s="0">
-        <x:v>33000000</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G17" s="0">
-        <x:v>1.96</x:v>
-      </x:c>
-      <x:c r="H17" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="0">
-        <x:v>125.2</x:v>
-      </x:c>
-      <x:c r="J17" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>100000</x:v>
+      <x:c r="C18" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>50000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F18" s="0">
-        <x:v>613000</x:v>
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>5.26</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>5.28</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>6.13</x:v>
-      </x:c>
-      <x:c r="K18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="D19" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E19" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F19" s="0">
+        <x:v>613000</x:v>
+      </x:c>
+      <x:c r="G19" s="0">
+        <x:v>5.26</x:v>
+      </x:c>
+      <x:c r="H19" s="0">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="I19" s="0">
+        <x:v>5.35</x:v>
+      </x:c>
+      <x:c r="J19" s="0">
+        <x:v>6.13</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>10366031</x:v>
-      </x:c>
-      <x:c r="D19" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="E19" s="0">
-        <x:v>240000000</x:v>
-      </x:c>
-      <x:c r="F19" s="0">
-        <x:v>102614742</x:v>
-      </x:c>
-      <x:c r="G19" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="0">
-        <x:v>0.43</x:v>
-      </x:c>
-      <x:c r="I19" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J19" s="0">
-        <x:v>9.9</x:v>
-      </x:c>
-      <x:c r="K19" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>1800452</x:v>
+        <x:v>10366031</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>15000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>150000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>17447883</x:v>
+        <x:v>102614742</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>8.82</x:v>
+        <x:v>9.89</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>9.69</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
         <x:v>50</x:v>
@@ -2056,63 +2059,66 @@
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>1800452</x:v>
+      </x:c>
+      <x:c r="D21" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E21" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F21" s="0">
+        <x:v>17447883</x:v>
+      </x:c>
+      <x:c r="G21" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H21" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="I21" s="0">
+        <x:v>8.64</x:v>
+      </x:c>
+      <x:c r="J21" s="0">
+        <x:v>9.69</x:v>
+      </x:c>
+      <x:c r="K21" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D21" s="0">
-        <x:v>13409218</x:v>
-      </x:c>
-      <x:c r="E21" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G21" s="0">
-        <x:v>9.01</x:v>
-      </x:c>
-      <x:c r="H21" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I21" s="0">
-        <x:v>18.25</x:v>
-      </x:c>
-      <x:c r="J21" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>55000000</x:v>
+        <x:v>13409218</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>5.09</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>1.63</x:v>
+        <x:v>18.1</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>0</x:v>
@@ -2123,174 +2129,171 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>200000</x:v>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>25000000</x:v>
+        <x:v>55000000</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>415500000</x:v>
-      </x:c>
-      <x:c r="F23" s="0">
-        <x:v>3174011</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>16.72</x:v>
+        <x:v>1.58</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>15.87</x:v>
-      </x:c>
-      <x:c r="K23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D24" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="E24" s="0">
+        <x:v>415500000</x:v>
+      </x:c>
+      <x:c r="F24" s="0">
+        <x:v>3174011</x:v>
+      </x:c>
+      <x:c r="G24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H24" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I24" s="0">
+        <x:v>16.58</x:v>
+      </x:c>
+      <x:c r="J24" s="0">
+        <x:v>15.87</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>6067182</x:v>
-      </x:c>
-      <x:c r="D24" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="E24" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F24" s="0">
-        <x:v>114062870</x:v>
-      </x:c>
-      <x:c r="G24" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H24" s="0">
-        <x:v>0.73</x:v>
-      </x:c>
-      <x:c r="I24" s="0">
-        <x:v>17.45</x:v>
-      </x:c>
-      <x:c r="J24" s="0">
-        <x:v>18.8</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="C25" s="0">
-        <x:v>12760028</x:v>
+        <x:v>6067182</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>60000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>45251910</x:v>
+        <x:v>114062870</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>0.72</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>4.07</x:v>
+        <x:v>16.4</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>3.55</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="C26" s="0">
-        <x:v>2500000</x:v>
+        <x:v>12760028</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>2500000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>950421206</x:v>
+        <x:v>45251910</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>429.75</x:v>
+        <x:v>3.87</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>380.17</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="C27" s="0">
-        <x:v>181529</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>230000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>15000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>12667063</x:v>
+        <x:v>950421206</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>1.66</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>1.31</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>69.25</x:v>
+        <x:v>415.75</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>69.78</x:v>
+        <x:v>380.17</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -2298,241 +2301,244 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>2501710</x:v>
+        <x:v>181529</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>10000000</x:v>
+        <x:v>230000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>450000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>97116052</x:v>
+        <x:v>12667063</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>0.67</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>35.86</x:v>
+        <x:v>69.3</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>38.82</x:v>
+        <x:v>69.78</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="C29" s="0">
-        <x:v>57675584</x:v>
+        <x:v>2501710</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>85125000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>5000000000</x:v>
+        <x:v>450000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>2781852532</x:v>
+        <x:v>97116052</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>1.8</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>52.25</x:v>
+        <x:v>32.96</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>48.23</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>57675584</x:v>
+      </x:c>
+      <x:c r="D30" s="0">
+        <x:v>85125000</x:v>
+      </x:c>
+      <x:c r="E30" s="0">
+        <x:v>5000000000</x:v>
+      </x:c>
+      <x:c r="F30" s="0">
+        <x:v>2781852532</x:v>
+      </x:c>
+      <x:c r="G30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="0">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="I30" s="0">
+        <x:v>50.45</x:v>
+      </x:c>
+      <x:c r="J30" s="0">
+        <x:v>48.23</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>49697313</x:v>
-      </x:c>
-      <x:c r="D30" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="E30" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F30" s="0">
-        <x:v>1701868254</x:v>
-      </x:c>
-      <x:c r="G30" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="0">
-        <x:v>1.68</x:v>
-      </x:c>
-      <x:c r="I30" s="0">
-        <x:v>35.14</x:v>
-      </x:c>
-      <x:c r="J30" s="0">
-        <x:v>34.24</x:v>
-      </x:c>
-      <x:c r="K30" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="C31" s="0">
-        <x:v>324474</x:v>
+        <x:v>49697313</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>3000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>40000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1781383</x:v>
+        <x:v>1701868254</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>0.08</x:v>
+        <x:v>1.68</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>16.82</x:v>
+        <x:v>33.54</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>5.49</x:v>
+        <x:v>34.24</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>324474</x:v>
+      </x:c>
+      <x:c r="D32" s="0">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="E32" s="0">
+        <x:v>40000000</x:v>
+      </x:c>
+      <x:c r="F32" s="0">
+        <x:v>1781383</x:v>
+      </x:c>
+      <x:c r="G32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="0">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="I32" s="0">
+        <x:v>15.69</x:v>
+      </x:c>
+      <x:c r="J32" s="0">
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>7999148</x:v>
-      </x:c>
-      <x:c r="D32" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="E32" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F32" s="0">
-        <x:v>168715651</x:v>
-      </x:c>
-      <x:c r="G32" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="0">
-        <x:v>2.11</x:v>
-      </x:c>
-      <x:c r="I32" s="0">
-        <x:v>22.26</x:v>
-      </x:c>
-      <x:c r="J32" s="0">
-        <x:v>21.09</x:v>
-      </x:c>
-      <x:c r="K32" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>7999148</x:v>
+      </x:c>
+      <x:c r="D33" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E33" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F33" s="0">
+        <x:v>168715651</x:v>
+      </x:c>
+      <x:c r="G33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H33" s="0">
+        <x:v>2.11</x:v>
+      </x:c>
+      <x:c r="I33" s="0">
+        <x:v>22.4</x:v>
+      </x:c>
+      <x:c r="J33" s="0">
+        <x:v>21.09</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>201000</x:v>
-      </x:c>
-      <x:c r="D33" s="0">
-        <x:v>21739600</x:v>
-      </x:c>
-      <x:c r="E33" s="0">
-        <x:v>350000000</x:v>
-      </x:c>
-      <x:c r="F33" s="0">
-        <x:v>2071755</x:v>
-      </x:c>
-      <x:c r="G33" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H33" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="I33" s="0">
-        <x:v>9.96</x:v>
-      </x:c>
-      <x:c r="J33" s="0">
-        <x:v>10.31</x:v>
-      </x:c>
-      <x:c r="K33" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="D34" s="0">
+        <x:v>21739600</x:v>
+      </x:c>
+      <x:c r="E34" s="0">
+        <x:v>350000000</x:v>
+      </x:c>
+      <x:c r="F34" s="0">
+        <x:v>2071755</x:v>
+      </x:c>
+      <x:c r="G34" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H34" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I34" s="0">
+        <x:v>9.71</x:v>
+      </x:c>
+      <x:c r="J34" s="0">
+        <x:v>10.31</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D34" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="E34" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I34" s="0">
-        <x:v>8.7</x:v>
-      </x:c>
-      <x:c r="J34" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
@@ -2540,789 +2546,786 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>1900000</x:v>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65000000</x:v>
-      </x:c>
-      <x:c r="F35" s="0">
-        <x:v>14177000</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>0.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>8.55</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>7.46</x:v>
-      </x:c>
-      <x:c r="K35" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>1900000</x:v>
+      </x:c>
+      <x:c r="D36" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E36" s="0">
+        <x:v>65000000</x:v>
+      </x:c>
+      <x:c r="F36" s="0">
+        <x:v>14177000</x:v>
+      </x:c>
+      <x:c r="G36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="0">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I36" s="0">
+        <x:v>8.15</x:v>
+      </x:c>
+      <x:c r="J36" s="0">
+        <x:v>7.46</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D36" s="0">
-        <x:v>26398084</x:v>
-      </x:c>
-      <x:c r="E36" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I36" s="0">
-        <x:v>160.2</x:v>
-      </x:c>
-      <x:c r="J36" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C37" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D37" s="0">
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F37" s="0">
-        <x:v>127481195</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>20.3</x:v>
+        <x:v>176.2</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>7.13</x:v>
-      </x:c>
-      <x:c r="K37" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="C38" s="0">
-        <x:v>970810</x:v>
-      </x:c>
-      <x:c r="D38" s="0">
-        <x:v>7300000</x:v>
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>225000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>28043898</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>22.66</x:v>
+        <x:v>19.99</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>28.89</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>970810</x:v>
+      </x:c>
+      <x:c r="D39" s="0">
+        <x:v>7300000</x:v>
+      </x:c>
+      <x:c r="E39" s="0">
+        <x:v>225000000</x:v>
+      </x:c>
+      <x:c r="F39" s="0">
+        <x:v>28043898</x:v>
+      </x:c>
+      <x:c r="G39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H39" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I39" s="0">
+        <x:v>22.12</x:v>
+      </x:c>
+      <x:c r="J39" s="0">
+        <x:v>28.89</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>1001579</x:v>
-      </x:c>
-      <x:c r="D39" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E39" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F39" s="0">
-        <x:v>15106723</x:v>
-      </x:c>
-      <x:c r="G39" s="0">
-        <x:v>2.56</x:v>
-      </x:c>
-      <x:c r="H39" s="0">
-        <x:v>0.26</x:v>
-      </x:c>
-      <x:c r="I39" s="0">
-        <x:v>9.07</x:v>
-      </x:c>
-      <x:c r="J39" s="0">
-        <x:v>15.08</x:v>
-      </x:c>
-      <x:c r="K39" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>1001579</x:v>
+      </x:c>
+      <x:c r="D40" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E40" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F40" s="0">
+        <x:v>15106723</x:v>
+      </x:c>
+      <x:c r="G40" s="0">
+        <x:v>2.56</x:v>
+      </x:c>
+      <x:c r="H40" s="0">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="I40" s="0">
+        <x:v>8.83</x:v>
+      </x:c>
+      <x:c r="J40" s="0">
+        <x:v>15.08</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D40" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="E40" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F40" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I40" s="0">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="J40" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>2097370</x:v>
+      <x:c r="C41" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>2000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F41" s="0">
-        <x:v>48772185</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>2.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>21.14</x:v>
+        <x:v>4.18</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>23.25</x:v>
-      </x:c>
-      <x:c r="K41" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="C42" s="0">
-        <x:v>28964237</x:v>
+        <x:v>2097370</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>80000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>811351010</x:v>
+        <x:v>48772185</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>1.11</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>40.78</x:v>
+        <x:v>20.94</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>28.01</x:v>
+        <x:v>23.25</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="C43" s="0">
-        <x:v>7024156</x:v>
+        <x:v>28964237</x:v>
       </x:c>
       <x:c r="D43" s="0">
         <x:v>80000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>93719334</x:v>
+        <x:v>811351010</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>0.78</x:v>
+        <x:v>1.11</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>11.06</x:v>
+        <x:v>41.1</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>13.34</x:v>
+        <x:v>28.01</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="C44" s="0">
-        <x:v>3500000</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>49400000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>137144284</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>38.52</x:v>
+        <x:v>10.82</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>39.18</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
       <x:c r="C45" s="0">
-        <x:v>3753472</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>6000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>432000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>224929072</x:v>
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>62</x:v>
+        <x:v>34.68</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>59.93</x:v>
+        <x:v>39.18</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>3753472</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E46" s="0">
+        <x:v>432000000</x:v>
+      </x:c>
+      <x:c r="F46" s="0">
+        <x:v>224929072</x:v>
+      </x:c>
+      <x:c r="G46" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" s="0">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="I46" s="0">
+        <x:v>59.9</x:v>
+      </x:c>
+      <x:c r="J46" s="0">
+        <x:v>59.93</x:v>
+      </x:c>
+      <x:c r="K46" s="0" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C46" s="0">
-        <x:v>3189049</x:v>
-      </x:c>
-      <x:c r="D46" s="0">
-        <x:v>4000000</x:v>
-      </x:c>
-      <x:c r="E46" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F46" s="0">
-        <x:v>154328962</x:v>
-      </x:c>
-      <x:c r="G46" s="0">
-        <x:v>3.74</x:v>
-      </x:c>
-      <x:c r="H46" s="0">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="I46" s="0">
-        <x:v>5.44</x:v>
-      </x:c>
-      <x:c r="J46" s="0">
-        <x:v>48.39</x:v>
-      </x:c>
-      <x:c r="K46" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>3189049</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
+        <x:v>4000000</x:v>
+      </x:c>
+      <x:c r="E47" s="0">
+        <x:v>400000000</x:v>
+      </x:c>
+      <x:c r="F47" s="0">
+        <x:v>154328962</x:v>
+      </x:c>
+      <x:c r="G47" s="0">
+        <x:v>3.74</x:v>
+      </x:c>
+      <x:c r="H47" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I47" s="0">
+        <x:v>5.14</x:v>
+      </x:c>
+      <x:c r="J47" s="0">
+        <x:v>48.39</x:v>
+      </x:c>
+      <x:c r="K47" s="0" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D47" s="0">
-        <x:v>35000000</x:v>
-      </x:c>
-      <x:c r="E47" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F47" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G47" s="0">
-        <x:v>0.63</x:v>
-      </x:c>
-      <x:c r="H47" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I47" s="0">
-        <x:v>3.72</x:v>
-      </x:c>
-      <x:c r="J47" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C48" s="0">
-        <x:v>3700000</x:v>
+      <x:c r="C48" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>10000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F48" s="0">
-        <x:v>163043763</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>0.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>22.28</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J48" s="0">
-        <x:v>44.07</x:v>
-      </x:c>
-      <x:c r="K48" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
       <x:c r="C49" s="0">
-        <x:v>18183248</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>35000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>300000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>159279425</x:v>
+        <x:v>163043763</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>4.55</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>8.96</x:v>
+        <x:v>21.66</x:v>
       </x:c>
       <x:c r="J49" s="0">
-        <x:v>8.76</x:v>
+        <x:v>44.07</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="C50" s="0">
-        <x:v>236122</x:v>
+        <x:v>19402860</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1700000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>110000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>14609667</x:v>
+        <x:v>170203839</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>0.18</x:v>
+        <x:v>4.85</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>70.4</x:v>
+        <x:v>8.81</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>61.87</x:v>
+        <x:v>8.77</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>236122</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>1700000</x:v>
+      </x:c>
+      <x:c r="E51" s="0">
+        <x:v>110000000</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>14609667</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
+        <x:v>68.55</x:v>
+      </x:c>
+      <x:c r="J51" s="0">
+        <x:v>61.87</x:v>
+      </x:c>
+      <x:c r="K51" s="0" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="D51" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E51" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F51" s="0">
-        <x:v>21055375</x:v>
-      </x:c>
-      <x:c r="G51" s="0">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="H51" s="0">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="I51" s="0">
-        <x:v>17.87</x:v>
-      </x:c>
-      <x:c r="J51" s="0">
-        <x:v>21.06</x:v>
-      </x:c>
-      <x:c r="K51" s="0" t="s">
-        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F52" s="0">
+        <x:v>21055375</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>17.75</x:v>
+      </x:c>
+      <x:c r="J52" s="0">
+        <x:v>21.06</x:v>
+      </x:c>
+      <x:c r="K52" s="0" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D52" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E52" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F52" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G52" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H52" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I52" s="0">
-        <x:v>5.44</x:v>
-      </x:c>
-      <x:c r="J52" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>105404634</x:v>
+      <x:c r="C53" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D53" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
         <x:v>200000000</x:v>
       </x:c>
-      <x:c r="E53" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F53" s="0">
-        <x:v>1032884452</x:v>
+      <x:c r="F53" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>12.4</x:v>
+        <x:v>5.14</x:v>
       </x:c>
       <x:c r="J53" s="0">
-        <x:v>9.8</x:v>
-      </x:c>
-      <x:c r="K53" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="C54" s="0">
-        <x:v>16445115</x:v>
+        <x:v>105404634</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>25000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>393919718</x:v>
+        <x:v>1032884452</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>3.29</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>44.5</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>23.95</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>16445115</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="E55" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F55" s="0">
+        <x:v>393919718</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H55" s="0">
+        <x:v>3.29</x:v>
+      </x:c>
+      <x:c r="I55" s="0">
+        <x:v>42.3</x:v>
+      </x:c>
+      <x:c r="J55" s="0">
+        <x:v>23.95</x:v>
+      </x:c>
+      <x:c r="K55" s="0" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="C55" s="0">
-        <x:v>1110000</x:v>
-      </x:c>
-      <x:c r="D55" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E55" s="0">
-        <x:v>1100000000</x:v>
-      </x:c>
-      <x:c r="F55" s="0">
-        <x:v>587039028</x:v>
-      </x:c>
-      <x:c r="G55" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H55" s="0">
-        <x:v>0.09</x:v>
-      </x:c>
-      <x:c r="I55" s="0">
-        <x:v>429.75</x:v>
-      </x:c>
-      <x:c r="J55" s="0">
-        <x:v>528.86</x:v>
-      </x:c>
-      <x:c r="K55" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>24398659</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>40000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>850000000</x:v>
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>590270273</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>40.78</x:v>
+        <x:v>415.75</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>24.19</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>46563878</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>50000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>500000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F57" s="0">
-        <x:v>500007798</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>12.4</x:v>
+        <x:v>41.1</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>10.74</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
         <x:v>131</x:v>
@@ -3330,346 +3333,346 @@
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C58" s="0">
+        <x:v>46563878</x:v>
+      </x:c>
+      <x:c r="D58" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E58" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F58" s="0">
+        <x:v>500007798</x:v>
+      </x:c>
+      <x:c r="G58" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H58" s="0">
+        <x:v>0.52</x:v>
+      </x:c>
+      <x:c r="I58" s="0">
+        <x:v>12.7</x:v>
+      </x:c>
+      <x:c r="J58" s="0">
+        <x:v>10.74</x:v>
+      </x:c>
+      <x:c r="K58" s="0" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="C58" s="0">
-        <x:v>6611571</x:v>
-      </x:c>
-      <x:c r="D58" s="0">
-        <x:v>9000000</x:v>
-      </x:c>
-      <x:c r="E58" s="0">
-        <x:v>240000000</x:v>
-      </x:c>
-      <x:c r="F58" s="0">
-        <x:v>39750803</x:v>
-      </x:c>
-      <x:c r="G58" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H58" s="0">
-        <x:v>0.69</x:v>
-      </x:c>
-      <x:c r="I58" s="0">
-        <x:v>6.27</x:v>
-      </x:c>
-      <x:c r="J58" s="0">
-        <x:v>6.01</x:v>
-      </x:c>
-      <x:c r="K58" s="0" t="s">
-        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C59" s="0">
+        <x:v>6611571</x:v>
+      </x:c>
+      <x:c r="D59" s="0">
+        <x:v>9000000</x:v>
+      </x:c>
+      <x:c r="E59" s="0">
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F59" s="0">
+        <x:v>39750803</x:v>
+      </x:c>
+      <x:c r="G59" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H59" s="0">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I59" s="0">
+        <x:v>6.15</x:v>
+      </x:c>
+      <x:c r="J59" s="0">
+        <x:v>6.01</x:v>
+      </x:c>
+      <x:c r="K59" s="0" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C59" s="0">
-        <x:v>2596120</x:v>
-      </x:c>
-      <x:c r="D59" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E59" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F59" s="0">
-        <x:v>66065196</x:v>
-      </x:c>
-      <x:c r="G59" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H59" s="0">
-        <x:v>1.36</x:v>
-      </x:c>
-      <x:c r="I59" s="0">
-        <x:v>18.4</x:v>
-      </x:c>
-      <x:c r="J59" s="0">
-        <x:v>25.45</x:v>
-      </x:c>
-      <x:c r="K59" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
       <x:c r="C60" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2596120</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E60" s="0">
-        <x:v>400000000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F60" s="0">
-        <x:v>4455000</x:v>
+        <x:v>66065196</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.36</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>3.93</x:v>
+        <x:v>17.43</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>4.46</x:v>
+        <x:v>25.45</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D61" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="E61" s="0">
+        <x:v>400000000</x:v>
+      </x:c>
+      <x:c r="F61" s="0">
+        <x:v>4455000</x:v>
+      </x:c>
+      <x:c r="G61" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H61" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I61" s="0">
+        <x:v>3.93</x:v>
+      </x:c>
+      <x:c r="J61" s="0">
+        <x:v>4.46</x:v>
+      </x:c>
+      <x:c r="K61" s="0" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="C61" s="0">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="D61" s="0">
-        <x:v>13760000</x:v>
-      </x:c>
-      <x:c r="E61" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F61" s="0">
-        <x:v>2564000</x:v>
-      </x:c>
-      <x:c r="G61" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H61" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="I61" s="0">
-        <x:v>6.9</x:v>
-      </x:c>
-      <x:c r="J61" s="0">
-        <x:v>12.82</x:v>
-      </x:c>
-      <x:c r="K61" s="0" t="s">
-        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C62" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D62" s="0">
+        <x:v>13760000</x:v>
+      </x:c>
+      <x:c r="E62" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F62" s="0">
+        <x:v>2564000</x:v>
+      </x:c>
+      <x:c r="G62" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I62" s="0">
+        <x:v>6.87</x:v>
+      </x:c>
+      <x:c r="J62" s="0">
+        <x:v>12.82</x:v>
+      </x:c>
+      <x:c r="K62" s="0" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D62" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E62" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F62" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G62" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H62" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I62" s="0">
-        <x:v>29.46</x:v>
-      </x:c>
-      <x:c r="J62" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C63" s="0">
-        <x:v>5831653</x:v>
+      <x:c r="C63" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>5000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F63" s="0">
-        <x:v>304086107</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G63" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>2.84</x:v>
+        <x:v>28.9</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>52.14</x:v>
-      </x:c>
-      <x:c r="K63" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C64" s="0">
+        <x:v>5831653</x:v>
+      </x:c>
+      <x:c r="D64" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E64" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F64" s="0">
+        <x:v>304086107</x:v>
+      </x:c>
+      <x:c r="G64" s="0">
+        <x:v>2.96</x:v>
+      </x:c>
+      <x:c r="H64" s="0">
+        <x:v>0.83</x:v>
+      </x:c>
+      <x:c r="I64" s="0">
+        <x:v>2.86</x:v>
+      </x:c>
+      <x:c r="J64" s="0">
+        <x:v>52.14</x:v>
+      </x:c>
+      <x:c r="K64" s="0" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C64" s="0">
-        <x:v>14512000</x:v>
-      </x:c>
-      <x:c r="D64" s="0">
-        <x:v>79451200</x:v>
-      </x:c>
-      <x:c r="E64" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F64" s="0">
-        <x:v>575005862</x:v>
-      </x:c>
-      <x:c r="G64" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H64" s="0">
-        <x:v>1.83</x:v>
-      </x:c>
-      <x:c r="I64" s="0">
-        <x:v>37.52</x:v>
-      </x:c>
-      <x:c r="J64" s="0">
-        <x:v>39.62</x:v>
-      </x:c>
-      <x:c r="K64" s="0" t="s">
-        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C65" s="0">
+        <x:v>14512000</x:v>
+      </x:c>
+      <x:c r="D65" s="0">
+        <x:v>79451200</x:v>
+      </x:c>
+      <x:c r="E65" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F65" s="0">
+        <x:v>575005862</x:v>
+      </x:c>
+      <x:c r="G65" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H65" s="0">
+        <x:v>1.83</x:v>
+      </x:c>
+      <x:c r="I65" s="0">
+        <x:v>35.94</x:v>
+      </x:c>
+      <x:c r="J65" s="0">
+        <x:v>39.62</x:v>
+      </x:c>
+      <x:c r="K65" s="0" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C65" s="0">
-        <x:v>3799828</x:v>
-      </x:c>
-      <x:c r="D65" s="0">
-        <x:v>3000000</x:v>
-      </x:c>
-      <x:c r="E65" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F65" s="0">
-        <x:v>177844244</x:v>
-      </x:c>
-      <x:c r="G65" s="0">
-        <x:v>3.75</x:v>
-      </x:c>
-      <x:c r="H65" s="0">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="I65" s="0">
-        <x:v>22.74</x:v>
-      </x:c>
-      <x:c r="J65" s="0">
-        <x:v>46.8</x:v>
-      </x:c>
-      <x:c r="K65" s="0" t="s">
-        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C66" s="0">
+        <x:v>3799828</x:v>
+      </x:c>
+      <x:c r="D66" s="0">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="E66" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F66" s="0">
+        <x:v>177844244</x:v>
+      </x:c>
+      <x:c r="G66" s="0">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="H66" s="0">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="I66" s="0">
+        <x:v>22.5</x:v>
+      </x:c>
+      <x:c r="J66" s="0">
+        <x:v>46.8</x:v>
+      </x:c>
+      <x:c r="K66" s="0" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D66" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="E66" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F66" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G66" s="0">
-        <x:v>5.49</x:v>
-      </x:c>
-      <x:c r="H66" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I66" s="0">
-        <x:v>24.98</x:v>
-      </x:c>
-      <x:c r="J66" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="C67" s="0">
-        <x:v>8337681</x:v>
+      <x:c r="C67" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>6500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F67" s="0">
-        <x:v>37235183</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G67" s="0">
-        <x:v>1.43</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>4.15</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>4.47</x:v>
-      </x:c>
-      <x:c r="K67" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -3677,31 +3680,34 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C68" s="0">
+        <x:v>8337681</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>9275000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>950000000</x:v>
-      </x:c>
-      <x:c r="F68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F68" s="0">
+        <x:v>37235183</x:v>
       </x:c>
       <x:c r="G68" s="0">
-        <x:v>0</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>37.84</x:v>
+        <x:v>4.22</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>0</x:v>
+        <x:v>4.47</x:v>
+      </x:c>
+      <x:c r="K68" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -3709,267 +3715,267 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C69" s="0">
-        <x:v>1364000</x:v>
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>23460000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>9000000000</x:v>
-      </x:c>
-      <x:c r="F69" s="0">
-        <x:v>409075556</x:v>
+        <x:v>950000000</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G69" s="0">
-        <x:v>1.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>295.5</x:v>
+        <x:v>36.56</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>299.91</x:v>
-      </x:c>
-      <x:c r="K69" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C70" s="0">
+        <x:v>1364000</x:v>
+      </x:c>
+      <x:c r="D70" s="0">
+        <x:v>23460000</x:v>
+      </x:c>
+      <x:c r="E70" s="0">
+        <x:v>9000000000</x:v>
+      </x:c>
+      <x:c r="F70" s="0">
+        <x:v>409075556</x:v>
+      </x:c>
+      <x:c r="G70" s="0">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H70" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I70" s="0">
+        <x:v>285.25</x:v>
+      </x:c>
+      <x:c r="J70" s="0">
+        <x:v>299.91</x:v>
+      </x:c>
+      <x:c r="K70" s="0" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D70" s="0">
-        <x:v>380000000</x:v>
-      </x:c>
-      <x:c r="E70" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F70" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G70" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H70" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I70" s="0">
-        <x:v>20.58</x:v>
-      </x:c>
-      <x:c r="J70" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="C71" s="0">
-        <x:v>507440</x:v>
+      <x:c r="C71" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>2500000</x:v>
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F71" s="0">
-        <x:v>42117724</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G71" s="0">
-        <x:v>2.67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>282</x:v>
+        <x:v>19.8</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K71" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
       <x:c r="C72" s="0">
-        <x:v>2000000</x:v>
+        <x:v>507440</x:v>
       </x:c>
       <x:c r="D72" s="0">
-        <x:v>2000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E72" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F72" s="0">
-        <x:v>81947000</x:v>
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>2</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>2</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>34.32</x:v>
+        <x:v>270.25</x:v>
       </x:c>
       <x:c r="J72" s="0">
-        <x:v>40.97</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>9854768</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D73" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F73" s="0">
-        <x:v>233360906</x:v>
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G73" s="0">
-        <x:v>0.63</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>0.62</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>19.1</x:v>
+        <x:v>34.24</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>23.68</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>324474</x:v>
+        <x:v>9854768</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>5000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>30000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>1781383</x:v>
+        <x:v>233360906</x:v>
       </x:c>
       <x:c r="G74" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>16.82</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>5.49</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E75" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F75" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C75" s="0">
+        <x:v>324474</x:v>
+      </x:c>
+      <x:c r="D75" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E75" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F75" s="0">
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>16.72</x:v>
+        <x:v>15.69</x:v>
       </x:c>
       <x:c r="J75" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K75" s="0" t="s">
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>169</x:v>
-      </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D76" s="0">
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="E76" s="0">
-        <x:v>7000000</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>5.41</x:v>
+        <x:v>16.58</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>0</x:v>
@@ -3977,92 +3983,89 @@
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C77" s="0">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="D77" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C77" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D77" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F77" s="0">
-        <x:v>85838440</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F77" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G77" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>6.36</x:v>
+        <x:v>5.19</x:v>
       </x:c>
       <x:c r="J77" s="0">
-        <x:v>6.6</x:v>
-      </x:c>
-      <x:c r="K77" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C78" s="0">
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E78" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F78" s="0">
+        <x:v>85838440</x:v>
+      </x:c>
+      <x:c r="G78" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H78" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I78" s="0">
+        <x:v>6.68</x:v>
+      </x:c>
+      <x:c r="J78" s="0">
+        <x:v>6.6</x:v>
+      </x:c>
+      <x:c r="K78" s="0" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C78" s="0">
-        <x:v>174500000</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E78" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F78" s="0">
-        <x:v>694527000</x:v>
-      </x:c>
-      <x:c r="G78" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H78" s="0">
-        <x:v>0.33</x:v>
-      </x:c>
-      <x:c r="I78" s="0">
-        <x:v>2.94</x:v>
-      </x:c>
-      <x:c r="J78" s="0">
-        <x:v>3.98</x:v>
-      </x:c>
-      <x:c r="K78" s="0" t="s">
-        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>635229</x:v>
+        <x:v>174500000</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F79" s="0">
-        <x:v>11323561</x:v>
+        <x:v>694527000</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>0</x:v>
@@ -4071,319 +4074,322 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>18.4</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="J79" s="0">
-        <x:v>17.83</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>130000</x:v>
-      </x:c>
-      <x:c r="D80" s="0">
-        <x:v>3500000</x:v>
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E80" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>4947800</x:v>
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G80" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>31.78</x:v>
+        <x:v>17.43</x:v>
       </x:c>
       <x:c r="J80" s="0">
-        <x:v>38.06</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C81" s="0">
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>5000000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F81" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F81" s="0">
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>0</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>0</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>221.9</x:v>
+        <x:v>31.7</x:v>
       </x:c>
       <x:c r="J81" s="0">
-        <x:v>0</x:v>
+        <x:v>38.06</x:v>
+      </x:c>
+      <x:c r="K81" s="0" t="s">
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="C82" s="0">
-        <x:v>447761</x:v>
+      <x:c r="C82" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>3000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F82" s="0">
-        <x:v>18415143</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>33.6</x:v>
+        <x:v>223.6</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>41.13</x:v>
-      </x:c>
-      <x:c r="K82" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C83" s="0">
+        <x:v>447761</x:v>
+      </x:c>
+      <x:c r="D83" s="0">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="E83" s="0">
+        <x:v>120000000</x:v>
+      </x:c>
+      <x:c r="F83" s="0">
+        <x:v>18415143</x:v>
+      </x:c>
+      <x:c r="G83" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H83" s="0">
+        <x:v>0.86</x:v>
+      </x:c>
+      <x:c r="I83" s="0">
+        <x:v>32.5</x:v>
+      </x:c>
+      <x:c r="J83" s="0">
+        <x:v>41.13</x:v>
+      </x:c>
+      <x:c r="K83" s="0" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="C83" s="0">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="D83" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E83" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F83" s="0">
-        <x:v>4022593</x:v>
-      </x:c>
-      <x:c r="G83" s="0">
-        <x:v>1.71</x:v>
-      </x:c>
-      <x:c r="H83" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="I83" s="0">
-        <x:v>4.15</x:v>
-      </x:c>
-      <x:c r="J83" s="0">
-        <x:v>20.11</x:v>
-      </x:c>
-      <x:c r="K83" s="0" t="s">
-        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C84" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D84" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E84" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F84" s="0">
+        <x:v>4022593</x:v>
+      </x:c>
+      <x:c r="G84" s="0">
+        <x:v>1.71</x:v>
+      </x:c>
+      <x:c r="H84" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I84" s="0">
+        <x:v>4.07</x:v>
+      </x:c>
+      <x:c r="J84" s="0">
+        <x:v>20.11</x:v>
+      </x:c>
+      <x:c r="K84" s="0" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="C84" s="0">
-        <x:v>946718</x:v>
-      </x:c>
-      <x:c r="D84" s="0">
-        <x:v>20000000</x:v>
-      </x:c>
-      <x:c r="E84" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F84" s="0">
-        <x:v>37333519</x:v>
-      </x:c>
-      <x:c r="G84" s="0">
-        <x:v>7.55</x:v>
-      </x:c>
-      <x:c r="H84" s="0">
-        <x:v>0.36</x:v>
-      </x:c>
-      <x:c r="I84" s="0">
-        <x:v>43.6</x:v>
-      </x:c>
-      <x:c r="J84" s="0">
-        <x:v>39.43</x:v>
-      </x:c>
-      <x:c r="K84" s="0" t="s">
-        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C85" s="0">
+        <x:v>946718</x:v>
+      </x:c>
+      <x:c r="D85" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="E85" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F85" s="0">
+        <x:v>37333519</x:v>
+      </x:c>
+      <x:c r="G85" s="0">
+        <x:v>7.55</x:v>
+      </x:c>
+      <x:c r="H85" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="I85" s="0">
+        <x:v>41.96</x:v>
+      </x:c>
+      <x:c r="J85" s="0">
+        <x:v>39.43</x:v>
+      </x:c>
+      <x:c r="K85" s="0" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E85" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F85" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G85" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H85" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I85" s="0">
-        <x:v>18.36</x:v>
-      </x:c>
-      <x:c r="J85" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C86" s="0">
-        <x:v>3043115</x:v>
-      </x:c>
-      <x:c r="D86" s="0">
-        <x:v>50000000</x:v>
+      <x:c r="C86" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F86" s="0">
-        <x:v>49736990</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>21.74</x:v>
+        <x:v>18.07</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>16.34</x:v>
-      </x:c>
-      <x:c r="K86" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C87" s="0">
+        <x:v>3043115</x:v>
+      </x:c>
+      <x:c r="D87" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E87" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F87" s="0">
+        <x:v>49736990</x:v>
+      </x:c>
+      <x:c r="G87" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H87" s="0">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="I87" s="0">
+        <x:v>21.34</x:v>
+      </x:c>
+      <x:c r="J87" s="0">
+        <x:v>16.34</x:v>
+      </x:c>
+      <x:c r="K87" s="0" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="C87" s="0">
-        <x:v>2382736</x:v>
-      </x:c>
-      <x:c r="D87" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E87" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F87" s="0">
-        <x:v>92635231</x:v>
-      </x:c>
-      <x:c r="G87" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H87" s="0">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="I87" s="0">
-        <x:v>72.7</x:v>
-      </x:c>
-      <x:c r="J87" s="0">
-        <x:v>38.88</x:v>
-      </x:c>
-      <x:c r="K87" s="0" t="s">
-        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C88" s="0">
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E88" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F88" s="0">
+        <x:v>92635231</x:v>
+      </x:c>
+      <x:c r="G88" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H88" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I88" s="0">
+        <x:v>69.65</x:v>
+      </x:c>
+      <x:c r="J88" s="0">
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="K88" s="0" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D88" s="0">
-        <x:v>4191000</x:v>
-      </x:c>
-      <x:c r="E88" s="0">
-        <x:v>160000000</x:v>
-      </x:c>
-      <x:c r="F88" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G88" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H88" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I88" s="0">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J88" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -4391,174 +4397,171 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C89" s="0">
-        <x:v>4650000</x:v>
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D89" s="0">
-        <x:v>75000000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F89" s="0">
-        <x:v>49978950</x:v>
+        <x:v>160000000</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>11.7</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>10.75</x:v>
-      </x:c>
-      <x:c r="K89" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C90" s="0">
+        <x:v>4650000</x:v>
+      </x:c>
+      <x:c r="D90" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="E90" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F90" s="0">
+        <x:v>49978950</x:v>
+      </x:c>
+      <x:c r="G90" s="0">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="H90" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I90" s="0">
+        <x:v>11.1</x:v>
+      </x:c>
+      <x:c r="J90" s="0">
+        <x:v>10.75</x:v>
+      </x:c>
+      <x:c r="K90" s="0" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="C90" s="0">
-        <x:v>806343</x:v>
-      </x:c>
-      <x:c r="D90" s="0">
-        <x:v>1862500</x:v>
-      </x:c>
-      <x:c r="E90" s="0">
-        <x:v>75000000</x:v>
-      </x:c>
-      <x:c r="F90" s="0">
-        <x:v>30363861</x:v>
-      </x:c>
-      <x:c r="G90" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H90" s="0">
-        <x:v>2.16</x:v>
-      </x:c>
-      <x:c r="I90" s="0">
-        <x:v>34.54</x:v>
-      </x:c>
-      <x:c r="J90" s="0">
-        <x:v>37.66</x:v>
-      </x:c>
-      <x:c r="K90" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>310000</x:v>
+        <x:v>806343</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F91" s="0">
-        <x:v>49980500</x:v>
+        <x:v>30363861</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0.01</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>11.7</x:v>
+        <x:v>34.16</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>161.23</x:v>
+        <x:v>37.66</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>2000000</x:v>
+        <x:v>310000</x:v>
       </x:c>
       <x:c r="D92" s="0">
         <x:v>5000000</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>31366572</x:v>
+        <x:v>49980500</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>8.82</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>15.68</x:v>
+        <x:v>161.23</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="C93" s="0">
-        <x:v>1250000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>25000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>11187500</x:v>
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>2.08</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>1.9</x:v>
+        <x:v>8.64</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>8.95</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
@@ -4566,31 +4569,34 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C94" s="0">
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>6950000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F94" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F94" s="0">
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>10</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>3.58</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>0</x:v>
+        <x:v>8.95</x:v>
+      </x:c>
+      <x:c r="K94" s="0" t="s">
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
@@ -4598,101 +4604,101 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="C95" s="0">
-        <x:v>12500000</x:v>
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D95" s="0">
-        <x:v>12500000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="F95" s="0">
-        <x:v>61582393</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F95" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>2.04</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>4.93</x:v>
-      </x:c>
-      <x:c r="K95" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
       <x:c r="C96" s="0">
-        <x:v>2093944</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D96" s="0">
-        <x:v>220000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>8500000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F96" s="0">
-        <x:v>200139168</x:v>
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>102.4</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="J96" s="0">
-        <x:v>95.58</x:v>
+        <x:v>4.93</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C97" s="0">
+        <x:v>2093944</x:v>
+      </x:c>
+      <x:c r="D97" s="0">
+        <x:v>220000000</x:v>
+      </x:c>
+      <x:c r="E97" s="0">
+        <x:v>8500000000</x:v>
+      </x:c>
+      <x:c r="F97" s="0">
+        <x:v>200139168</x:v>
+      </x:c>
+      <x:c r="G97" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H97" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I97" s="0">
+        <x:v>99.4</x:v>
+      </x:c>
+      <x:c r="J97" s="0">
+        <x:v>95.58</x:v>
+      </x:c>
+      <x:c r="K97" s="0" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D97" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="E97" s="0">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="F97" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G97" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H97" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I97" s="0">
-        <x:v>47.08</x:v>
-      </x:c>
-      <x:c r="J97" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
@@ -4700,279 +4706,276 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="C98" s="0">
-        <x:v>51245979</x:v>
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>85000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F98" s="0">
-        <x:v>125342407</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>2.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>1.31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>2.83</x:v>
+        <x:v>46.08</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>2.45</x:v>
-      </x:c>
-      <x:c r="K98" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>1584837</x:v>
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D99" s="0">
-        <x:v>2500000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>100000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F99" s="0">
-        <x:v>92450176</x:v>
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>0</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>1.08</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>66</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>58.33</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>7999148</x:v>
+        <x:v>1584837</x:v>
       </x:c>
       <x:c r="D100" s="0">
-        <x:v>11000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>200000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F100" s="0">
-        <x:v>168715651</x:v>
+        <x:v>92450176</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>2.11</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>22.26</x:v>
+        <x:v>64.55</x:v>
       </x:c>
       <x:c r="J100" s="0">
-        <x:v>21.09</x:v>
+        <x:v>58.33</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>14000000</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>10000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E101" s="0">
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F101" s="0">
-        <x:v>236130680</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>1.17</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>24.58</x:v>
+        <x:v>22.4</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>16.87</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>1700005</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>95000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>1425000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F102" s="0">
-        <x:v>20390731</x:v>
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>10</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>5.28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>11.99</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C103" s="0">
+        <x:v>1700005</x:v>
+      </x:c>
+      <x:c r="D103" s="0">
+        <x:v>95000000</x:v>
+      </x:c>
+      <x:c r="E103" s="0">
+        <x:v>1425000000</x:v>
+      </x:c>
+      <x:c r="F103" s="0">
+        <x:v>20390731</x:v>
+      </x:c>
+      <x:c r="G103" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H103" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I103" s="0">
+        <x:v>5.35</x:v>
+      </x:c>
+      <x:c r="J103" s="0">
+        <x:v>11.99</x:v>
+      </x:c>
+      <x:c r="K103" s="0" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C103" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="D103" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="E103" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F103" s="0">
-        <x:v>132286928</x:v>
-      </x:c>
-      <x:c r="G103" s="0">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="H103" s="0">
-        <x:v>0.16</x:v>
-      </x:c>
-      <x:c r="I103" s="0">
-        <x:v>15.32</x:v>
-      </x:c>
-      <x:c r="J103" s="0">
-        <x:v>22.05</x:v>
-      </x:c>
-      <x:c r="K103" s="0" t="s">
-        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C104" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="D104" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E104" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F104" s="0">
+        <x:v>132286928</x:v>
+      </x:c>
+      <x:c r="G104" s="0">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="H104" s="0">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="I104" s="0">
+        <x:v>14.74</x:v>
+      </x:c>
+      <x:c r="J104" s="0">
+        <x:v>22.05</x:v>
+      </x:c>
+      <x:c r="K104" s="0" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C104" s="0">
-        <x:v>1675000</x:v>
-      </x:c>
-      <x:c r="D104" s="0">
-        <x:v>9000000</x:v>
-      </x:c>
-      <x:c r="E104" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F104" s="0">
-        <x:v>114158717</x:v>
-      </x:c>
-      <x:c r="G104" s="0">
-        <x:v>7.81</x:v>
-      </x:c>
-      <x:c r="H104" s="0">
-        <x:v>1.45</x:v>
-      </x:c>
-      <x:c r="I104" s="0">
-        <x:v>81.65</x:v>
-      </x:c>
-      <x:c r="J104" s="0">
-        <x:v>68.15</x:v>
-      </x:c>
-      <x:c r="K104" s="0" t="s">
-        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C105" s="0">
+        <x:v>1675000</x:v>
+      </x:c>
+      <x:c r="D105" s="0">
+        <x:v>9000000</x:v>
+      </x:c>
+      <x:c r="E105" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F105" s="0">
+        <x:v>114158717</x:v>
+      </x:c>
+      <x:c r="G105" s="0">
+        <x:v>7.81</x:v>
+      </x:c>
+      <x:c r="H105" s="0">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="I105" s="0">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J105" s="0">
+        <x:v>68.15</x:v>
+      </x:c>
+      <x:c r="K105" s="0" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C105" s="0">
-        <x:v>1824868</x:v>
-      </x:c>
-      <x:c r="D105" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E105" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F105" s="0">
-        <x:v>64572720</x:v>
-      </x:c>
-      <x:c r="G105" s="0">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="H105" s="0">
-        <x:v>0.68</x:v>
-      </x:c>
-      <x:c r="I105" s="0">
-        <x:v>30.38</x:v>
-      </x:c>
-      <x:c r="J105" s="0">
-        <x:v>35.38</x:v>
-      </x:c>
-      <x:c r="K105" s="0" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
@@ -4980,31 +4983,34 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C106" s="0">
+        <x:v>1824868</x:v>
       </x:c>
       <x:c r="D106" s="0">
-        <x:v>50000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F106" s="0">
+        <x:v>64572720</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>5</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>6.55</x:v>
+        <x:v>27.94</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>0</x:v>
+        <x:v>35.38</x:v>
+      </x:c>
+      <x:c r="K106" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -5012,69 +5018,66 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C107" s="0">
-        <x:v>1000000</x:v>
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>1000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F107" s="0">
-        <x:v>19787700</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F107" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>0.67</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>8.75</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>19.79</x:v>
-      </x:c>
-      <x:c r="K107" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C108" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D108" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E108" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F108" s="0">
+        <x:v>19787700</x:v>
+      </x:c>
+      <x:c r="G108" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="H108" s="0">
+        <x:v>0.27</x:v>
+      </x:c>
+      <x:c r="I108" s="0">
+        <x:v>8.54</x:v>
+      </x:c>
+      <x:c r="J108" s="0">
+        <x:v>19.79</x:v>
+      </x:c>
+      <x:c r="K108" s="0" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C108" s="0">
-        <x:v>98551</x:v>
-      </x:c>
-      <x:c r="D108" s="0">
-        <x:v>6500000</x:v>
-      </x:c>
-      <x:c r="E108" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F108" s="0">
-        <x:v>1295684</x:v>
-      </x:c>
-      <x:c r="G108" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H108" s="0">
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="I108" s="0">
-        <x:v>10.59</x:v>
-      </x:c>
-      <x:c r="J108" s="0">
-        <x:v>13.15</x:v>
-      </x:c>
-      <x:c r="K108" s="0" t="s">
-        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
@@ -5082,821 +5085,824 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>6049315</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D109" s="0">
-        <x:v>15000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>150000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F109" s="0">
-        <x:v>66439559</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>11.26</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="J109" s="0">
-        <x:v>10.98</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>37225000</x:v>
+        <x:v>6049315</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>12000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E110" s="0">
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F110" s="0">
-        <x:v>149982056</x:v>
+        <x:v>66439559</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>8.99</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>3.45</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>1.63</x:v>
+        <x:v>11.02</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>4.03</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>1000000</x:v>
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>1000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>350000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>284578907</x:v>
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>0.8</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>0.8</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>234.7</x:v>
+        <x:v>1.58</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>284.58</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C112" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D112" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E112" s="0">
+        <x:v>350000000</x:v>
+      </x:c>
+      <x:c r="F112" s="0">
+        <x:v>284578907</x:v>
+      </x:c>
+      <x:c r="G112" s="0">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H112" s="0">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="I112" s="0">
+        <x:v>220.3</x:v>
+      </x:c>
+      <x:c r="J112" s="0">
+        <x:v>284.58</x:v>
+      </x:c>
+      <x:c r="K112" s="0" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C112" s="0">
-        <x:v>600000</x:v>
-      </x:c>
-      <x:c r="D112" s="0">
-        <x:v>600000</x:v>
-      </x:c>
-      <x:c r="E112" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="F112" s="0">
-        <x:v>22814140</x:v>
-      </x:c>
-      <x:c r="G112" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H112" s="0">
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="I112" s="0">
-        <x:v>5.9</x:v>
-      </x:c>
-      <x:c r="J112" s="0">
-        <x:v>38.02</x:v>
-      </x:c>
-      <x:c r="K112" s="0" t="s">
-        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C113" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="D113" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="E113" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="F113" s="0">
+        <x:v>22814140</x:v>
+      </x:c>
+      <x:c r="G113" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H113" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="I113" s="0">
+        <x:v>5.87</x:v>
+      </x:c>
+      <x:c r="J113" s="0">
+        <x:v>38.02</x:v>
+      </x:c>
+      <x:c r="K113" s="0" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C113" s="0">
-        <x:v>11703083</x:v>
-      </x:c>
-      <x:c r="D113" s="0">
-        <x:v>16000000</x:v>
-      </x:c>
-      <x:c r="E113" s="0">
-        <x:v>720000000</x:v>
-      </x:c>
-      <x:c r="F113" s="0">
-        <x:v>978644023</x:v>
-      </x:c>
-      <x:c r="G113" s="0">
-        <x:v>10.16</x:v>
-      </x:c>
-      <x:c r="H113" s="0">
-        <x:v>1.67</x:v>
-      </x:c>
-      <x:c r="I113" s="0">
-        <x:v>215.8</x:v>
-      </x:c>
-      <x:c r="J113" s="0">
-        <x:v>83.62</x:v>
-      </x:c>
-      <x:c r="K113" s="0" t="s">
-        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C114" s="0">
+        <x:v>11703083</x:v>
+      </x:c>
+      <x:c r="D114" s="0">
+        <x:v>16000000</x:v>
+      </x:c>
+      <x:c r="E114" s="0">
+        <x:v>720000000</x:v>
+      </x:c>
+      <x:c r="F114" s="0">
+        <x:v>978644023</x:v>
+      </x:c>
+      <x:c r="G114" s="0">
+        <x:v>10.16</x:v>
+      </x:c>
+      <x:c r="H114" s="0">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="I114" s="0">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="J114" s="0">
+        <x:v>83.62</x:v>
+      </x:c>
+      <x:c r="K114" s="0" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="C114" s="0">
-        <x:v>5100000</x:v>
-      </x:c>
-      <x:c r="D114" s="0">
-        <x:v>9000000</x:v>
-      </x:c>
-      <x:c r="E114" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F114" s="0">
-        <x:v>90022686</x:v>
-      </x:c>
-      <x:c r="G114" s="0">
-        <x:v>7.6</x:v>
-      </x:c>
-      <x:c r="H114" s="0">
-        <x:v>4.31</x:v>
-      </x:c>
-      <x:c r="I114" s="0">
-        <x:v>30.48</x:v>
-      </x:c>
-      <x:c r="J114" s="0">
-        <x:v>17.65</x:v>
-      </x:c>
-      <x:c r="K114" s="0" t="s">
-        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>3228679</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>10000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>175000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F115" s="0">
-        <x:v>51395842</x:v>
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>0.9</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>0.29</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>8.21</x:v>
+        <x:v>29.76</x:v>
       </x:c>
       <x:c r="J115" s="0">
-        <x:v>15.92</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>150000</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>6000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>240000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F116" s="0">
-        <x:v>6145450</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>5.26</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J116" s="0">
-        <x:v>40.97</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C117" s="0">
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F117" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F117" s="0">
+        <x:v>6145450</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>11.06</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>0</x:v>
+        <x:v>40.97</x:v>
+      </x:c>
+      <x:c r="K117" s="0" t="s">
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="C118" s="0">
-        <x:v>366107</x:v>
+      <x:c r="C118" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>1200000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F118" s="0">
-        <x:v>6010300</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>14.26</x:v>
+        <x:v>10.95</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>16.42</x:v>
-      </x:c>
-      <x:c r="K118" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>120000</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>26398084</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>100000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F119" s="0">
-        <x:v>3830160</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>160.2</x:v>
+        <x:v>13.96</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>31.92</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>13050000</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D120" s="0">
-        <x:v>13050000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>1305000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F120" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>3.13</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>113.2</x:v>
+        <x:v>176.2</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>94.36</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>36605658</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>100000000</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1305000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>174340918</x:v>
+        <x:v>1231340857</x:v>
       </x:c>
       <x:c r="G121" s="0">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>4.71</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>4.76</x:v>
+        <x:v>94.36</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>1000000</x:v>
+        <x:v>36605658</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>4000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>429817200</x:v>
+        <x:v>174340918</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>0.08</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>429.75</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>429.82</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>300000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>60000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>171000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F123" s="0">
-        <x:v>791000</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>3.04</x:v>
+        <x:v>415.75</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>2.64</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>2175097</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>15000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>175000000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>17901652</x:v>
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>14.15</x:v>
+        <x:v>2.9</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>8.23</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C125" s="0">
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>50000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F125" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>175000000</x:v>
+      </x:c>
+      <x:c r="F125" s="0">
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>0</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>3.03</x:v>
+        <x:v>13.48</x:v>
       </x:c>
       <x:c r="J125" s="0">
-        <x:v>0</x:v>
+        <x:v>8.23</x:v>
+      </x:c>
+      <x:c r="K125" s="0" t="s">
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C126" s="0">
-        <x:v>43000</x:v>
+      <x:c r="C126" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>200000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="F126" s="0">
-        <x:v>1024885</x:v>
+        <x:v>152000000</x:v>
+      </x:c>
+      <x:c r="F126" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G126" s="0">
-        <x:v>0.43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>26.66</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="J126" s="0">
-        <x:v>23.83</x:v>
-      </x:c>
-      <x:c r="K126" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>9937037</x:v>
+        <x:v>43000</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>11000000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>50000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="F127" s="0">
-        <x:v>50001023</x:v>
+        <x:v>1024885</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>0</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0.53</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>2.25</x:v>
+        <x:v>25.78</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>5.03</x:v>
+        <x:v>23.83</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C128" s="0">
+        <x:v>9937037</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>5500000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F128" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F128" s="0">
+        <x:v>50001023</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>0</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>2.6</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>0</x:v>
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="K128" s="0" t="s">
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C129" s="0">
-        <x:v>13064888</x:v>
+      <x:c r="C129" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>30000000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F129" s="0">
-        <x:v>268254173</x:v>
+        <x:v>139000000</x:v>
+      </x:c>
+      <x:c r="F129" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G129" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>40.78</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>20.53</x:v>
-      </x:c>
-      <x:c r="K129" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>111673026</x:v>
+        <x:v>13064888</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>150000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>500000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F130" s="0">
-        <x:v>500005947</x:v>
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>12.4</x:v>
+        <x:v>41.1</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>4.48</x:v>
+        <x:v>20.53</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C131" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D131" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C131" s="0">
+        <x:v>111673026</x:v>
+      </x:c>
+      <x:c r="D131" s="0">
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F131" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F131" s="0">
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>0</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>3.62</x:v>
+        <x:v>12.7</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>0</x:v>
+        <x:v>4.48</x:v>
+      </x:c>
+      <x:c r="K131" s="0" t="s">
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D132" s="0">
-        <x:v>19600000</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>92000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>6.85</x:v>
+        <x:v>3.46</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>0</x:v>
@@ -5904,573 +5910,573 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C133" s="0">
-        <x:v>1100000</x:v>
+      <x:c r="C133" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D133" s="0">
-        <x:v>2000000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F133" s="0">
-        <x:v>56064346</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F133" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>189</x:v>
+        <x:v>6.61</x:v>
       </x:c>
       <x:c r="J133" s="0">
-        <x:v>50.97</x:v>
-      </x:c>
-      <x:c r="K133" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>6598092</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>11160000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>125000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F134" s="0">
-        <x:v>72091269</x:v>
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>5.91</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>16.72</x:v>
+        <x:v>170.1</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>10.93</x:v>
+        <x:v>50.97</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>1590000</x:v>
+        <x:v>6598092</x:v>
       </x:c>
       <x:c r="D135" s="0">
-        <x:v>2160000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>35000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F135" s="0">
-        <x:v>60641600</x:v>
+        <x:v>72091269</x:v>
       </x:c>
       <x:c r="G135" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>0.91</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>36.26</x:v>
+        <x:v>16.58</x:v>
       </x:c>
       <x:c r="J135" s="0">
-        <x:v>38.14</x:v>
+        <x:v>10.93</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>1989802</x:v>
+        <x:v>1590000</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2160000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>250000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="F136" s="0">
-        <x:v>78711752</x:v>
+        <x:v>60641600</x:v>
       </x:c>
       <x:c r="G136" s="0">
-        <x:v>2.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>139</x:v>
+        <x:v>36.9</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>39.56</x:v>
+        <x:v>38.14</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C137" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C137" s="0">
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>1000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F137" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F137" s="0">
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G137" s="0">
-        <x:v>0</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>0</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>543.5</x:v>
+        <x:v>130.1</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>0</x:v>
+        <x:v>39.56</x:v>
+      </x:c>
+      <x:c r="K137" s="0" t="s">
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C138" s="0">
-        <x:v>300000</x:v>
+      <x:c r="C138" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>67500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>326000000</x:v>
-      </x:c>
-      <x:c r="F138" s="0">
-        <x:v>1369300</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F138" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>7.01</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>4.56</x:v>
-      </x:c>
-      <x:c r="K138" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>76908759</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D139" s="0">
-        <x:v>250000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>12000000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F139" s="0">
-        <x:v>1979731803</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>35.74</x:v>
+        <x:v>6.97</x:v>
       </x:c>
       <x:c r="J139" s="0">
-        <x:v>25.74</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>8291656</x:v>
+        <x:v>76908759</x:v>
       </x:c>
       <x:c r="D140" s="0">
-        <x:v>11000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>200000000</x:v>
+        <x:v>12000000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>126004459</x:v>
+        <x:v>1979731803</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>16.23</x:v>
+        <x:v>33.88</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>15.2</x:v>
+        <x:v>25.74</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>2975773</x:v>
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>6000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F141" s="0">
-        <x:v>44771095</x:v>
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G141" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>0.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>23.42</x:v>
+        <x:v>15.58</x:v>
       </x:c>
       <x:c r="J141" s="0">
-        <x:v>15.05</x:v>
+        <x:v>15.2</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>10994323</x:v>
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>21600000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F142" s="0">
-        <x:v>183002238</x:v>
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>5.09</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>13.52</x:v>
+        <x:v>22.36</x:v>
       </x:c>
       <x:c r="J142" s="0">
-        <x:v>16.65</x:v>
+        <x:v>15.05</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>36870641</x:v>
+        <x:v>10994323</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>195000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>416172590</x:v>
+        <x:v>183002238</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>1.89</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>16.4</x:v>
+        <x:v>13.16</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>11.29</x:v>
+        <x:v>16.65</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>271</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>5100000</x:v>
+        <x:v>36970641</x:v>
       </x:c>
       <x:c r="D144" s="0">
-        <x:v>20000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>700000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F144" s="0">
-        <x:v>155318227</x:v>
+        <x:v>417821090</x:v>
       </x:c>
       <x:c r="G144" s="0">
-        <x:v>6.81</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>0.93</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>59.25</x:v>
+        <x:v>16.17</x:v>
       </x:c>
       <x:c r="J144" s="0">
-        <x:v>30.45</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="C145" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C145" s="0">
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>300000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E145" s="0">
         <x:v>700000000</x:v>
       </x:c>
-      <x:c r="F145" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F145" s="0">
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G145" s="0">
-        <x:v>6.67</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>0</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>2.04</x:v>
+        <x:v>56.55</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>0</x:v>
+        <x:v>30.45</x:v>
+      </x:c>
+      <x:c r="K145" s="0" t="s">
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="C146" s="0">
-        <x:v>5000000</x:v>
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D146" s="0">
-        <x:v>5000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F146" s="0">
-        <x:v>39090077</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F146" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>0</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J146" s="0">
-        <x:v>7.82</x:v>
-      </x:c>
-      <x:c r="K146" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>905991</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="D147" s="0">
-        <x:v>21000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>500000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F147" s="0">
-        <x:v>17447317</x:v>
+        <x:v>39090077</x:v>
       </x:c>
       <x:c r="G147" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>16.3</x:v>
+        <x:v>9.89</x:v>
       </x:c>
       <x:c r="J147" s="0">
-        <x:v>19.26</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C148" s="0">
+        <x:v>905991</x:v>
       </x:c>
       <x:c r="D148" s="0">
-        <x:v>11700000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F148" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F148" s="0">
+        <x:v>17447317</x:v>
       </x:c>
       <x:c r="G148" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>0</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>39.68</x:v>
+        <x:v>16.15</x:v>
       </x:c>
       <x:c r="J148" s="0">
-        <x:v>0</x:v>
+        <x:v>19.26</x:v>
+      </x:c>
+      <x:c r="K148" s="0" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D149" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>270000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G149" s="0">
         <x:v>0</x:v>
@@ -6479,7 +6485,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>543.5</x:v>
+        <x:v>37.94</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>0</x:v>
@@ -6487,279 +6493,276 @@
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="C150" s="0">
-        <x:v>53584</x:v>
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>640000000</x:v>
-      </x:c>
-      <x:c r="F150" s="0">
-        <x:v>8271098</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F150" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>248</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="J150" s="0">
-        <x:v>154.36</x:v>
-      </x:c>
-      <x:c r="K150" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>7550000</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D151" s="0">
-        <x:v>30000000</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>500000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F151" s="0">
-        <x:v>111777791</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>14.23</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="J151" s="0">
-        <x:v>14.81</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K151" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>2097716</x:v>
+        <x:v>7550000</x:v>
       </x:c>
       <x:c r="D152" s="0">
-        <x:v>10112561</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>120000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F152" s="0">
-        <x:v>28985167</x:v>
+        <x:v>111777791</x:v>
       </x:c>
       <x:c r="G152" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>1.19</x:v>
+        <x:v>15.65</x:v>
       </x:c>
       <x:c r="J152" s="0">
-        <x:v>13.82</x:v>
+        <x:v>14.81</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>5185302</x:v>
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>57000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>513000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F153" s="0">
-        <x:v>37061183</x:v>
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G153" s="0">
-        <x:v>5.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>5.55</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="J153" s="0">
-        <x:v>7.15</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="K153" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>669111</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D154" s="0">
-        <x:v>1000000</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>260000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F154" s="0">
-        <x:v>151220429</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G154" s="0">
-        <x:v>0</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>777.5</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="J154" s="0">
-        <x:v>226</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>293</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>38840</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D155" s="0">
         <x:v>1000000</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>270000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F155" s="0">
-        <x:v>9431791</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G155" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>543.5</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="J155" s="0">
-        <x:v>242.84</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>2250000</x:v>
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D156" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>300000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F156" s="0">
-        <x:v>31750000</x:v>
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G156" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>14.23</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="J156" s="0">
-        <x:v>14.11</x:v>
+        <x:v>242.84</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>1500000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D157" s="0">
-        <x:v>10112561</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>175000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F157" s="0">
-        <x:v>21870885</x:v>
+        <x:v>31750000</x:v>
       </x:c>
       <x:c r="G157" s="0">
-        <x:v>10</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>1.19</x:v>
+        <x:v>15.65</x:v>
       </x:c>
       <x:c r="J157" s="0">
-        <x:v>14.58</x:v>
+        <x:v>14.11</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
         <x:v>295</x:v>
@@ -6767,124 +6770,124 @@
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>1430040</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D158" s="0">
-        <x:v>8299326</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>600000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F158" s="0">
-        <x:v>198303629</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G158" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>1.51</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>139.5</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="J158" s="0">
-        <x:v>138.67</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="C159" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="C159" s="0">
+        <x:v>1430040</x:v>
       </x:c>
       <x:c r="D159" s="0">
-        <x:v>2500000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F159" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F159" s="0">
+        <x:v>198303629</x:v>
       </x:c>
       <x:c r="G159" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>0</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>282</x:v>
+        <x:v>134.4</x:v>
       </x:c>
       <x:c r="J159" s="0">
-        <x:v>0</x:v>
+        <x:v>138.67</x:v>
+      </x:c>
+      <x:c r="K159" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="C160" s="0">
-        <x:v>845945</x:v>
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D160" s="0">
-        <x:v>15000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F160" s="0">
-        <x:v>10058606</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F160" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G160" s="0">
-        <x:v>0</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>4.15</x:v>
+        <x:v>270.25</x:v>
       </x:c>
       <x:c r="J160" s="0">
-        <x:v>11.89</x:v>
-      </x:c>
-      <x:c r="K160" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>21446</x:v>
+        <x:v>845945</x:v>
       </x:c>
       <x:c r="D161" s="0">
-        <x:v>1000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>200000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F161" s="0">
-        <x:v>2015907</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>0</x:v>
@@ -6893,502 +6896,537 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>43.2</x:v>
+        <x:v>4.22</x:v>
       </x:c>
       <x:c r="J161" s="0">
-        <x:v>94</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K161" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>850000</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D162" s="0">
-        <x:v>4250000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>40000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F162" s="0">
-        <x:v>6548328</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G162" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>1</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>6.89</x:v>
+        <x:v>42.38</x:v>
       </x:c>
       <x:c r="J162" s="0">
-        <x:v>7.7</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>15000000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D163" s="0">
-        <x:v>300000000</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>600000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F163" s="0">
-        <x:v>23990000</x:v>
+        <x:v>6548328</x:v>
       </x:c>
       <x:c r="G163" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>0.22</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>3.07</x:v>
+        <x:v>6.76</x:v>
       </x:c>
       <x:c r="J163" s="0">
-        <x:v>1.6</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>6397124</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="D164" s="0">
-        <x:v>35300000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>1046645000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F164" s="0">
-        <x:v>122892213</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>3.94</x:v>
+        <x:v>2.87</x:v>
       </x:c>
       <x:c r="J164" s="0">
-        <x:v>19.21</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>17495257</x:v>
+        <x:v>6397124</x:v>
       </x:c>
       <x:c r="D165" s="0">
-        <x:v>17500000</x:v>
+        <x:v>35300000</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>525000000</x:v>
+        <x:v>1046645000</x:v>
       </x:c>
       <x:c r="F165" s="0">
-        <x:v>409385433</x:v>
+        <x:v>122892213</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>5</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>17.87</x:v>
+        <x:v>3.82</x:v>
       </x:c>
       <x:c r="J165" s="0">
-        <x:v>23.4</x:v>
+        <x:v>19.21</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>9350000</x:v>
+        <x:v>17495257</x:v>
       </x:c>
       <x:c r="D166" s="0">
-        <x:v>14710247</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>150000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F166" s="0">
-        <x:v>69547091</x:v>
+        <x:v>409385433</x:v>
       </x:c>
       <x:c r="G166" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>1.1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>2.25</x:v>
+        <x:v>17.75</x:v>
       </x:c>
       <x:c r="J166" s="0">
-        <x:v>7.44</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D167" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>9350000</x:v>
+      </x:c>
+      <x:c r="D167" s="0">
+        <x:v>14710247</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>100000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F167" s="0">
-        <x:v>75911475</x:v>
+        <x:v>69547091</x:v>
       </x:c>
       <x:c r="G167" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>0.37</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>22.74</x:v>
+        <x:v>2.23</x:v>
       </x:c>
       <x:c r="J167" s="0">
-        <x:v>51.7</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="D168" s="0">
-        <x:v>2000000</x:v>
+        <x:v>1468255</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>60000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F168" s="0">
-        <x:v>13401783</x:v>
+        <x:v>75911475</x:v>
       </x:c>
       <x:c r="G168" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>2.23</x:v>
+        <x:v>22.5</x:v>
       </x:c>
       <x:c r="J168" s="0">
-        <x:v>26.8</x:v>
+        <x:v>51.7</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>725000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D169" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F169" s="0">
-        <x:v>48539975</x:v>
+        <x:v>13401783</x:v>
       </x:c>
       <x:c r="G169" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>37.84</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="J169" s="0">
-        <x:v>66.95</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>1060056</x:v>
+        <x:v>725000</x:v>
       </x:c>
       <x:c r="D170" s="0">
-        <x:v>7000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F170" s="0">
-        <x:v>60762934</x:v>
+        <x:v>48539975</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>0.44</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>221.9</x:v>
+        <x:v>36.56</x:v>
       </x:c>
       <x:c r="J170" s="0">
-        <x:v>57.32</x:v>
+        <x:v>66.95</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>132750000</x:v>
-      </x:c>
-      <x:c r="D171" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1060056</x:v>
+      </x:c>
+      <x:c r="D171" s="0">
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F171" s="0">
-        <x:v>565141750</x:v>
+        <x:v>60762934</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>2.94</x:v>
+        <x:v>223.6</x:v>
       </x:c>
       <x:c r="J171" s="0">
-        <x:v>4.26</x:v>
+        <x:v>57.32</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>373000</x:v>
-      </x:c>
-      <x:c r="D172" s="0">
-        <x:v>1000000</x:v>
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>75000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F172" s="0">
-        <x:v>23786370</x:v>
+        <x:v>565141750</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>8</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="J172" s="0">
-        <x:v>63.77</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>10000000</x:v>
+        <x:v>373000</x:v>
       </x:c>
       <x:c r="D173" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>140000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F173" s="0">
-        <x:v>133271568</x:v>
+        <x:v>23786370</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>10.5</x:v>
+        <x:v>8.25</x:v>
       </x:c>
       <x:c r="J173" s="0">
-        <x:v>13.33</x:v>
+        <x:v>63.77</x:v>
       </x:c>
       <x:c r="K173" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:11">
       <x:c r="A174" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>66142950</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="D174" s="0">
-        <x:v>105000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>650000000</x:v>
+        <x:v>140000000</x:v>
       </x:c>
       <x:c r="F174" s="0">
-        <x:v>384952260</x:v>
+        <x:v>133271568</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>2.71</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>6.8</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="J174" s="0">
-        <x:v>5.82</x:v>
+        <x:v>13.33</x:v>
       </x:c>
       <x:c r="K174" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C175" s="0">
+        <x:v>66142950</x:v>
+      </x:c>
+      <x:c r="D175" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="E175" s="0">
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F175" s="0">
+        <x:v>384952260</x:v>
+      </x:c>
+      <x:c r="G175" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H175" s="0">
+        <x:v>2.71</x:v>
+      </x:c>
+      <x:c r="I175" s="0">
+        <x:v>6.6</x:v>
+      </x:c>
+      <x:c r="J175" s="0">
+        <x:v>5.82</x:v>
+      </x:c>
+      <x:c r="K175" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:11">
+      <x:c r="A176" s="0" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="B175" s="0" t="s">
+      <x:c r="B176" s="0" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="C175" s="0">
+      <x:c r="C176" s="0">
         <x:v>3081843</x:v>
       </x:c>
-      <x:c r="D175" s="0">
+      <x:c r="D176" s="0">
         <x:v>5000000</x:v>
       </x:c>
-      <x:c r="E175" s="0">
+      <x:c r="E176" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F175" s="0">
+      <x:c r="F176" s="0">
         <x:v>43986444</x:v>
       </x:c>
-      <x:c r="G175" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H175" s="0">
+      <x:c r="G176" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H176" s="0">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="I175" s="0">
-        <x:v>5.55</x:v>
-      </x:c>
-      <x:c r="J175" s="0">
+      <x:c r="I176" s="0">
+        <x:v>5.52</x:v>
+      </x:c>
+      <x:c r="J176" s="0">
         <x:v>14.27</x:v>
       </x:c>
-      <x:c r="K175" s="0" t="s">
+      <x:c r="K176" s="0" t="s">
         <x:v>276</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,6 +49,15 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
     <x:t>GRSEL</x:t>
   </x:si>
   <x:si>
@@ -58,9 +67,6 @@
     <x:t>PCILT</x:t>
   </x:si>
   <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>TTKOM</x:t>
   </x:si>
   <x:si>
@@ -271,9 +277,6 @@
     <x:t>29.07.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
     <x:t>31.03.2026</x:t>
   </x:si>
   <x:si>
@@ -470,9 +473,6 @@
   </x:si>
   <x:si>
     <x:t>27.05.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.09.2026</x:t>
   </x:si>
   <x:si>
     <x:t>MOPAS</x:t>
@@ -1369,7 +1369,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K176"/>
+  <x:dimension ref="A1:K177"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1414,96 +1414,99 @@
       <x:c r="B2" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C2" s="0">
-        <x:v>14092</x:v>
+      <x:c r="C2" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>1000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F2" s="0">
-        <x:v>4152925</x:v>
+        <x:v>1750000000</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>293</x:v>
+        <x:v>171.5</x:v>
       </x:c>
       <x:c r="J2" s="0">
-        <x:v>294.7</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E3" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F3" s="0">
+        <x:v>14714923</x:v>
+      </x:c>
+      <x:c r="G3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H3" s="0">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="I3" s="0">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="J3" s="0">
+        <x:v>294.3</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="0">
-        <x:v>2850000</x:v>
-      </x:c>
-      <x:c r="E3" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3" s="0">
-        <x:v>2.41</x:v>
-      </x:c>
-      <x:c r="H3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I3" s="0">
-        <x:v>29.76</x:v>
-      </x:c>
-      <x:c r="J3" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C4" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>20000000</x:v>
+        <x:v>2850000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>2500000000</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F4" s="0">
+        <x:v>3013600</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>0</x:v>
+        <x:v>2.41</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>54.85</x:v>
+        <x:v>29.34</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>0</x:v>
+        <x:v>30.14</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
@@ -1514,25 +1517,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>10000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>8.11</x:v>
+        <x:v>49.84</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1545,32 +1548,29 @@
       <x:c r="B6" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C6" s="0">
-        <x:v>12450000</x:v>
+      <x:c r="C6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>96033600</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>650000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>60880500</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>2.42</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>4.89</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -1580,29 +1580,32 @@
       <x:c r="B7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C7" s="0">
+        <x:v>12450000</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>36000000</x:v>
+        <x:v>96033600</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F7" s="0">
+        <x:v>60880500</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>0</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>6.15</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>0</x:v>
+        <x:v>4.89</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -1612,32 +1615,29 @@
       <x:c r="B8" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="0">
-        <x:v>500000</x:v>
+      <x:c r="C8" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>15000000</x:v>
+        <x:v>36000000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F8" s="0">
-        <x:v>4367500</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>8.64</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>8.74</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -1648,28 +1648,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>350000</x:v>
+        <x:v>510440</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>13500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>400000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>8213000</x:v>
+        <x:v>4457388</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>22.36</x:v>
+        <x:v>8.32</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>23.47</x:v>
+        <x:v>8.73</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
         <x:v>12</x:v>
@@ -1680,150 +1680,150 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>20746859</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>30000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>210000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>145013995</x:v>
+        <x:v>13823000</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>3.7</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>6.87</x:v>
+        <x:v>20.14</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>6.99</x:v>
+        <x:v>23.04</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="C11" s="0">
-        <x:v>11397816</x:v>
+        <x:v>20746859</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>15000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>210000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>269900283</x:v>
+        <x:v>145013995</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.71</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>19</x:v>
+        <x:v>6.34</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>23.68</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11397816</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>50000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>8385000</x:v>
+        <x:v>269900283</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.05</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>6.6</x:v>
+        <x:v>17.66</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>8.39</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="C13" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D13" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E13" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F13" s="0">
+        <x:v>8385000</x:v>
+      </x:c>
+      <x:c r="G13" s="0">
+        <x:v>2.05</x:v>
+      </x:c>
+      <x:c r="H13" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I13" s="0">
+        <x:v>5.94</x:v>
+      </x:c>
+      <x:c r="J13" s="0">
+        <x:v>8.39</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>2300000</x:v>
-      </x:c>
-      <x:c r="D13" s="0">
-        <x:v>12000000</x:v>
-      </x:c>
-      <x:c r="E13" s="0">
-        <x:v>12000000</x:v>
-      </x:c>
-      <x:c r="F13" s="0">
-        <x:v>1739216</x:v>
-      </x:c>
-      <x:c r="G13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="0">
-        <x:v>3.83</x:v>
-      </x:c>
-      <x:c r="I13" s="0">
-        <x:v>14.3</x:v>
-      </x:c>
-      <x:c r="J13" s="0">
-        <x:v>0.76</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="C14" s="0">
-        <x:v>4790000</x:v>
+        <x:v>2300000</x:v>
       </x:c>
       <x:c r="D14" s="0">
         <x:v>12000000</x:v>
@@ -1832,19 +1832,19 @@
         <x:v>12000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>7029498</x:v>
+        <x:v>1739216</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>7.98</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>4.61</x:v>
+        <x:v>14.15</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>1.47</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
         <x:v>36</x:v>
@@ -1855,10 +1855,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>4850000</x:v>
+        <x:v>4790000</x:v>
       </x:c>
       <x:c r="D15" s="0">
         <x:v>12000000</x:v>
@@ -1867,19 +1867,19 @@
         <x:v>12000000</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>3543837</x:v>
+        <x:v>7029498</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>8.08</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>12.79</x:v>
+        <x:v>4.58</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>0.73</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
         <x:v>38</x:v>
@@ -1890,34 +1890,34 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>4850000</x:v>
+      </x:c>
+      <x:c r="D16" s="0">
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="E16" s="0">
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="F16" s="0">
+        <x:v>3543837</x:v>
+      </x:c>
+      <x:c r="G16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="0">
+        <x:v>8.08</x:v>
+      </x:c>
+      <x:c r="I16" s="0">
+        <x:v>11.52</x:v>
+      </x:c>
+      <x:c r="J16" s="0">
+        <x:v>0.73</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>61493</x:v>
-      </x:c>
-      <x:c r="D16" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E16" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F16" s="0">
-        <x:v>3995647</x:v>
-      </x:c>
-      <x:c r="G16" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="I16" s="0">
-        <x:v>64.55</x:v>
-      </x:c>
-      <x:c r="J16" s="0">
-        <x:v>64.98</x:v>
-      </x:c>
-      <x:c r="K16" s="0" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1928,63 +1928,66 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>20000000</x:v>
+        <x:v>61493</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>750000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>26500000</x:v>
+        <x:v>3995647</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>1.29</x:v>
+        <x:v>60.4</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>1.33</x:v>
+        <x:v>64.98</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="C18" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="D18" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="E18" s="0">
+        <x:v>750000000</x:v>
+      </x:c>
+      <x:c r="F18" s="0">
+        <x:v>26500000</x:v>
+      </x:c>
+      <x:c r="G18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I18" s="0">
+        <x:v>1.18</x:v>
+      </x:c>
+      <x:c r="J18" s="0">
+        <x:v>1.33</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D18" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="E18" s="0">
-        <x:v>33000000</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G18" s="0">
-        <x:v>1.96</x:v>
-      </x:c>
-      <x:c r="H18" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I18" s="0">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="J18" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1992,34 +1995,31 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>100000</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>50000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F19" s="0">
-        <x:v>613000</x:v>
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>5.26</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>5.35</x:v>
+        <x:v>113.1</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>6.13</x:v>
-      </x:c>
-      <x:c r="K19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -2027,101 +2027,104 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="D20" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E20" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F20" s="0">
+        <x:v>613000</x:v>
+      </x:c>
+      <x:c r="G20" s="0">
+        <x:v>5.26</x:v>
+      </x:c>
+      <x:c r="H20" s="0">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="I20" s="0">
+        <x:v>5.19</x:v>
+      </x:c>
+      <x:c r="J20" s="0">
+        <x:v>6.13</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>10366031</x:v>
-      </x:c>
-      <x:c r="D20" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="E20" s="0">
-        <x:v>240000000</x:v>
-      </x:c>
-      <x:c r="F20" s="0">
-        <x:v>102614742</x:v>
-      </x:c>
-      <x:c r="G20" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="0">
-        <x:v>0.43</x:v>
-      </x:c>
-      <x:c r="I20" s="0">
-        <x:v>9.89</x:v>
-      </x:c>
-      <x:c r="J20" s="0">
-        <x:v>9.9</x:v>
-      </x:c>
-      <x:c r="K20" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>1800452</x:v>
+        <x:v>10366031</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>15000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>150000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>17447883</x:v>
+        <x:v>102614742</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>8.64</x:v>
+        <x:v>9.61</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>9.69</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>1800452</x:v>
+      </x:c>
+      <x:c r="D22" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E22" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F22" s="0">
+        <x:v>17447883</x:v>
+      </x:c>
+      <x:c r="G22" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H22" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="I22" s="0">
+        <x:v>8.32</x:v>
+      </x:c>
+      <x:c r="J22" s="0">
+        <x:v>9.69</x:v>
+      </x:c>
+      <x:c r="K22" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D22" s="0">
-        <x:v>13409218</x:v>
-      </x:c>
-      <x:c r="E22" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G22" s="0">
-        <x:v>9.01</x:v>
-      </x:c>
-      <x:c r="H22" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I22" s="0">
-        <x:v>18.1</x:v>
-      </x:c>
-      <x:c r="J22" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -2129,28 +2132,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>55000000</x:v>
+        <x:v>13409218</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>5.09</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>1.58</x:v>
+        <x:v>17.44</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>0</x:v>
@@ -2158,72 +2161,69 @@
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>200000</x:v>
+      <x:c r="C24" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>25000000</x:v>
+        <x:v>55000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>415500000</x:v>
-      </x:c>
-      <x:c r="F24" s="0">
-        <x:v>3174011</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>16.58</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>15.87</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
+      <x:c r="C25" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D25" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="E25" s="0">
+        <x:v>415500000</x:v>
+      </x:c>
+      <x:c r="F25" s="0">
+        <x:v>3174011</x:v>
+      </x:c>
+      <x:c r="G25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I25" s="0">
+        <x:v>15.68</x:v>
+      </x:c>
+      <x:c r="J25" s="0">
+        <x:v>15.87</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>6067182</x:v>
-      </x:c>
-      <x:c r="D25" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="E25" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F25" s="0">
-        <x:v>114062870</x:v>
-      </x:c>
-      <x:c r="G25" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H25" s="0">
-        <x:v>0.73</x:v>
-      </x:c>
-      <x:c r="I25" s="0">
-        <x:v>16.4</x:v>
-      </x:c>
-      <x:c r="J25" s="0">
-        <x:v>18.8</x:v>
-      </x:c>
-      <x:c r="K25" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -2234,31 +2234,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>12760028</x:v>
+        <x:v>6067182</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>60000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>45251910</x:v>
+        <x:v>114062870</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0.72</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>3.87</x:v>
+        <x:v>16.49</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>3.55</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -2269,31 +2269,31 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>2500000</x:v>
+        <x:v>14060028</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>2500000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>950421206</x:v>
+        <x:v>50371310</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>415.75</x:v>
+        <x:v>3.77</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>380.17</x:v>
+        <x:v>3.58</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -2301,69 +2301,69 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>181529</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>230000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>15000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>12667063</x:v>
+        <x:v>950421206</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>1.66</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>1.31</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>69.3</x:v>
+        <x:v>405.5</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>69.78</x:v>
+        <x:v>380.17</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
+      <x:c r="C29" s="0">
+        <x:v>184529</x:v>
+      </x:c>
+      <x:c r="D29" s="0">
+        <x:v>230000</x:v>
+      </x:c>
+      <x:c r="E29" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="F29" s="0">
+        <x:v>12872363</x:v>
+      </x:c>
+      <x:c r="G29" s="0">
+        <x:v>1.66</x:v>
+      </x:c>
+      <x:c r="H29" s="0">
+        <x:v>1.33</x:v>
+      </x:c>
+      <x:c r="I29" s="0">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C29" s="0">
-        <x:v>2501710</x:v>
-      </x:c>
-      <x:c r="D29" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E29" s="0">
-        <x:v>450000000</x:v>
-      </x:c>
-      <x:c r="F29" s="0">
-        <x:v>97116052</x:v>
-      </x:c>
-      <x:c r="G29" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="0">
-        <x:v>0.67</x:v>
-      </x:c>
-      <x:c r="I29" s="0">
-        <x:v>32.96</x:v>
-      </x:c>
       <x:c r="J29" s="0">
-        <x:v>38.82</x:v>
+        <x:v>69.76</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -2374,66 +2374,66 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>57675584</x:v>
+        <x:v>2501710</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>85125000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>5000000000</x:v>
+        <x:v>450000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>2781852532</x:v>
+        <x:v>97116052</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>1.8</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>50.45</x:v>
+        <x:v>29.68</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>48.23</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B31" s="0" t="s">
+      <x:c r="C31" s="0">
+        <x:v>57675584</x:v>
+      </x:c>
+      <x:c r="D31" s="0">
+        <x:v>85125000</x:v>
+      </x:c>
+      <x:c r="E31" s="0">
+        <x:v>5000000000</x:v>
+      </x:c>
+      <x:c r="F31" s="0">
+        <x:v>2781852532</x:v>
+      </x:c>
+      <x:c r="G31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H31" s="0">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="I31" s="0">
+        <x:v>47.34</x:v>
+      </x:c>
+      <x:c r="J31" s="0">
+        <x:v>48.23</x:v>
+      </x:c>
+      <x:c r="K31" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>49697313</x:v>
-      </x:c>
-      <x:c r="D31" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="E31" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F31" s="0">
-        <x:v>1701868254</x:v>
-      </x:c>
-      <x:c r="G31" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H31" s="0">
-        <x:v>1.68</x:v>
-      </x:c>
-      <x:c r="I31" s="0">
-        <x:v>33.54</x:v>
-      </x:c>
-      <x:c r="J31" s="0">
-        <x:v>34.24</x:v>
-      </x:c>
-      <x:c r="K31" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
@@ -2444,923 +2444,923 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>324474</x:v>
+        <x:v>49697313</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>40000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1781383</x:v>
+        <x:v>1701868254</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0.08</x:v>
+        <x:v>1.68</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>15.69</x:v>
+        <x:v>33.62</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>5.49</x:v>
+        <x:v>34.24</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B33" s="0" t="s">
+      <x:c r="C33" s="0">
+        <x:v>324474</x:v>
+      </x:c>
+      <x:c r="D33" s="0">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="E33" s="0">
+        <x:v>40000000</x:v>
+      </x:c>
+      <x:c r="F33" s="0">
+        <x:v>1781383</x:v>
+      </x:c>
+      <x:c r="G33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H33" s="0">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="I33" s="0">
+        <x:v>14.13</x:v>
+      </x:c>
+      <x:c r="J33" s="0">
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>7999148</x:v>
-      </x:c>
-      <x:c r="D33" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="E33" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F33" s="0">
-        <x:v>168715651</x:v>
-      </x:c>
-      <x:c r="G33" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H33" s="0">
-        <x:v>2.11</x:v>
-      </x:c>
-      <x:c r="I33" s="0">
-        <x:v>22.4</x:v>
-      </x:c>
-      <x:c r="J33" s="0">
-        <x:v>21.09</x:v>
-      </x:c>
-      <x:c r="K33" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B34" s="0" t="s">
+      <x:c r="C34" s="0">
+        <x:v>7999148</x:v>
+      </x:c>
+      <x:c r="D34" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E34" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F34" s="0">
+        <x:v>168715651</x:v>
+      </x:c>
+      <x:c r="G34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="0">
+        <x:v>2.11</x:v>
+      </x:c>
+      <x:c r="I34" s="0">
+        <x:v>20.16</x:v>
+      </x:c>
+      <x:c r="J34" s="0">
+        <x:v>21.09</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>201000</x:v>
-      </x:c>
-      <x:c r="D34" s="0">
-        <x:v>21739600</x:v>
-      </x:c>
-      <x:c r="E34" s="0">
-        <x:v>350000000</x:v>
-      </x:c>
-      <x:c r="F34" s="0">
-        <x:v>2071755</x:v>
-      </x:c>
-      <x:c r="G34" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H34" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="I34" s="0">
-        <x:v>9.71</x:v>
-      </x:c>
-      <x:c r="J34" s="0">
-        <x:v>10.31</x:v>
-      </x:c>
-      <x:c r="K34" s="0" t="s">
-        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C35" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C35" s="0">
+        <x:v>201000</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>1500000000</x:v>
+        <x:v>21739600</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>350000000</x:v>
+      </x:c>
+      <x:c r="F35" s="0">
+        <x:v>2071755</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>8.4</x:v>
+        <x:v>9.04</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>0</x:v>
+        <x:v>10.31</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>1900000</x:v>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65000000</x:v>
-      </x:c>
-      <x:c r="F36" s="0">
-        <x:v>14177000</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>8.15</x:v>
+        <x:v>7.99</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>7.46</x:v>
-      </x:c>
-      <x:c r="K36" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B37" s="0" t="s">
+      <x:c r="C37" s="0">
+        <x:v>1900000</x:v>
+      </x:c>
+      <x:c r="D37" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E37" s="0">
+        <x:v>65000000</x:v>
+      </x:c>
+      <x:c r="F37" s="0">
+        <x:v>14177000</x:v>
+      </x:c>
+      <x:c r="G37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" s="0">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="I37" s="0">
+        <x:v>7.58</x:v>
+      </x:c>
+      <x:c r="J37" s="0">
+        <x:v>7.46</x:v>
+      </x:c>
+      <x:c r="K37" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="C37" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D37" s="0">
-        <x:v>26398084</x:v>
-      </x:c>
-      <x:c r="E37" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I37" s="0">
-        <x:v>176.2</x:v>
-      </x:c>
-      <x:c r="J37" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C38" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D38" s="0">
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F38" s="0">
-        <x:v>127481195</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>19.99</x:v>
+        <x:v>171.5</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>7.13</x:v>
-      </x:c>
-      <x:c r="K38" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="C39" s="0">
-        <x:v>970810</x:v>
-      </x:c>
-      <x:c r="D39" s="0">
-        <x:v>7300000</x:v>
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>225000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>28043898</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>22.12</x:v>
+        <x:v>19.9</x:v>
       </x:c>
       <x:c r="J39" s="0">
-        <x:v>28.89</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>970810</x:v>
+      </x:c>
+      <x:c r="D40" s="0">
+        <x:v>7300000</x:v>
+      </x:c>
+      <x:c r="E40" s="0">
+        <x:v>225000000</x:v>
+      </x:c>
+      <x:c r="F40" s="0">
+        <x:v>28043898</x:v>
+      </x:c>
+      <x:c r="G40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I40" s="0">
+        <x:v>21.26</x:v>
+      </x:c>
+      <x:c r="J40" s="0">
+        <x:v>28.89</x:v>
+      </x:c>
+      <x:c r="K40" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>1001579</x:v>
-      </x:c>
-      <x:c r="D40" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E40" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F40" s="0">
-        <x:v>15106723</x:v>
-      </x:c>
-      <x:c r="G40" s="0">
-        <x:v>2.56</x:v>
-      </x:c>
-      <x:c r="H40" s="0">
-        <x:v>0.26</x:v>
-      </x:c>
-      <x:c r="I40" s="0">
-        <x:v>8.83</x:v>
-      </x:c>
-      <x:c r="J40" s="0">
-        <x:v>15.08</x:v>
-      </x:c>
-      <x:c r="K40" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>1001579</x:v>
+      </x:c>
+      <x:c r="D41" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E41" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F41" s="0">
+        <x:v>15106723</x:v>
+      </x:c>
+      <x:c r="G41" s="0">
+        <x:v>2.56</x:v>
+      </x:c>
+      <x:c r="H41" s="0">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="I41" s="0">
+        <x:v>8.47</x:v>
+      </x:c>
+      <x:c r="J41" s="0">
+        <x:v>15.08</x:v>
+      </x:c>
+      <x:c r="K41" s="0" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D41" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="E41" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I41" s="0">
-        <x:v>4.18</x:v>
-      </x:c>
-      <x:c r="J41" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>2097370</x:v>
+      <x:c r="C42" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>2000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F42" s="0">
-        <x:v>48772185</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>2.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>20.94</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>23.25</x:v>
-      </x:c>
-      <x:c r="K42" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="C43" s="0">
-        <x:v>28964237</x:v>
+        <x:v>2097370</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>80000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>811351010</x:v>
+        <x:v>48772185</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>1.11</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>41.1</x:v>
+        <x:v>18.98</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>28.01</x:v>
+        <x:v>23.25</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="C44" s="0">
-        <x:v>7024156</x:v>
+        <x:v>29346813</x:v>
       </x:c>
       <x:c r="D44" s="0">
         <x:v>80000000</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>93719334</x:v>
+        <x:v>826937156</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>0.78</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>10.82</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>13.34</x:v>
+        <x:v>28.18</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="C45" s="0">
-        <x:v>3500000</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>49400000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>137144284</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>34.68</x:v>
+        <x:v>10.34</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>39.18</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
       <x:c r="C46" s="0">
-        <x:v>3753472</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>6000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>432000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>224929072</x:v>
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>59.9</x:v>
+        <x:v>31.22</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>59.93</x:v>
+        <x:v>39.18</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>3753472</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E47" s="0">
+        <x:v>432000000</x:v>
+      </x:c>
+      <x:c r="F47" s="0">
+        <x:v>224929072</x:v>
+      </x:c>
+      <x:c r="G47" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" s="0">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="I47" s="0">
+        <x:v>57.5</x:v>
+      </x:c>
+      <x:c r="J47" s="0">
+        <x:v>59.93</x:v>
+      </x:c>
+      <x:c r="K47" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C47" s="0">
-        <x:v>3189049</x:v>
-      </x:c>
-      <x:c r="D47" s="0">
-        <x:v>4000000</x:v>
-      </x:c>
-      <x:c r="E47" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F47" s="0">
-        <x:v>154328962</x:v>
-      </x:c>
-      <x:c r="G47" s="0">
-        <x:v>3.74</x:v>
-      </x:c>
-      <x:c r="H47" s="0">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="I47" s="0">
-        <x:v>5.14</x:v>
-      </x:c>
-      <x:c r="J47" s="0">
-        <x:v>48.39</x:v>
-      </x:c>
-      <x:c r="K47" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>3189049</x:v>
+      </x:c>
+      <x:c r="D48" s="0">
+        <x:v>4000000</x:v>
+      </x:c>
+      <x:c r="E48" s="0">
+        <x:v>400000000</x:v>
+      </x:c>
+      <x:c r="F48" s="0">
+        <x:v>154328962</x:v>
+      </x:c>
+      <x:c r="G48" s="0">
+        <x:v>3.74</x:v>
+      </x:c>
+      <x:c r="H48" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I48" s="0">
+        <x:v>4.68</x:v>
+      </x:c>
+      <x:c r="J48" s="0">
+        <x:v>48.39</x:v>
+      </x:c>
+      <x:c r="K48" s="0" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D48" s="0">
-        <x:v>35000000</x:v>
-      </x:c>
-      <x:c r="E48" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G48" s="0">
-        <x:v>0.63</x:v>
-      </x:c>
-      <x:c r="H48" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I48" s="0">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="J48" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C49" s="0">
-        <x:v>3700000</x:v>
+      <x:c r="C49" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>10000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F49" s="0">
-        <x:v>163043763</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>0.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>21.66</x:v>
+        <x:v>3.36</x:v>
       </x:c>
       <x:c r="J49" s="0">
-        <x:v>44.07</x:v>
-      </x:c>
-      <x:c r="K49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
       <x:c r="C50" s="0">
-        <x:v>19402860</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>35000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>300000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>170203839</x:v>
+        <x:v>163043763</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>4.85</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>8.81</x:v>
+        <x:v>19.5</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>8.77</x:v>
+        <x:v>44.07</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="C51" s="0">
-        <x:v>236122</x:v>
+        <x:v>19636071</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1700000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>110000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>14609667</x:v>
+        <x:v>172238528</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>0.18</x:v>
+        <x:v>4.91</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>68.55</x:v>
+        <x:v>8.3</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>61.87</x:v>
+        <x:v>8.77</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>236122</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>1700000</x:v>
+      </x:c>
+      <x:c r="E52" s="0">
+        <x:v>110000000</x:v>
+      </x:c>
+      <x:c r="F52" s="0">
+        <x:v>14609667</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>61.7</x:v>
+      </x:c>
+      <x:c r="J52" s="0">
+        <x:v>61.87</x:v>
+      </x:c>
+      <x:c r="K52" s="0" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C52" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="D52" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E52" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F52" s="0">
-        <x:v>21055375</x:v>
-      </x:c>
-      <x:c r="G52" s="0">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="H52" s="0">
-        <x:v>0.29</x:v>
-      </x:c>
-      <x:c r="I52" s="0">
-        <x:v>17.75</x:v>
-      </x:c>
-      <x:c r="J52" s="0">
-        <x:v>21.06</x:v>
-      </x:c>
-      <x:c r="K52" s="0" t="s">
-        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>21055375</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>17.07</x:v>
+      </x:c>
+      <x:c r="J53" s="0">
+        <x:v>21.06</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D53" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E53" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G53" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H53" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I53" s="0">
-        <x:v>5.14</x:v>
-      </x:c>
-      <x:c r="J53" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C54" s="0">
-        <x:v>105404634</x:v>
+      <x:c r="C54" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D54" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E54" s="0">
         <x:v>200000000</x:v>
       </x:c>
-      <x:c r="E54" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F54" s="0">
-        <x:v>1032884452</x:v>
+      <x:c r="F54" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>12.7</x:v>
+        <x:v>4.68</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>9.8</x:v>
-      </x:c>
-      <x:c r="K54" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="C55" s="0">
-        <x:v>16445115</x:v>
+        <x:v>105404634</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>25000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>393919718</x:v>
+        <x:v>1032884452</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>3.29</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>42.3</x:v>
+        <x:v>11.94</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>23.95</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>16445115</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="E56" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F56" s="0">
+        <x:v>393919718</x:v>
+      </x:c>
+      <x:c r="G56" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" s="0">
+        <x:v>3.29</x:v>
+      </x:c>
+      <x:c r="I56" s="0">
+        <x:v>41.48</x:v>
+      </x:c>
+      <x:c r="J56" s="0">
+        <x:v>23.95</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="C56" s="0">
-        <x:v>1110000</x:v>
-      </x:c>
-      <x:c r="D56" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E56" s="0">
-        <x:v>1100000000</x:v>
-      </x:c>
-      <x:c r="F56" s="0">
-        <x:v>587039028</x:v>
-      </x:c>
-      <x:c r="G56" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H56" s="0">
-        <x:v>0.09</x:v>
-      </x:c>
-      <x:c r="I56" s="0">
-        <x:v>415.75</x:v>
-      </x:c>
-      <x:c r="J56" s="0">
-        <x:v>528.86</x:v>
-      </x:c>
-      <x:c r="K56" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>24398659</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>40000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>850000000</x:v>
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F57" s="0">
-        <x:v>590270273</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>41.1</x:v>
+        <x:v>405.5</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>24.19</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>46563878</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D58" s="0">
-        <x:v>50000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>500000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F58" s="0">
-        <x:v>500007798</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>12.7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J58" s="0">
-        <x:v>10.74</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
         <x:v>132</x:v>
@@ -3368,646 +3368,649 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C59" s="0">
+        <x:v>46563878</x:v>
+      </x:c>
+      <x:c r="D59" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E59" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F59" s="0">
+        <x:v>500007798</x:v>
+      </x:c>
+      <x:c r="G59" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H59" s="0">
+        <x:v>0.52</x:v>
+      </x:c>
+      <x:c r="I59" s="0">
+        <x:v>11.94</x:v>
+      </x:c>
+      <x:c r="J59" s="0">
+        <x:v>10.74</x:v>
+      </x:c>
+      <x:c r="K59" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="C59" s="0">
-        <x:v>6611571</x:v>
-      </x:c>
-      <x:c r="D59" s="0">
-        <x:v>9000000</x:v>
-      </x:c>
-      <x:c r="E59" s="0">
-        <x:v>240000000</x:v>
-      </x:c>
-      <x:c r="F59" s="0">
-        <x:v>39750803</x:v>
-      </x:c>
-      <x:c r="G59" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H59" s="0">
-        <x:v>0.69</x:v>
-      </x:c>
-      <x:c r="I59" s="0">
-        <x:v>6.15</x:v>
-      </x:c>
-      <x:c r="J59" s="0">
-        <x:v>6.01</x:v>
-      </x:c>
-      <x:c r="K59" s="0" t="s">
-        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C60" s="0">
+        <x:v>6611571</x:v>
+      </x:c>
+      <x:c r="D60" s="0">
+        <x:v>9000000</x:v>
+      </x:c>
+      <x:c r="E60" s="0">
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F60" s="0">
+        <x:v>39750803</x:v>
+      </x:c>
+      <x:c r="G60" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H60" s="0">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I60" s="0">
+        <x:v>5.91</x:v>
+      </x:c>
+      <x:c r="J60" s="0">
+        <x:v>6.01</x:v>
+      </x:c>
+      <x:c r="K60" s="0" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C60" s="0">
-        <x:v>2596120</x:v>
-      </x:c>
-      <x:c r="D60" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F60" s="0">
-        <x:v>66065196</x:v>
-      </x:c>
-      <x:c r="G60" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H60" s="0">
-        <x:v>1.36</x:v>
-      </x:c>
-      <x:c r="I60" s="0">
-        <x:v>17.43</x:v>
-      </x:c>
-      <x:c r="J60" s="0">
-        <x:v>25.45</x:v>
-      </x:c>
-      <x:c r="K60" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
       <x:c r="C61" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2596120</x:v>
       </x:c>
       <x:c r="D61" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E61" s="0">
-        <x:v>400000000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F61" s="0">
-        <x:v>4455000</x:v>
+        <x:v>66065196</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.36</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.93</x:v>
+        <x:v>16.85</x:v>
       </x:c>
       <x:c r="J61" s="0">
-        <x:v>4.46</x:v>
+        <x:v>25.45</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C62" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D62" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="E62" s="0">
+        <x:v>400000000</x:v>
+      </x:c>
+      <x:c r="F62" s="0">
+        <x:v>4455000</x:v>
+      </x:c>
+      <x:c r="G62" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H62" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I62" s="0">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="J62" s="0">
+        <x:v>4.46</x:v>
+      </x:c>
+      <x:c r="K62" s="0" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="C62" s="0">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="D62" s="0">
-        <x:v>13760000</x:v>
-      </x:c>
-      <x:c r="E62" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F62" s="0">
-        <x:v>2564000</x:v>
-      </x:c>
-      <x:c r="G62" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H62" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="I62" s="0">
-        <x:v>6.87</x:v>
-      </x:c>
-      <x:c r="J62" s="0">
-        <x:v>12.82</x:v>
-      </x:c>
-      <x:c r="K62" s="0" t="s">
-        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C63" s="0">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D63" s="0">
+        <x:v>13760000</x:v>
+      </x:c>
+      <x:c r="E63" s="0">
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F63" s="0">
+        <x:v>2564000</x:v>
+      </x:c>
+      <x:c r="G63" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H63" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I63" s="0">
+        <x:v>6.34</x:v>
+      </x:c>
+      <x:c r="J63" s="0">
+        <x:v>12.82</x:v>
+      </x:c>
+      <x:c r="K63" s="0" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D63" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E63" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F63" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G63" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H63" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I63" s="0">
-        <x:v>28.9</x:v>
-      </x:c>
-      <x:c r="J63" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="C64" s="0">
-        <x:v>5831653</x:v>
+      <x:c r="C64" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>5000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F64" s="0">
-        <x:v>304086107</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G64" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>2.86</x:v>
+        <x:v>26.68</x:v>
       </x:c>
       <x:c r="J64" s="0">
-        <x:v>52.14</x:v>
-      </x:c>
-      <x:c r="K64" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C65" s="0">
+        <x:v>5831653</x:v>
+      </x:c>
+      <x:c r="D65" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E65" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F65" s="0">
+        <x:v>304086107</x:v>
+      </x:c>
+      <x:c r="G65" s="0">
+        <x:v>2.96</x:v>
+      </x:c>
+      <x:c r="H65" s="0">
+        <x:v>0.83</x:v>
+      </x:c>
+      <x:c r="I65" s="0">
+        <x:v>2.58</x:v>
+      </x:c>
+      <x:c r="J65" s="0">
+        <x:v>52.14</x:v>
+      </x:c>
+      <x:c r="K65" s="0" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C65" s="0">
-        <x:v>14512000</x:v>
-      </x:c>
-      <x:c r="D65" s="0">
-        <x:v>79451200</x:v>
-      </x:c>
-      <x:c r="E65" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F65" s="0">
-        <x:v>575005862</x:v>
-      </x:c>
-      <x:c r="G65" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H65" s="0">
-        <x:v>1.83</x:v>
-      </x:c>
-      <x:c r="I65" s="0">
-        <x:v>35.94</x:v>
-      </x:c>
-      <x:c r="J65" s="0">
-        <x:v>39.62</x:v>
-      </x:c>
-      <x:c r="K65" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C66" s="0">
+        <x:v>14512000</x:v>
+      </x:c>
+      <x:c r="D66" s="0">
+        <x:v>79451200</x:v>
+      </x:c>
+      <x:c r="E66" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F66" s="0">
+        <x:v>575005862</x:v>
+      </x:c>
+      <x:c r="G66" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H66" s="0">
+        <x:v>1.83</x:v>
+      </x:c>
+      <x:c r="I66" s="0">
+        <x:v>34.3</x:v>
+      </x:c>
+      <x:c r="J66" s="0">
+        <x:v>39.62</x:v>
+      </x:c>
+      <x:c r="K66" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C66" s="0">
-        <x:v>3799828</x:v>
-      </x:c>
-      <x:c r="D66" s="0">
-        <x:v>3000000</x:v>
-      </x:c>
-      <x:c r="E66" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F66" s="0">
-        <x:v>177844244</x:v>
-      </x:c>
-      <x:c r="G66" s="0">
-        <x:v>3.75</x:v>
-      </x:c>
-      <x:c r="H66" s="0">
-        <x:v>0.95</x:v>
-      </x:c>
-      <x:c r="I66" s="0">
-        <x:v>22.5</x:v>
-      </x:c>
-      <x:c r="J66" s="0">
-        <x:v>46.8</x:v>
-      </x:c>
-      <x:c r="K66" s="0" t="s">
-        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C67" s="0">
+        <x:v>4339828</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>15000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F67" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F67" s="0">
+        <x:v>189961844</x:v>
       </x:c>
       <x:c r="G67" s="0">
-        <x:v>5.49</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>0</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>23.8</x:v>
+        <x:v>21.9</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>0</x:v>
+        <x:v>43.77</x:v>
+      </x:c>
+      <x:c r="K67" s="0" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C68" s="0">
-        <x:v>8337681</x:v>
+      <x:c r="C68" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>6500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F68" s="0">
-        <x:v>37235183</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G68" s="0">
-        <x:v>1.43</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>4.22</x:v>
+        <x:v>22.08</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>4.47</x:v>
-      </x:c>
-      <x:c r="K68" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C69" s="0">
+        <x:v>8337681</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>9275000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>950000000</x:v>
-      </x:c>
-      <x:c r="F69" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F69" s="0">
+        <x:v>37235183</x:v>
       </x:c>
       <x:c r="G69" s="0">
-        <x:v>0</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>36.56</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>0</x:v>
+        <x:v>4.47</x:v>
+      </x:c>
+      <x:c r="K69" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="C70" s="0">
-        <x:v>1364000</x:v>
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>23460000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>9000000000</x:v>
-      </x:c>
-      <x:c r="F70" s="0">
-        <x:v>409075556</x:v>
+        <x:v>950000000</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G70" s="0">
-        <x:v>1.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>285.25</x:v>
+        <x:v>34.88</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>299.91</x:v>
-      </x:c>
-      <x:c r="K70" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C71" s="0">
+        <x:v>1364000</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>380000000</x:v>
+        <x:v>23460000</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F71" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>9000000000</x:v>
+      </x:c>
+      <x:c r="F71" s="0">
+        <x:v>409075556</x:v>
       </x:c>
       <x:c r="G71" s="0">
-        <x:v>10</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>19.8</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>0</x:v>
+        <x:v>299.91</x:v>
+      </x:c>
+      <x:c r="K71" s="0" t="s">
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="C72" s="0">
-        <x:v>507440</x:v>
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D72" s="0">
-        <x:v>2500000</x:v>
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F72" s="0">
-        <x:v>42117724</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>2.67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>270.25</x:v>
+        <x:v>18.2</x:v>
       </x:c>
       <x:c r="J72" s="0">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K72" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>2000000</x:v>
+        <x:v>507440</x:v>
       </x:c>
       <x:c r="D73" s="0">
-        <x:v>2000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E73" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F73" s="0">
-        <x:v>81947000</x:v>
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G73" s="0">
-        <x:v>2</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>2</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>34.24</x:v>
+        <x:v>267.75</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>40.97</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>165</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>9854768</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>233360906</x:v>
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G74" s="0">
-        <x:v>0.63</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>0.62</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>19</x:v>
+        <x:v>32.66</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>23.68</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>324474</x:v>
+        <x:v>9854768</x:v>
       </x:c>
       <x:c r="D75" s="0">
-        <x:v>5000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>30000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F75" s="0">
-        <x:v>1781383</x:v>
+        <x:v>233360906</x:v>
       </x:c>
       <x:c r="G75" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>15.69</x:v>
+        <x:v>17.66</x:v>
       </x:c>
       <x:c r="J75" s="0">
-        <x:v>5.49</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C76" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D76" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E76" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F76" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C76" s="0">
+        <x:v>324474</x:v>
+      </x:c>
+      <x:c r="D76" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E76" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F76" s="0">
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G76" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>16.58</x:v>
+        <x:v>14.13</x:v>
       </x:c>
       <x:c r="J76" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K76" s="0" t="s">
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D77" s="0">
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="E77" s="0">
-        <x:v>7000000</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G77" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>5.19</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>0</x:v>
@@ -4015,92 +4018,89 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C78" s="0">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D78" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F78" s="0">
-        <x:v>85838440</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F78" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G78" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>6.68</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="J78" s="0">
-        <x:v>6.6</x:v>
-      </x:c>
-      <x:c r="K78" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>172</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>174500000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F79" s="0">
-        <x:v>694527000</x:v>
+        <x:v>85838440</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>0.33</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>2.8</x:v>
+        <x:v>6.83</x:v>
       </x:c>
       <x:c r="J79" s="0">
-        <x:v>3.98</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>635229</x:v>
+        <x:v>174500000</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>11323561</x:v>
+        <x:v>694527000</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>0</x:v>
@@ -4109,1832 +4109,1835 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>17.43</x:v>
+        <x:v>2.52</x:v>
       </x:c>
       <x:c r="J80" s="0">
-        <x:v>17.83</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>130000</x:v>
-      </x:c>
-      <x:c r="D81" s="0">
-        <x:v>3500000</x:v>
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E81" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>4947800</x:v>
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>31.7</x:v>
+        <x:v>16.85</x:v>
       </x:c>
       <x:c r="J81" s="0">
-        <x:v>38.06</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C82" s="0">
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>5000000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F82" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F82" s="0">
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G82" s="0">
-        <x:v>0</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>0</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>223.6</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>0</x:v>
+        <x:v>38.06</x:v>
+      </x:c>
+      <x:c r="K82" s="0" t="s">
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="C83" s="0">
-        <x:v>447761</x:v>
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D83" s="0">
-        <x:v>3000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F83" s="0">
-        <x:v>18415143</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>32.5</x:v>
+        <x:v>214.1</x:v>
       </x:c>
       <x:c r="J83" s="0">
-        <x:v>41.13</x:v>
-      </x:c>
-      <x:c r="K83" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>200000</x:v>
+        <x:v>447761</x:v>
       </x:c>
       <x:c r="D84" s="0">
-        <x:v>2000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>100000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>4022593</x:v>
+        <x:v>18415143</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>1.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>4.07</x:v>
+        <x:v>31.34</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>20.11</x:v>
+        <x:v>41.13</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>946718</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D85" s="0">
-        <x:v>20000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F85" s="0">
-        <x:v>37333519</x:v>
+        <x:v>4022593</x:v>
       </x:c>
       <x:c r="G85" s="0">
-        <x:v>7.55</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>41.96</x:v>
+        <x:v>3.89</x:v>
       </x:c>
       <x:c r="J85" s="0">
-        <x:v>39.43</x:v>
+        <x:v>20.11</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C86" s="0">
+        <x:v>946718</x:v>
+      </x:c>
+      <x:c r="D86" s="0">
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F86" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F86" s="0">
+        <x:v>37333519</x:v>
       </x:c>
       <x:c r="G86" s="0">
-        <x:v>0</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>0</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>18.07</x:v>
+        <x:v>37.78</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>0</x:v>
+        <x:v>39.43</x:v>
+      </x:c>
+      <x:c r="K86" s="0" t="s">
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="C87" s="0">
-        <x:v>3043115</x:v>
-      </x:c>
-      <x:c r="D87" s="0">
-        <x:v>50000000</x:v>
+      <x:c r="C87" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F87" s="0">
-        <x:v>49736990</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>21.34</x:v>
+        <x:v>16.27</x:v>
       </x:c>
       <x:c r="J87" s="0">
-        <x:v>16.34</x:v>
-      </x:c>
-      <x:c r="K87" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>2382736</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>3043115</x:v>
+      </x:c>
+      <x:c r="D88" s="0">
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F88" s="0">
-        <x:v>92635231</x:v>
+        <x:v>49736990</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>69.65</x:v>
+        <x:v>20.52</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>38.88</x:v>
+        <x:v>16.34</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D89" s="0">
-        <x:v>4191000</x:v>
+      <x:c r="C89" s="0">
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>160000000</x:v>
-      </x:c>
-      <x:c r="F89" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F89" s="0">
+        <x:v>92635231</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>52</x:v>
+        <x:v>62.7</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>0</x:v>
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="K89" s="0" t="s">
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="C90" s="0">
-        <x:v>4650000</x:v>
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D90" s="0">
-        <x:v>75000000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F90" s="0">
-        <x:v>49978950</x:v>
+        <x:v>160000000</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>11.1</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>10.75</x:v>
-      </x:c>
-      <x:c r="K90" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>806343</x:v>
+        <x:v>4650000</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>1862500</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>75000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F91" s="0">
-        <x:v>30363861</x:v>
+        <x:v>49978950</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>5</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>34.16</x:v>
+        <x:v>9.99</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>37.66</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>203</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>310000</x:v>
+        <x:v>806343</x:v>
       </x:c>
       <x:c r="D92" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>49980500</x:v>
+        <x:v>30363861</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0.01</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>11.1</x:v>
+        <x:v>33.2</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>161.23</x:v>
+        <x:v>37.66</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>203</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>2000000</x:v>
+        <x:v>310000</x:v>
       </x:c>
       <x:c r="D93" s="0">
         <x:v>5000000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>31366572</x:v>
+        <x:v>49980500</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>8.64</x:v>
+        <x:v>9.99</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>15.68</x:v>
+        <x:v>161.23</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>203</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>1250000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>25000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F94" s="0">
-        <x:v>11187500</x:v>
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>2.08</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>1.9</x:v>
+        <x:v>8.32</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>8.95</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C95" s="0">
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D95" s="0">
-        <x:v>6950000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F95" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F95" s="0">
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>10</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>3.41</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>0</x:v>
+        <x:v>8.95</x:v>
+      </x:c>
+      <x:c r="K95" s="0" t="s">
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="C96" s="0">
-        <x:v>12500000</x:v>
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D96" s="0">
-        <x:v>12500000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="F96" s="0">
-        <x:v>61582393</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>2.04</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="J96" s="0">
-        <x:v>4.93</x:v>
-      </x:c>
-      <x:c r="K96" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>207</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>2093944</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>220000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>8500000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F97" s="0">
-        <x:v>200139168</x:v>
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>99.4</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>95.58</x:v>
+        <x:v>4.93</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C98" s="0">
+        <x:v>2093944</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>150000000</x:v>
+        <x:v>220000000</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="F98" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>8500000000</x:v>
+      </x:c>
+      <x:c r="F98" s="0">
+        <x:v>200139168</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>46.08</x:v>
+        <x:v>95.75</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>0</x:v>
+        <x:v>95.58</x:v>
+      </x:c>
+      <x:c r="K98" s="0" t="s">
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="C99" s="0">
-        <x:v>51245979</x:v>
+      <x:c r="C99" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D99" s="0">
-        <x:v>85000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F99" s="0">
-        <x:v>125342407</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>2.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>1.31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>2.71</x:v>
+        <x:v>46.78</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>2.45</x:v>
-      </x:c>
-      <x:c r="K99" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>207</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>1584837</x:v>
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D100" s="0">
-        <x:v>2500000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>100000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F100" s="0">
-        <x:v>92450176</x:v>
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>0</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>1.08</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>64.55</x:v>
+        <x:v>2.54</x:v>
       </x:c>
       <x:c r="J100" s="0">
-        <x:v>58.33</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>207</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>7999148</x:v>
+        <x:v>1584837</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>11000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>200000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F101" s="0">
-        <x:v>168715651</x:v>
+        <x:v>92450176</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>2.11</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>22.4</x:v>
+        <x:v>60.4</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>21.09</x:v>
+        <x:v>58.33</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>207</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>14000000</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>10000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E102" s="0">
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F102" s="0">
-        <x:v>236130680</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>1.17</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>23</x:v>
+        <x:v>20.16</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>16.87</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>207</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>1700005</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D103" s="0">
-        <x:v>95000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>1425000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F103" s="0">
-        <x:v>20390731</x:v>
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>10</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>5.35</x:v>
+        <x:v>21.7</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>11.99</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>6000000</x:v>
+        <x:v>1700005</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>6000000</x:v>
+        <x:v>95000000</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>150000000</x:v>
+        <x:v>1425000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>132286928</x:v>
+        <x:v>20390731</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>0.94</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>14.74</x:v>
+        <x:v>5.19</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>22.05</x:v>
+        <x:v>11.99</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>1675000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>9000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>500000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F105" s="0">
-        <x:v>114158717</x:v>
+        <x:v>132286928</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>7.81</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>80</x:v>
+        <x:v>13.88</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>68.15</x:v>
+        <x:v>22.05</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>1824868</x:v>
+        <x:v>1675000</x:v>
       </x:c>
       <x:c r="D106" s="0">
-        <x:v>10000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>200000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F106" s="0">
-        <x:v>64572720</x:v>
+        <x:v>114158717</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>3.73</x:v>
+        <x:v>7.81</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0.68</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>27.94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>35.38</x:v>
+        <x:v>68.15</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C107" s="0">
+        <x:v>1824868</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>50000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F107" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F107" s="0">
+        <x:v>64572720</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>5</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>6.63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>0</x:v>
+        <x:v>35.38</x:v>
+      </x:c>
+      <x:c r="K107" s="0" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="C108" s="0">
-        <x:v>1000000</x:v>
+      <x:c r="C108" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D108" s="0">
-        <x:v>1000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F108" s="0">
-        <x:v>19787700</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F108" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>0.67</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>8.54</x:v>
+        <x:v>6.32</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>19.79</x:v>
-      </x:c>
-      <x:c r="K108" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>98551</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D109" s="0">
-        <x:v>6500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>100000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F109" s="0">
-        <x:v>1295684</x:v>
+        <x:v>19787700</x:v>
       </x:c>
       <x:c r="G109" s="0">
-        <x:v>0</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>10.3</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="J109" s="0">
-        <x:v>13.15</x:v>
+        <x:v>19.79</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>6049315</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>15000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>150000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F110" s="0">
-        <x:v>66439559</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>11.02</x:v>
+        <x:v>11.33</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>10.98</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>37225000</x:v>
+        <x:v>6049315</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>12000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E111" s="0">
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>149982056</x:v>
+        <x:v>66439559</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>8.99</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>3.45</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>1.58</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>4.03</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>1000000</x:v>
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D112" s="0">
-        <x:v>1000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>350000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>284578907</x:v>
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G112" s="0">
-        <x:v>0.8</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>0.8</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>220.3</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>284.58</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>600000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>600000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>25000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F113" s="0">
-        <x:v>22814140</x:v>
+        <x:v>284578907</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>5.87</x:v>
+        <x:v>198.3</x:v>
       </x:c>
       <x:c r="J113" s="0">
-        <x:v>38.02</x:v>
+        <x:v>284.58</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>11703083</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>16000000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>720000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F114" s="0">
-        <x:v>978644023</x:v>
+        <x:v>22814140</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>10.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>224</x:v>
+        <x:v>5.29</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>83.62</x:v>
+        <x:v>38.02</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>5100000</x:v>
+        <x:v>11703083</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>9000000</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>200000000</x:v>
+        <x:v>720000000</x:v>
       </x:c>
       <x:c r="F115" s="0">
-        <x:v>90022686</x:v>
+        <x:v>978644023</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>7.6</x:v>
+        <x:v>10.16</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>4.31</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>29.76</x:v>
+        <x:v>201.6</x:v>
       </x:c>
       <x:c r="J115" s="0">
-        <x:v>17.65</x:v>
+        <x:v>83.62</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>3228679</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>10000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>175000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F116" s="0">
-        <x:v>51395842</x:v>
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>0.9</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>0.29</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>8.11</x:v>
+        <x:v>29.34</x:v>
       </x:c>
       <x:c r="J116" s="0">
-        <x:v>15.92</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>150000</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>6000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>240000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F117" s="0">
-        <x:v>6145450</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G117" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>5.09</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>40.97</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C118" s="0">
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F118" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F118" s="0">
+        <x:v>6145450</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>10.95</x:v>
+        <x:v>4.83</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>0</x:v>
+        <x:v>40.97</x:v>
+      </x:c>
+      <x:c r="K118" s="0" t="s">
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="C119" s="0">
-        <x:v>366107</x:v>
+      <x:c r="C119" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>1200000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F119" s="0">
-        <x:v>6010300</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F119" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>13.96</x:v>
+        <x:v>11.18</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>16.42</x:v>
-      </x:c>
-      <x:c r="K119" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>120000</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D120" s="0">
-        <x:v>26398084</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>100000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F120" s="0">
-        <x:v>3830160</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G120" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>176.2</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>31.92</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>13050000</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>13050000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>1305000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G121" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>3.13</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>109</x:v>
+        <x:v>171.5</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>94.36</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>36605658</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>100000000</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1305000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>174340918</x:v>
+        <x:v>1231340857</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>4.6</x:v>
+        <x:v>104.6</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>4.76</x:v>
+        <x:v>94.36</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>1000000</x:v>
+        <x:v>36605658</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>4000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F123" s="0">
-        <x:v>429817200</x:v>
+        <x:v>174340918</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>0.08</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>415.75</x:v>
+        <x:v>4.37</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>429.82</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>300000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>60000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>171000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>791000</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>2.9</x:v>
+        <x:v>405.5</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>2.64</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>2175097</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>15000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>175000000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F125" s="0">
-        <x:v>17901652</x:v>
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>13.48</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="J125" s="0">
-        <x:v>8.23</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C126" s="0">
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>50000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F126" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>175000000</x:v>
+      </x:c>
+      <x:c r="F126" s="0">
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>0</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>2.74</x:v>
+        <x:v>12.98</x:v>
       </x:c>
       <x:c r="J126" s="0">
-        <x:v>0</x:v>
+        <x:v>8.23</x:v>
+      </x:c>
+      <x:c r="K126" s="0" t="s">
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C127" s="0">
-        <x:v>43000</x:v>
+      <x:c r="C127" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>200000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="F127" s="0">
-        <x:v>1024885</x:v>
+        <x:v>152000000</x:v>
+      </x:c>
+      <x:c r="F127" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>0.43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>25.78</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>23.83</x:v>
-      </x:c>
-      <x:c r="K127" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>9937037</x:v>
+        <x:v>43000</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>11000000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>50000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="F128" s="0">
-        <x:v>50001023</x:v>
+        <x:v>1024885</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>0</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>0.53</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>2.16</x:v>
+        <x:v>24.96</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>5.03</x:v>
+        <x:v>23.83</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C129" s="0">
+        <x:v>9937037</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>5500000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F129" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F129" s="0">
+        <x:v>50001023</x:v>
       </x:c>
       <x:c r="G129" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>0</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2.56</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>0</x:v>
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="K129" s="0" t="s">
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C130" s="0">
-        <x:v>13064888</x:v>
+      <x:c r="C130" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>30000000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F130" s="0">
-        <x:v>268254173</x:v>
+        <x:v>139000000</x:v>
+      </x:c>
+      <x:c r="F130" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>41.1</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>20.53</x:v>
-      </x:c>
-      <x:c r="K130" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>111673026</x:v>
+        <x:v>13064888</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>150000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>500000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F131" s="0">
-        <x:v>500005947</x:v>
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>12.7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>4.48</x:v>
+        <x:v>20.53</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C132" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D132" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C132" s="0">
+        <x:v>111673026</x:v>
+      </x:c>
+      <x:c r="D132" s="0">
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F132" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F132" s="0">
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G132" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>0</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>3.46</x:v>
+        <x:v>11.94</x:v>
       </x:c>
       <x:c r="J132" s="0">
-        <x:v>0</x:v>
+        <x:v>4.48</x:v>
+      </x:c>
+      <x:c r="K132" s="0" t="s">
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D133" s="0">
-        <x:v>19600000</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>92000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H133" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>6.61</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>0</x:v>
@@ -5942,573 +5945,573 @@
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C134" s="0">
-        <x:v>1100000</x:v>
+      <x:c r="C134" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>2000000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F134" s="0">
-        <x:v>56064346</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F134" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G134" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>170.1</x:v>
+        <x:v>5.97</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>50.97</x:v>
-      </x:c>
-      <x:c r="K134" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>6598092</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D135" s="0">
-        <x:v>11160000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>125000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F135" s="0">
-        <x:v>72091269</x:v>
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G135" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>5.91</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>16.58</x:v>
+        <x:v>161.9</x:v>
       </x:c>
       <x:c r="J135" s="0">
-        <x:v>10.93</x:v>
+        <x:v>50.97</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>1590000</x:v>
+        <x:v>6598092</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>2160000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>35000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F136" s="0">
-        <x:v>60641600</x:v>
+        <x:v>72091269</x:v>
       </x:c>
       <x:c r="G136" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>0.91</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>36.9</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>38.14</x:v>
+        <x:v>10.93</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>1989802</x:v>
+        <x:v>1590000</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2160000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>250000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="F137" s="0">
-        <x:v>78711752</x:v>
+        <x:v>60641600</x:v>
       </x:c>
       <x:c r="G137" s="0">
-        <x:v>2.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>130.1</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>39.56</x:v>
+        <x:v>38.14</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="C138" s="0">
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>1000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F138" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F138" s="0">
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>0</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>0</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>523</x:v>
+        <x:v>117.1</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>0</x:v>
+        <x:v>39.56</x:v>
+      </x:c>
+      <x:c r="K138" s="0" t="s">
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C139" s="0">
-        <x:v>300000</x:v>
+      <x:c r="C139" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D139" s="0">
-        <x:v>67500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>326000000</x:v>
-      </x:c>
-      <x:c r="F139" s="0">
-        <x:v>1369300</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F139" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>6.97</x:v>
+        <x:v>519.5</x:v>
       </x:c>
       <x:c r="J139" s="0">
-        <x:v>4.56</x:v>
-      </x:c>
-      <x:c r="K139" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>76908759</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D140" s="0">
-        <x:v>250000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>12000000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>1979731803</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G140" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>33.88</x:v>
+        <x:v>6.45</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>25.74</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>8291656</x:v>
+        <x:v>76908759</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>11000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>200000000</x:v>
+        <x:v>12000000000</x:v>
       </x:c>
       <x:c r="F141" s="0">
-        <x:v>126004459</x:v>
+        <x:v>1979731803</x:v>
       </x:c>
       <x:c r="G141" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>15.58</x:v>
+        <x:v>30.86</x:v>
       </x:c>
       <x:c r="J141" s="0">
-        <x:v>15.2</x:v>
+        <x:v>25.74</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>2975773</x:v>
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>6000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F142" s="0">
-        <x:v>44771095</x:v>
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G142" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>0.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>22.36</x:v>
+        <x:v>15.5</x:v>
       </x:c>
       <x:c r="J142" s="0">
-        <x:v>15.05</x:v>
+        <x:v>15.2</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>10994323</x:v>
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>21600000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>183002238</x:v>
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G143" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>5.09</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>13.16</x:v>
+        <x:v>21.74</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>16.65</x:v>
+        <x:v>15.05</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>36970641</x:v>
+        <x:v>10994323</x:v>
       </x:c>
       <x:c r="D144" s="0">
-        <x:v>195000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F144" s="0">
-        <x:v>417821090</x:v>
+        <x:v>183002238</x:v>
       </x:c>
       <x:c r="G144" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>1.9</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>16.17</x:v>
+        <x:v>12.34</x:v>
       </x:c>
       <x:c r="J144" s="0">
-        <x:v>11.3</x:v>
+        <x:v>16.65</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>271</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>5100000</x:v>
+        <x:v>37170641</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>20000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>700000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F145" s="0">
-        <x:v>155318227</x:v>
+        <x:v>421071090</x:v>
       </x:c>
       <x:c r="G145" s="0">
-        <x:v>6.81</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>0.93</x:v>
+        <x:v>1.91</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>56.55</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>30.45</x:v>
+        <x:v>11.33</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C146" s="0">
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D146" s="0">
-        <x:v>300000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E146" s="0">
         <x:v>700000000</x:v>
       </x:c>
-      <x:c r="F146" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="F146" s="0">
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>6.67</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>0</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>2</x:v>
+        <x:v>53.95</x:v>
       </x:c>
       <x:c r="J146" s="0">
-        <x:v>0</x:v>
+        <x:v>30.45</x:v>
+      </x:c>
+      <x:c r="K146" s="0" t="s">
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="C147" s="0">
-        <x:v>5000000</x:v>
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D147" s="0">
-        <x:v>5000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F147" s="0">
-        <x:v>39090077</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F147" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G147" s="0">
-        <x:v>0</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>9.89</x:v>
+        <x:v>1.91</x:v>
       </x:c>
       <x:c r="J147" s="0">
-        <x:v>7.82</x:v>
-      </x:c>
-      <x:c r="K147" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>905991</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="D148" s="0">
-        <x:v>21000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>500000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F148" s="0">
-        <x:v>17447317</x:v>
+        <x:v>39090077</x:v>
       </x:c>
       <x:c r="G148" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>16.15</x:v>
+        <x:v>9.61</x:v>
       </x:c>
       <x:c r="J148" s="0">
-        <x:v>19.26</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="C149" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C149" s="0">
+        <x:v>905991</x:v>
       </x:c>
       <x:c r="D149" s="0">
-        <x:v>11700000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F149" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F149" s="0">
+        <x:v>17447317</x:v>
       </x:c>
       <x:c r="G149" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>0</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>37.94</x:v>
+        <x:v>15.24</x:v>
       </x:c>
       <x:c r="J149" s="0">
-        <x:v>0</x:v>
+        <x:v>19.26</x:v>
+      </x:c>
+      <x:c r="K149" s="0" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>270000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>0</x:v>
@@ -6517,7 +6520,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>523</x:v>
+        <x:v>37.4</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>0</x:v>
@@ -6525,279 +6528,276 @@
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="C151" s="0">
-        <x:v>53584</x:v>
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D151" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>640000000</x:v>
-      </x:c>
-      <x:c r="F151" s="0">
-        <x:v>8271098</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F151" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>244</x:v>
+        <x:v>519.5</x:v>
       </x:c>
       <x:c r="J151" s="0">
-        <x:v>154.36</x:v>
-      </x:c>
-      <x:c r="K151" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>7550000</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D152" s="0">
-        <x:v>30000000</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>500000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F152" s="0">
-        <x:v>111777791</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>15.65</x:v>
+        <x:v>235.7</x:v>
       </x:c>
       <x:c r="J152" s="0">
-        <x:v>14.81</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>2097716</x:v>
+        <x:v>7550000</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>10112561</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>120000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F153" s="0">
-        <x:v>28985167</x:v>
+        <x:v>111777791</x:v>
       </x:c>
       <x:c r="G153" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>1.15</x:v>
+        <x:v>14.21</x:v>
       </x:c>
       <x:c r="J153" s="0">
-        <x:v>13.82</x:v>
+        <x:v>14.81</x:v>
       </x:c>
       <x:c r="K153" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>5185302</x:v>
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D154" s="0">
-        <x:v>57000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>513000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F154" s="0">
-        <x:v>37061183</x:v>
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G154" s="0">
-        <x:v>5.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>5.5</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="J154" s="0">
-        <x:v>7.15</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>669111</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D155" s="0">
-        <x:v>1000000</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>260000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F155" s="0">
-        <x:v>151220429</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G155" s="0">
-        <x:v>0</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>773</x:v>
+        <x:v>5.26</x:v>
       </x:c>
       <x:c r="J155" s="0">
-        <x:v>226</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>293</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>38840</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D156" s="0">
         <x:v>1000000</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>270000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F156" s="0">
-        <x:v>9431791</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G156" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>523</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="J156" s="0">
-        <x:v>242.84</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>2250000</x:v>
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D157" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>300000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F157" s="0">
-        <x:v>31750000</x:v>
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G157" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>15.65</x:v>
+        <x:v>519.5</x:v>
       </x:c>
       <x:c r="J157" s="0">
-        <x:v>14.11</x:v>
+        <x:v>242.84</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>1500000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D158" s="0">
-        <x:v>10112561</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>175000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F158" s="0">
-        <x:v>21870885</x:v>
+        <x:v>31750000</x:v>
       </x:c>
       <x:c r="G158" s="0">
-        <x:v>10</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>1.15</x:v>
+        <x:v>14.21</x:v>
       </x:c>
       <x:c r="J158" s="0">
-        <x:v>14.58</x:v>
+        <x:v>14.11</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
         <x:v>295</x:v>
@@ -6805,124 +6805,124 @@
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>1430040</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D159" s="0">
-        <x:v>8299326</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>600000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F159" s="0">
-        <x:v>198303629</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G159" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>1.51</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>134.4</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="J159" s="0">
-        <x:v>138.67</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="C160" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="C160" s="0">
+        <x:v>1430040</x:v>
       </x:c>
       <x:c r="D160" s="0">
-        <x:v>2500000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F160" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F160" s="0">
+        <x:v>198303629</x:v>
       </x:c>
       <x:c r="G160" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>0</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>270.25</x:v>
+        <x:v>127.4</x:v>
       </x:c>
       <x:c r="J160" s="0">
-        <x:v>0</x:v>
+        <x:v>138.67</x:v>
+      </x:c>
+      <x:c r="K160" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="C161" s="0">
-        <x:v>845945</x:v>
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D161" s="0">
-        <x:v>15000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F161" s="0">
-        <x:v>10058606</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F161" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G161" s="0">
-        <x:v>0</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>4.22</x:v>
+        <x:v>267.75</x:v>
       </x:c>
       <x:c r="J161" s="0">
-        <x:v>11.89</x:v>
-      </x:c>
-      <x:c r="K161" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>21446</x:v>
+        <x:v>845945</x:v>
       </x:c>
       <x:c r="D162" s="0">
-        <x:v>1000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>200000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F162" s="0">
-        <x:v>2015907</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>0</x:v>
@@ -6931,502 +6931,537 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>42.38</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="J162" s="0">
-        <x:v>94</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>850000</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D163" s="0">
-        <x:v>4250000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>40000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F163" s="0">
-        <x:v>6548328</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G163" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>1</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>6.76</x:v>
+        <x:v>41.16</x:v>
       </x:c>
       <x:c r="J163" s="0">
-        <x:v>7.7</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>15000000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D164" s="0">
-        <x:v>300000000</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>600000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F164" s="0">
-        <x:v>23990000</x:v>
+        <x:v>6548328</x:v>
       </x:c>
       <x:c r="G164" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>0.22</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>2.87</x:v>
+        <x:v>6.58</x:v>
       </x:c>
       <x:c r="J164" s="0">
-        <x:v>1.6</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>6397124</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="D165" s="0">
-        <x:v>35300000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>1046645000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F165" s="0">
-        <x:v>122892213</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>3.82</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J165" s="0">
-        <x:v>19.21</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>307</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>17495257</x:v>
+        <x:v>6397124</x:v>
       </x:c>
       <x:c r="D166" s="0">
-        <x:v>17500000</x:v>
+        <x:v>35300000</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>525000000</x:v>
+        <x:v>1046645000</x:v>
       </x:c>
       <x:c r="F166" s="0">
-        <x:v>409385433</x:v>
+        <x:v>122892213</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>5</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>17.75</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="J166" s="0">
-        <x:v>23.4</x:v>
+        <x:v>19.21</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>9350000</x:v>
+        <x:v>17495257</x:v>
       </x:c>
       <x:c r="D167" s="0">
-        <x:v>14710247</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>150000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F167" s="0">
-        <x:v>69547091</x:v>
+        <x:v>409385433</x:v>
       </x:c>
       <x:c r="G167" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>1.1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>2.23</x:v>
+        <x:v>17.07</x:v>
       </x:c>
       <x:c r="J167" s="0">
-        <x:v>7.44</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D168" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>9350000</x:v>
+      </x:c>
+      <x:c r="D168" s="0">
+        <x:v>14710247</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>100000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F168" s="0">
-        <x:v>75911475</x:v>
+        <x:v>69547091</x:v>
       </x:c>
       <x:c r="G168" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>0.37</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>22.5</x:v>
+        <x:v>2.23</x:v>
       </x:c>
       <x:c r="J168" s="0">
-        <x:v>51.7</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="D169" s="0">
-        <x:v>2000000</x:v>
+        <x:v>1468255</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>60000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F169" s="0">
-        <x:v>13401783</x:v>
+        <x:v>75911475</x:v>
       </x:c>
       <x:c r="G169" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>2.2</x:v>
+        <x:v>21.9</x:v>
       </x:c>
       <x:c r="J169" s="0">
-        <x:v>26.8</x:v>
+        <x:v>51.7</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>725000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D170" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F170" s="0">
-        <x:v>48539975</x:v>
+        <x:v>13401783</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>36.56</x:v>
+        <x:v>2.13</x:v>
       </x:c>
       <x:c r="J170" s="0">
-        <x:v>66.95</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>1060056</x:v>
+        <x:v>725000</x:v>
       </x:c>
       <x:c r="D171" s="0">
-        <x:v>7000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F171" s="0">
-        <x:v>60762934</x:v>
+        <x:v>48539975</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>0.44</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>223.6</x:v>
+        <x:v>34.88</x:v>
       </x:c>
       <x:c r="J171" s="0">
-        <x:v>57.32</x:v>
+        <x:v>66.95</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>132750000</x:v>
-      </x:c>
-      <x:c r="D172" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>1060056</x:v>
+      </x:c>
+      <x:c r="D172" s="0">
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F172" s="0">
-        <x:v>565141750</x:v>
+        <x:v>60762934</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>2.8</x:v>
+        <x:v>214.1</x:v>
       </x:c>
       <x:c r="J172" s="0">
-        <x:v>4.26</x:v>
+        <x:v>57.32</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>373000</x:v>
-      </x:c>
-      <x:c r="D173" s="0">
-        <x:v>1000000</x:v>
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>75000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F173" s="0">
-        <x:v>23786370</x:v>
+        <x:v>565141750</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>8.25</x:v>
+        <x:v>2.52</x:v>
       </x:c>
       <x:c r="J173" s="0">
-        <x:v>63.77</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="K173" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:11">
       <x:c r="A174" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>10000000</x:v>
+        <x:v>373000</x:v>
       </x:c>
       <x:c r="D174" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>140000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F174" s="0">
-        <x:v>133271568</x:v>
+        <x:v>23786370</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>10.5</x:v>
+        <x:v>7.43</x:v>
       </x:c>
       <x:c r="J174" s="0">
-        <x:v>13.33</x:v>
+        <x:v>63.77</x:v>
       </x:c>
       <x:c r="K174" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>66142950</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="D175" s="0">
-        <x:v>105000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>650000000</x:v>
+        <x:v>140000000</x:v>
       </x:c>
       <x:c r="F175" s="0">
-        <x:v>384952260</x:v>
+        <x:v>133271568</x:v>
       </x:c>
       <x:c r="G175" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>2.71</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>6.6</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="J175" s="0">
-        <x:v>5.82</x:v>
+        <x:v>13.33</x:v>
       </x:c>
       <x:c r="K175" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:11">
       <x:c r="A176" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C176" s="0">
+        <x:v>66142950</x:v>
+      </x:c>
+      <x:c r="D176" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="E176" s="0">
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F176" s="0">
+        <x:v>384952260</x:v>
+      </x:c>
+      <x:c r="G176" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H176" s="0">
+        <x:v>2.71</x:v>
+      </x:c>
+      <x:c r="I176" s="0">
+        <x:v>5.94</x:v>
+      </x:c>
+      <x:c r="J176" s="0">
+        <x:v>5.82</x:v>
+      </x:c>
+      <x:c r="K176" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:11">
+      <x:c r="A177" s="0" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="B176" s="0" t="s">
+      <x:c r="B177" s="0" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="C176" s="0">
+      <x:c r="C177" s="0">
         <x:v>3081843</x:v>
       </x:c>
-      <x:c r="D176" s="0">
+      <x:c r="D177" s="0">
         <x:v>5000000</x:v>
       </x:c>
-      <x:c r="E176" s="0">
+      <x:c r="E177" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F176" s="0">
+      <x:c r="F177" s="0">
         <x:v>43986444</x:v>
       </x:c>
-      <x:c r="G176" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H176" s="0">
+      <x:c r="G177" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H177" s="0">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="I176" s="0">
-        <x:v>5.52</x:v>
-      </x:c>
-      <x:c r="J176" s="0">
+      <x:c r="I177" s="0">
+        <x:v>5.33</x:v>
+      </x:c>
+      <x:c r="J177" s="0">
         <x:v>14.27</x:v>
       </x:c>
-      <x:c r="K176" s="0" t="s">
+      <x:c r="K177" s="0" t="s">
         <x:v>276</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,15 +49,42 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORZAX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16.09.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
     <x:t>15.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>GRSEL</x:t>
   </x:si>
   <x:si>
@@ -316,9 +343,6 @@
     <x:t>27.01.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
@@ -391,9 +415,6 @@
     <x:t>06.11.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
     <x:t>06.10.2025</x:t>
   </x:si>
   <x:si>
@@ -460,9 +481,6 @@
     <x:t>17.09.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
     <x:t>10.06.2025</x:t>
   </x:si>
   <x:si>
@@ -649,9 +667,6 @@
     <x:t>HALKB</x:t>
   </x:si>
   <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>11.03.2026</x:t>
   </x:si>
   <x:si>
@@ -821,9 +836,6 @@
   </x:si>
   <x:si>
     <x:t>16.03.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26.02.2026</x:t>
   </x:si>
   <x:si>
     <x:t>GLYHO</x:t>
@@ -1369,7 +1381,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K177"/>
+  <x:dimension ref="A1:K184"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1418,22 +1430,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>12000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>1750000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>0</x:v>
+        <x:v>1.54</x:v>
       </x:c>
       <x:c r="H2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>171.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1444,98 +1456,92 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>50000</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>14714923</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>284</x:v>
+        <x:v>40.98</x:v>
       </x:c>
       <x:c r="J3" s="0">
-        <x:v>294.3</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>100000</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2850000</x:v>
+        <x:v>180000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>3013600</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.41</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>29.34</x:v>
+        <x:v>12.66</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>30.14</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>20000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>0</x:v>
+        <x:v>4.84</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>49.84</x:v>
+        <x:v>22.24</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1543,31 +1549,31 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>10000000</x:v>
+        <x:v>9260000</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>7.3</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J6" s="0">
         <x:v>0</x:v>
@@ -1575,66 +1581,63 @@
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>12450000</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>96033600</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>650000000</x:v>
-      </x:c>
-      <x:c r="F7" s="0">
-        <x:v>60880500</x:v>
+        <x:v>225000000</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>2.18</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>4.89</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>36000000</x:v>
+        <x:v>39725600</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>5.91</x:v>
+        <x:v>37.72</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>0</x:v>
@@ -1642,395 +1645,389 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>510440</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>15000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>150000000</x:v>
+        <x:v>1750000000</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>4457388</x:v>
+        <x:v>17346100</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>8.32</x:v>
+        <x:v>176.9</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>8.73</x:v>
+        <x:v>173.46</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>600000</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>13500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>400000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>13823000</x:v>
+        <x:v>14714923</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>20.14</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>23.04</x:v>
+        <x:v>294.3</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>20746859</x:v>
+        <x:v>240110</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>30000000</x:v>
+        <x:v>2850000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>210000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>145013995</x:v>
+        <x:v>7160296</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0</x:v>
+        <x:v>2.41</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>3.7</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>6.34</x:v>
+        <x:v>30.74</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>6.99</x:v>
+        <x:v>29.82</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>11397816</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>15000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F12" s="0">
-        <x:v>269900283</x:v>
+        <x:v>2500000000</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>17.66</x:v>
+        <x:v>52.8</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>23.68</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>1000000</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>50000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F13" s="0">
-        <x:v>8385000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.05</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>5.94</x:v>
+        <x:v>6.95</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>8.39</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>2300000</x:v>
+        <x:v>12450000</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>12000000</x:v>
+        <x:v>96033600</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>12000000</x:v>
+        <x:v>650000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1739216</x:v>
+        <x:v>60880500</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>3.83</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>14.15</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>0.76</x:v>
+        <x:v>4.89</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>4790000</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>12000000</x:v>
+        <x:v>36000000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>12000000</x:v>
-      </x:c>
-      <x:c r="F15" s="0">
-        <x:v>7029498</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>7.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>4.58</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>1.47</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>4850000</x:v>
+        <x:v>742639</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>12000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>12000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>3543837</x:v>
+        <x:v>6383247</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>8.08</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>11.52</x:v>
+        <x:v>8.15</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>0.73</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>61493</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>2000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>250000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>3995647</x:v>
+        <x:v>15837000</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>60.4</x:v>
+        <x:v>18.13</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>64.98</x:v>
+        <x:v>22.62</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>20000000</x:v>
+        <x:v>20746859</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>500000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>750000000</x:v>
+        <x:v>210000000</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>26500000</x:v>
+        <x:v>145013995</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>0.1</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>1.18</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>1.33</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>11397816</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>150000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>33000000</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F19" s="0">
+        <x:v>269900283</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.96</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>113.1</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>0</x:v>
+        <x:v>23.68</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>100000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D20" s="0">
         <x:v>50000000</x:v>
@@ -2039,1016 +2036,1019 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>613000</x:v>
+        <x:v>8385000</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>5.26</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>5.19</x:v>
+        <x:v>5.35</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>6.13</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>10366031</x:v>
+        <x:v>2300000</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>25000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>240000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>102614742</x:v>
+        <x:v>1739216</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>0.43</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>9.61</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>9.9</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>1800452</x:v>
+        <x:v>4790000</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>15000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>150000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>17447883</x:v>
+        <x:v>7029498</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>0.36</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>8.32</x:v>
+        <x:v>4.27</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>9.69</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>4850000</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>13409218</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="F23" s="0">
+        <x:v>3543837</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>9.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>0</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>17.44</x:v>
+        <x:v>10.37</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>0</x:v>
+        <x:v>0.73</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>61493</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>55000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F24" s="0">
+        <x:v>3995647</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>5.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>1.5</x:v>
+        <x:v>63.4</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>0</x:v>
+        <x:v>64.98</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>200000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>25000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>415500000</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>3174011</x:v>
+        <x:v>26500000</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>15.68</x:v>
+        <x:v>1.11</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>15.87</x:v>
+        <x:v>1.33</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>6067182</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>40000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F26" s="0">
-        <x:v>114062870</x:v>
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>16.49</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>18.8</x:v>
-      </x:c>
-      <x:c r="K26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>14060028</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>60000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>250000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>50371310</x:v>
+        <x:v>613000</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0</x:v>
+        <x:v>5.26</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>3.77</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>3.58</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>2500000</x:v>
+        <x:v>10366031</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2500000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>950421206</x:v>
+        <x:v>102614742</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>405.5</x:v>
+        <x:v>9.56</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>380.17</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>184529</x:v>
+        <x:v>1800452</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>230000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>15000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>12872363</x:v>
+        <x:v>17447883</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>1.66</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>1.33</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>66</x:v>
+        <x:v>8.15</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>69.76</x:v>
+        <x:v>9.69</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>2501710</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>10000000</x:v>
+        <x:v>13409218</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>450000000</x:v>
-      </x:c>
-      <x:c r="F30" s="0">
-        <x:v>97116052</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>29.68</x:v>
+        <x:v>17.06</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>38.82</x:v>
-      </x:c>
-      <x:c r="K30" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>57675584</x:v>
+        <x:v>6550000</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>85125000</x:v>
+        <x:v>55000000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>5000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2781852532</x:v>
+        <x:v>9962550</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>1.8</x:v>
+        <x:v>0.61</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>47.34</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>48.23</x:v>
+        <x:v>1.52</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>49697313</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D32" s="0">
         <x:v>25000000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>415500000</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1701868254</x:v>
+        <x:v>3174011</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>1.68</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>33.62</x:v>
+        <x:v>15.63</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>34.24</x:v>
+        <x:v>15.87</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>324474</x:v>
+        <x:v>6067182</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>40000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1781383</x:v>
+        <x:v>114062870</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>14.13</x:v>
+        <x:v>16.99</x:v>
       </x:c>
       <x:c r="J33" s="0">
-        <x:v>5.49</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>7999148</x:v>
+        <x:v>15160028</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>15000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>300000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>168715651</x:v>
+        <x:v>54496310</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>2.11</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>20.16</x:v>
+        <x:v>3.82</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>21.09</x:v>
+        <x:v>3.59</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>201000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>21739600</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>350000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>2071755</x:v>
+        <x:v>950421206</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>9.04</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>10.31</x:v>
+        <x:v>380.17</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C36" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>199722</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>1500000000</x:v>
+        <x:v>230000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F36" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="F36" s="0">
+        <x:v>13877494</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>7.99</x:v>
+        <x:v>66.45</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>0</x:v>
+        <x:v>69.48</x:v>
+      </x:c>
+      <x:c r="K36" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>1900000</x:v>
+        <x:v>2501710</x:v>
       </x:c>
       <x:c r="D37" s="0">
         <x:v>10000000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65000000</x:v>
+        <x:v>450000000</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>14177000</x:v>
+        <x:v>97116052</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0.35</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>7.58</x:v>
+        <x:v>29.5</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>7.46</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>57675584</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>26398084</x:v>
+        <x:v>85125000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>5000000000</x:v>
+      </x:c>
+      <x:c r="F38" s="0">
+        <x:v>2781852532</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>171.5</x:v>
+        <x:v>49.56</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>0</x:v>
+        <x:v>48.23</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>57026857</x:v>
+      </x:c>
+      <x:c r="D39" s="0">
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>127481195</x:v>
+        <x:v>1946074001</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>0.82</x:v>
+        <x:v>1.93</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>19.9</x:v>
+        <x:v>30.26</x:v>
       </x:c>
       <x:c r="J39" s="0">
-        <x:v>7.13</x:v>
+        <x:v>34.13</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>970810</x:v>
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>7300000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>225000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>28043898</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>21.26</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="J40" s="0">
-        <x:v>28.89</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>1001579</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>10000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>100000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>15106723</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.56</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>0.26</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>8.47</x:v>
+        <x:v>18.15</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>15.08</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>201000</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>40000000</x:v>
+        <x:v>21739600</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>350000000</x:v>
+      </x:c>
+      <x:c r="F42" s="0">
+        <x:v>2071755</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>4</x:v>
+        <x:v>9.03</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>0</x:v>
+        <x:v>10.31</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C43" s="0">
-        <x:v>2097370</x:v>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>2000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F43" s="0">
-        <x:v>48772185</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>2.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>18.98</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>23.25</x:v>
-      </x:c>
-      <x:c r="K43" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>29346813</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>80000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>65000000</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>826937156</x:v>
+        <x:v>14177000</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>1.13</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>39</x:v>
+        <x:v>7.12</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>28.18</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C45" s="0">
-        <x:v>7024156</x:v>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>80000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F45" s="0">
-        <x:v>93719334</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>10.34</x:v>
+        <x:v>176.9</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>13.34</x:v>
-      </x:c>
-      <x:c r="K45" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>3500000</x:v>
-      </x:c>
-      <x:c r="D46" s="0">
-        <x:v>49400000</x:v>
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>137144284</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>31.22</x:v>
+        <x:v>18.19</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>39.18</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>3753472</x:v>
+        <x:v>970810</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>6000000</x:v>
+        <x:v>7300000</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>432000000</x:v>
+        <x:v>225000000</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>224929072</x:v>
+        <x:v>28043898</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>57.5</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="J47" s="0">
-        <x:v>59.93</x:v>
+        <x:v>28.89</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>3189049</x:v>
+        <x:v>1001579</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>400000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>154328962</x:v>
+        <x:v>15106723</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.74</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>4.68</x:v>
+        <x:v>8.33</x:v>
       </x:c>
       <x:c r="J48" s="0">
-        <x:v>48.39</x:v>
+        <x:v>15.08</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>35000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>150000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>3.36</x:v>
+        <x:v>4.14</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>0</x:v>
@@ -3056,949 +3056,952 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>3700000</x:v>
+        <x:v>2097370</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>10000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>400000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>163043763</x:v>
+        <x:v>48772185</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>0.45</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>19.5</x:v>
+        <x:v>17.85</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>44.07</x:v>
+        <x:v>23.25</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>19636071</x:v>
+        <x:v>29346813</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>35000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>300000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>172238528</x:v>
+        <x:v>826937156</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>4.91</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>8.3</x:v>
+        <x:v>40.98</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>8.77</x:v>
+        <x:v>28.18</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>236122</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1700000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>110000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>14609667</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>61.7</x:v>
+        <x:v>10.73</x:v>
       </x:c>
       <x:c r="J52" s="0">
-        <x:v>61.87</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>1000000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E53" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>49400000</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>21055375</x:v>
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>0.29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>17.07</x:v>
+        <x:v>28.1</x:v>
       </x:c>
       <x:c r="J53" s="0">
-        <x:v>21.06</x:v>
+        <x:v>39.18</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>3753472</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>2000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F54" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>432000000</x:v>
+      </x:c>
+      <x:c r="F54" s="0">
+        <x:v>224929072</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>0</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>4.68</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>0</x:v>
+        <x:v>59.93</x:v>
+      </x:c>
+      <x:c r="K54" s="0" t="s">
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>105404634</x:v>
+        <x:v>3189049</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>200000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>1032884452</x:v>
+        <x:v>154328962</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>0</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>11.94</x:v>
+        <x:v>4.75</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>9.8</x:v>
+        <x:v>48.39</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C56" s="0">
-        <x:v>16445115</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>25000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F56" s="0">
-        <x:v>393919718</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G56" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>3.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>41.48</x:v>
+        <x:v>3.11</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>23.95</x:v>
-      </x:c>
-      <x:c r="K56" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>1110000</x:v>
+        <x:v>5350000</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>2000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>1100000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F57" s="0">
-        <x:v>587039028</x:v>
+        <x:v>196494213</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>405.5</x:v>
+        <x:v>17.55</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>528.86</x:v>
+        <x:v>36.73</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>24398659</x:v>
+        <x:v>20226071</x:v>
       </x:c>
       <x:c r="D58" s="0">
-        <x:v>40000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>850000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F58" s="0">
-        <x:v>590270273</x:v>
+        <x:v>177200428</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>0.94</x:v>
+        <x:v>5.06</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>39</x:v>
+        <x:v>7.47</x:v>
       </x:c>
       <x:c r="J58" s="0">
-        <x:v>24.19</x:v>
+        <x:v>8.76</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>46563878</x:v>
+        <x:v>236122</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>50000000</x:v>
+        <x:v>1700000</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>500000000</x:v>
+        <x:v>110000000</x:v>
       </x:c>
       <x:c r="F59" s="0">
-        <x:v>500007798</x:v>
+        <x:v>14609667</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>11.94</x:v>
+        <x:v>55.55</x:v>
       </x:c>
       <x:c r="J59" s="0">
-        <x:v>10.74</x:v>
+        <x:v>61.87</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>6611571</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>9000000</x:v>
-      </x:c>
-      <x:c r="E60" s="0">
-        <x:v>240000000</x:v>
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F60" s="0">
-        <x:v>39750803</x:v>
+        <x:v>21055375</x:v>
       </x:c>
       <x:c r="G60" s="0">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>0.69</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>5.91</x:v>
+        <x:v>17.8</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>6.01</x:v>
+        <x:v>21.06</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C61" s="0">
-        <x:v>2596120</x:v>
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D61" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F61" s="0">
-        <x:v>66065196</x:v>
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E61" s="0">
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>1.36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>16.85</x:v>
+        <x:v>4.75</x:v>
       </x:c>
       <x:c r="J61" s="0">
-        <x:v>25.45</x:v>
-      </x:c>
-      <x:c r="K61" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>1000000</x:v>
+        <x:v>105404634</x:v>
       </x:c>
       <x:c r="D62" s="0">
-        <x:v>30000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>400000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F62" s="0">
-        <x:v>4455000</x:v>
+        <x:v>1032884452</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>3.92</x:v>
+        <x:v>12.66</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>4.46</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>200000</x:v>
+        <x:v>16445115</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>13760000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>300000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>2564000</x:v>
+        <x:v>393919718</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>0.04</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>6.34</x:v>
+        <x:v>37.34</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>12.82</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C64" s="0">
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>30000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1100000000</x:v>
+      </x:c>
+      <x:c r="F64" s="0">
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>26.68</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="J64" s="0">
-        <x:v>0</x:v>
+        <x:v>528.86</x:v>
+      </x:c>
+      <x:c r="K64" s="0" t="s">
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>5831653</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D65" s="0">
-        <x:v>5000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>500000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F65" s="0">
-        <x:v>304086107</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G65" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>2.58</x:v>
+        <x:v>40.98</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>52.14</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>14512000</x:v>
+        <x:v>46563878</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>79451200</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F66" s="0">
-        <x:v>575005862</x:v>
+        <x:v>500007798</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>1.83</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>34.3</x:v>
+        <x:v>12.66</x:v>
       </x:c>
       <x:c r="J66" s="0">
-        <x:v>39.62</x:v>
+        <x:v>10.74</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>4339828</x:v>
+        <x:v>6611571</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>3000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>300000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>189961844</x:v>
+        <x:v>39750803</x:v>
       </x:c>
       <x:c r="G67" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>21.9</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>43.77</x:v>
+        <x:v>6.01</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C68" s="0">
+        <x:v>2596120</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="E68" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F68" s="0">
+        <x:v>66065196</x:v>
       </x:c>
       <x:c r="G68" s="0">
-        <x:v>5.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>0</x:v>
+        <x:v>1.36</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>22.08</x:v>
+        <x:v>15.97</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>0</x:v>
+        <x:v>25.45</x:v>
+      </x:c>
+      <x:c r="K68" s="0" t="s">
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>8337681</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>6500000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>100000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>37235183</x:v>
+        <x:v>4455000</x:v>
       </x:c>
       <x:c r="G69" s="0">
-        <x:v>1.43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>3.8</x:v>
+        <x:v>4.02</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>4.47</x:v>
+        <x:v>4.46</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C70" s="0">
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>9275000</x:v>
+        <x:v>13760000</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>950000000</x:v>
-      </x:c>
-      <x:c r="F70" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F70" s="0">
+        <x:v>2564000</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>0</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>34.88</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>0</x:v>
+        <x:v>12.82</x:v>
+      </x:c>
+      <x:c r="K70" s="0" t="s">
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="C71" s="0">
-        <x:v>1364000</x:v>
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>23460000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>9000000000</x:v>
-      </x:c>
-      <x:c r="F71" s="0">
-        <x:v>409075556</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G71" s="0">
-        <x:v>1.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>273</x:v>
+        <x:v>24.42</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>299.91</x:v>
-      </x:c>
-      <x:c r="K71" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C72" s="0">
+        <x:v>5831653</x:v>
       </x:c>
       <x:c r="D72" s="0">
-        <x:v>380000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F72" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F72" s="0">
+        <x:v>304086107</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>10</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>0</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>18.2</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="J72" s="0">
-        <x:v>0</x:v>
+        <x:v>52.14</x:v>
+      </x:c>
+      <x:c r="K72" s="0" t="s">
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>507440</x:v>
+        <x:v>14512000</x:v>
       </x:c>
       <x:c r="D73" s="0">
-        <x:v>2500000</x:v>
+        <x:v>79451200</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F73" s="0">
-        <x:v>42117724</x:v>
+        <x:v>575005862</x:v>
       </x:c>
       <x:c r="G73" s="0">
-        <x:v>2.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>0.54</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>267.75</x:v>
+        <x:v>37.72</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>83</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>2000000</x:v>
+        <x:v>5139828</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>2000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>100000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>81947000</x:v>
+        <x:v>207321844</x:v>
       </x:c>
       <x:c r="G74" s="0">
-        <x:v>2</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>2</x:v>
+        <x:v>1.28</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>32.66</x:v>
+        <x:v>22.36</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>40.97</x:v>
+        <x:v>40.34</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>9854768</x:v>
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D75" s="0">
-        <x:v>10000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F75" s="0">
-        <x:v>233360906</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G75" s="0">
-        <x:v>0.63</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>0.62</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>17.66</x:v>
+        <x:v>21.74</x:v>
       </x:c>
       <x:c r="J75" s="0">
-        <x:v>23.68</x:v>
-      </x:c>
-      <x:c r="K75" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>324474</x:v>
+        <x:v>8337681</x:v>
       </x:c>
       <x:c r="D76" s="0">
-        <x:v>5000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>30000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F76" s="0">
-        <x:v>1781383</x:v>
+        <x:v>37235183</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>0</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>14.13</x:v>
+        <x:v>3.42</x:v>
       </x:c>
       <x:c r="J76" s="0">
-        <x:v>5.49</x:v>
+        <x:v>4.47</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D77" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E77" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="D77" s="0">
+        <x:v>9275000</x:v>
+      </x:c>
+      <x:c r="E77" s="0">
+        <x:v>950000000</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
         <x:v>13</x:v>
@@ -4010,7 +4013,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>15.68</x:v>
+        <x:v>33.8</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>0</x:v>
@@ -4018,430 +4021,430 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C78" s="0">
+        <x:v>1364000</x:v>
       </x:c>
       <x:c r="D78" s="0">
-        <x:v>100000</x:v>
+        <x:v>23460000</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="F78" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>9000000000</x:v>
+      </x:c>
+      <x:c r="F78" s="0">
+        <x:v>409075556</x:v>
       </x:c>
       <x:c r="G78" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>4.8</x:v>
+        <x:v>289.25</x:v>
       </x:c>
       <x:c r="J78" s="0">
-        <x:v>0</x:v>
+        <x:v>299.91</x:v>
+      </x:c>
+      <x:c r="K78" s="0" t="s">
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C79" s="0">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D79" s="0">
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F79" s="0">
-        <x:v>85838440</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F79" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G79" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>6.83</x:v>
+        <x:v>19.24</x:v>
       </x:c>
       <x:c r="J79" s="0">
-        <x:v>6.6</x:v>
-      </x:c>
-      <x:c r="K79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>174500000</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>507440</x:v>
+      </x:c>
+      <x:c r="D80" s="0">
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>694527000</x:v>
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G80" s="0">
-        <x:v>0</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>2.52</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="J80" s="0">
-        <x:v>3.98</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>635229</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D81" s="0">
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E81" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>11323561</x:v>
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>0.33</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>16.85</x:v>
+        <x:v>32.78</x:v>
       </x:c>
       <x:c r="J81" s="0">
-        <x:v>17.83</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>130000</x:v>
+        <x:v>9854768</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>3500000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>100000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F82" s="0">
-        <x:v>4947800</x:v>
+        <x:v>233360906</x:v>
       </x:c>
       <x:c r="G82" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>29</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>38.06</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C83" s="0">
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D83" s="0">
         <x:v>5000000</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F83" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F83" s="0">
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>214.1</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="J83" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K83" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="C84" s="0">
-        <x:v>447761</x:v>
-      </x:c>
-      <x:c r="D84" s="0">
-        <x:v>3000000</x:v>
-      </x:c>
-      <x:c r="E84" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F84" s="0">
-        <x:v>18415143</x:v>
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F84" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>31.34</x:v>
+        <x:v>15.63</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>41.13</x:v>
-      </x:c>
-      <x:c r="K84" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C85" s="0">
-        <x:v>200000</x:v>
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D85" s="0">
-        <x:v>2000000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F85" s="0">
-        <x:v>4022593</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G85" s="0">
-        <x:v>1.71</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>3.89</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="J85" s="0">
-        <x:v>20.11</x:v>
-      </x:c>
-      <x:c r="K85" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>946718</x:v>
-      </x:c>
-      <x:c r="D86" s="0">
-        <x:v>20000000</x:v>
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F86" s="0">
-        <x:v>37333519</x:v>
+        <x:v>85838440</x:v>
       </x:c>
       <x:c r="G86" s="0">
-        <x:v>7.55</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>0.36</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>37.78</x:v>
+        <x:v>6.83</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>39.43</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C87" s="0">
+        <x:v>174500000</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F87" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F87" s="0">
+        <x:v>694527000</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>16.27</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="J87" s="0">
-        <x:v>0</x:v>
+        <x:v>3.98</x:v>
+      </x:c>
+      <x:c r="K87" s="0" t="s">
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>3043115</x:v>
-      </x:c>
-      <x:c r="D88" s="0">
-        <x:v>50000000</x:v>
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F88" s="0">
-        <x:v>49736990</x:v>
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>20.52</x:v>
+        <x:v>15.97</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>16.34</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>2382736</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>130000</x:v>
+      </x:c>
+      <x:c r="D89" s="0">
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F89" s="0">
-        <x:v>92635231</x:v>
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>0</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>62.7</x:v>
+        <x:v>28.14</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>38.88</x:v>
+        <x:v>38.06</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D90" s="0">
-        <x:v>4191000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>160000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
         <x:v>13</x:v>
@@ -4453,7 +4456,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>48</x:v>
+        <x:v>216.3</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>0</x:v>
@@ -4461,1503 +4464,1506 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>4650000</x:v>
+        <x:v>447761</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>75000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F91" s="0">
-        <x:v>49978950</x:v>
+        <x:v>18415143</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>9.99</x:v>
+        <x:v>30.06</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>10.75</x:v>
+        <x:v>41.13</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>806343</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D92" s="0">
-        <x:v>1862500</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>75000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>30363861</x:v>
+        <x:v>4022593</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>5</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>33.2</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>37.66</x:v>
+        <x:v>20.11</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>310000</x:v>
+        <x:v>946718</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>5000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>49980500</x:v>
+        <x:v>37333519</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>0</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>9.99</x:v>
+        <x:v>36.1</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>161.23</x:v>
+        <x:v>39.43</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="C94" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="D94" s="0">
-        <x:v>5000000</x:v>
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E94" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F94" s="0">
-        <x:v>31366572</x:v>
+      <x:c r="F94" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>8.32</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>15.68</x:v>
-      </x:c>
-      <x:c r="K94" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>1250000</x:v>
+        <x:v>3043115</x:v>
       </x:c>
       <x:c r="D95" s="0">
-        <x:v>25000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F95" s="0">
-        <x:v>11187500</x:v>
+        <x:v>49736990</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>2.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>1.8</x:v>
+        <x:v>20.86</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>8.95</x:v>
+        <x:v>16.34</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E96" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F96" s="0">
+        <x:v>92635231</x:v>
+      </x:c>
+      <x:c r="G96" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H96" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I96" s="0">
+        <x:v>56.45</x:v>
+      </x:c>
+      <x:c r="J96" s="0">
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="K96" s="0" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D96" s="0">
-        <x:v>6950000</x:v>
-      </x:c>
-      <x:c r="E96" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F96" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G96" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H96" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I96" s="0">
-        <x:v>3.19</x:v>
-      </x:c>
-      <x:c r="J96" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="C97" s="0">
-        <x:v>12500000</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>12500000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="F97" s="0">
-        <x:v>61582393</x:v>
+        <x:v>160000000</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>1.96</x:v>
+        <x:v>48.1</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>4.93</x:v>
-      </x:c>
-      <x:c r="K97" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>2093944</x:v>
+        <x:v>4650000</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>220000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>8500000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F98" s="0">
-        <x:v>200139168</x:v>
+        <x:v>49978950</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>0</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="H98" s="0">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>95.75</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>95.58</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C99" s="0">
+        <x:v>806343</x:v>
       </x:c>
       <x:c r="D99" s="0">
-        <x:v>150000000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="F99" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F99" s="0">
+        <x:v>30363861</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>0</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>46.78</x:v>
+        <x:v>31.9</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>0</x:v>
+        <x:v>37.66</x:v>
+      </x:c>
+      <x:c r="K99" s="0" t="s">
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C100" s="0">
+        <x:v>310000</x:v>
+      </x:c>
+      <x:c r="D100" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E100" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F100" s="0">
+        <x:v>49980500</x:v>
+      </x:c>
+      <x:c r="G100" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H100" s="0">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="I100" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J100" s="0">
+        <x:v>161.23</x:v>
+      </x:c>
+      <x:c r="K100" s="0" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="C100" s="0">
-        <x:v>51245979</x:v>
-      </x:c>
-      <x:c r="D100" s="0">
-        <x:v>85000000</x:v>
-      </x:c>
-      <x:c r="E100" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F100" s="0">
-        <x:v>125342407</x:v>
-      </x:c>
-      <x:c r="G100" s="0">
-        <x:v>2.18</x:v>
-      </x:c>
-      <x:c r="H100" s="0">
-        <x:v>1.31</x:v>
-      </x:c>
-      <x:c r="I100" s="0">
-        <x:v>2.54</x:v>
-      </x:c>
-      <x:c r="J100" s="0">
-        <x:v>2.45</x:v>
-      </x:c>
-      <x:c r="K100" s="0" t="s">
-        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>1584837</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>2500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E101" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F101" s="0">
-        <x:v>92450176</x:v>
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>60.4</x:v>
+        <x:v>8.15</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>58.33</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>7999148</x:v>
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>11000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>200000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F102" s="0">
-        <x:v>168715651</x:v>
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>0</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>2.11</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>20.16</x:v>
+        <x:v>1.74</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>21.09</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="C103" s="0">
-        <x:v>14000000</x:v>
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D103" s="0">
-        <x:v>10000000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F103" s="0">
-        <x:v>236130680</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F103" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>0.84</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>21.7</x:v>
+        <x:v>2.88</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>16.87</x:v>
-      </x:c>
-      <x:c r="K103" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>1700005</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>95000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>1425000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>20390731</x:v>
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>5.19</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>11.99</x:v>
+        <x:v>4.93</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C105" s="0">
+        <x:v>2093944</x:v>
+      </x:c>
+      <x:c r="D105" s="0">
+        <x:v>220000000</x:v>
+      </x:c>
+      <x:c r="E105" s="0">
+        <x:v>8500000000</x:v>
+      </x:c>
+      <x:c r="F105" s="0">
+        <x:v>200139168</x:v>
+      </x:c>
+      <x:c r="G105" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H105" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I105" s="0">
+        <x:v>99.15</x:v>
+      </x:c>
+      <x:c r="J105" s="0">
+        <x:v>95.58</x:v>
+      </x:c>
+      <x:c r="K105" s="0" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="C105" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="D105" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="E105" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F105" s="0">
-        <x:v>132286928</x:v>
-      </x:c>
-      <x:c r="G105" s="0">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="H105" s="0">
-        <x:v>0.16</x:v>
-      </x:c>
-      <x:c r="I105" s="0">
-        <x:v>13.88</x:v>
-      </x:c>
-      <x:c r="J105" s="0">
-        <x:v>22.05</x:v>
-      </x:c>
-      <x:c r="K105" s="0" t="s">
-        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="C106" s="0">
-        <x:v>1675000</x:v>
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D106" s="0">
-        <x:v>9000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0">
-        <x:v>114158717</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>7.81</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>83</x:v>
+        <x:v>47.8</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>68.15</x:v>
-      </x:c>
-      <x:c r="K106" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>1824868</x:v>
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>10000000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E107" s="0">
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F107" s="0">
-        <x:v>64572720</x:v>
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>3.73</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0.68</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>26</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>35.38</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C108" s="0">
+        <x:v>1584837</x:v>
       </x:c>
       <x:c r="D108" s="0">
-        <x:v>50000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F108" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F108" s="0">
+        <x:v>92450176</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>0</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>6.32</x:v>
+        <x:v>63.4</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>0</x:v>
+        <x:v>58.33</x:v>
+      </x:c>
+      <x:c r="K108" s="0" t="s">
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>1000000</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D109" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>30000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F109" s="0">
-        <x:v>19787700</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G109" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>0.27</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>7.69</x:v>
+        <x:v>18.15</x:v>
       </x:c>
       <x:c r="J109" s="0">
-        <x:v>19.79</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>98551</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>6500000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>100000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F110" s="0">
-        <x:v>1295684</x:v>
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>0</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>0.06</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>11.33</x:v>
+        <x:v>21.6</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>13.15</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>6049315</x:v>
+        <x:v>1700005</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>15000000</x:v>
+        <x:v>95000000</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>150000000</x:v>
+        <x:v>1425000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>66439559</x:v>
+        <x:v>20390731</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>10.4</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>10.98</x:v>
+        <x:v>11.99</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>37225000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="D112" s="0">
-        <x:v>12000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E112" s="0">
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>149982056</x:v>
+        <x:v>132286928</x:v>
       </x:c>
       <x:c r="G112" s="0">
-        <x:v>8.99</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>3.45</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>1.5</x:v>
+        <x:v>13.95</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>4.03</x:v>
+        <x:v>22.05</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1675000</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>1000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>350000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F113" s="0">
-        <x:v>284578907</x:v>
+        <x:v>114158717</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>0.8</x:v>
+        <x:v>7.81</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>198.3</x:v>
+        <x:v>89.5</x:v>
       </x:c>
       <x:c r="J113" s="0">
-        <x:v>284.58</x:v>
+        <x:v>68.15</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>600000</x:v>
+        <x:v>1824868</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>600000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>25000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F114" s="0">
-        <x:v>22814140</x:v>
+        <x:v>64572720</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>0</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>5.29</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>38.02</x:v>
+        <x:v>35.38</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="C115" s="0">
-        <x:v>11703083</x:v>
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>16000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>720000000</x:v>
-      </x:c>
-      <x:c r="F115" s="0">
-        <x:v>978644023</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F115" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>10.16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>201.6</x:v>
+        <x:v>6.15</x:v>
       </x:c>
       <x:c r="J115" s="0">
-        <x:v>83.62</x:v>
-      </x:c>
-      <x:c r="K115" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>5100000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>9000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>200000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F116" s="0">
-        <x:v>90022686</x:v>
+        <x:v>19787700</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>7.6</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>4.31</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>29.34</x:v>
+        <x:v>6.93</x:v>
       </x:c>
       <x:c r="J116" s="0">
-        <x:v>17.65</x:v>
+        <x:v>19.79</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>3228679</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>10000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>175000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F117" s="0">
-        <x:v>51395842</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G117" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>7.3</x:v>
+        <x:v>10.54</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>15.92</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>150000</x:v>
+        <x:v>6049315</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>6000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>240000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F118" s="0">
-        <x:v>6145450</x:v>
+        <x:v>66439559</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>4.83</x:v>
+        <x:v>10.31</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>40.97</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C119" s="0">
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>1000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F119" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F119" s="0">
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G119" s="0">
-        <x:v>0</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>0</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>11.18</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>0</x:v>
+        <x:v>4.03</x:v>
+      </x:c>
+      <x:c r="K119" s="0" t="s">
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>366107</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D120" s="0">
-        <x:v>1200000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>30000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F120" s="0">
-        <x:v>6010300</x:v>
+        <x:v>284578907</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>13.1</x:v>
+        <x:v>178.5</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>16.42</x:v>
+        <x:v>284.58</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>120000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>26398084</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>100000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>3830160</x:v>
+        <x:v>22814140</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>171.5</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>31.92</x:v>
+        <x:v>38.02</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>13050000</x:v>
+        <x:v>11703083</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>13050000</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>1305000000</x:v>
+        <x:v>720000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>978644023</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>3</x:v>
+        <x:v>10.16</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>3.13</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>104.6</x:v>
+        <x:v>181.5</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>94.36</x:v>
+        <x:v>83.62</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>36605658</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>100000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>500000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F123" s="0">
-        <x:v>174340918</x:v>
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>10</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>3.66</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>4.37</x:v>
+        <x:v>30.74</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>4.76</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>1000000</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>4000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>429817200</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>405.5</x:v>
+        <x:v>6.95</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>429.82</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>300000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>60000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>171000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F125" s="0">
-        <x:v>791000</x:v>
+        <x:v>6145450</x:v>
       </x:c>
       <x:c r="G125" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>2.68</x:v>
+        <x:v>4.71</x:v>
       </x:c>
       <x:c r="J125" s="0">
-        <x:v>2.64</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C126" s="0">
-        <x:v>2175097</x:v>
+      <x:c r="C126" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>15000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>175000000</x:v>
-      </x:c>
-      <x:c r="F126" s="0">
-        <x:v>17901652</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F126" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G126" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>12.98</x:v>
+        <x:v>10.25</x:v>
       </x:c>
       <x:c r="J126" s="0">
-        <x:v>8.23</x:v>
-      </x:c>
-      <x:c r="K126" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C127" s="0">
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>50000000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F127" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="F127" s="0">
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>2.64</x:v>
+        <x:v>13.31</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>0</x:v>
+        <x:v>16.42</x:v>
+      </x:c>
+      <x:c r="K127" s="0" t="s">
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>43000</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>200000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>5000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F128" s="0">
-        <x:v>1024885</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>24.96</x:v>
+        <x:v>176.9</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>23.83</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>9937037</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>11000000</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>50000000</x:v>
+        <x:v>1305000000</x:v>
       </x:c>
       <x:c r="F129" s="0">
-        <x:v>50001023</x:v>
+        <x:v>1231340857</x:v>
       </x:c>
       <x:c r="G129" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>0.53</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>2</x:v>
+        <x:v>109.5</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>5.03</x:v>
+        <x:v>94.36</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C130" s="0">
+        <x:v>36605658</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>5500000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F130" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F130" s="0">
+        <x:v>174340918</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>0</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>2.4</x:v>
+        <x:v>4.32</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>0</x:v>
+        <x:v>4.76</x:v>
+      </x:c>
+      <x:c r="K130" s="0" t="s">
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>13064888</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>30000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>600000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F131" s="0">
-        <x:v>268254173</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>39</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>20.53</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>111673026</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D132" s="0">
-        <x:v>150000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>500000000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F132" s="0">
-        <x:v>500005947</x:v>
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>11.94</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="J132" s="0">
-        <x:v>4.48</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C133" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D133" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C133" s="0">
+        <x:v>2175097</x:v>
+      </x:c>
+      <x:c r="D133" s="0">
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F133" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>175000000</x:v>
+      </x:c>
+      <x:c r="F133" s="0">
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>0</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>3.15</x:v>
+        <x:v>13.48</x:v>
       </x:c>
       <x:c r="J133" s="0">
-        <x:v>0</x:v>
+        <x:v>8.23</x:v>
+      </x:c>
+      <x:c r="K133" s="0" t="s">
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>19600000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>92000000</x:v>
+        <x:v>152000000</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
         <x:v>13</x:v>
@@ -5969,7 +5975,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>5.97</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>0</x:v>
@@ -5977,34 +5983,34 @@
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>1100000</x:v>
+        <x:v>43000</x:v>
       </x:c>
       <x:c r="D135" s="0">
-        <x:v>2000000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>100000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="F135" s="0">
-        <x:v>56064346</x:v>
+        <x:v>1024885</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>0</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>2</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>161.9</x:v>
+        <x:v>25.08</x:v>
       </x:c>
       <x:c r="J135" s="0">
-        <x:v>50.97</x:v>
+        <x:v>23.83</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
         <x:v>252</x:v>
@@ -6012,1457 +6018,1693 @@
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>6598092</x:v>
+        <x:v>9937037</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>11160000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>125000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F136" s="0">
-        <x:v>72091269</x:v>
+        <x:v>50001023</x:v>
       </x:c>
       <x:c r="G136" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>5.91</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>15.68</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>10.93</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C137" s="0">
-        <x:v>1590000</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>2160000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>35000000</x:v>
-      </x:c>
-      <x:c r="F137" s="0">
-        <x:v>60641600</x:v>
+        <x:v>139000000</x:v>
+      </x:c>
+      <x:c r="F137" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G137" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>0.91</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>36</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>38.14</x:v>
-      </x:c>
-      <x:c r="K137" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>1989802</x:v>
+        <x:v>13064888</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>5000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>250000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F138" s="0">
-        <x:v>78711752</x:v>
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>2.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>117.1</x:v>
+        <x:v>40.98</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>39.56</x:v>
+        <x:v>20.53</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C139" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C139" s="0">
+        <x:v>111673026</x:v>
       </x:c>
       <x:c r="D139" s="0">
-        <x:v>1000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F139" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F139" s="0">
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G139" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>0</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>519.5</x:v>
+        <x:v>12.66</x:v>
       </x:c>
       <x:c r="J139" s="0">
-        <x:v>0</x:v>
+        <x:v>4.48</x:v>
+      </x:c>
+      <x:c r="K139" s="0" t="s">
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C140" s="0">
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="D140" s="0">
-        <x:v>67500000</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>326000000</x:v>
-      </x:c>
-      <x:c r="F140" s="0">
-        <x:v>1369300</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F140" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G140" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>6.45</x:v>
+        <x:v>3.46</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>4.56</x:v>
-      </x:c>
-      <x:c r="K140" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C141" s="0">
-        <x:v>76908759</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>250000000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>12000000000</x:v>
-      </x:c>
-      <x:c r="F141" s="0">
-        <x:v>1979731803</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F141" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G141" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>30.86</x:v>
+        <x:v>5.38</x:v>
       </x:c>
       <x:c r="J141" s="0">
-        <x:v>25.74</x:v>
-      </x:c>
-      <x:c r="K141" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>8291656</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>11000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>200000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F142" s="0">
-        <x:v>126004459</x:v>
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G142" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>1.9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>15.5</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="J142" s="0">
-        <x:v>15.2</x:v>
+        <x:v>50.97</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>2975773</x:v>
+        <x:v>6598092</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>6000000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>150000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>44771095</x:v>
+        <x:v>72091269</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>0.3</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>21.74</x:v>
+        <x:v>15.63</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>15.05</x:v>
+        <x:v>10.93</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>10994323</x:v>
+        <x:v>1590000</x:v>
       </x:c>
       <x:c r="D144" s="0">
-        <x:v>21600000</x:v>
+        <x:v>2160000</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="F144" s="0">
-        <x:v>183002238</x:v>
+        <x:v>60641600</x:v>
       </x:c>
       <x:c r="G144" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>5.09</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>12.34</x:v>
+        <x:v>38.3</x:v>
       </x:c>
       <x:c r="J144" s="0">
-        <x:v>16.65</x:v>
+        <x:v>38.14</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>37170641</x:v>
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>195000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F145" s="0">
-        <x:v>421071090</x:v>
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G145" s="0">
-        <x:v>10</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>1.91</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>15.17</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>11.33</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="C146" s="0">
-        <x:v>5100000</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D146" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>700000000</x:v>
-      </x:c>
-      <x:c r="F146" s="0">
-        <x:v>155318227</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F146" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>6.81</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>0.93</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>53.95</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="J146" s="0">
-        <x:v>30.45</x:v>
-      </x:c>
-      <x:c r="K146" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C147" s="0">
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D147" s="0">
-        <x:v>300000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>700000000</x:v>
-      </x:c>
-      <x:c r="F147" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>326000000</x:v>
+      </x:c>
+      <x:c r="F147" s="0">
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G147" s="0">
-        <x:v>6.67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>0</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>1.91</x:v>
+        <x:v>5.81</x:v>
       </x:c>
       <x:c r="J147" s="0">
-        <x:v>0</x:v>
+        <x:v>4.56</x:v>
+      </x:c>
+      <x:c r="K147" s="0" t="s">
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>5000000</x:v>
+        <x:v>76908759</x:v>
       </x:c>
       <x:c r="D148" s="0">
-        <x:v>5000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>50000000</x:v>
+        <x:v>12000000000</x:v>
       </x:c>
       <x:c r="F148" s="0">
-        <x:v>39090077</x:v>
+        <x:v>1979731803</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>9.61</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J148" s="0">
-        <x:v>7.82</x:v>
+        <x:v>25.74</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>905991</x:v>
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D149" s="0">
-        <x:v>21000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>500000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F149" s="0">
-        <x:v>17447317</x:v>
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G149" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>0.13</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>15.24</x:v>
+        <x:v>15.65</x:v>
       </x:c>
       <x:c r="J149" s="0">
-        <x:v>19.26</x:v>
+        <x:v>15.2</x:v>
       </x:c>
       <x:c r="K149" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="C150" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C150" s="0">
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>11700000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F150" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F150" s="0">
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>0</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>37.4</x:v>
+        <x:v>22.5</x:v>
       </x:c>
       <x:c r="J150" s="0">
-        <x:v>0</x:v>
+        <x:v>15.05</x:v>
+      </x:c>
+      <x:c r="K150" s="0" t="s">
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="C151" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="C151" s="0">
+        <x:v>11039823</x:v>
       </x:c>
       <x:c r="D151" s="0">
-        <x:v>1000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F151" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1200000000</x:v>
+      </x:c>
+      <x:c r="F151" s="0">
+        <x:v>183556428</x:v>
       </x:c>
       <x:c r="G151" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>0</x:v>
+        <x:v>5.11</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>519.5</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="J151" s="0">
-        <x:v>0</x:v>
+        <x:v>16.63</x:v>
+      </x:c>
+      <x:c r="K151" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>53584</x:v>
+        <x:v>37920641</x:v>
       </x:c>
       <x:c r="D152" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>640000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F152" s="0">
-        <x:v>8271098</x:v>
+        <x:v>432820590</x:v>
       </x:c>
       <x:c r="G152" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1.94</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>235.7</x:v>
+        <x:v>15.75</x:v>
       </x:c>
       <x:c r="J152" s="0">
-        <x:v>154.36</x:v>
+        <x:v>11.41</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>7550000</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>30000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>500000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F153" s="0">
-        <x:v>111777791</x:v>
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G153" s="0">
-        <x:v>0</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>14.21</x:v>
+        <x:v>49.52</x:v>
       </x:c>
       <x:c r="J153" s="0">
-        <x:v>14.81</x:v>
+        <x:v>30.45</x:v>
       </x:c>
       <x:c r="K153" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="C154" s="0">
-        <x:v>2097716</x:v>
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D154" s="0">
-        <x:v>10112561</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F154" s="0">
-        <x:v>28985167</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F154" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G154" s="0">
-        <x:v>10</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>1.12</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="J154" s="0">
-        <x:v>13.82</x:v>
-      </x:c>
-      <x:c r="K154" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>5185302</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="D155" s="0">
-        <x:v>57000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>513000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F155" s="0">
-        <x:v>37061183</x:v>
+        <x:v>39090077</x:v>
       </x:c>
       <x:c r="G155" s="0">
-        <x:v>5.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>5.26</x:v>
+        <x:v>9.56</x:v>
       </x:c>
       <x:c r="J155" s="0">
-        <x:v>7.15</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>669111</x:v>
+        <x:v>905991</x:v>
       </x:c>
       <x:c r="D156" s="0">
-        <x:v>1000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>260000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F156" s="0">
-        <x:v>151220429</x:v>
+        <x:v>17447317</x:v>
       </x:c>
       <x:c r="G156" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>781</x:v>
+        <x:v>15.48</x:v>
       </x:c>
       <x:c r="J156" s="0">
-        <x:v>226</x:v>
+        <x:v>19.26</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="C157" s="0">
-        <x:v>38840</x:v>
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D157" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F157" s="0">
-        <x:v>9431791</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F157" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>519.5</x:v>
+        <x:v>35.3</x:v>
       </x:c>
       <x:c r="J157" s="0">
-        <x:v>242.84</x:v>
-      </x:c>
-      <x:c r="K157" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="C158" s="0">
-        <x:v>2250000</x:v>
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D158" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F158" s="0">
-        <x:v>31750000</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F158" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G158" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>14.21</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="J158" s="0">
-        <x:v>14.11</x:v>
-      </x:c>
-      <x:c r="K158" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>296</x:v>
-      </x:c>
       <x:c r="C159" s="0">
-        <x:v>1500000</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D159" s="0">
-        <x:v>10112561</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>175000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F159" s="0">
-        <x:v>21870885</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G159" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>1.12</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="J159" s="0">
-        <x:v>14.58</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>1430040</x:v>
+        <x:v>7550000</x:v>
       </x:c>
       <x:c r="D160" s="0">
-        <x:v>8299326</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>600000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F160" s="0">
-        <x:v>198303629</x:v>
+        <x:v>111777791</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>1.51</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>127.4</x:v>
+        <x:v>12.79</x:v>
       </x:c>
       <x:c r="J160" s="0">
-        <x:v>138.67</x:v>
+        <x:v>14.81</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="C161" s="0">
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D161" s="0">
-        <x:v>2500000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F161" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>120000000</x:v>
+      </x:c>
+      <x:c r="F161" s="0">
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G161" s="0">
-        <x:v>2.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>0</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>267.75</x:v>
+        <x:v>1.09</x:v>
       </x:c>
       <x:c r="J161" s="0">
-        <x:v>0</x:v>
+        <x:v>13.82</x:v>
+      </x:c>
+      <x:c r="K161" s="0" t="s">
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>845945</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D162" s="0">
-        <x:v>15000000</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>250000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F162" s="0">
-        <x:v>10058606</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G162" s="0">
-        <x:v>0</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>3.8</x:v>
+        <x:v>4.99</x:v>
       </x:c>
       <x:c r="J162" s="0">
-        <x:v>11.89</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>21446</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D163" s="0">
         <x:v>1000000</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>200000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F163" s="0">
-        <x:v>2015907</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>41.16</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="J163" s="0">
-        <x:v>94</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>850000</x:v>
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D164" s="0">
-        <x:v>4250000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>40000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F164" s="0">
-        <x:v>6548328</x:v>
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G164" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>1</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>6.58</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="J164" s="0">
-        <x:v>7.7</x:v>
+        <x:v>242.84</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>15000000</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D165" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="E165" s="0">
         <x:v>300000000</x:v>
       </x:c>
-      <x:c r="E165" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
       <x:c r="F165" s="0">
-        <x:v>23990000</x:v>
+        <x:v>31750000</x:v>
       </x:c>
       <x:c r="G165" s="0">
-        <x:v>0</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>0.22</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>2.59</x:v>
+        <x:v>12.79</x:v>
       </x:c>
       <x:c r="J165" s="0">
-        <x:v>1.6</x:v>
+        <x:v>14.11</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>6397124</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D166" s="0">
-        <x:v>35300000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>1046645000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F166" s="0">
-        <x:v>122892213</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G166" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>3.73</x:v>
+        <x:v>1.09</x:v>
       </x:c>
       <x:c r="J166" s="0">
-        <x:v>19.21</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>17495257</x:v>
+        <x:v>1430040</x:v>
       </x:c>
       <x:c r="D167" s="0">
-        <x:v>17500000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>525000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F167" s="0">
-        <x:v>409385433</x:v>
+        <x:v>198303629</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>5</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>17.07</x:v>
+        <x:v>138.4</x:v>
       </x:c>
       <x:c r="J167" s="0">
-        <x:v>23.4</x:v>
+        <x:v>138.67</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="C168" s="0">
-        <x:v>9350000</x:v>
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D168" s="0">
-        <x:v>14710247</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F168" s="0">
-        <x:v>69547091</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F168" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G168" s="0">
-        <x:v>10</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>1.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>2.23</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="J168" s="0">
-        <x:v>7.44</x:v>
-      </x:c>
-      <x:c r="K168" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>845945</x:v>
+      </x:c>
+      <x:c r="D169" s="0">
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>100000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F169" s="0">
-        <x:v>75911475</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G169" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>0.37</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>21.9</x:v>
+        <x:v>3.42</x:v>
       </x:c>
       <x:c r="J169" s="0">
-        <x:v>51.7</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>500000</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D170" s="0">
-        <x:v>2000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>60000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F170" s="0">
-        <x:v>13401783</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>2.13</x:v>
+        <x:v>39.88</x:v>
       </x:c>
       <x:c r="J170" s="0">
-        <x:v>26.8</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>725000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="D171" s="0">
-        <x:v>10000000</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F171" s="0">
-        <x:v>48539975</x:v>
+        <x:v>6548328</x:v>
       </x:c>
       <x:c r="G171" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>0.2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>34.88</x:v>
+        <x:v>6.44</x:v>
       </x:c>
       <x:c r="J171" s="0">
-        <x:v>66.95</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>1060056</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="D172" s="0">
-        <x:v>7000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>250000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F172" s="0">
-        <x:v>60762934</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>0.44</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>214.1</x:v>
+        <x:v>2.34</x:v>
       </x:c>
       <x:c r="J172" s="0">
-        <x:v>57.32</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>132750000</x:v>
-      </x:c>
-      <x:c r="D173" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>6397124</x:v>
+      </x:c>
+      <x:c r="D173" s="0">
+        <x:v>35300000</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>1046645000</x:v>
       </x:c>
       <x:c r="F173" s="0">
-        <x:v>565141750</x:v>
+        <x:v>122892213</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>2.52</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="J173" s="0">
-        <x:v>4.26</x:v>
+        <x:v>19.21</x:v>
       </x:c>
       <x:c r="K173" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:11">
       <x:c r="A174" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>373000</x:v>
+        <x:v>17495257</x:v>
       </x:c>
       <x:c r="D174" s="0">
-        <x:v>1000000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>75000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F174" s="0">
-        <x:v>23786370</x:v>
+        <x:v>409385433</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>0.02</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>7.43</x:v>
+        <x:v>17.8</x:v>
       </x:c>
       <x:c r="J174" s="0">
-        <x:v>63.77</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="K174" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>10000000</x:v>
+        <x:v>9350000</x:v>
       </x:c>
       <x:c r="D175" s="0">
-        <x:v>10000000</x:v>
+        <x:v>14710247</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>140000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F175" s="0">
-        <x:v>133271568</x:v>
+        <x:v>69547091</x:v>
       </x:c>
       <x:c r="G175" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>0.67</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>10.8</x:v>
+        <x:v>2.01</x:v>
       </x:c>
       <x:c r="J175" s="0">
-        <x:v>13.33</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="K175" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:11">
       <x:c r="A176" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>66142950</x:v>
-      </x:c>
-      <x:c r="D176" s="0">
-        <x:v>105000000</x:v>
+        <x:v>1468255</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>650000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F176" s="0">
-        <x:v>384952260</x:v>
+        <x:v>75911475</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>2.71</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>5.94</x:v>
+        <x:v>22.36</x:v>
       </x:c>
       <x:c r="J176" s="0">
-        <x:v>5.82</x:v>
+        <x:v>51.7</x:v>
       </x:c>
       <x:c r="K176" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:11">
       <x:c r="A177" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="C177" s="0">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="D177" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E177" s="0">
+        <x:v>60000000</x:v>
+      </x:c>
+      <x:c r="F177" s="0">
+        <x:v>13401783</x:v>
+      </x:c>
+      <x:c r="G177" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H177" s="0">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="I177" s="0">
+        <x:v>2.05</x:v>
+      </x:c>
+      <x:c r="J177" s="0">
+        <x:v>26.8</x:v>
+      </x:c>
+      <x:c r="K177" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:11">
+      <x:c r="A178" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="C178" s="0">
+        <x:v>725000</x:v>
+      </x:c>
+      <x:c r="D178" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E178" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F178" s="0">
+        <x:v>48539975</x:v>
+      </x:c>
+      <x:c r="G178" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H178" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="I178" s="0">
+        <x:v>33.8</x:v>
+      </x:c>
+      <x:c r="J178" s="0">
+        <x:v>66.95</x:v>
+      </x:c>
+      <x:c r="K178" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:11">
+      <x:c r="A179" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C179" s="0">
+        <x:v>1060056</x:v>
+      </x:c>
+      <x:c r="D179" s="0">
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="E179" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F179" s="0">
+        <x:v>60762934</x:v>
+      </x:c>
+      <x:c r="G179" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H179" s="0">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I179" s="0">
+        <x:v>216.3</x:v>
+      </x:c>
+      <x:c r="J179" s="0">
+        <x:v>57.32</x:v>
+      </x:c>
+      <x:c r="K179" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:11">
+      <x:c r="A180" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="C180" s="0">
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E180" s="0">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F180" s="0">
+        <x:v>565141750</x:v>
+      </x:c>
+      <x:c r="G180" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H180" s="0">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="I180" s="0">
+        <x:v>2.42</x:v>
+      </x:c>
+      <x:c r="J180" s="0">
+        <x:v>4.26</x:v>
+      </x:c>
+      <x:c r="K180" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:11">
+      <x:c r="A181" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="C181" s="0">
+        <x:v>373000</x:v>
+      </x:c>
+      <x:c r="D181" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E181" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F181" s="0">
+        <x:v>23786370</x:v>
+      </x:c>
+      <x:c r="G181" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H181" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I181" s="0">
+        <x:v>6.69</x:v>
+      </x:c>
+      <x:c r="J181" s="0">
+        <x:v>63.77</x:v>
+      </x:c>
+      <x:c r="K181" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:11">
+      <x:c r="A182" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="B177" s="0" t="s">
+      <x:c r="C182" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="D182" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E182" s="0">
+        <x:v>140000000</x:v>
+      </x:c>
+      <x:c r="F182" s="0">
+        <x:v>133271568</x:v>
+      </x:c>
+      <x:c r="G182" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H182" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I182" s="0">
+        <x:v>11.88</x:v>
+      </x:c>
+      <x:c r="J182" s="0">
+        <x:v>13.33</x:v>
+      </x:c>
+      <x:c r="K182" s="0" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="C177" s="0">
+    </x:row>
+    <x:row r="183" spans="1:11">
+      <x:c r="A183" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C183" s="0">
+        <x:v>66142950</x:v>
+      </x:c>
+      <x:c r="D183" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="E183" s="0">
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F183" s="0">
+        <x:v>384952260</x:v>
+      </x:c>
+      <x:c r="G183" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H183" s="0">
+        <x:v>2.71</x:v>
+      </x:c>
+      <x:c r="I183" s="0">
+        <x:v>5.35</x:v>
+      </x:c>
+      <x:c r="J183" s="0">
+        <x:v>5.82</x:v>
+      </x:c>
+      <x:c r="K183" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:11">
+      <x:c r="A184" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="C184" s="0">
         <x:v>3081843</x:v>
       </x:c>
-      <x:c r="D177" s="0">
+      <x:c r="D184" s="0">
         <x:v>5000000</x:v>
       </x:c>
-      <x:c r="E177" s="0">
+      <x:c r="E184" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F177" s="0">
+      <x:c r="F184" s="0">
         <x:v>43986444</x:v>
       </x:c>
-      <x:c r="G177" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H177" s="0">
+      <x:c r="G184" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H184" s="0">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="I177" s="0">
-        <x:v>5.33</x:v>
-      </x:c>
-      <x:c r="J177" s="0">
+      <x:c r="I184" s="0">
+        <x:v>5.24</x:v>
+      </x:c>
+      <x:c r="J184" s="0">
         <x:v>14.27</x:v>
       </x:c>
-      <x:c r="K177" s="0" t="s">
-        <x:v>276</x:v>
+      <x:c r="K184" s="0" t="s">
+        <x:v>280</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,15 +49,27 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFGY</x:t>
   </x:si>
   <x:si>
     <x:t>17.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
@@ -67,6 +79,9 @@
     <x:t>LMKDC</x:t>
   </x:si>
   <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>MCARD</x:t>
   </x:si>
   <x:si>
@@ -256,9 +271,6 @@
     <x:t>29.06.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>12.08.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>MAGEN</x:t>
   </x:si>
   <x:si>
@@ -820,9 +832,6 @@
     <x:t>VAKBN</x:t>
   </x:si>
   <x:si>
-    <x:t>18.11.2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>ENDAE</x:t>
   </x:si>
   <x:si>
@@ -898,9 +907,6 @@
     <x:t>10.02.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>31.01.2025</x:t>
   </x:si>
   <x:si>
@@ -980,9 +986,6 @@
   </x:si>
   <x:si>
     <x:t>25.02.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
   </x:si>
   <x:si>
     <x:t>13.06.2024</x:t>
@@ -1381,7 +1384,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K184"/>
+  <x:dimension ref="A1:K188"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1430,22 +1433,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>60000000</x:v>
+        <x:v>4200000</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>200000000</x:v>
+        <x:v>45000000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>1.54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>2.45</x:v>
+        <x:v>8.73</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1462,11 +1465,11 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E3" s="0">
         <x:v>50000000</x:v>
       </x:c>
-      <x:c r="E3" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -1477,7 +1480,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>40.98</x:v>
+        <x:v>6.23</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>0</x:v>
@@ -1494,10 +1497,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>180000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>13</x:v>
@@ -1509,7 +1512,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>12.66</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1520,83 +1523,89 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>25000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F5" s="0">
+        <x:v>1960500</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.84</x:v>
+        <x:v>1.54</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>22.24</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="J5" s="0">
-        <x:v>0</x:v>
+        <x:v>2.45</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C6" s="0">
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>9260000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>1200000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>124</x:v>
+        <x:v>41.76</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>0</x:v>
+        <x:v>38.75</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2500000</x:v>
+        <x:v>180000000</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>225000000</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F7" s="0">
+        <x:v>3495000</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>0</x:v>
@@ -1605,39 +1614,42 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>74.6</x:v>
+        <x:v>12.85</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>0</x:v>
+        <x:v>11.65</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>39725600</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0</x:v>
+        <x:v>4.84</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>37.72</x:v>
+        <x:v>22.3</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>0</x:v>
@@ -1648,121 +1660,112 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>100000</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>12000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>1750000000</x:v>
-      </x:c>
-      <x:c r="F9" s="0">
-        <x:v>17346100</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>176.9</x:v>
+        <x:v>2.19</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>173.46</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>50000</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1000000</x:v>
+        <x:v>9260000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F10" s="0">
-        <x:v>14714923</x:v>
+        <x:v>1200000000</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>276</x:v>
+        <x:v>111.6</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>294.3</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>240110</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>2850000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F11" s="0">
-        <x:v>7160296</x:v>
+        <x:v>225000000</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.41</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>30.74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>29.82</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>20000000</x:v>
+        <x:v>39725600</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>13</x:v>
@@ -1774,7 +1777,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>52.8</x:v>
+        <x:v>34.98</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>0</x:v>
@@ -1782,617 +1785,617 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>267427</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>10000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1750000000</x:v>
+      </x:c>
+      <x:c r="F13" s="0">
+        <x:v>46136512</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>6.95</x:v>
+        <x:v>159.3</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>0</x:v>
+        <x:v>172.52</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>12450000</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>96033600</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>650000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>60880500</x:v>
+        <x:v>14714923</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>1.97</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>4.89</x:v>
+        <x:v>294.3</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>295110</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>36000000</x:v>
+        <x:v>2850000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F15" s="0">
+        <x:v>8818271</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>3.75</x:v>
+        <x:v>2.41</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>0</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>5.91</x:v>
+        <x:v>29.76</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>0</x:v>
+        <x:v>29.88</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>742639</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>15000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F16" s="0">
-        <x:v>6383247</x:v>
+        <x:v>2500000000</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>8.15</x:v>
+        <x:v>52.45</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>8.6</x:v>
-      </x:c>
-      <x:c r="K16" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>700000</x:v>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>13500000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F17" s="0">
-        <x:v>15837000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>18.13</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>22.62</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>20746859</x:v>
+        <x:v>12450000</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>30000000</x:v>
+        <x:v>96033600</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>210000000</x:v>
+        <x:v>650000000</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>145013995</x:v>
+        <x:v>60880500</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>3.7</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>6.1</x:v>
+        <x:v>1.78</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>6.99</x:v>
+        <x:v>4.89</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>11397816</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>15000000</x:v>
+        <x:v>36000000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F19" s="0">
-        <x:v>269900283</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.94</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>15.9</x:v>
+        <x:v>5.74</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>23.68</x:v>
-      </x:c>
-      <x:c r="K19" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="C20" s="0">
-        <x:v>1000000</x:v>
+        <x:v>842639</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>50000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>500000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>8385000</x:v>
+        <x:v>7199247</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>2.05</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.17</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>5.35</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>8.39</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>2300000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>12000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>12000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1739216</x:v>
+        <x:v>24902000</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>3.83</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>13.9</x:v>
+        <x:v>16.32</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>0.76</x:v>
+        <x:v>20.75</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>4790000</x:v>
+        <x:v>20746859</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>12000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>12000000</x:v>
+        <x:v>210000000</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>7029498</x:v>
+        <x:v>145013995</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>7.98</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>4.27</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>1.47</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>4850000</x:v>
+        <x:v>11397816</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>12000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>12000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>3543837</x:v>
+        <x:v>269900283</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>8.08</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>10.37</x:v>
+        <x:v>14.31</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>0.73</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>61493</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>2000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>250000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>3995647</x:v>
+        <x:v>8385000</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>63.4</x:v>
+        <x:v>4.82</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>64.98</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>20000000</x:v>
+        <x:v>2300000</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>500000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>750000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>26500000</x:v>
+        <x:v>1739216</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>0.1</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>1.11</x:v>
+        <x:v>12.51</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>1.33</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>4790000</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>150000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>33000000</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="F26" s="0">
+        <x:v>7029498</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>1.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>106</x:v>
+        <x:v>4.09</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>0</x:v>
+        <x:v>1.47</x:v>
+      </x:c>
+      <x:c r="K26" s="0" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>100000</x:v>
+        <x:v>4850000</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>50000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>500000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>613000</x:v>
+        <x:v>3543837</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>5.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>0.01</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>5.03</x:v>
+        <x:v>9.34</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>6.13</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>10366031</x:v>
+        <x:v>61493</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>25000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>240000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>102614742</x:v>
+        <x:v>3995647</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>9.56</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>9.9</x:v>
+        <x:v>64.98</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>1800452</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>15000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>150000000</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>17447883</x:v>
+        <x:v>26500000</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>8.15</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>9.69</x:v>
+        <x:v>1.33</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>13409218</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>500000000</x:v>
+        <x:v>33000000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>9.01</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="H30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>17.06</x:v>
+        <x:v>99.3</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>0</x:v>
@@ -2400,643 +2403,643 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>6550000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>55000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>9962550</x:v>
+        <x:v>613000</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>5.09</x:v>
+        <x:v>5.26</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>0.61</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>1.5</x:v>
+        <x:v>4.61</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>1.52</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>200000</x:v>
+        <x:v>10366031</x:v>
       </x:c>
       <x:c r="D32" s="0">
         <x:v>25000000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>415500000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>3174011</x:v>
+        <x:v>102614742</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>15.63</x:v>
+        <x:v>9.27</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>15.87</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>6067182</x:v>
+        <x:v>1800452</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>40000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>114062870</x:v>
+        <x:v>17447883</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>16.99</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J33" s="0">
-        <x:v>18.8</x:v>
+        <x:v>9.69</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>15160028</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>60000000</x:v>
+        <x:v>13409218</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F34" s="0">
-        <x:v>54496310</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>3.82</x:v>
+        <x:v>16.36</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>3.59</x:v>
-      </x:c>
-      <x:c r="K34" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>2500000</x:v>
+        <x:v>6550000</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>2500000</x:v>
+        <x:v>55000000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>950421206</x:v>
+        <x:v>9962550</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.61</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>418</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>380.17</x:v>
+        <x:v>1.52</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>199722</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>230000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>15000000</x:v>
+        <x:v>415500000</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>13877494</x:v>
+        <x:v>3174011</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.66</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>1.44</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>66.45</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>69.48</x:v>
+        <x:v>15.87</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>2501710</x:v>
+        <x:v>6067182</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>10000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>450000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>97116052</x:v>
+        <x:v>114062870</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>29.5</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>38.82</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>57675584</x:v>
+        <x:v>15160028</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>85125000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>5000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>2781852532</x:v>
+        <x:v>54496310</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>1.8</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>49.56</x:v>
+        <x:v>3.59</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>48.23</x:v>
+        <x:v>3.59</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>57026857</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>25000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>1946074001</x:v>
+        <x:v>950421206</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>1.93</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>30.26</x:v>
+        <x:v>419.75</x:v>
       </x:c>
       <x:c r="J39" s="0">
-        <x:v>34.13</x:v>
+        <x:v>380.17</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>324474</x:v>
+        <x:v>200821</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>3000000</x:v>
+        <x:v>230000</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>40000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>1781383</x:v>
+        <x:v>13949918</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>0.08</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>13.6</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J40" s="0">
-        <x:v>5.49</x:v>
+        <x:v>69.46</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>7999148</x:v>
+        <x:v>2501710</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>15000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>300000000</x:v>
+        <x:v>450000000</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>168715651</x:v>
+        <x:v>97116052</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>2.11</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>18.15</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>21.09</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>201000</x:v>
+        <x:v>58811536</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>21739600</x:v>
+        <x:v>85125000</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>350000000</x:v>
+        <x:v>5000000000</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>2071755</x:v>
+        <x:v>2837309709</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>0.02</x:v>
+        <x:v>1.84</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>9.03</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>10.31</x:v>
+        <x:v>48.24</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>62686718</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1500000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F43" s="0">
+        <x:v>2118794265</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>0</x:v>
+        <x:v>2.12</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>8.54</x:v>
+        <x:v>27.24</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>0</x:v>
+        <x:v>33.8</x:v>
+      </x:c>
+      <x:c r="K43" s="0" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>1900000</x:v>
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>10000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>14177000</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>0.35</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>7.12</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>7.46</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>26398084</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F45" s="0">
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>0</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>176.9</x:v>
+        <x:v>17.25</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>0</x:v>
+        <x:v>21.09</x:v>
+      </x:c>
+      <x:c r="K45" s="0" t="s">
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>201000</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>21739600</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>127481195</x:v>
+        <x:v>2071755</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>18.19</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>7.13</x:v>
+        <x:v>10.31</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C47" s="0">
-        <x:v>970810</x:v>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>7300000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>225000000</x:v>
-      </x:c>
-      <x:c r="F47" s="0">
-        <x:v>28043898</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>21.5</x:v>
+        <x:v>8.72</x:v>
       </x:c>
       <x:c r="J47" s="0">
-        <x:v>28.89</x:v>
-      </x:c>
-      <x:c r="K47" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>1001579</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="D48" s="0">
         <x:v>10000000</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>100000000</x:v>
+        <x:v>65000000</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>15106723</x:v>
+        <x:v>14177000</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>2.56</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>8.33</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="J48" s="0">
-        <x:v>15.08</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>40000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
         <x:v>13</x:v>
@@ -3048,7 +3051,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>4.14</x:v>
+        <x:v>159.3</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>0</x:v>
@@ -3056,897 +3059,897 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>2097370</x:v>
-      </x:c>
-      <x:c r="D50" s="0">
-        <x:v>2000000</x:v>
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>40000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>48772185</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>2.78</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>17.85</x:v>
+        <x:v>19.4</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>23.25</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>29346813</x:v>
+        <x:v>970810</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>80000000</x:v>
+        <x:v>7300000</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>225000000</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>826937156</x:v>
+        <x:v>28043898</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>1.13</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>40.98</x:v>
+        <x:v>21.48</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>28.18</x:v>
+        <x:v>28.89</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>7024156</x:v>
+        <x:v>1001579</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>80000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>93719334</x:v>
+        <x:v>15106723</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>0</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>10.73</x:v>
+        <x:v>8.14</x:v>
       </x:c>
       <x:c r="J52" s="0">
-        <x:v>13.34</x:v>
+        <x:v>15.08</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>3500000</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>49400000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F53" s="0">
-        <x:v>137144284</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>28.1</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="J53" s="0">
-        <x:v>39.18</x:v>
-      </x:c>
-      <x:c r="K53" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>3753472</x:v>
+        <x:v>2097370</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>6000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>432000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>224929072</x:v>
+        <x:v>48772185</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>0.82</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>58.7</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>59.93</x:v>
+        <x:v>23.25</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>3189049</x:v>
+        <x:v>29346813</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>4000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>400000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>154328962</x:v>
+        <x:v>826937156</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>3.74</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>0.6</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>4.75</x:v>
+        <x:v>41.76</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>48.39</x:v>
+        <x:v>28.18</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>35000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F56" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F56" s="0">
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G56" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>0</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>3.11</x:v>
+        <x:v>10.21</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>0</x:v>
+        <x:v>13.34</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>5350000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>10000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>400000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F57" s="0">
-        <x:v>196494213</x:v>
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G57" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>17.55</x:v>
+        <x:v>25.3</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>36.73</x:v>
+        <x:v>39.18</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>20226071</x:v>
+        <x:v>3753472</x:v>
       </x:c>
       <x:c r="D58" s="0">
-        <x:v>35000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>300000000</x:v>
+        <x:v>432000000</x:v>
       </x:c>
       <x:c r="F58" s="0">
-        <x:v>177200428</x:v>
+        <x:v>224929072</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>5.06</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>7.47</x:v>
+        <x:v>56.35</x:v>
       </x:c>
       <x:c r="J58" s="0">
-        <x:v>8.76</x:v>
+        <x:v>59.93</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>236122</x:v>
+        <x:v>3189049</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>1700000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>110000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F59" s="0">
-        <x:v>14609667</x:v>
+        <x:v>154328962</x:v>
       </x:c>
       <x:c r="G59" s="0">
-        <x:v>0</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>55.55</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="J59" s="0">
-        <x:v>61.87</x:v>
+        <x:v>48.39</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C60" s="0">
-        <x:v>1000000</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F60" s="0">
-        <x:v>21055375</x:v>
+        <x:v>35000000</x:v>
+      </x:c>
+      <x:c r="E60" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G60" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>17.8</x:v>
+        <x:v>2.91</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>21.06</x:v>
-      </x:c>
-      <x:c r="K60" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>5350000</x:v>
       </x:c>
       <x:c r="D61" s="0">
-        <x:v>2000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F61" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>400000000</x:v>
+      </x:c>
+      <x:c r="F61" s="0">
+        <x:v>196494213</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>0</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>4.75</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="J61" s="0">
-        <x:v>0</x:v>
+        <x:v>36.73</x:v>
+      </x:c>
+      <x:c r="K61" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>105404634</x:v>
+        <x:v>21416071</x:v>
       </x:c>
       <x:c r="D62" s="0">
-        <x:v>200000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F62" s="0">
-        <x:v>1032884452</x:v>
+        <x:v>186756128</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>1.17</x:v>
+        <x:v>5.35</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>12.66</x:v>
+        <x:v>6.73</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>9.8</x:v>
+        <x:v>8.72</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>16445115</x:v>
+        <x:v>236122</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>25000000</x:v>
+        <x:v>1700000</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>500000000</x:v>
+        <x:v>110000000</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>393919718</x:v>
+        <x:v>14609667</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>3.29</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>37.34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>23.95</x:v>
+        <x:v>61.87</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>1110000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E64" s="0">
-        <x:v>1100000000</x:v>
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F64" s="0">
-        <x:v>587039028</x:v>
+        <x:v>21055375</x:v>
       </x:c>
       <x:c r="G64" s="0">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>418</x:v>
+        <x:v>17.49</x:v>
       </x:c>
       <x:c r="J64" s="0">
-        <x:v>528.86</x:v>
+        <x:v>21.06</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C65" s="0">
-        <x:v>24398659</x:v>
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D65" s="0">
-        <x:v>40000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>850000000</x:v>
-      </x:c>
-      <x:c r="F65" s="0">
-        <x:v>590270273</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>40.98</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>24.19</x:v>
-      </x:c>
-      <x:c r="K65" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>46563878</x:v>
+        <x:v>105404634</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>50000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F66" s="0">
-        <x:v>500007798</x:v>
+        <x:v>1032884452</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>0.52</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>12.66</x:v>
+        <x:v>12.85</x:v>
       </x:c>
       <x:c r="J66" s="0">
-        <x:v>10.74</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>6611571</x:v>
+        <x:v>16445115</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>9000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>240000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>39750803</x:v>
+        <x:v>393919718</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>0.69</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>5.91</x:v>
+        <x:v>33.62</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>6.01</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>2596120</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E68" s="0">
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F68" s="0">
-        <x:v>66065196</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>1.36</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>15.97</x:v>
+        <x:v>419.75</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>25.45</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>1000000</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>30000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>400000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>4455000</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>4.02</x:v>
+        <x:v>41.76</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>4.46</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>200000</x:v>
+        <x:v>46563878</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>13760000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>300000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F70" s="0">
-        <x:v>2564000</x:v>
+        <x:v>500007798</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>6.1</x:v>
+        <x:v>12.85</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>12.82</x:v>
+        <x:v>10.74</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C71" s="0">
+        <x:v>6611571</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>30000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F71" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F71" s="0">
+        <x:v>39750803</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>24.42</x:v>
+        <x:v>5.74</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>0</x:v>
+        <x:v>6.01</x:v>
+      </x:c>
+      <x:c r="K71" s="0" t="s">
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>5831653</x:v>
+        <x:v>2596120</x:v>
       </x:c>
       <x:c r="D72" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E72" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F72" s="0">
-        <x:v>304086107</x:v>
+        <x:v>66065196</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>0.83</x:v>
+        <x:v>1.36</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>2.37</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="J72" s="0">
-        <x:v>52.14</x:v>
+        <x:v>25.45</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>14512000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D73" s="0">
-        <x:v>79451200</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F73" s="0">
-        <x:v>575005862</x:v>
+        <x:v>4455000</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>1.83</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>37.72</x:v>
+        <x:v>3.88</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>39.62</x:v>
+        <x:v>4.46</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>5139828</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>3000000</x:v>
+        <x:v>13760000</x:v>
       </x:c>
       <x:c r="E74" s="0">
         <x:v>300000000</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>207321844</x:v>
+        <x:v>2564000</x:v>
       </x:c>
       <x:c r="G74" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>1.28</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>22.36</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>40.34</x:v>
+        <x:v>12.82</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D75" s="0">
-        <x:v>15000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>600000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G75" s="0">
-        <x:v>5.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>21.74</x:v>
+        <x:v>23.88</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>0</x:v>
@@ -3954,133 +3957,136 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>8337681</x:v>
+        <x:v>5831653</x:v>
       </x:c>
       <x:c r="D76" s="0">
-        <x:v>6500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F76" s="0">
-        <x:v>37235183</x:v>
+        <x:v>304086107</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>1.43</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>3.42</x:v>
+        <x:v>2.28</x:v>
       </x:c>
       <x:c r="J76" s="0">
-        <x:v>4.47</x:v>
+        <x:v>52.14</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C77" s="0">
+        <x:v>14512000</x:v>
+      </x:c>
+      <x:c r="D77" s="0">
+        <x:v>79451200</x:v>
+      </x:c>
+      <x:c r="E77" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F77" s="0">
+        <x:v>575005862</x:v>
+      </x:c>
+      <x:c r="G77" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H77" s="0">
+        <x:v>1.83</x:v>
+      </x:c>
+      <x:c r="I77" s="0">
+        <x:v>34.98</x:v>
+      </x:c>
+      <x:c r="J77" s="0">
+        <x:v>39.62</x:v>
+      </x:c>
+      <x:c r="K77" s="0" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D77" s="0">
-        <x:v>9275000</x:v>
-      </x:c>
-      <x:c r="E77" s="0">
-        <x:v>950000000</x:v>
-      </x:c>
-      <x:c r="F77" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G77" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H77" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I77" s="0">
-        <x:v>33.8</x:v>
-      </x:c>
-      <x:c r="J77" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>1364000</x:v>
+        <x:v>5139828</x:v>
       </x:c>
       <x:c r="D78" s="0">
-        <x:v>23460000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>9000000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F78" s="0">
-        <x:v>409075556</x:v>
+        <x:v>207321844</x:v>
       </x:c>
       <x:c r="G78" s="0">
-        <x:v>1.7</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.28</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>289.25</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="J78" s="0">
-        <x:v>299.91</x:v>
+        <x:v>40.34</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D79" s="0">
-        <x:v>380000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G79" s="0">
-        <x:v>10</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H79" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>19.24</x:v>
+        <x:v>21.42</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>0</x:v>
@@ -4088,500 +4094,500 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>507440</x:v>
+        <x:v>8337681</x:v>
       </x:c>
       <x:c r="D80" s="0">
-        <x:v>2500000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E80" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>42117724</x:v>
+        <x:v>37235183</x:v>
       </x:c>
       <x:c r="G80" s="0">
-        <x:v>2.67</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>265</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="J80" s="0">
-        <x:v>83</x:v>
+        <x:v>4.47</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>2000000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>2000000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>100000000</x:v>
+        <x:v>950000000</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>81947000</x:v>
+        <x:v>3266000</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>2</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>32.78</x:v>
+        <x:v>33.56</x:v>
       </x:c>
       <x:c r="J81" s="0">
-        <x:v>40.97</x:v>
+        <x:v>32.66</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>9854768</x:v>
+        <x:v>1364000</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>10000000</x:v>
+        <x:v>23460000</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>250000000</x:v>
+        <x:v>9000000000</x:v>
       </x:c>
       <x:c r="F82" s="0">
-        <x:v>233360906</x:v>
+        <x:v>409075556</x:v>
       </x:c>
       <x:c r="G82" s="0">
-        <x:v>0.63</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>0.62</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>15.9</x:v>
+        <x:v>285.5</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>23.68</x:v>
+        <x:v>299.91</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C83" s="0">
-        <x:v>324474</x:v>
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D83" s="0">
-        <x:v>5000000</x:v>
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F83" s="0">
-        <x:v>1781383</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G83" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>13.6</x:v>
+        <x:v>19.01</x:v>
       </x:c>
       <x:c r="J83" s="0">
-        <x:v>5.49</x:v>
-      </x:c>
-      <x:c r="K83" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E84" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F84" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C84" s="0">
+        <x:v>507440</x:v>
+      </x:c>
+      <x:c r="D84" s="0">
+        <x:v>2500000</x:v>
+      </x:c>
+      <x:c r="E84" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F84" s="0">
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>0</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>0</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>15.63</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K84" s="0" t="s">
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="B85" s="0" t="s">
+      <x:c r="C85" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D85" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E85" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F85" s="0">
+        <x:v>81947000</x:v>
+      </x:c>
+      <x:c r="G85" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H85" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I85" s="0">
+        <x:v>30.7</x:v>
+      </x:c>
+      <x:c r="J85" s="0">
+        <x:v>40.97</x:v>
+      </x:c>
+      <x:c r="K85" s="0" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D85" s="0">
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="E85" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="F85" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G85" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="H85" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I85" s="0">
-        <x:v>4.73</x:v>
-      </x:c>
-      <x:c r="J85" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>9854768</x:v>
+      </x:c>
+      <x:c r="D86" s="0">
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>100000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F86" s="0">
-        <x:v>85838440</x:v>
+        <x:v>233360906</x:v>
       </x:c>
       <x:c r="G86" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>1</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>6.83</x:v>
+        <x:v>14.31</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>6.6</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>174500000</x:v>
-      </x:c>
-      <x:c r="D87" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>324474</x:v>
+      </x:c>
+      <x:c r="D87" s="0">
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F87" s="0">
-        <x:v>694527000</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>2.42</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="J87" s="0">
-        <x:v>3.98</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="C88" s="0">
-        <x:v>635229</x:v>
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E88" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F88" s="0">
-        <x:v>11323561</x:v>
+      <x:c r="E88" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>15.97</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>17.83</x:v>
-      </x:c>
-      <x:c r="K88" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="C89" s="0">
-        <x:v>130000</x:v>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D89" s="0">
-        <x:v>3500000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F89" s="0">
-        <x:v>4947800</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>28.14</x:v>
+        <x:v>4.39</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>38.06</x:v>
-      </x:c>
-      <x:c r="K89" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D90" s="0">
-        <x:v>5000000</x:v>
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C90" s="0">
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F90" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F90" s="0">
+        <x:v>85838440</x:v>
       </x:c>
       <x:c r="G90" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>216.3</x:v>
+        <x:v>7.01</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>0</x:v>
+        <x:v>6.6</x:v>
+      </x:c>
+      <x:c r="K90" s="0" t="s">
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>447761</x:v>
-      </x:c>
-      <x:c r="D91" s="0">
-        <x:v>3000000</x:v>
+        <x:v>174500000</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>120000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F91" s="0">
-        <x:v>18415143</x:v>
+        <x:v>694527000</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>30.06</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>41.13</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="D92" s="0">
-        <x:v>2000000</x:v>
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E92" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>4022593</x:v>
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>1.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.75</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>20.11</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>946718</x:v>
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>20000000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>37333519</x:v>
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>7.55</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>36.1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>39.43</x:v>
+        <x:v>38.06</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D94" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="D94" s="0">
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>100000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
         <x:v>13</x:v>
@@ -4593,7 +4599,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>15.71</x:v>
+        <x:v>221.4</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>0</x:v>
@@ -4601,174 +4607,174 @@
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>3043115</x:v>
+        <x:v>447761</x:v>
       </x:c>
       <x:c r="D95" s="0">
-        <x:v>50000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F95" s="0">
-        <x:v>49736990</x:v>
+        <x:v>18415143</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>20.86</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>16.34</x:v>
+        <x:v>41.13</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>2382736</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D96" s="0">
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F96" s="0">
-        <x:v>92635231</x:v>
+        <x:v>4022593</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>0</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>56.45</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J96" s="0">
-        <x:v>38.88</x:v>
+        <x:v>20.11</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C97" s="0">
+        <x:v>946718</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>4191000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>160000000</x:v>
-      </x:c>
-      <x:c r="F97" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F97" s="0">
+        <x:v>37333519</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>0</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>0</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>48.1</x:v>
+        <x:v>34.6</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>0</x:v>
+        <x:v>39.43</x:v>
+      </x:c>
+      <x:c r="K97" s="0" t="s">
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="C98" s="0">
-        <x:v>4650000</x:v>
-      </x:c>
-      <x:c r="D98" s="0">
-        <x:v>75000000</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F98" s="0">
-        <x:v>49978950</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>9</x:v>
+        <x:v>14.43</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>10.75</x:v>
-      </x:c>
-      <x:c r="K98" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>806343</x:v>
+        <x:v>3043115</x:v>
       </x:c>
       <x:c r="D99" s="0">
-        <x:v>1862500</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>75000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F99" s="0">
-        <x:v>30363861</x:v>
+        <x:v>49736990</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>31.9</x:v>
+        <x:v>20.2</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>37.66</x:v>
+        <x:v>16.34</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
@@ -4776,31 +4782,31 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>310000</x:v>
-      </x:c>
-      <x:c r="D100" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F100" s="0">
-        <x:v>49980500</x:v>
+        <x:v>92635231</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>9</x:v>
+        <x:v>50.85</x:v>
       </x:c>
       <x:c r="J100" s="0">
-        <x:v>161.23</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
         <x:v>207</x:v>
@@ -4808,462 +4814,459 @@
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="C101" s="0">
-        <x:v>2000000</x:v>
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>5000000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F101" s="0">
-        <x:v>31366572</x:v>
+        <x:v>160000000</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>8.15</x:v>
+        <x:v>46.5</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>15.68</x:v>
-      </x:c>
-      <x:c r="K101" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>209</x:v>
-      </x:c>
       <x:c r="C102" s="0">
-        <x:v>1250000</x:v>
+        <x:v>4650000</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>25000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F102" s="0">
-        <x:v>11187500</x:v>
+        <x:v>49978950</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>2.08</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>1.74</x:v>
+        <x:v>8.16</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>8.95</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C103" s="0">
+        <x:v>806343</x:v>
       </x:c>
       <x:c r="D103" s="0">
-        <x:v>6950000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F103" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F103" s="0">
+        <x:v>30363861</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>0</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>2.88</x:v>
+        <x:v>28.94</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>0</x:v>
+        <x:v>37.66</x:v>
+      </x:c>
+      <x:c r="K103" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>213</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>12500000</x:v>
+        <x:v>310000</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>12500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>60000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>61582393</x:v>
+        <x:v>49980500</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>1.95</x:v>
+        <x:v>8.16</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>4.93</x:v>
+        <x:v>161.23</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>213</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>2093944</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>220000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>8500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F105" s="0">
-        <x:v>200139168</x:v>
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>99.15</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>95.58</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C106" s="0">
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D106" s="0">
-        <x:v>150000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F106" s="0">
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>0</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>47.8</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>0</x:v>
+        <x:v>8.95</x:v>
+      </x:c>
+      <x:c r="K106" s="0" t="s">
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="C107" s="0">
-        <x:v>51245979</x:v>
+      <x:c r="C107" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>85000000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F107" s="0">
-        <x:v>125342407</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F107" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>2.18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>1.31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>2.45</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>2.45</x:v>
-      </x:c>
-      <x:c r="K107" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>1584837</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D108" s="0">
-        <x:v>2500000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>100000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F108" s="0">
-        <x:v>92450176</x:v>
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>1.08</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>63.4</x:v>
+        <x:v>1.82</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>58.33</x:v>
+        <x:v>4.93</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>7999148</x:v>
+        <x:v>2093944</x:v>
       </x:c>
       <x:c r="D109" s="0">
-        <x:v>11000000</x:v>
+        <x:v>220000000</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>200000000</x:v>
+        <x:v>8500000000</x:v>
       </x:c>
       <x:c r="F109" s="0">
-        <x:v>168715651</x:v>
+        <x:v>200139168</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>2.11</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>18.15</x:v>
+        <x:v>97.2</x:v>
       </x:c>
       <x:c r="J109" s="0">
-        <x:v>21.09</x:v>
+        <x:v>95.58</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="C110" s="0">
-        <x:v>14000000</x:v>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>10000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F110" s="0">
-        <x:v>236130680</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F110" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>21.6</x:v>
+        <x:v>46.52</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>16.87</x:v>
-      </x:c>
-      <x:c r="K110" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>1700005</x:v>
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>95000000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>1425000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>20390731</x:v>
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>10</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>5.03</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>11.99</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C112" s="0">
+        <x:v>1584837</x:v>
+      </x:c>
+      <x:c r="D112" s="0">
+        <x:v>2500000</x:v>
+      </x:c>
+      <x:c r="E112" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F112" s="0">
+        <x:v>92450176</x:v>
+      </x:c>
+      <x:c r="G112" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H112" s="0">
+        <x:v>1.08</x:v>
+      </x:c>
+      <x:c r="I112" s="0">
+        <x:v>60.9</x:v>
+      </x:c>
+      <x:c r="J112" s="0">
+        <x:v>58.33</x:v>
+      </x:c>
+      <x:c r="K112" s="0" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="C112" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="D112" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="E112" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F112" s="0">
-        <x:v>132286928</x:v>
-      </x:c>
-      <x:c r="G112" s="0">
-        <x:v>0.94</x:v>
-      </x:c>
-      <x:c r="H112" s="0">
-        <x:v>0.16</x:v>
-      </x:c>
-      <x:c r="I112" s="0">
-        <x:v>13.95</x:v>
-      </x:c>
-      <x:c r="J112" s="0">
-        <x:v>22.05</x:v>
-      </x:c>
-      <x:c r="K112" s="0" t="s">
-        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>1675000</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>9000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>500000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F113" s="0">
-        <x:v>114158717</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>7.81</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>1.45</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>89.5</x:v>
+        <x:v>17.25</x:v>
       </x:c>
       <x:c r="J113" s="0">
-        <x:v>68.15</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>1824868</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D114" s="0">
         <x:v>10000000</x:v>
@@ -5272,202 +5275,202 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F114" s="0">
-        <x:v>64572720</x:v>
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>3.73</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>0.68</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>23.4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>35.38</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C115" s="0">
+        <x:v>1700005</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>50000000</x:v>
+        <x:v>95000000</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F115" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1425000000</x:v>
+      </x:c>
+      <x:c r="F115" s="0">
+        <x:v>20390731</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>0</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>6.15</x:v>
+        <x:v>4.61</x:v>
       </x:c>
       <x:c r="J115" s="0">
-        <x:v>0</x:v>
+        <x:v>11.99</x:v>
+      </x:c>
+      <x:c r="K115" s="0" t="s">
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>30000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F116" s="0">
-        <x:v>19787700</x:v>
+        <x:v>132286928</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>6.93</x:v>
+        <x:v>15.34</x:v>
       </x:c>
       <x:c r="J116" s="0">
-        <x:v>19.79</x:v>
+        <x:v>22.05</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>98551</x:v>
+        <x:v>1675000</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>6500000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F117" s="0">
-        <x:v>1295684</x:v>
+        <x:v>114158717</x:v>
       </x:c>
       <x:c r="G117" s="0">
-        <x:v>0</x:v>
+        <x:v>7.81</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0.06</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>10.54</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>13.15</x:v>
+        <x:v>68.15</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>6049315</x:v>
+        <x:v>1824868</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>15000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F118" s="0">
-        <x:v>66439559</x:v>
+        <x:v>64572720</x:v>
       </x:c>
       <x:c r="G118" s="0">
-        <x:v>0</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>10.31</x:v>
+        <x:v>21.06</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>10.98</x:v>
+        <x:v>35.38</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="C119" s="0">
-        <x:v>37225000</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>12000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F119" s="0">
-        <x:v>149982056</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F119" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G119" s="0">
-        <x:v>8.99</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>3.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>1.5</x:v>
+        <x:v>6.38</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>4.03</x:v>
-      </x:c>
-      <x:c r="K119" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C120" s="0">
         <x:v>1000000</x:v>
@@ -5476,442 +5479,442 @@
         <x:v>1000000</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>350000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F120" s="0">
-        <x:v>284578907</x:v>
+        <x:v>19787700</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>178.5</x:v>
+        <x:v>6.66</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>284.58</x:v>
+        <x:v>19.79</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>600000</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>600000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>25000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>22814140</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>4.77</x:v>
+        <x:v>11.59</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>38.02</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>11703083</x:v>
+        <x:v>6049315</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>16000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>720000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>978644023</x:v>
+        <x:v>66439559</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>10.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>181.5</x:v>
+        <x:v>10.06</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>83.62</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>5100000</x:v>
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>9000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>200000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F123" s="0">
-        <x:v>90022686</x:v>
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>7.6</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>4.31</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>30.74</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>17.65</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>3228679</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>175000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>51395842</x:v>
+        <x:v>284578907</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>6.95</x:v>
+        <x:v>160.7</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>15.92</x:v>
+        <x:v>284.58</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C125" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="D125" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="E125" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="F125" s="0">
+        <x:v>22814140</x:v>
+      </x:c>
+      <x:c r="G125" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H125" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="I125" s="0">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="J125" s="0">
+        <x:v>38.02</x:v>
+      </x:c>
+      <x:c r="K125" s="0" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="C125" s="0">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="D125" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="E125" s="0">
-        <x:v>240000000</x:v>
-      </x:c>
-      <x:c r="F125" s="0">
-        <x:v>6145450</x:v>
-      </x:c>
-      <x:c r="G125" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H125" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="I125" s="0">
-        <x:v>4.71</x:v>
-      </x:c>
-      <x:c r="J125" s="0">
-        <x:v>40.97</x:v>
-      </x:c>
-      <x:c r="K125" s="0" t="s">
-        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C126" s="0">
+        <x:v>11703083</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>1000000</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F126" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>720000000</x:v>
+      </x:c>
+      <x:c r="F126" s="0">
+        <x:v>978644023</x:v>
       </x:c>
       <x:c r="G126" s="0">
-        <x:v>0</x:v>
+        <x:v>10.16</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>0</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>10.25</x:v>
+        <x:v>163.4</x:v>
       </x:c>
       <x:c r="J126" s="0">
-        <x:v>0</x:v>
+        <x:v>83.62</x:v>
+      </x:c>
+      <x:c r="K126" s="0" t="s">
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>366107</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>1200000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>30000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F127" s="0">
-        <x:v>6010300</x:v>
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>0</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0.33</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>13.31</x:v>
+        <x:v>29.76</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>16.42</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>120000</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>26398084</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>100000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F128" s="0">
-        <x:v>3830160</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>176.9</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>31.92</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="C129" s="0">
+        <x:v>150000</x:v>
+      </x:c>
+      <x:c r="D129" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E129" s="0">
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F129" s="0">
+        <x:v>6145450</x:v>
+      </x:c>
+      <x:c r="G129" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H129" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I129" s="0">
+        <x:v>4.46</x:v>
+      </x:c>
+      <x:c r="J129" s="0">
+        <x:v>40.97</x:v>
+      </x:c>
+      <x:c r="K129" s="0" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C129" s="0">
-        <x:v>13050000</x:v>
-      </x:c>
-      <x:c r="D129" s="0">
-        <x:v>13050000</x:v>
-      </x:c>
-      <x:c r="E129" s="0">
-        <x:v>1305000000</x:v>
-      </x:c>
-      <x:c r="F129" s="0">
-        <x:v>1231340857</x:v>
-      </x:c>
-      <x:c r="G129" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H129" s="0">
-        <x:v>3.13</x:v>
-      </x:c>
-      <x:c r="I129" s="0">
-        <x:v>109.5</x:v>
-      </x:c>
-      <x:c r="J129" s="0">
-        <x:v>94.36</x:v>
-      </x:c>
-      <x:c r="K129" s="0" t="s">
-        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C130" s="0">
-        <x:v>36605658</x:v>
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F130" s="0">
-        <x:v>174340918</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F130" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>3.66</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>4.32</x:v>
+        <x:v>9.59</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>4.76</x:v>
-      </x:c>
-      <x:c r="K130" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>1000000</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>4000000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F131" s="0">
-        <x:v>429817200</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>418</x:v>
+        <x:v>12.64</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>429.82</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
       <x:c r="C132" s="0">
-        <x:v>300000</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D132" s="0">
-        <x:v>60000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>171000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F132" s="0">
-        <x:v>791000</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="0">
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>2.42</x:v>
+        <x:v>159.3</x:v>
       </x:c>
       <x:c r="J132" s="0">
-        <x:v>2.64</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
@@ -5919,270 +5922,276 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>2175097</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="D133" s="0">
-        <x:v>15000000</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>175000000</x:v>
+        <x:v>1305000000</x:v>
       </x:c>
       <x:c r="F133" s="0">
-        <x:v>17901652</x:v>
+        <x:v>1231340857</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>1.45</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>13.48</x:v>
+        <x:v>107.8</x:v>
       </x:c>
       <x:c r="J133" s="0">
-        <x:v>8.23</x:v>
+        <x:v>94.36</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C134" s="0">
+        <x:v>36605658</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>50000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F134" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F134" s="0">
+        <x:v>174340918</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>0</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>2.5</x:v>
+        <x:v>4.17</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>0</x:v>
+        <x:v>4.76</x:v>
+      </x:c>
+      <x:c r="K134" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>43000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D135" s="0">
-        <x:v>200000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F135" s="0">
-        <x:v>1024885</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>25.08</x:v>
+        <x:v>419.75</x:v>
       </x:c>
       <x:c r="J135" s="0">
-        <x:v>23.83</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>9937037</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>11000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>50000000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F136" s="0">
-        <x:v>50001023</x:v>
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G136" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>0.53</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>1.96</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>5.03</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C137" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C137" s="0">
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>5500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F137" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>175000000</x:v>
+      </x:c>
+      <x:c r="F137" s="0">
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>0</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>2.16</x:v>
+        <x:v>12.75</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>0</x:v>
+        <x:v>8.23</x:v>
+      </x:c>
+      <x:c r="K137" s="0" t="s">
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C138" s="0">
-        <x:v>13064888</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>30000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F138" s="0">
-        <x:v>268254173</x:v>
+        <x:v>152000000</x:v>
+      </x:c>
+      <x:c r="F138" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>40.98</x:v>
+        <x:v>2.32</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>20.53</x:v>
-      </x:c>
-      <x:c r="K138" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>111673026</x:v>
+        <x:v>43000</x:v>
       </x:c>
       <x:c r="D139" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>500000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="F139" s="0">
-        <x:v>500005947</x:v>
+        <x:v>1024885</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>0</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>12.66</x:v>
+        <x:v>24.8</x:v>
       </x:c>
       <x:c r="J139" s="0">
-        <x:v>4.48</x:v>
+        <x:v>23.83</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C140" s="0">
+        <x:v>9937037</x:v>
+      </x:c>
+      <x:c r="D140" s="0">
+        <x:v>11000000</x:v>
+      </x:c>
+      <x:c r="E140" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F140" s="0">
+        <x:v>50001023</x:v>
+      </x:c>
+      <x:c r="G140" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H140" s="0">
+        <x:v>0.53</x:v>
+      </x:c>
+      <x:c r="I140" s="0">
+        <x:v>1.92</x:v>
+      </x:c>
+      <x:c r="J140" s="0">
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="K140" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D140" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E140" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F140" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G140" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H140" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I140" s="0">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="J140" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
@@ -6190,16 +6199,16 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>19600000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>92000000</x:v>
+        <x:v>139000000</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
         <x:v>13</x:v>
@@ -6211,7 +6220,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>5.38</x:v>
+        <x:v>1.95</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>0</x:v>
@@ -6219,107 +6228,104 @@
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C142" s="0">
+        <x:v>13064888</x:v>
+      </x:c>
+      <x:c r="D142" s="0">
+        <x:v>30000000</x:v>
+      </x:c>
+      <x:c r="E142" s="0">
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F142" s="0">
+        <x:v>268254173</x:v>
+      </x:c>
+      <x:c r="G142" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H142" s="0">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="I142" s="0">
+        <x:v>41.76</x:v>
+      </x:c>
+      <x:c r="J142" s="0">
+        <x:v>20.53</x:v>
+      </x:c>
+      <x:c r="K142" s="0" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C142" s="0">
-        <x:v>1100000</x:v>
-      </x:c>
-      <x:c r="D142" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E142" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F142" s="0">
-        <x:v>56064346</x:v>
-      </x:c>
-      <x:c r="G142" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H142" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I142" s="0">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="J142" s="0">
-        <x:v>50.97</x:v>
-      </x:c>
-      <x:c r="K142" s="0" t="s">
-        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>6598092</x:v>
+        <x:v>111673026</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>11160000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>125000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>72091269</x:v>
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>5.91</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>15.63</x:v>
+        <x:v>12.85</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>10.93</x:v>
+        <x:v>4.48</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C144" s="0">
-        <x:v>1590000</x:v>
-      </x:c>
-      <x:c r="D144" s="0">
-        <x:v>2160000</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>35000000</x:v>
-      </x:c>
-      <x:c r="F144" s="0">
-        <x:v>60641600</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F144" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G144" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>0.91</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>38.3</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="J144" s="0">
-        <x:v>38.14</x:v>
-      </x:c>
-      <x:c r="K144" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
@@ -6327,474 +6333,477 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C145" s="0">
-        <x:v>1989802</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>5000000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F145" s="0">
-        <x:v>78711752</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F145" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G145" s="0">
-        <x:v>2.94</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>117</x:v>
+        <x:v>4.85</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>39.56</x:v>
-      </x:c>
-      <x:c r="K145" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C146" s="0">
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D146" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F146" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F146" s="0">
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>490</x:v>
+        <x:v>178.8</x:v>
       </x:c>
       <x:c r="J146" s="0">
-        <x:v>0</x:v>
+        <x:v>50.97</x:v>
+      </x:c>
+      <x:c r="K146" s="0" t="s">
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>300000</x:v>
+        <x:v>6598092</x:v>
       </x:c>
       <x:c r="D147" s="0">
-        <x:v>67500000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>326000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F147" s="0">
-        <x:v>1369300</x:v>
+        <x:v>72091269</x:v>
       </x:c>
       <x:c r="G147" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>0.04</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>5.81</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="J147" s="0">
-        <x:v>4.56</x:v>
+        <x:v>10.93</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>76908759</x:v>
+        <x:v>1590000</x:v>
       </x:c>
       <x:c r="D148" s="0">
-        <x:v>250000000</x:v>
+        <x:v>2160000</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>12000000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="F148" s="0">
-        <x:v>1979731803</x:v>
+        <x:v>60641600</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>33</x:v>
+        <x:v>34.9</x:v>
       </x:c>
       <x:c r="J148" s="0">
-        <x:v>25.74</x:v>
+        <x:v>38.14</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>8291656</x:v>
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D149" s="0">
-        <x:v>11000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>200000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F149" s="0">
-        <x:v>126004459</x:v>
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G149" s="0">
-        <x:v>0</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>1.9</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>15.65</x:v>
+        <x:v>116.5</x:v>
       </x:c>
       <x:c r="J149" s="0">
-        <x:v>15.2</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="K149" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="C150" s="0">
-        <x:v>2975773</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>6000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F150" s="0">
-        <x:v>44771095</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F150" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>22.5</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="J150" s="0">
-        <x:v>15.05</x:v>
-      </x:c>
-      <x:c r="K150" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>11039823</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D151" s="0">
-        <x:v>21600000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F151" s="0">
-        <x:v>183556428</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>5.11</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>13.1</x:v>
+        <x:v>5.23</x:v>
       </x:c>
       <x:c r="J151" s="0">
-        <x:v>16.63</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K151" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>37920641</x:v>
+        <x:v>77158759</x:v>
       </x:c>
       <x:c r="D152" s="0">
-        <x:v>195000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>12000000000</x:v>
       </x:c>
       <x:c r="F152" s="0">
-        <x:v>432820590</x:v>
+        <x:v>1987735371</x:v>
       </x:c>
       <x:c r="G152" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>1.94</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>15.75</x:v>
+        <x:v>33.1</x:v>
       </x:c>
       <x:c r="J152" s="0">
-        <x:v>11.41</x:v>
+        <x:v>25.76</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>5100000</x:v>
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>20000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>700000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F153" s="0">
-        <x:v>155318227</x:v>
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G153" s="0">
-        <x:v>6.81</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>0.93</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>49.52</x:v>
+        <x:v>14.84</x:v>
       </x:c>
       <x:c r="J153" s="0">
-        <x:v>30.45</x:v>
+        <x:v>15.2</x:v>
       </x:c>
       <x:c r="K153" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="C154" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="C154" s="0">
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D154" s="0">
-        <x:v>300000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>700000000</x:v>
-      </x:c>
-      <x:c r="F154" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F154" s="0">
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G154" s="0">
-        <x:v>6.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>0</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>1.9</x:v>
+        <x:v>21.92</x:v>
       </x:c>
       <x:c r="J154" s="0">
-        <x:v>0</x:v>
+        <x:v>15.05</x:v>
+      </x:c>
+      <x:c r="K154" s="0" t="s">
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>5000000</x:v>
+        <x:v>11039823</x:v>
       </x:c>
       <x:c r="D155" s="0">
-        <x:v>5000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>50000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F155" s="0">
-        <x:v>39090077</x:v>
+        <x:v>183556428</x:v>
       </x:c>
       <x:c r="G155" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>0.21</x:v>
+        <x:v>5.11</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>9.56</x:v>
+        <x:v>12.48</x:v>
       </x:c>
       <x:c r="J155" s="0">
-        <x:v>7.82</x:v>
+        <x:v>16.63</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>905991</x:v>
+        <x:v>37920641</x:v>
       </x:c>
       <x:c r="D156" s="0">
-        <x:v>21000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F156" s="0">
-        <x:v>17447317</x:v>
+        <x:v>432820590</x:v>
       </x:c>
       <x:c r="G156" s="0">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>0.13</x:v>
+        <x:v>1.94</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>15.48</x:v>
+        <x:v>15.33</x:v>
       </x:c>
       <x:c r="J156" s="0">
-        <x:v>19.26</x:v>
+        <x:v>11.41</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="C157" s="0">
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D157" s="0">
-        <x:v>11700000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F157" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F157" s="0">
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G157" s="0">
-        <x:v>0</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>0</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>35.3</x:v>
+        <x:v>49.14</x:v>
       </x:c>
       <x:c r="J157" s="0">
-        <x:v>0</x:v>
+        <x:v>30.45</x:v>
+      </x:c>
+      <x:c r="K157" s="0" t="s">
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D158" s="0">
-        <x:v>1000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>270000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G158" s="0">
-        <x:v>0</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H158" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>490</x:v>
+        <x:v>1.84</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>0</x:v>
@@ -6802,909 +6811,1043 @@
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>53584</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="D159" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>640000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F159" s="0">
-        <x:v>8271098</x:v>
+        <x:v>39090077</x:v>
       </x:c>
       <x:c r="G159" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>241</x:v>
+        <x:v>9.27</x:v>
       </x:c>
       <x:c r="J159" s="0">
-        <x:v>154.36</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>7550000</x:v>
+        <x:v>905991</x:v>
       </x:c>
       <x:c r="D160" s="0">
-        <x:v>30000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E160" s="0">
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F160" s="0">
-        <x:v>111777791</x:v>
+        <x:v>17447317</x:v>
       </x:c>
       <x:c r="G160" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>12.79</x:v>
+        <x:v>15.1</x:v>
       </x:c>
       <x:c r="J160" s="0">
-        <x:v>14.81</x:v>
+        <x:v>19.26</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="C161" s="0">
-        <x:v>2097716</x:v>
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D161" s="0">
-        <x:v>10112561</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F161" s="0">
-        <x:v>28985167</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F161" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G161" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>1.09</x:v>
+        <x:v>35.02</x:v>
       </x:c>
       <x:c r="J161" s="0">
-        <x:v>13.82</x:v>
-      </x:c>
-      <x:c r="K161" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="C162" s="0">
-        <x:v>5185302</x:v>
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D162" s="0">
-        <x:v>57000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>513000000</x:v>
-      </x:c>
-      <x:c r="F162" s="0">
-        <x:v>37061183</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F162" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G162" s="0">
-        <x:v>5.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>4.99</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="J162" s="0">
-        <x:v>7.15</x:v>
-      </x:c>
-      <x:c r="K162" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>669111</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D163" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>260000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F163" s="0">
-        <x:v>151220429</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>782</x:v>
+        <x:v>240.5</x:v>
       </x:c>
       <x:c r="J163" s="0">
-        <x:v>226</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>38840</x:v>
+        <x:v>7550000</x:v>
       </x:c>
       <x:c r="D164" s="0">
-        <x:v>1000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>270000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F164" s="0">
-        <x:v>9431791</x:v>
+        <x:v>111777791</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>490</x:v>
+        <x:v>11.52</x:v>
       </x:c>
       <x:c r="J164" s="0">
-        <x:v>242.84</x:v>
+        <x:v>14.81</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>2250000</x:v>
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D165" s="0">
-        <x:v>20000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>300000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F165" s="0">
-        <x:v>31750000</x:v>
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G165" s="0">
-        <x:v>4.98</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>12.79</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="J165" s="0">
-        <x:v>14.11</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>1500000</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D166" s="0">
-        <x:v>10112561</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>175000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F166" s="0">
-        <x:v>21870885</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G166" s="0">
-        <x:v>10</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>1.09</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="J166" s="0">
-        <x:v>14.58</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K166" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>1430040</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D167" s="0">
-        <x:v>8299326</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>600000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F167" s="0">
-        <x:v>198303629</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>1.51</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>138.4</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="J167" s="0">
-        <x:v>138.67</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C168" s="0">
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D168" s="0">
-        <x:v>2500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F168" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F168" s="0">
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G168" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>0</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>265</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="J168" s="0">
-        <x:v>0</x:v>
+        <x:v>242.84</x:v>
+      </x:c>
+      <x:c r="K168" s="0" t="s">
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>845945</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D169" s="0">
-        <x:v>15000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>250000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F169" s="0">
-        <x:v>10058606</x:v>
+        <x:v>31750000</x:v>
       </x:c>
       <x:c r="G169" s="0">
-        <x:v>0</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>3.42</x:v>
+        <x:v>11.52</x:v>
       </x:c>
       <x:c r="J169" s="0">
-        <x:v>11.89</x:v>
+        <x:v>14.11</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>21446</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D170" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>200000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F170" s="0">
-        <x:v>2015907</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G170" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>39.88</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="J170" s="0">
-        <x:v>94</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>850000</x:v>
+        <x:v>1522517</x:v>
       </x:c>
       <x:c r="D171" s="0">
-        <x:v>4250000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>40000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F171" s="0">
-        <x:v>6548328</x:v>
+        <x:v>210687547</x:v>
       </x:c>
       <x:c r="G171" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>1</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>6.44</x:v>
+        <x:v>143.5</x:v>
       </x:c>
       <x:c r="J171" s="0">
-        <x:v>7.7</x:v>
+        <x:v>138.38</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="C172" s="0">
-        <x:v>15000000</x:v>
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D172" s="0">
-        <x:v>300000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F172" s="0">
-        <x:v>23990000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F172" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G172" s="0">
-        <x:v>0</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>0.22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>2.34</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="J172" s="0">
-        <x:v>1.6</x:v>
-      </x:c>
-      <x:c r="K172" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>6397124</x:v>
+        <x:v>845945</x:v>
       </x:c>
       <x:c r="D173" s="0">
-        <x:v>35300000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>1046645000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F173" s="0">
-        <x:v>122892213</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="J173" s="0">
-        <x:v>19.21</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K173" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:11">
       <x:c r="A174" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>17495257</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D174" s="0">
-        <x:v>17500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>525000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F174" s="0">
-        <x:v>409385433</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>5</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>17.8</x:v>
+        <x:v>37.36</x:v>
       </x:c>
       <x:c r="J174" s="0">
-        <x:v>23.4</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K174" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>9350000</x:v>
+        <x:v>1024369</x:v>
       </x:c>
       <x:c r="D175" s="0">
-        <x:v>14710247</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>150000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F175" s="0">
-        <x:v>69547091</x:v>
+        <x:v>7639928</x:v>
       </x:c>
       <x:c r="G175" s="0">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>1.1</x:v>
+        <x:v>1.21</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>2.01</x:v>
+        <x:v>6.22</x:v>
       </x:c>
       <x:c r="J175" s="0">
-        <x:v>7.44</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="K175" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:11">
       <x:c r="A176" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D176" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="D176" s="0">
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>100000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F176" s="0">
-        <x:v>75911475</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>0.37</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>22.36</x:v>
+        <x:v>2.23</x:v>
       </x:c>
       <x:c r="J176" s="0">
-        <x:v>51.7</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K176" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:11">
       <x:c r="A177" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>500000</x:v>
+        <x:v>6397124</x:v>
       </x:c>
       <x:c r="D177" s="0">
-        <x:v>2000000</x:v>
+        <x:v>35300000</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>60000000</x:v>
+        <x:v>1046645000</x:v>
       </x:c>
       <x:c r="F177" s="0">
-        <x:v>13401783</x:v>
+        <x:v>122892213</x:v>
       </x:c>
       <x:c r="G177" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>2.05</x:v>
+        <x:v>3.58</x:v>
       </x:c>
       <x:c r="J177" s="0">
-        <x:v>26.8</x:v>
+        <x:v>19.21</x:v>
       </x:c>
       <x:c r="K177" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:11">
       <x:c r="A178" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>725000</x:v>
+        <x:v>17495257</x:v>
       </x:c>
       <x:c r="D178" s="0">
-        <x:v>10000000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E178" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F178" s="0">
-        <x:v>48539975</x:v>
+        <x:v>409385433</x:v>
       </x:c>
       <x:c r="G178" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H178" s="0">
-        <x:v>0.2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>33.8</x:v>
+        <x:v>17.49</x:v>
       </x:c>
       <x:c r="J178" s="0">
-        <x:v>66.95</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="K178" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:11">
       <x:c r="A179" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>1060056</x:v>
+        <x:v>9350000</x:v>
       </x:c>
       <x:c r="D179" s="0">
-        <x:v>7000000</x:v>
+        <x:v>14710247</x:v>
       </x:c>
       <x:c r="E179" s="0">
-        <x:v>250000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F179" s="0">
-        <x:v>60762934</x:v>
+        <x:v>69547091</x:v>
       </x:c>
       <x:c r="G179" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H179" s="0">
-        <x:v>0.44</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>216.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="J179" s="0">
-        <x:v>57.32</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="K179" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>321</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:11">
       <x:c r="A180" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>132750000</x:v>
+        <x:v>1468255</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E180" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F180" s="0">
-        <x:v>565141750</x:v>
+        <x:v>75911475</x:v>
       </x:c>
       <x:c r="G180" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H180" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>2.42</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="J180" s="0">
-        <x:v>4.26</x:v>
+        <x:v>51.7</x:v>
       </x:c>
       <x:c r="K180" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:11">
       <x:c r="A181" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>373000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D181" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E181" s="0">
-        <x:v>75000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F181" s="0">
-        <x:v>23786370</x:v>
+        <x:v>13401783</x:v>
       </x:c>
       <x:c r="G181" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H181" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>6.69</x:v>
+        <x:v>2.19</x:v>
       </x:c>
       <x:c r="J181" s="0">
-        <x:v>63.77</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="K181" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:11">
       <x:c r="A182" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>10000000</x:v>
+        <x:v>725000</x:v>
       </x:c>
       <x:c r="D182" s="0">
         <x:v>10000000</x:v>
       </x:c>
       <x:c r="E182" s="0">
-        <x:v>140000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F182" s="0">
-        <x:v>133271568</x:v>
+        <x:v>48539975</x:v>
       </x:c>
       <x:c r="G182" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H182" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>11.88</x:v>
+        <x:v>33.56</x:v>
       </x:c>
       <x:c r="J182" s="0">
-        <x:v>13.33</x:v>
+        <x:v>66.95</x:v>
       </x:c>
       <x:c r="K182" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:11">
       <x:c r="A183" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>66142950</x:v>
+        <x:v>1060056</x:v>
       </x:c>
       <x:c r="D183" s="0">
-        <x:v>105000000</x:v>
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="E183" s="0">
-        <x:v>650000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F183" s="0">
-        <x:v>384952260</x:v>
+        <x:v>60762934</x:v>
       </x:c>
       <x:c r="G183" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H183" s="0">
-        <x:v>2.71</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>5.35</x:v>
+        <x:v>221.4</x:v>
       </x:c>
       <x:c r="J183" s="0">
-        <x:v>5.82</x:v>
+        <x:v>57.32</x:v>
       </x:c>
       <x:c r="K183" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:11">
       <x:c r="A184" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C184" s="0">
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E184" s="0">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F184" s="0">
+        <x:v>565141750</x:v>
+      </x:c>
+      <x:c r="G184" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H184" s="0">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="I184" s="0">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="J184" s="0">
+        <x:v>4.26</x:v>
+      </x:c>
+      <x:c r="K184" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:11">
+      <x:c r="A185" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C185" s="0">
+        <x:v>373000</x:v>
+      </x:c>
+      <x:c r="D185" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E185" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F185" s="0">
+        <x:v>23786370</x:v>
+      </x:c>
+      <x:c r="G185" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H185" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I185" s="0">
+        <x:v>6.03</x:v>
+      </x:c>
+      <x:c r="J185" s="0">
+        <x:v>63.77</x:v>
+      </x:c>
+      <x:c r="K185" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:11">
+      <x:c r="A186" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C186" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="D186" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E186" s="0">
+        <x:v>140000000</x:v>
+      </x:c>
+      <x:c r="F186" s="0">
+        <x:v>133271568</x:v>
+      </x:c>
+      <x:c r="G186" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H186" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I186" s="0">
+        <x:v>11.14</x:v>
+      </x:c>
+      <x:c r="J186" s="0">
+        <x:v>13.33</x:v>
+      </x:c>
+      <x:c r="K186" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:11">
+      <x:c r="A187" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="C187" s="0">
+        <x:v>66142950</x:v>
+      </x:c>
+      <x:c r="D187" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="E187" s="0">
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F187" s="0">
+        <x:v>384952260</x:v>
+      </x:c>
+      <x:c r="G187" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H187" s="0">
+        <x:v>2.71</x:v>
+      </x:c>
+      <x:c r="I187" s="0">
+        <x:v>4.82</x:v>
+      </x:c>
+      <x:c r="J187" s="0">
+        <x:v>5.82</x:v>
+      </x:c>
+      <x:c r="K187" s="0" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="B184" s="0" t="s">
+    </x:row>
+    <x:row r="188" spans="1:11">
+      <x:c r="A188" s="0" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="C184" s="0">
+      <x:c r="B188" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="C188" s="0">
         <x:v>3081843</x:v>
       </x:c>
-      <x:c r="D184" s="0">
+      <x:c r="D188" s="0">
         <x:v>5000000</x:v>
       </x:c>
-      <x:c r="E184" s="0">
+      <x:c r="E188" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F184" s="0">
+      <x:c r="F188" s="0">
         <x:v>43986444</x:v>
       </x:c>
-      <x:c r="G184" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H184" s="0">
+      <x:c r="G188" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H188" s="0">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="I184" s="0">
-        <x:v>5.24</x:v>
-      </x:c>
-      <x:c r="J184" s="0">
+      <x:c r="I188" s="0">
+        <x:v>5.19</x:v>
+      </x:c>
+      <x:c r="J188" s="0">
         <x:v>14.27</x:v>
       </x:c>
-      <x:c r="K184" s="0" t="s">
-        <x:v>280</x:v>
+      <x:c r="K188" s="0" t="s">
+        <x:v>283</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,21 +49,48 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASFN</x:t>
+  </x:si>
+  <x:si>
     <x:t>MTRYO</x:t>
   </x:si>
   <x:si>
     <x:t>18.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>ATLAS</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CITAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFGY</x:t>
   </x:si>
   <x:si>
@@ -193,9 +220,6 @@
     <x:t>04.08.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>10.09.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>OTTO</x:t>
   </x:si>
   <x:si>
@@ -235,126 +259,126 @@
     <x:t>17.07.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>EKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.06.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.12.2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYLGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.08.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.04.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.07.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.05.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.03.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.02.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.01.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>24.07.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>EKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.12.2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYLGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.08.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.04.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.07.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.05.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.03.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.02.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27.01.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
@@ -730,9 +754,6 @@
     <x:t>31.12.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
     <x:t>12.05.2025</x:t>
   </x:si>
   <x:si>
@@ -853,15 +874,9 @@
     <x:t>14.03.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>23.06.2025</x:t>
   </x:si>
   <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>13.03.2025</x:t>
   </x:si>
   <x:si>
@@ -935,9 +950,6 @@
   </x:si>
   <x:si>
     <x:t>15.10.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
   </x:si>
   <x:si>
     <x:t>08.10.2024</x:t>
@@ -1384,7 +1396,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K188"/>
+  <x:dimension ref="A1:K196"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1433,22 +1445,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>4200000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>45000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>0</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="H2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>8.73</x:v>
+        <x:v>49.38</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1461,29 +1473,32 @@
       <x:c r="B3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C3" s="0">
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>6000000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="F3" s="0">
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>0</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>6.23</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J3" s="0">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
@@ -1497,22 +1512,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>700000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>0</x:v>
+        <x:v>11.11</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>5.25</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1523,136 +1538,130 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>800000</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>60000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>1960500</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.54</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>2.46</x:v>
+        <x:v>4.27</x:v>
       </x:c>
       <x:c r="J5" s="0">
-        <x:v>2.45</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>800000</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>50000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>31000000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>41.76</x:v>
+        <x:v>8.28</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>38.75</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>300000</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>180000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F7" s="0">
-        <x:v>3495000</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>12.85</x:v>
+        <x:v>37.58</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>11.65</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C8" s="0">
+        <x:v>486291</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>25000000</x:v>
+        <x:v>4200000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>45000000</x:v>
+      </x:c>
+      <x:c r="F8" s="0">
+        <x:v>4196275</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>4.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>22.3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>0</x:v>
+        <x:v>8.63</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -1660,31 +1669,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>622155</x:v>
       </x:c>
       <x:c r="D9" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E9" s="0">
         <x:v>50000000</x:v>
       </x:c>
-      <x:c r="E9" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F9" s="0">
+        <x:v>3496991</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>2.19</x:v>
+        <x:v>6.04</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>0</x:v>
+        <x:v>5.62</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1692,31 +1704,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>985122</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>9260000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>1200000000</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F10" s="0">
+        <x:v>5122634</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>111.6</x:v>
+        <x:v>5.33</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>0</x:v>
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -1724,16 +1739,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>2500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>225000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>13</x:v>
@@ -1745,7 +1760,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>73</x:v>
+        <x:v>38.92</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>0</x:v>
@@ -1756,13 +1771,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>39725600</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>1000000000</x:v>
@@ -1777,7 +1792,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>34.98</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>0</x:v>
@@ -1785,1573 +1800,1573 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C13" s="0">
-        <x:v>267427</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>12000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>1750000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>46136512</x:v>
+        <x:v>7177500</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0</x:v>
+        <x:v>1.54</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>159.3</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>172.52</x:v>
+        <x:v>2.39</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>50000</x:v>
+        <x:v>1153776</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>300000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>14714923</x:v>
+        <x:v>45391608</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>266</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>294.3</x:v>
+        <x:v>39.34</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>295110</x:v>
+        <x:v>9201797</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>2850000</x:v>
+        <x:v>180000000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>8818271</x:v>
+        <x:v>117794073</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.41</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>29.76</x:v>
+        <x:v>11.84</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>29.88</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>126000</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>20000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>2500000000</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F16" s="0">
+        <x:v>2914758</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0</x:v>
+        <x:v>4.84</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>52.45</x:v>
+        <x:v>22.38</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>0</x:v>
+        <x:v>23.13</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>5003974</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>10000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F17" s="0">
+        <x:v>849087760</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>6.26</x:v>
+        <x:v>2.13</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>0</x:v>
+        <x:v>169.68</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>12450000</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>96033600</x:v>
+        <x:v>9260000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>650000000</x:v>
-      </x:c>
-      <x:c r="F18" s="0">
-        <x:v>60880500</x:v>
+        <x:v>1200000000</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>1.78</x:v>
+        <x:v>100.5</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>4.89</x:v>
-      </x:c>
-      <x:c r="K18" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>155000</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>36000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>225000000</x:v>
+      </x:c>
+      <x:c r="F19" s="0">
+        <x:v>11266950</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>5.74</x:v>
+        <x:v>75.35</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>0</x:v>
+        <x:v>72.69</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>842639</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>15000000</x:v>
+        <x:v>39725600</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>150000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>7199247</x:v>
+        <x:v>11018400</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>0.17</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>8.11</x:v>
+        <x:v>37.4</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>8.54</x:v>
+        <x:v>36.73</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>1200000</x:v>
+        <x:v>747427</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>13500000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>400000000</x:v>
+        <x:v>1750000000</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>24902000</x:v>
+        <x:v>126721792</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>16.32</x:v>
+        <x:v>149.8</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>20.75</x:v>
+        <x:v>169.54</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>20746859</x:v>
+        <x:v>62059</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>30000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>210000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>145013995</x:v>
+        <x:v>17949617</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>3.7</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>5.9</x:v>
+        <x:v>267.75</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>6.99</x:v>
+        <x:v>289.23</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>11397816</x:v>
+        <x:v>365110</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>15000000</x:v>
+        <x:v>2850000</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>269900283</x:v>
+        <x:v>10900001</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.94</x:v>
+        <x:v>2.41</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.31</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>14.31</x:v>
+        <x:v>29.64</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>23.68</x:v>
+        <x:v>29.85</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>1000000</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>50000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F24" s="0">
-        <x:v>8385000</x:v>
+        <x:v>2500000000</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>2.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>4.82</x:v>
+        <x:v>53.4</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>8.39</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>2300000</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>12000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>12000000</x:v>
-      </x:c>
-      <x:c r="F25" s="0">
-        <x:v>1739216</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>3.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>12.51</x:v>
+        <x:v>6.88</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>0.76</x:v>
-      </x:c>
-      <x:c r="K25" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>4790000</x:v>
+        <x:v>12450000</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>12000000</x:v>
+        <x:v>96033600</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>12000000</x:v>
+        <x:v>650000000</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>7029498</x:v>
+        <x:v>60880500</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>7.98</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>4.09</x:v>
+        <x:v>1.61</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>1.47</x:v>
+        <x:v>4.89</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>4850000</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>12000000</x:v>
+        <x:v>36000000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>12000000</x:v>
-      </x:c>
-      <x:c r="F27" s="0">
-        <x:v>3543837</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>8.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>9.34</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>0.73</x:v>
-      </x:c>
-      <x:c r="K27" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>61493</x:v>
+        <x:v>895789</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>250000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3995647</x:v>
+        <x:v>7629018</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>60.9</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>64.98</x:v>
+        <x:v>8.52</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>500000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>750000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>26500000</x:v>
+        <x:v>24902000</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>1.05</x:v>
+        <x:v>14.69</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>1.33</x:v>
+        <x:v>20.75</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>20746859</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>150000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>33000000</x:v>
-      </x:c>
-      <x:c r="F30" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>210000000</x:v>
+      </x:c>
+      <x:c r="F30" s="0">
+        <x:v>145013995</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>1.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>0</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>99.3</x:v>
+        <x:v>5.37</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>0</x:v>
+        <x:v>6.99</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>100000</x:v>
+        <x:v>11397816</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>50000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>613000</x:v>
+        <x:v>269900283</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>5.26</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>4.61</x:v>
+        <x:v>12.88</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>6.13</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>10366031</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>25000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>240000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>102614742</x:v>
+        <x:v>8385000</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>9.27</x:v>
+        <x:v>4.34</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>9.9</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>1800452</x:v>
+        <x:v>2300000</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>15000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>150000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>17447883</x:v>
+        <x:v>1739216</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0.36</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>8.11</x:v>
+        <x:v>11.26</x:v>
       </x:c>
       <x:c r="J33" s="0">
-        <x:v>9.69</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>4790000</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>13409218</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="F34" s="0">
+        <x:v>7029498</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>9.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>0</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>16.36</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>0</x:v>
+        <x:v>1.47</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>6550000</x:v>
+        <x:v>4850000</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>55000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>100000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>9962550</x:v>
+        <x:v>3543837</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>5.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>0.61</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>1.48</x:v>
+        <x:v>8.41</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>1.52</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>200000</x:v>
+        <x:v>111250</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>25000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>415500000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>3174011</x:v>
+        <x:v>6994999</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>16.42</x:v>
+        <x:v>59.65</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>15.87</x:v>
+        <x:v>62.88</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>6067182</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>40000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>114062870</x:v>
+        <x:v>36200000</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>15.8</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>18.8</x:v>
+        <x:v>1.21</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>15160028</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>60000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F38" s="0">
-        <x:v>54496310</x:v>
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>3.59</x:v>
+        <x:v>94.45</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>3.59</x:v>
-      </x:c>
-      <x:c r="K38" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>2500000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>2500000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>950421206</x:v>
+        <x:v>613000</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0</x:v>
+        <x:v>5.26</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>419.75</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="J39" s="0">
-        <x:v>380.17</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>200821</x:v>
+        <x:v>10366031</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>230000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>15000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>13949918</x:v>
+        <x:v>102614742</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>1.66</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>66</x:v>
+        <x:v>9.49</x:v>
       </x:c>
       <x:c r="J40" s="0">
-        <x:v>69.46</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>2501710</x:v>
+        <x:v>1800452</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>10000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>450000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>97116052</x:v>
+        <x:v>17447883</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>26.96</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>38.82</x:v>
+        <x:v>9.69</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>58811536</x:v>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>85125000</x:v>
+        <x:v>13409218</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>5000000000</x:v>
-      </x:c>
-      <x:c r="F42" s="0">
-        <x:v>2837309709</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>1.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>50.2</x:v>
+        <x:v>15.98</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>48.24</x:v>
-      </x:c>
-      <x:c r="K42" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>62686718</x:v>
+        <x:v>6550000</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>25000000</x:v>
+        <x:v>55000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>2118794265</x:v>
+        <x:v>9962550</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>2.12</x:v>
+        <x:v>0.61</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>27.24</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>33.8</x:v>
+        <x:v>1.52</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>324474</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>3000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>40000000</x:v>
+        <x:v>415500000</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>1781383</x:v>
+        <x:v>4769662</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>13.6</x:v>
+        <x:v>15.18</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>5.49</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>7999148</x:v>
+        <x:v>6997674</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>15000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>300000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>168715651</x:v>
+        <x:v>128412350</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>2.11</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>17.25</x:v>
+        <x:v>14.64</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>21.09</x:v>
+        <x:v>18.35</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>201000</x:v>
+        <x:v>15160028</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>21739600</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>350000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>2071755</x:v>
+        <x:v>54496310</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>8.6</x:v>
+        <x:v>3.43</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>10.31</x:v>
+        <x:v>3.59</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1500000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F47" s="0">
+        <x:v>950421206</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>0</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>8.72</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="J47" s="0">
-        <x:v>0</x:v>
+        <x:v>380.17</x:v>
+      </x:c>
+      <x:c r="K47" s="0" t="s">
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>1900000</x:v>
+        <x:v>207649</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>10000000</x:v>
+        <x:v>230000</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>65000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>14177000</x:v>
+        <x:v>14403966</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>0.35</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>6.75</x:v>
+        <x:v>59.4</x:v>
       </x:c>
       <x:c r="J48" s="0">
-        <x:v>7.46</x:v>
+        <x:v>69.37</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>2501710</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>26398084</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>450000000</x:v>
+      </x:c>
+      <x:c r="F49" s="0">
+        <x:v>97116052</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>0</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>159.3</x:v>
+        <x:v>25.78</x:v>
       </x:c>
       <x:c r="J49" s="0">
-        <x:v>0</x:v>
+        <x:v>38.82</x:v>
+      </x:c>
+      <x:c r="K49" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>59486536</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>85125000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>5000000000</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>127481195</x:v>
+        <x:v>2871687459</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>0.82</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>19.4</x:v>
+        <x:v>51.15</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>7.13</x:v>
+        <x:v>48.27</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>970810</x:v>
+        <x:v>69686718</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>7300000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>225000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>28043898</x:v>
+        <x:v>2290434265</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>0.18</x:v>
+        <x:v>2.36</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>21.48</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>28.89</x:v>
+        <x:v>32.87</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>1001579</x:v>
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>10000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>100000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>15106723</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>2.56</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>8.14</x:v>
+        <x:v>13.4</x:v>
       </x:c>
       <x:c r="J52" s="0">
-        <x:v>15.08</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>40000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F53" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>0</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>4.04</x:v>
+        <x:v>16.9</x:v>
       </x:c>
       <x:c r="J53" s="0">
-        <x:v>0</x:v>
+        <x:v>21.09</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>2097370</x:v>
+        <x:v>201000</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>2000000</x:v>
+        <x:v>21739600</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>40000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>48772185</x:v>
+        <x:v>2071755</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>2.78</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>18.9</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>23.25</x:v>
+        <x:v>10.31</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C55" s="0">
-        <x:v>29346813</x:v>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>80000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F55" s="0">
-        <x:v>826937156</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>1.13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>41.76</x:v>
+        <x:v>8.53</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>28.18</x:v>
-      </x:c>
-      <x:c r="K55" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>7024156</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>80000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>65000000</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>93719334</x:v>
+        <x:v>14177000</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>10.21</x:v>
+        <x:v>6.48</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>13.34</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C57" s="0">
-        <x:v>3500000</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>49400000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F57" s="0">
-        <x:v>137144284</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G57" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>25.3</x:v>
+        <x:v>149.8</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>39.18</x:v>
-      </x:c>
-      <x:c r="K57" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>3753472</x:v>
-      </x:c>
-      <x:c r="D58" s="0">
-        <x:v>6000000</x:v>
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>432000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F58" s="0">
-        <x:v>224929072</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>0</x:v>
@@ -3360,855 +3375,858 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>56.35</x:v>
+        <x:v>17.59</x:v>
       </x:c>
       <x:c r="J58" s="0">
-        <x:v>59.93</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>3189049</x:v>
+        <x:v>970810</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>4000000</x:v>
+        <x:v>7300000</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>400000000</x:v>
+        <x:v>225000000</x:v>
       </x:c>
       <x:c r="F59" s="0">
-        <x:v>154328962</x:v>
+        <x:v>28043898</x:v>
       </x:c>
       <x:c r="G59" s="0">
-        <x:v>3.74</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>4.3</x:v>
+        <x:v>20.8</x:v>
       </x:c>
       <x:c r="J59" s="0">
-        <x:v>48.39</x:v>
+        <x:v>28.89</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C60" s="0">
+        <x:v>1001579</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>35000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F60" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F60" s="0">
+        <x:v>15106723</x:v>
       </x:c>
       <x:c r="G60" s="0">
-        <x:v>0.63</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>0</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>2.91</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>0</x:v>
+        <x:v>15.08</x:v>
+      </x:c>
+      <x:c r="K60" s="0" t="s">
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C61" s="0">
-        <x:v>5350000</x:v>
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D61" s="0">
-        <x:v>10000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F61" s="0">
-        <x:v>196494213</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>15.8</x:v>
+        <x:v>3.97</x:v>
       </x:c>
       <x:c r="J61" s="0">
-        <x:v>36.73</x:v>
-      </x:c>
-      <x:c r="K61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>21416071</x:v>
+        <x:v>2097370</x:v>
       </x:c>
       <x:c r="D62" s="0">
-        <x:v>35000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>300000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F62" s="0">
-        <x:v>186756128</x:v>
+        <x:v>48772185</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>5.35</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>6.73</x:v>
+        <x:v>18.1</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>8.72</x:v>
+        <x:v>23.25</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>236122</x:v>
+        <x:v>29346813</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>1700000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>110000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>14609667</x:v>
+        <x:v>826937156</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>50</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>61.87</x:v>
+        <x:v>28.18</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>1000000</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80000000</x:v>
+      </x:c>
+      <x:c r="E64" s="0">
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F64" s="0">
-        <x:v>21055375</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G64" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>17.49</x:v>
+        <x:v>10.09</x:v>
       </x:c>
       <x:c r="J64" s="0">
-        <x:v>21.06</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C65" s="0">
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D65" s="0">
-        <x:v>2000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F65" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F65" s="0">
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G65" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>4.3</x:v>
+        <x:v>22.78</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>0</x:v>
+        <x:v>39.18</x:v>
+      </x:c>
+      <x:c r="K65" s="0" t="s">
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>105404634</x:v>
+        <x:v>3753472</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>200000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>432000000</x:v>
       </x:c>
       <x:c r="F66" s="0">
-        <x:v>1032884452</x:v>
+        <x:v>224929072</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>12.85</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J66" s="0">
-        <x:v>9.8</x:v>
+        <x:v>59.93</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>16445115</x:v>
+        <x:v>3189049</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>25000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>500000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>393919718</x:v>
+        <x:v>154328962</x:v>
       </x:c>
       <x:c r="G67" s="0">
-        <x:v>0</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>3.29</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>33.62</x:v>
+        <x:v>4.13</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>23.95</x:v>
+        <x:v>48.39</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C68" s="0">
-        <x:v>1110000</x:v>
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>2000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>1100000000</x:v>
-      </x:c>
-      <x:c r="F68" s="0">
-        <x:v>587039028</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G68" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>419.75</x:v>
+        <x:v>2.62</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>528.86</x:v>
-      </x:c>
-      <x:c r="K68" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>24398659</x:v>
+        <x:v>5350000</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>40000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>850000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>590270273</x:v>
+        <x:v>196494213</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>41.76</x:v>
+        <x:v>14.22</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>24.19</x:v>
+        <x:v>36.73</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>46563878</x:v>
+        <x:v>21416071</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>50000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>500000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F70" s="0">
-        <x:v>500007798</x:v>
+        <x:v>186756128</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>0.52</x:v>
+        <x:v>5.35</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>12.85</x:v>
+        <x:v>6.06</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>10.74</x:v>
+        <x:v>8.72</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>6611571</x:v>
+        <x:v>236122</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>9000000</x:v>
+        <x:v>1700000</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>240000000</x:v>
+        <x:v>110000000</x:v>
       </x:c>
       <x:c r="F71" s="0">
-        <x:v>39750803</x:v>
+        <x:v>14609667</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0.69</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>5.74</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>6.01</x:v>
+        <x:v>61.87</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>2596120</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D72" s="0">
-        <x:v>100000000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F72" s="0">
-        <x:v>66065196</x:v>
+        <x:v>21055375</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>1.36</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>15.17</x:v>
+        <x:v>15.75</x:v>
       </x:c>
       <x:c r="J72" s="0">
-        <x:v>25.45</x:v>
+        <x:v>21.06</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C73" s="0">
-        <x:v>1000000</x:v>
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D73" s="0">
-        <x:v>30000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>400000000</x:v>
-      </x:c>
-      <x:c r="F73" s="0">
-        <x:v>4455000</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F73" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>3.88</x:v>
+        <x:v>4.13</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>4.46</x:v>
-      </x:c>
-      <x:c r="K73" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>200000</x:v>
+        <x:v>105404634</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>13760000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>300000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>2564000</x:v>
+        <x:v>1032884452</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>5.9</x:v>
+        <x:v>11.84</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>12.82</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C75" s="0">
+        <x:v>16445115</x:v>
       </x:c>
       <x:c r="D75" s="0">
-        <x:v>30000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F75" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F75" s="0">
+        <x:v>393919718</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>0</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>23.88</x:v>
+        <x:v>30.26</x:v>
       </x:c>
       <x:c r="J75" s="0">
-        <x:v>0</x:v>
+        <x:v>23.95</x:v>
+      </x:c>
+      <x:c r="K75" s="0" t="s">
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>5831653</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D76" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F76" s="0">
-        <x:v>304086107</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>2.28</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="J76" s="0">
-        <x:v>52.14</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>14512000</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D77" s="0">
-        <x:v>79451200</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F77" s="0">
-        <x:v>575005862</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>1.83</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>34.98</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="J77" s="0">
-        <x:v>39.62</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>5139828</x:v>
+        <x:v>46563878</x:v>
       </x:c>
       <x:c r="D78" s="0">
-        <x:v>3000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>300000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F78" s="0">
-        <x:v>207321844</x:v>
+        <x:v>500007798</x:v>
       </x:c>
       <x:c r="G78" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>1.28</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>22.2</x:v>
+        <x:v>11.84</x:v>
       </x:c>
       <x:c r="J78" s="0">
-        <x:v>40.34</x:v>
+        <x:v>10.74</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C79" s="0">
+        <x:v>6611571</x:v>
       </x:c>
       <x:c r="D79" s="0">
-        <x:v>15000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F79" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>240000000</x:v>
+      </x:c>
+      <x:c r="F79" s="0">
+        <x:v>39750803</x:v>
       </x:c>
       <x:c r="G79" s="0">
-        <x:v>5.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>0</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>21.42</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="J79" s="0">
-        <x:v>0</x:v>
+        <x:v>6.01</x:v>
+      </x:c>
+      <x:c r="K79" s="0" t="s">
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>8337681</x:v>
+        <x:v>2696120</x:v>
       </x:c>
       <x:c r="D80" s="0">
-        <x:v>6500000</x:v>
-      </x:c>
-      <x:c r="E80" s="0">
         <x:v>100000000</x:v>
       </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="F80" s="0">
-        <x:v>37235183</x:v>
+        <x:v>67477196</x:v>
       </x:c>
       <x:c r="G80" s="0">
-        <x:v>1.43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>0.33</x:v>
+        <x:v>1.42</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>3.08</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="J80" s="0">
-        <x:v>4.47</x:v>
+        <x:v>25.03</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>100000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>9275000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>950000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>3266000</x:v>
+        <x:v>4455000</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>33.56</x:v>
+        <x:v>3.86</x:v>
       </x:c>
       <x:c r="J81" s="0">
-        <x:v>32.66</x:v>
+        <x:v>4.46</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>1364000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>23460000</x:v>
+        <x:v>13760000</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>9000000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F82" s="0">
-        <x:v>409075556</x:v>
+        <x:v>2564000</x:v>
       </x:c>
       <x:c r="G82" s="0">
-        <x:v>1.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>285.5</x:v>
+        <x:v>5.37</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>299.91</x:v>
+        <x:v>12.82</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D83" s="0">
-        <x:v>380000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E83" s="0">
         <x:v>1000000000</x:v>
@@ -4217,13 +4235,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="G83" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H83" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>19.01</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>0</x:v>
@@ -4231,494 +4249,491 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>507440</x:v>
+        <x:v>5831653</x:v>
       </x:c>
       <x:c r="D84" s="0">
-        <x:v>2500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>42117724</x:v>
+        <x:v>304086107</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>2.67</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>250</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>83</x:v>
+        <x:v>52.14</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>2000000</x:v>
+        <x:v>14512000</x:v>
       </x:c>
       <x:c r="D85" s="0">
-        <x:v>2000000</x:v>
+        <x:v>79451200</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F85" s="0">
-        <x:v>81947000</x:v>
+        <x:v>575005862</x:v>
       </x:c>
       <x:c r="G85" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>2</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>30.7</x:v>
+        <x:v>37.4</x:v>
       </x:c>
       <x:c r="J85" s="0">
-        <x:v>40.97</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>9854768</x:v>
+        <x:v>5829828</x:v>
       </x:c>
       <x:c r="D86" s="0">
-        <x:v>10000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>250000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F86" s="0">
-        <x:v>233360906</x:v>
+        <x:v>222446644</x:v>
       </x:c>
       <x:c r="G86" s="0">
-        <x:v>0.63</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>0.62</x:v>
+        <x:v>1.46</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>14.31</x:v>
+        <x:v>22.42</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>23.68</x:v>
+        <x:v>38.16</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C87" s="0">
-        <x:v>324474</x:v>
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D87" s="0">
-        <x:v>5000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F87" s="0">
-        <x:v>1781383</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G87" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>13.6</x:v>
+        <x:v>20.74</x:v>
       </x:c>
       <x:c r="J87" s="0">
-        <x:v>5.49</x:v>
-      </x:c>
-      <x:c r="K87" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E88" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F88" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C88" s="0">
+        <x:v>8337681</x:v>
+      </x:c>
+      <x:c r="D88" s="0">
+        <x:v>6500000</x:v>
+      </x:c>
+      <x:c r="E88" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F88" s="0">
+        <x:v>37235183</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>0</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>16.42</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>0</x:v>
+        <x:v>4.47</x:v>
+      </x:c>
+      <x:c r="K88" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="C89" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D89" s="0">
-        <x:v>100000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="F89" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>950000000</x:v>
+      </x:c>
+      <x:c r="F89" s="0">
+        <x:v>3266000</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>4.39</x:v>
+        <x:v>33.04</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>0</x:v>
+        <x:v>32.66</x:v>
+      </x:c>
+      <x:c r="K89" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1364000</x:v>
+      </x:c>
+      <x:c r="D90" s="0">
+        <x:v>23460000</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>100000000</x:v>
+        <x:v>9000000000</x:v>
       </x:c>
       <x:c r="F90" s="0">
-        <x:v>85838440</x:v>
+        <x:v>409075556</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>0</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>1</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>7.01</x:v>
+        <x:v>293.5</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>6.6</x:v>
+        <x:v>299.91</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="C91" s="0">
-        <x:v>174500000</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D91" s="0">
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F91" s="0">
-        <x:v>694527000</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>2.35</x:v>
+        <x:v>19.2</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>3.98</x:v>
-      </x:c>
-      <x:c r="K91" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>635229</x:v>
-      </x:c>
-      <x:c r="D92" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>507440</x:v>
+      </x:c>
+      <x:c r="D92" s="0">
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E92" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>11323561</x:v>
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>0</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>15.17</x:v>
+        <x:v>244.5</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>17.83</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>130000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>3500000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E93" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>4947800</x:v>
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>1.6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0.03</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>27</x:v>
+        <x:v>30.7</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>38.06</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C94" s="0">
+        <x:v>9854768</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>5000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F94" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F94" s="0">
+        <x:v>233360906</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>0</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>221.4</x:v>
+        <x:v>12.88</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>0</x:v>
+        <x:v>23.68</x:v>
+      </x:c>
+      <x:c r="K94" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>447761</x:v>
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D95" s="0">
-        <x:v>3000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>120000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F95" s="0">
-        <x:v>18415143</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>28.76</x:v>
+        <x:v>13.4</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>41.13</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="C96" s="0">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="D96" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="E96" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F96" s="0">
-        <x:v>4022593</x:v>
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>1.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>3.5</x:v>
+        <x:v>15.18</x:v>
       </x:c>
       <x:c r="J96" s="0">
-        <x:v>20.11</x:v>
-      </x:c>
-      <x:c r="K96" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C97" s="0">
-        <x:v>946718</x:v>
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>20000000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F97" s="0">
-        <x:v>37333519</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>7.55</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>34.6</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>39.43</x:v>
-      </x:c>
-      <x:c r="K97" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C98" s="0">
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>13</x:v>
@@ -4726,536 +4741,539 @@
       <x:c r="E98" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F98" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F98" s="0">
+        <x:v>85838440</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>14.43</x:v>
+        <x:v>6.96</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>0</x:v>
+        <x:v>6.6</x:v>
+      </x:c>
+      <x:c r="K98" s="0" t="s">
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>3043115</x:v>
-      </x:c>
-      <x:c r="D99" s="0">
-        <x:v>50000000</x:v>
+        <x:v>174500000</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F99" s="0">
-        <x:v>49736990</x:v>
+        <x:v>694527000</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>20.2</x:v>
+        <x:v>2.31</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>16.34</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>2382736</x:v>
+        <x:v>635229</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F100" s="0">
-        <x:v>92635231</x:v>
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>50.85</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="J100" s="0">
-        <x:v>38.88</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="C101" s="0">
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>4191000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>160000000</x:v>
-      </x:c>
-      <x:c r="F101" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F101" s="0">
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>0</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>0</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>46.5</x:v>
+        <x:v>28.82</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>0</x:v>
+        <x:v>38.06</x:v>
+      </x:c>
+      <x:c r="K101" s="0" t="s">
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="C102" s="0">
-        <x:v>4650000</x:v>
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>75000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F102" s="0">
-        <x:v>49978950</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F102" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>8.16</x:v>
+        <x:v>215.2</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>10.75</x:v>
-      </x:c>
-      <x:c r="K102" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>806343</x:v>
+        <x:v>447761</x:v>
       </x:c>
       <x:c r="D103" s="0">
-        <x:v>1862500</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>75000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F103" s="0">
-        <x:v>30363861</x:v>
+        <x:v>18415143</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>28.94</x:v>
+        <x:v>27.92</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>37.66</x:v>
+        <x:v>41.13</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>310000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>49980500</x:v>
+        <x:v>4022593</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>0</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>8.16</x:v>
+        <x:v>3.47</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>161.23</x:v>
+        <x:v>20.11</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>2000000</x:v>
+        <x:v>946718</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>5000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F105" s="0">
-        <x:v>31366572</x:v>
+        <x:v>37333519</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>1</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>8.11</x:v>
+        <x:v>3.59</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>15.68</x:v>
+        <x:v>39.43</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="C106" s="0">
-        <x:v>1250000</x:v>
-      </x:c>
-      <x:c r="D106" s="0">
-        <x:v>25000000</x:v>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0">
-        <x:v>11187500</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>2.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>1.66</x:v>
+        <x:v>12.99</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>8.95</x:v>
-      </x:c>
-      <x:c r="K106" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C107" s="0">
+        <x:v>3043115</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>6950000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F107" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F107" s="0">
+        <x:v>49736990</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>2.6</x:v>
+        <x:v>19.84</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>0</x:v>
+        <x:v>16.34</x:v>
+      </x:c>
+      <x:c r="K107" s="0" t="s">
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>12500000</x:v>
-      </x:c>
-      <x:c r="D108" s="0">
-        <x:v>12500000</x:v>
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>60000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F108" s="0">
-        <x:v>61582393</x:v>
+        <x:v>92635231</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>1.82</x:v>
+        <x:v>45.78</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>4.93</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="C109" s="0">
-        <x:v>2093944</x:v>
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D109" s="0">
-        <x:v>220000000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>8500000000</x:v>
-      </x:c>
-      <x:c r="F109" s="0">
-        <x:v>200139168</x:v>
+        <x:v>160000000</x:v>
+      </x:c>
+      <x:c r="F109" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>97.2</x:v>
+        <x:v>46.12</x:v>
       </x:c>
       <x:c r="J109" s="0">
-        <x:v>95.58</x:v>
-      </x:c>
-      <x:c r="K109" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C110" s="0">
+        <x:v>4650000</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>150000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="F110" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F110" s="0">
+        <x:v>49978950</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>0</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>46.52</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>0</x:v>
+        <x:v>10.75</x:v>
+      </x:c>
+      <x:c r="K110" s="0" t="s">
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>51245979</x:v>
+        <x:v>806343</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>85000000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>200000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>125342407</x:v>
+        <x:v>30363861</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>2.18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>1.31</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>2.46</x:v>
+        <x:v>26.7</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>2.45</x:v>
+        <x:v>37.66</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>1584837</x:v>
+        <x:v>310000</x:v>
       </x:c>
       <x:c r="D112" s="0">
-        <x:v>2500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>92450176</x:v>
+        <x:v>49980500</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>60.9</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>58.33</x:v>
+        <x:v>161.23</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>7999148</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>11000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>200000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F113" s="0">
-        <x:v>168715651</x:v>
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>2.11</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>17.25</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="J113" s="0">
-        <x:v>21.09</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
@@ -5263,69 +5281,66 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>14000000</x:v>
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>10000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>200000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F114" s="0">
-        <x:v>236130680</x:v>
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>0.84</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>22</x:v>
+        <x:v>1.58</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>16.87</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="C115" s="0">
-        <x:v>1700005</x:v>
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>95000000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>1425000000</x:v>
-      </x:c>
-      <x:c r="F115" s="0">
-        <x:v>20390731</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F115" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G115" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>4.61</x:v>
+        <x:v>2.34</x:v>
       </x:c>
       <x:c r="J115" s="0">
-        <x:v>11.99</x:v>
-      </x:c>
-      <x:c r="K115" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
@@ -5336,238 +5351,238 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>6000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>6000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>150000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F116" s="0">
-        <x:v>132286928</x:v>
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>0.94</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>0.16</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>15.34</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="J116" s="0">
-        <x:v>22.05</x:v>
+        <x:v>4.93</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>225</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>1675000</x:v>
+        <x:v>2093944</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>9000000</x:v>
+        <x:v>220000000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>500000000</x:v>
+        <x:v>8500000000</x:v>
       </x:c>
       <x:c r="F117" s="0">
-        <x:v>114158717</x:v>
+        <x:v>200139168</x:v>
       </x:c>
       <x:c r="G117" s="0">
-        <x:v>7.81</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>88</x:v>
+        <x:v>99.9</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>68.15</x:v>
+        <x:v>95.58</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="C118" s="0">
-        <x:v>1824868</x:v>
+      <x:c r="C118" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>10000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F118" s="0">
-        <x:v>64572720</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G118" s="0">
-        <x:v>3.73</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>0.68</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>21.06</x:v>
+        <x:v>47.24</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>35.38</x:v>
-      </x:c>
-      <x:c r="K118" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C119" s="0">
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>50000000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F119" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F119" s="0">
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G119" s="0">
-        <x:v>5</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>0</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>6.38</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>0</x:v>
+        <x:v>2.45</x:v>
+      </x:c>
+      <x:c r="K119" s="0" t="s">
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>225</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1584837</x:v>
       </x:c>
       <x:c r="D120" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>30000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F120" s="0">
-        <x:v>19787700</x:v>
+        <x:v>92450176</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>0.27</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>6.66</x:v>
+        <x:v>59.65</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>19.79</x:v>
+        <x:v>58.33</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>225</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>98551</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>6500000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>100000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>1295684</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>0.06</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>11.59</x:v>
+        <x:v>16.9</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>13.15</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>225</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>6049315</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>15000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>66439559</x:v>
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>0</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>10.06</x:v>
+        <x:v>3.49</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>10.98</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5578,547 +5593,547 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>37225000</x:v>
+        <x:v>1700005</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>12000000</x:v>
+        <x:v>95000000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>150000000</x:v>
+        <x:v>1425000000</x:v>
       </x:c>
       <x:c r="F123" s="0">
-        <x:v>149982056</x:v>
+        <x:v>20390731</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>8.99</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>3.45</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>1.48</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>4.03</x:v>
+        <x:v>11.99</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>350000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>284578907</x:v>
+        <x:v>132286928</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>160.7</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>284.58</x:v>
+        <x:v>22.05</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>600000</x:v>
+        <x:v>1675000</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>600000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>25000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F125" s="0">
-        <x:v>22814140</x:v>
+        <x:v>114158717</x:v>
       </x:c>
       <x:c r="G125" s="0">
-        <x:v>0</x:v>
+        <x:v>7.81</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>4.3</x:v>
+        <x:v>6.91</x:v>
       </x:c>
       <x:c r="J125" s="0">
-        <x:v>38.02</x:v>
+        <x:v>68.15</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>11703083</x:v>
+        <x:v>1824868</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>16000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>720000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F126" s="0">
-        <x:v>978644023</x:v>
+        <x:v>64572720</x:v>
       </x:c>
       <x:c r="G126" s="0">
-        <x:v>10.16</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>163.4</x:v>
+        <x:v>18.96</x:v>
       </x:c>
       <x:c r="J126" s="0">
-        <x:v>83.62</x:v>
+        <x:v>35.38</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="C127" s="0">
-        <x:v>5100000</x:v>
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>9000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F127" s="0">
-        <x:v>90022686</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F127" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>7.6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>4.31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>29.76</x:v>
+        <x:v>6.36</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>17.65</x:v>
-      </x:c>
-      <x:c r="K127" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>3228679</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>175000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F128" s="0">
-        <x:v>51395842</x:v>
+        <x:v>19787700</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>6.26</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>15.92</x:v>
+        <x:v>19.79</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>150000</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>6000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>240000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F129" s="0">
-        <x:v>6145450</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>4.46</x:v>
+        <x:v>12.74</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>40.97</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C130" s="0">
+        <x:v>6049315</x:v>
+      </x:c>
+      <x:c r="D130" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E130" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F130" s="0">
+        <x:v>66439559</x:v>
+      </x:c>
+      <x:c r="G130" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H130" s="0">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="I130" s="0">
+        <x:v>9.81</x:v>
+      </x:c>
+      <x:c r="J130" s="0">
+        <x:v>10.98</x:v>
+      </x:c>
+      <x:c r="K130" s="0" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D130" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="E130" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F130" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G130" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H130" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I130" s="0">
-        <x:v>9.59</x:v>
-      </x:c>
-      <x:c r="J130" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>366107</x:v>
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>1200000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>30000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F131" s="0">
-        <x:v>6010300</x:v>
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G131" s="0">
-        <x:v>0</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>0.33</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>12.64</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>16.42</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>120000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D132" s="0">
-        <x:v>26398084</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>100000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F132" s="0">
-        <x:v>3830160</x:v>
+        <x:v>284578907</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>159.3</x:v>
+        <x:v>144.7</x:v>
       </x:c>
       <x:c r="J132" s="0">
-        <x:v>31.92</x:v>
+        <x:v>284.58</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>13050000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D133" s="0">
-        <x:v>13050000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>1305000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F133" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>22814140</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>3.13</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>107.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J133" s="0">
-        <x:v>94.36</x:v>
+        <x:v>38.02</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C134" s="0">
+        <x:v>11703083</x:v>
+      </x:c>
+      <x:c r="D134" s="0">
+        <x:v>16000000</x:v>
+      </x:c>
+      <x:c r="E134" s="0">
+        <x:v>720000000</x:v>
+      </x:c>
+      <x:c r="F134" s="0">
+        <x:v>978644023</x:v>
+      </x:c>
+      <x:c r="G134" s="0">
+        <x:v>10.16</x:v>
+      </x:c>
+      <x:c r="H134" s="0">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="I134" s="0">
+        <x:v>147.1</x:v>
+      </x:c>
+      <x:c r="J134" s="0">
+        <x:v>83.62</x:v>
+      </x:c>
+      <x:c r="K134" s="0" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="C134" s="0">
-        <x:v>36605658</x:v>
-      </x:c>
-      <x:c r="D134" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E134" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F134" s="0">
-        <x:v>174340918</x:v>
-      </x:c>
-      <x:c r="G134" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H134" s="0">
-        <x:v>3.66</x:v>
-      </x:c>
-      <x:c r="I134" s="0">
-        <x:v>4.17</x:v>
-      </x:c>
-      <x:c r="J134" s="0">
-        <x:v>4.76</x:v>
-      </x:c>
-      <x:c r="K134" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>1000000</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D135" s="0">
-        <x:v>4000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F135" s="0">
-        <x:v>429817200</x:v>
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>0</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>0.08</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>419.75</x:v>
+        <x:v>29.64</x:v>
       </x:c>
       <x:c r="J135" s="0">
-        <x:v>429.82</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>300000</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>60000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>171000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F136" s="0">
-        <x:v>791000</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G136" s="0">
-        <x:v>10</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>2.18</x:v>
+        <x:v>6.88</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>2.64</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>2175097</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>15000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>175000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F137" s="0">
-        <x:v>17901652</x:v>
+        <x:v>6145450</x:v>
       </x:c>
       <x:c r="G137" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>12.75</x:v>
+        <x:v>4.34</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>8.23</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>50000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>152000000</x:v>
+        <x:v>28000000</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H138" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>2.32</x:v>
+        <x:v>9.21</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>0</x:v>
@@ -6126,684 +6141,684 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>43000</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D139" s="0">
-        <x:v>200000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>5000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F139" s="0">
-        <x:v>1024885</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>24.8</x:v>
+        <x:v>12.31</x:v>
       </x:c>
       <x:c r="J139" s="0">
-        <x:v>23.83</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>9937037</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D140" s="0">
-        <x:v>11000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>50000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>50001023</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>0.53</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>1.92</x:v>
+        <x:v>149.8</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>5.03</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C141" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C141" s="0">
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>5500000</x:v>
+        <x:v>13050000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F141" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1305000000</x:v>
+      </x:c>
+      <x:c r="F141" s="0">
+        <x:v>1231340857</x:v>
       </x:c>
       <x:c r="G141" s="0">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>0</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>1.95</x:v>
+        <x:v>107.4</x:v>
       </x:c>
       <x:c r="J141" s="0">
-        <x:v>0</x:v>
+        <x:v>94.36</x:v>
+      </x:c>
+      <x:c r="K141" s="0" t="s">
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>13064888</x:v>
+        <x:v>36605658</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>30000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>600000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F142" s="0">
-        <x:v>268254173</x:v>
+        <x:v>174340918</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>0.5</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>41.76</x:v>
+        <x:v>4.07</x:v>
       </x:c>
       <x:c r="J142" s="0">
-        <x:v>20.53</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>111673026</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>150000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>500005947</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>12.85</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>4.48</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C144" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D144" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C144" s="0">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="D144" s="0">
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F144" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>171000000</x:v>
+      </x:c>
+      <x:c r="F144" s="0">
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G144" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>3.8</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="J144" s="0">
-        <x:v>0</x:v>
+        <x:v>2.64</x:v>
+      </x:c>
+      <x:c r="K144" s="0" t="s">
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C145" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C145" s="0">
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>19600000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>92000000</x:v>
-      </x:c>
-      <x:c r="F145" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>175000000</x:v>
+      </x:c>
+      <x:c r="F145" s="0">
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>0</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>4.85</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>0</x:v>
+        <x:v>8.23</x:v>
+      </x:c>
+      <x:c r="K145" s="0" t="s">
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C146" s="0">
-        <x:v>1100000</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D146" s="0">
-        <x:v>2000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F146" s="0">
-        <x:v>56064346</x:v>
+        <x:v>152000000</x:v>
+      </x:c>
+      <x:c r="F146" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>178.8</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="J146" s="0">
-        <x:v>50.97</x:v>
-      </x:c>
-      <x:c r="K146" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>6598092</x:v>
+        <x:v>43000</x:v>
       </x:c>
       <x:c r="D147" s="0">
-        <x:v>11160000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>125000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="F147" s="0">
-        <x:v>72091269</x:v>
+        <x:v>1024885</x:v>
       </x:c>
       <x:c r="G147" s="0">
-        <x:v>0</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>5.91</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>16.42</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="J147" s="0">
-        <x:v>10.93</x:v>
+        <x:v>23.83</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C148" s="0">
+        <x:v>9937037</x:v>
+      </x:c>
+      <x:c r="D148" s="0">
+        <x:v>11000000</x:v>
+      </x:c>
+      <x:c r="E148" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F148" s="0">
+        <x:v>50001023</x:v>
+      </x:c>
+      <x:c r="G148" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H148" s="0">
+        <x:v>0.53</x:v>
+      </x:c>
+      <x:c r="I148" s="0">
+        <x:v>1.94</x:v>
+      </x:c>
+      <x:c r="J148" s="0">
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="K148" s="0" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C148" s="0">
-        <x:v>1590000</x:v>
-      </x:c>
-      <x:c r="D148" s="0">
-        <x:v>2160000</x:v>
-      </x:c>
-      <x:c r="E148" s="0">
-        <x:v>35000000</x:v>
-      </x:c>
-      <x:c r="F148" s="0">
-        <x:v>60641600</x:v>
-      </x:c>
-      <x:c r="G148" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H148" s="0">
-        <x:v>0.91</x:v>
-      </x:c>
-      <x:c r="I148" s="0">
-        <x:v>34.9</x:v>
-      </x:c>
-      <x:c r="J148" s="0">
-        <x:v>38.14</x:v>
-      </x:c>
-      <x:c r="K148" s="0" t="s">
-        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C149" s="0">
-        <x:v>1989802</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D149" s="0">
-        <x:v>5000000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F149" s="0">
-        <x:v>78711752</x:v>
+        <x:v>139000000</x:v>
+      </x:c>
+      <x:c r="F149" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G149" s="0">
-        <x:v>2.94</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>116.5</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="J149" s="0">
-        <x:v>39.56</x:v>
-      </x:c>
-      <x:c r="K149" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C150" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C150" s="0">
+        <x:v>13064888</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>1000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F150" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F150" s="0">
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>496</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="J150" s="0">
-        <x:v>0</x:v>
+        <x:v>20.53</x:v>
+      </x:c>
+      <x:c r="K150" s="0" t="s">
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>300000</x:v>
+        <x:v>111673026</x:v>
       </x:c>
       <x:c r="D151" s="0">
-        <x:v>67500000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>326000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F151" s="0">
-        <x:v>1369300</x:v>
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G151" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>5.23</x:v>
+        <x:v>11.84</x:v>
       </x:c>
       <x:c r="J151" s="0">
-        <x:v>4.56</x:v>
+        <x:v>4.48</x:v>
       </x:c>
       <x:c r="K151" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C152" s="0">
-        <x:v>77158759</x:v>
-      </x:c>
-      <x:c r="D152" s="0">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E152" s="0">
         <x:v>250000000</x:v>
       </x:c>
-      <x:c r="E152" s="0">
-        <x:v>12000000000</x:v>
-      </x:c>
-      <x:c r="F152" s="0">
-        <x:v>1987735371</x:v>
+      <x:c r="F152" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>33.1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J152" s="0">
-        <x:v>25.76</x:v>
-      </x:c>
-      <x:c r="K152" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="C153" s="0">
-        <x:v>8291656</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>11000000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F153" s="0">
-        <x:v>126004459</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F153" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G153" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>14.84</x:v>
+        <x:v>4.37</x:v>
       </x:c>
       <x:c r="J153" s="0">
-        <x:v>15.2</x:v>
-      </x:c>
-      <x:c r="K153" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>2975773</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D154" s="0">
-        <x:v>6000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>150000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F154" s="0">
-        <x:v>44771095</x:v>
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G154" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>0.3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>21.92</x:v>
+        <x:v>186.7</x:v>
       </x:c>
       <x:c r="J154" s="0">
-        <x:v>15.05</x:v>
+        <x:v>50.97</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>11039823</x:v>
+        <x:v>6598092</x:v>
       </x:c>
       <x:c r="D155" s="0">
-        <x:v>21600000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F155" s="0">
-        <x:v>183556428</x:v>
+        <x:v>72091269</x:v>
       </x:c>
       <x:c r="G155" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>5.11</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>12.48</x:v>
+        <x:v>15.18</x:v>
       </x:c>
       <x:c r="J155" s="0">
-        <x:v>16.63</x:v>
+        <x:v>10.93</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>37920641</x:v>
+        <x:v>1590000</x:v>
       </x:c>
       <x:c r="D156" s="0">
-        <x:v>195000000</x:v>
+        <x:v>2160000</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="F156" s="0">
-        <x:v>432820590</x:v>
+        <x:v>60641600</x:v>
       </x:c>
       <x:c r="G156" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>1.94</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>15.33</x:v>
+        <x:v>32.42</x:v>
       </x:c>
       <x:c r="J156" s="0">
-        <x:v>11.41</x:v>
+        <x:v>38.14</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>5100000</x:v>
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D157" s="0">
-        <x:v>20000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>700000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F157" s="0">
-        <x:v>155318227</x:v>
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G157" s="0">
-        <x:v>6.81</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>0.93</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>49.14</x:v>
+        <x:v>112.7</x:v>
       </x:c>
       <x:c r="J157" s="0">
-        <x:v>30.45</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D158" s="0">
-        <x:v>300000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>700000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G158" s="0">
-        <x:v>6.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H158" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>1.84</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>0</x:v>
@@ -6811,241 +6826,247 @@
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>5000000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D159" s="0">
-        <x:v>5000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>50000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F159" s="0">
-        <x:v>39090077</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G159" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>9.27</x:v>
+        <x:v>4.71</x:v>
       </x:c>
       <x:c r="J159" s="0">
-        <x:v>7.82</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>905991</x:v>
+        <x:v>77158759</x:v>
       </x:c>
       <x:c r="D160" s="0">
-        <x:v>21000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>500000000</x:v>
+        <x:v>12000000000</x:v>
       </x:c>
       <x:c r="F160" s="0">
-        <x:v>17447317</x:v>
+        <x:v>1987735371</x:v>
       </x:c>
       <x:c r="G160" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>15.1</x:v>
+        <x:v>34.36</x:v>
       </x:c>
       <x:c r="J160" s="0">
-        <x:v>19.26</x:v>
+        <x:v>25.76</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C161" s="0">
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D161" s="0">
-        <x:v>11700000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E161" s="0">
         <x:v>200000000</x:v>
       </x:c>
-      <x:c r="F161" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F161" s="0">
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>0</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>35.02</x:v>
+        <x:v>14.63</x:v>
       </x:c>
       <x:c r="J161" s="0">
-        <x:v>0</x:v>
+        <x:v>15.2</x:v>
+      </x:c>
+      <x:c r="K161" s="0" t="s">
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="C162" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="C162" s="0">
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D162" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F162" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F162" s="0">
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>0</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>496</x:v>
+        <x:v>22.18</x:v>
       </x:c>
       <x:c r="J162" s="0">
-        <x:v>0</x:v>
+        <x:v>15.05</x:v>
+      </x:c>
+      <x:c r="K162" s="0" t="s">
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>53584</x:v>
+        <x:v>11039823</x:v>
       </x:c>
       <x:c r="D163" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>640000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F163" s="0">
-        <x:v>8271098</x:v>
+        <x:v>183556428</x:v>
       </x:c>
       <x:c r="G163" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>0.03</x:v>
+        <x:v>5.11</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>240.5</x:v>
+        <x:v>12.14</x:v>
       </x:c>
       <x:c r="J163" s="0">
-        <x:v>154.36</x:v>
+        <x:v>16.63</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>7550000</x:v>
+        <x:v>37920641</x:v>
       </x:c>
       <x:c r="D164" s="0">
-        <x:v>30000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>500000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F164" s="0">
-        <x:v>111777791</x:v>
+        <x:v>432820590</x:v>
       </x:c>
       <x:c r="G164" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>0.33</x:v>
+        <x:v>1.94</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>11.52</x:v>
+        <x:v>15.52</x:v>
       </x:c>
       <x:c r="J164" s="0">
-        <x:v>14.81</x:v>
+        <x:v>11.41</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>2097716</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D165" s="0">
-        <x:v>10112561</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>120000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F165" s="0">
-        <x:v>28985167</x:v>
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G165" s="0">
-        <x:v>10</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>1.04</x:v>
+        <x:v>49.38</x:v>
       </x:c>
       <x:c r="J165" s="0">
-        <x:v>13.82</x:v>
+        <x:v>30.45</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
@@ -7053,104 +7074,101 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="C166" s="0">
-        <x:v>5185302</x:v>
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D166" s="0">
-        <x:v>57000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>513000000</x:v>
-      </x:c>
-      <x:c r="F166" s="0">
-        <x:v>37061183</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F166" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G166" s="0">
-        <x:v>5.7</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>5.25</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="J166" s="0">
-        <x:v>7.15</x:v>
-      </x:c>
-      <x:c r="K166" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>669111</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="D167" s="0">
-        <x:v>1000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>260000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F167" s="0">
-        <x:v>151220429</x:v>
+        <x:v>39090077</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>795</x:v>
+        <x:v>9.49</x:v>
       </x:c>
       <x:c r="J167" s="0">
-        <x:v>226</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>38840</x:v>
+        <x:v>905991</x:v>
       </x:c>
       <x:c r="D168" s="0">
-        <x:v>1000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>270000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F168" s="0">
-        <x:v>9431791</x:v>
+        <x:v>17447317</x:v>
       </x:c>
       <x:c r="G168" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>496</x:v>
+        <x:v>14.85</x:v>
       </x:c>
       <x:c r="J168" s="0">
-        <x:v>242.84</x:v>
+        <x:v>19.26</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
@@ -7158,696 +7176,970 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="C169" s="0">
-        <x:v>2250000</x:v>
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D169" s="0">
-        <x:v>20000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F169" s="0">
-        <x:v>31750000</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F169" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G169" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>11.52</x:v>
+        <x:v>32.38</x:v>
       </x:c>
       <x:c r="J169" s="0">
-        <x:v>14.11</x:v>
-      </x:c>
-      <x:c r="K169" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="C170" s="0">
-        <x:v>1500000</x:v>
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D170" s="0">
-        <x:v>10112561</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>175000000</x:v>
-      </x:c>
-      <x:c r="F170" s="0">
-        <x:v>21870885</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F170" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G170" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>1.04</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="J170" s="0">
-        <x:v>14.58</x:v>
-      </x:c>
-      <x:c r="K170" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>1522517</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D171" s="0">
-        <x:v>8299326</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>600000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F171" s="0">
-        <x:v>210687547</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>143.5</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J171" s="0">
-        <x:v>138.38</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="C172" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="C172" s="0">
+        <x:v>7550000</x:v>
       </x:c>
       <x:c r="D172" s="0">
-        <x:v>2500000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F172" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F172" s="0">
+        <x:v>111777791</x:v>
       </x:c>
       <x:c r="G172" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>250</x:v>
+        <x:v>10.37</x:v>
       </x:c>
       <x:c r="J172" s="0">
-        <x:v>0</x:v>
+        <x:v>14.81</x:v>
+      </x:c>
+      <x:c r="K172" s="0" t="s">
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>845945</x:v>
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D173" s="0">
-        <x:v>15000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>250000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F173" s="0">
-        <x:v>10058606</x:v>
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G173" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>3.08</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="J173" s="0">
-        <x:v>11.89</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="K173" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:11">
       <x:c r="A174" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>21446</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D174" s="0">
-        <x:v>1000000</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>200000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F174" s="0">
-        <x:v>2015907</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G174" s="0">
-        <x:v>0</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>37.36</x:v>
+        <x:v>5.33</x:v>
       </x:c>
       <x:c r="J174" s="0">
-        <x:v>94</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K174" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>1024369</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D175" s="0">
-        <x:v>4250000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>40000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F175" s="0">
-        <x:v>7639928</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G175" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>1.21</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>6.22</x:v>
+        <x:v>748.5</x:v>
       </x:c>
       <x:c r="J175" s="0">
-        <x:v>7.46</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K175" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:11">
       <x:c r="A176" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>15000000</x:v>
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D176" s="0">
-        <x:v>300000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>600000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F176" s="0">
-        <x:v>23990000</x:v>
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>0.22</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>2.23</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="J176" s="0">
-        <x:v>1.6</x:v>
+        <x:v>242.84</x:v>
       </x:c>
       <x:c r="K176" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:11">
       <x:c r="A177" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>6397124</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D177" s="0">
-        <x:v>35300000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>1046645000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F177" s="0">
-        <x:v>122892213</x:v>
+        <x:v>31750000</x:v>
       </x:c>
       <x:c r="G177" s="0">
-        <x:v>0</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>3.58</x:v>
+        <x:v>10.37</x:v>
       </x:c>
       <x:c r="J177" s="0">
-        <x:v>19.21</x:v>
+        <x:v>14.11</x:v>
       </x:c>
       <x:c r="K177" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:11">
       <x:c r="A178" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>17495257</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D178" s="0">
-        <x:v>17500000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E178" s="0">
-        <x:v>525000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F178" s="0">
-        <x:v>409385433</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G178" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H178" s="0">
-        <x:v>5</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>17.49</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="J178" s="0">
-        <x:v>23.4</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K178" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:11">
       <x:c r="A179" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>9350000</x:v>
+        <x:v>1656401</x:v>
       </x:c>
       <x:c r="D179" s="0">
-        <x:v>14710247</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E179" s="0">
-        <x:v>150000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F179" s="0">
-        <x:v>69547091</x:v>
+        <x:v>229213803</x:v>
       </x:c>
       <x:c r="G179" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H179" s="0">
-        <x:v>1.1</x:v>
+        <x:v>1.74</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>1.9</x:v>
+        <x:v>138.8</x:v>
       </x:c>
       <x:c r="J179" s="0">
-        <x:v>7.44</x:v>
+        <x:v>138.38</x:v>
       </x:c>
       <x:c r="K179" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:11">
       <x:c r="A180" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="C180" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D180" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D180" s="0">
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E180" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F180" s="0">
-        <x:v>75911475</x:v>
+      <x:c r="F180" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G180" s="0">
-        <x:v>0</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H180" s="0">
-        <x:v>0.37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>22.2</x:v>
+        <x:v>244.5</x:v>
       </x:c>
       <x:c r="J180" s="0">
-        <x:v>51.7</x:v>
-      </x:c>
-      <x:c r="K180" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:11">
       <x:c r="A181" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>500000</x:v>
+        <x:v>845945</x:v>
       </x:c>
       <x:c r="D181" s="0">
-        <x:v>2000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E181" s="0">
-        <x:v>60000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F181" s="0">
-        <x:v>13401783</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G181" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H181" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>2.19</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="J181" s="0">
-        <x:v>26.8</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K181" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:11">
       <x:c r="A182" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>725000</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D182" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E182" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F182" s="0">
-        <x:v>48539975</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G182" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H182" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>33.56</x:v>
+        <x:v>38.92</x:v>
       </x:c>
       <x:c r="J182" s="0">
-        <x:v>66.95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K182" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:11">
       <x:c r="A183" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>1060056</x:v>
+        <x:v>1164369</x:v>
       </x:c>
       <x:c r="D183" s="0">
-        <x:v>7000000</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E183" s="0">
-        <x:v>250000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F183" s="0">
-        <x:v>60762934</x:v>
+        <x:v>8459528</x:v>
       </x:c>
       <x:c r="G183" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H183" s="0">
-        <x:v>0.44</x:v>
+        <x:v>1.37</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>221.4</x:v>
+        <x:v>6.36</x:v>
       </x:c>
       <x:c r="J183" s="0">
-        <x:v>57.32</x:v>
+        <x:v>7.27</x:v>
       </x:c>
       <x:c r="K183" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:11">
       <x:c r="A184" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>132750000</x:v>
-      </x:c>
-      <x:c r="D184" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="D184" s="0">
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E184" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F184" s="0">
-        <x:v>565141750</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G184" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H184" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>2.35</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="J184" s="0">
-        <x:v>4.26</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K184" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:11">
       <x:c r="A185" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>373000</x:v>
+        <x:v>6397124</x:v>
       </x:c>
       <x:c r="D185" s="0">
-        <x:v>1000000</x:v>
+        <x:v>35300000</x:v>
       </x:c>
       <x:c r="E185" s="0">
-        <x:v>75000000</x:v>
+        <x:v>1046645000</x:v>
       </x:c>
       <x:c r="F185" s="0">
-        <x:v>23786370</x:v>
+        <x:v>122892213</x:v>
       </x:c>
       <x:c r="G185" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H185" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>6.03</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="J185" s="0">
-        <x:v>63.77</x:v>
+        <x:v>19.21</x:v>
       </x:c>
       <x:c r="K185" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:11">
       <x:c r="A186" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>10000000</x:v>
+        <x:v>17495257</x:v>
       </x:c>
       <x:c r="D186" s="0">
-        <x:v>10000000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E186" s="0">
-        <x:v>140000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F186" s="0">
-        <x:v>133271568</x:v>
+        <x:v>409385433</x:v>
       </x:c>
       <x:c r="G186" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H186" s="0">
-        <x:v>0.67</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>11.14</x:v>
+        <x:v>15.75</x:v>
       </x:c>
       <x:c r="J186" s="0">
-        <x:v>13.33</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="K186" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:11">
       <x:c r="A187" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>66142950</x:v>
+        <x:v>9350000</x:v>
       </x:c>
       <x:c r="D187" s="0">
-        <x:v>105000000</x:v>
+        <x:v>14710247</x:v>
       </x:c>
       <x:c r="E187" s="0">
-        <x:v>650000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F187" s="0">
-        <x:v>384952260</x:v>
+        <x:v>69547091</x:v>
       </x:c>
       <x:c r="G187" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H187" s="0">
-        <x:v>2.71</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I187" s="0">
-        <x:v>4.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="J187" s="0">
-        <x:v>5.82</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="K187" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:11">
       <x:c r="A188" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>3081843</x:v>
-      </x:c>
-      <x:c r="D188" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1468255</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E188" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F188" s="0">
+        <x:v>75911475</x:v>
+      </x:c>
+      <x:c r="G188" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H188" s="0">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="I188" s="0">
+        <x:v>22.42</x:v>
+      </x:c>
+      <x:c r="J188" s="0">
+        <x:v>51.7</x:v>
+      </x:c>
+      <x:c r="K188" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:11">
+      <x:c r="A189" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="C189" s="0">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="D189" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E189" s="0">
+        <x:v>60000000</x:v>
+      </x:c>
+      <x:c r="F189" s="0">
+        <x:v>13401783</x:v>
+      </x:c>
+      <x:c r="G189" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H189" s="0">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="I189" s="0">
+        <x:v>2.13</x:v>
+      </x:c>
+      <x:c r="J189" s="0">
+        <x:v>26.8</x:v>
+      </x:c>
+      <x:c r="K189" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:11">
+      <x:c r="A190" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C190" s="0">
+        <x:v>725000</x:v>
+      </x:c>
+      <x:c r="D190" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E190" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F190" s="0">
+        <x:v>48539975</x:v>
+      </x:c>
+      <x:c r="G190" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H190" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="I190" s="0">
+        <x:v>33.04</x:v>
+      </x:c>
+      <x:c r="J190" s="0">
+        <x:v>66.95</x:v>
+      </x:c>
+      <x:c r="K190" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:11">
+      <x:c r="A191" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C191" s="0">
+        <x:v>1060056</x:v>
+      </x:c>
+      <x:c r="D191" s="0">
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="E191" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F191" s="0">
+        <x:v>60762934</x:v>
+      </x:c>
+      <x:c r="G191" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H191" s="0">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I191" s="0">
+        <x:v>215.2</x:v>
+      </x:c>
+      <x:c r="J191" s="0">
+        <x:v>57.32</x:v>
+      </x:c>
+      <x:c r="K191" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:11">
+      <x:c r="A192" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="C192" s="0">
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E192" s="0">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F192" s="0">
+        <x:v>565141750</x:v>
+      </x:c>
+      <x:c r="G192" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H192" s="0">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="I192" s="0">
+        <x:v>2.31</x:v>
+      </x:c>
+      <x:c r="J192" s="0">
+        <x:v>4.26</x:v>
+      </x:c>
+      <x:c r="K192" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:11">
+      <x:c r="A193" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C193" s="0">
+        <x:v>373000</x:v>
+      </x:c>
+      <x:c r="D193" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E193" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F193" s="0">
+        <x:v>23786370</x:v>
+      </x:c>
+      <x:c r="G193" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H193" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I193" s="0">
+        <x:v>5.43</x:v>
+      </x:c>
+      <x:c r="J193" s="0">
+        <x:v>63.77</x:v>
+      </x:c>
+      <x:c r="K193" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:11">
+      <x:c r="A194" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="C194" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="D194" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E194" s="0">
+        <x:v>140000000</x:v>
+      </x:c>
+      <x:c r="F194" s="0">
+        <x:v>133271568</x:v>
+      </x:c>
+      <x:c r="G194" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H194" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I194" s="0">
+        <x:v>10.03</x:v>
+      </x:c>
+      <x:c r="J194" s="0">
+        <x:v>13.33</x:v>
+      </x:c>
+      <x:c r="K194" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:11">
+      <x:c r="A195" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="C195" s="0">
+        <x:v>66142950</x:v>
+      </x:c>
+      <x:c r="D195" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="E195" s="0">
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F195" s="0">
+        <x:v>384952260</x:v>
+      </x:c>
+      <x:c r="G195" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H195" s="0">
+        <x:v>2.71</x:v>
+      </x:c>
+      <x:c r="I195" s="0">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="J195" s="0">
+        <x:v>5.82</x:v>
+      </x:c>
+      <x:c r="K195" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:11">
+      <x:c r="A196" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="C196" s="0">
+        <x:v>3081843</x:v>
+      </x:c>
+      <x:c r="D196" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E196" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F196" s="0">
         <x:v>43986444</x:v>
       </x:c>
-      <x:c r="G188" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H188" s="0">
+      <x:c r="G196" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H196" s="0">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="I188" s="0">
-        <x:v>5.19</x:v>
-      </x:c>
-      <x:c r="J188" s="0">
+      <x:c r="I196" s="0">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="J196" s="0">
         <x:v>14.27</x:v>
       </x:c>
-      <x:c r="K188" s="0" t="s">
-        <x:v>283</x:v>
+      <x:c r="K196" s="0" t="s">
+        <x:v>288</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,15 +49,24 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>EKDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21.09.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>ADGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>21.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>DCTTR</x:t>
   </x:si>
   <x:si>
@@ -70,6 +79,9 @@
     <x:t>MEYSU</x:t>
   </x:si>
   <x:si>
+    <x:t>ALBTN</x:t>
+  </x:si>
+  <x:si>
     <x:t>MASFN</x:t>
   </x:si>
   <x:si>
@@ -334,9 +346,6 @@
     <x:t>06.04.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>29.07.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>31.03.2026</x:t>
   </x:si>
   <x:si>
@@ -665,9 +674,6 @@
   </x:si>
   <x:si>
     <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
   </x:si>
   <x:si>
     <x:t>27.03.2025</x:t>
@@ -1396,7 +1402,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K196"/>
+  <x:dimension ref="A1:K199"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1445,22 +1451,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>250000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>49.38</x:v>
+        <x:v>33.96</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1471,63 +1477,60 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>50000</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1500000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>200000</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>0</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>4</x:v>
+        <x:v>7.48</x:v>
       </x:c>
       <x:c r="J3" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>500000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>11.11</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>2.02</x:v>
+        <x:v>51.75</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1535,133 +1538,139 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>1500000</x:v>
+      </x:c>
+      <x:c r="E5" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="F5" s="0">
+        <x:v>400000</x:v>
+      </x:c>
+      <x:c r="G5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="0">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="I5" s="0">
+        <x:v>3.91</x:v>
+      </x:c>
+      <x:c r="J5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="0">
-        <x:v>21000000</x:v>
-      </x:c>
-      <x:c r="E5" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G5" s="0">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="H5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I5" s="0">
-        <x:v>4.27</x:v>
-      </x:c>
-      <x:c r="J5" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>46500000</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>10000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>90814500</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0</x:v>
+        <x:v>11.11</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0</x:v>
+        <x:v>1.03</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>8.28</x:v>
+        <x:v>2.13</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>0</x:v>
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>12000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F7" s="0">
+        <x:v>4270000</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2.16</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>0</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>37.58</x:v>
+        <x:v>3.85</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>0</x:v>
+        <x:v>4.27</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>486291</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4200000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>45000000</x:v>
-      </x:c>
-      <x:c r="F8" s="0">
-        <x:v>4196275</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>9</x:v>
+        <x:v>8.45</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>8.63</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -1669,34 +1678,31 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>622155</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>6000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="F9" s="0">
-        <x:v>3496991</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>1.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>6.04</x:v>
+        <x:v>24.36</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>5.62</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1704,34 +1710,34 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>985122</x:v>
+        <x:v>300298</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>100000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>700000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>5122634</x:v>
+        <x:v>10900817</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="H10" s="0">
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>5.33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>5.2</x:v>
+        <x:v>36.3</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -1739,98 +1745,104 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>5000000</x:v>
+        <x:v>4200000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>45000000</x:v>
+      </x:c>
+      <x:c r="F11" s="0">
+        <x:v>8865394</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>38.92</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>0</x:v>
+        <x:v>8.87</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C12" s="0">
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>10000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F12" s="0">
+        <x:v>5948224</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>104.4</x:v>
+        <x:v>5.76</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>0</x:v>
+        <x:v>5.95</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>3000000</x:v>
+        <x:v>1160122</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>60000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>200000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>7177500</x:v>
+        <x:v>6040159</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>2.4</x:v>
+        <x:v>5.23</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>2.39</x:v>
+        <x:v>5.21</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
@@ -1838,34 +1850,31 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>1153776</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>50000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F14" s="0">
-        <x:v>45391608</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>41.6</x:v>
+        <x:v>39.22</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>39.34</x:v>
-      </x:c>
-      <x:c r="K14" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1873,34 +1882,34 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>9201797</x:v>
+        <x:v>210000</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>180000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>117794073</x:v>
+        <x:v>21924000</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>11.84</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>12.8</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1908,171 +1917,174 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>126000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>25000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>500000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>2914758</x:v>
+        <x:v>7177500</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>4.84</x:v>
+        <x:v>1.54</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>22.38</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>23.13</x:v>
+        <x:v>2.39</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="C17" s="0">
-        <x:v>5003974</x:v>
+        <x:v>1637343</x:v>
       </x:c>
       <x:c r="D17" s="0">
         <x:v>50000000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>200000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>849087760</x:v>
+        <x:v>65200930</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>2.13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>169.68</x:v>
+        <x:v>39.82</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>20896797</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>9260000</x:v>
+        <x:v>180000000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>1200000000</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F18" s="0">
+        <x:v>260975958</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>0</x:v>
+        <x:v>0.23</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>100.5</x:v>
+        <x:v>12.61</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>0</x:v>
+        <x:v>12.49</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>155000</x:v>
+        <x:v>176000</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>2500000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>225000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>11266950</x:v>
+        <x:v>4034608</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0</x:v>
+        <x:v>4.84</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>75.35</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>72.69</x:v>
+        <x:v>22.92</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>300000</x:v>
+        <x:v>5003974</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>39725600</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>11018400</x:v>
+        <x:v>849087760</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>37.4</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>36.73</x:v>
+        <x:v>169.68</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -2080,232 +2092,235 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>747427</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>12000000</x:v>
+        <x:v>9260000</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>1750000000</x:v>
-      </x:c>
-      <x:c r="F21" s="0">
-        <x:v>126721792</x:v>
+        <x:v>1200000000</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>0.28</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>149.8</x:v>
+        <x:v>101.2</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>169.54</x:v>
-      </x:c>
-      <x:c r="K21" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>62059</x:v>
+        <x:v>492277</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>300000000</x:v>
+        <x:v>225000000</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>17949617</x:v>
+        <x:v>34896577</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>267.75</x:v>
+        <x:v>76.1</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>289.23</x:v>
+        <x:v>70.89</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>365110</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>2850000</x:v>
+        <x:v>39725600</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>10900001</x:v>
+        <x:v>11018400</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.41</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>0.31</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>29.64</x:v>
+        <x:v>38.5</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>29.85</x:v>
+        <x:v>36.73</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C24" s="0">
+        <x:v>747427</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>20000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>2500000000</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1750000000</x:v>
+      </x:c>
+      <x:c r="F24" s="0">
+        <x:v>126721792</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>53.4</x:v>
+        <x:v>134.9</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>0</x:v>
+        <x:v>169.54</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C25" s="0">
+        <x:v>105000</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F25" s="0">
+        <x:v>30022828</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>6.88</x:v>
+        <x:v>279.25</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>0</x:v>
+        <x:v>285.93</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>12450000</x:v>
+        <x:v>463601</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>96033600</x:v>
+        <x:v>2850000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>650000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>60880500</x:v>
+        <x:v>13773377</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0</x:v>
+        <x:v>2.41</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>1.61</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>4.89</x:v>
+        <x:v>29.71</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>36000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>250000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>5.55</x:v>
+        <x:v>54.1</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>0</x:v>
@@ -2313,142 +2328,139 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>895789</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>15000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F28" s="0">
-        <x:v>7629018</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>3</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>7.82</x:v>
+        <x:v>6.64</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>8.52</x:v>
-      </x:c>
-      <x:c r="K28" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>1200000</x:v>
+        <x:v>12450000</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>13500000</x:v>
+        <x:v>96033600</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>400000000</x:v>
+        <x:v>650000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>24902000</x:v>
+        <x:v>60880500</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>14.69</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>20.75</x:v>
+        <x:v>4.89</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>20746859</x:v>
+        <x:v>479103</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>30000000</x:v>
+        <x:v>36000000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>210000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>145013995</x:v>
+        <x:v>2606320</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>3.7</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>5.37</x:v>
+        <x:v>5.67</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>6.99</x:v>
+        <x:v>5.44</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="C31" s="0">
-        <x:v>11397816</x:v>
+        <x:v>895789</x:v>
       </x:c>
       <x:c r="D31" s="0">
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>269900283</x:v>
+        <x:v>7629018</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.94</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>12.88</x:v>
+        <x:v>7.83</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>23.68</x:v>
+        <x:v>8.52</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
@@ -2459,2666 +2471,2672 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>1000000</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>50000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>500000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>8385000</x:v>
+        <x:v>61627000</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>4.34</x:v>
+        <x:v>15.29</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>8.39</x:v>
+        <x:v>16.66</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>2300000</x:v>
+        <x:v>20746859</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>12000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>12000000</x:v>
+        <x:v>210000000</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1739216</x:v>
+        <x:v>145013995</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>3.83</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>11.26</x:v>
+        <x:v>5.43</x:v>
       </x:c>
       <x:c r="J33" s="0">
-        <x:v>0.76</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>4790000</x:v>
+        <x:v>11397816</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>12000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>12000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>7029498</x:v>
+        <x:v>269900283</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>7.98</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>3.69</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>1.47</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>4850000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>12000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>12000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>3543837</x:v>
+        <x:v>8385000</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>8.08</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>8.41</x:v>
+        <x:v>4.23</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>0.73</x:v>
+        <x:v>8.39</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>111250</x:v>
+        <x:v>2300000</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>2000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>250000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>6994999</x:v>
+        <x:v>1739216</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0.08</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>59.65</x:v>
+        <x:v>10.14</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>62.88</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>30000000</x:v>
+        <x:v>4790000</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>500000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>750000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>36200000</x:v>
+        <x:v>7029498</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0.15</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>1.02</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>1.21</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>4850000</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>150000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>33000000</x:v>
-      </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="F38" s="0">
+        <x:v>3543837</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>1.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>94.45</x:v>
+        <x:v>7.57</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>0</x:v>
+        <x:v>0.73</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>100000</x:v>
+        <x:v>111250</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>50000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>500000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>613000</x:v>
+        <x:v>6994999</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>4.28</x:v>
+        <x:v>59.4</x:v>
       </x:c>
       <x:c r="J39" s="0">
-        <x:v>6.13</x:v>
+        <x:v>62.88</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>10366031</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>25000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>240000000</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>102614742</x:v>
+        <x:v>36200000</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>9.49</x:v>
+        <x:v>1.03</x:v>
       </x:c>
       <x:c r="J40" s="0">
-        <x:v>9.9</x:v>
+        <x:v>1.21</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C41" s="0">
-        <x:v>1800452</x:v>
+      <x:c r="C41" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>15000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F41" s="0">
-        <x:v>17447883</x:v>
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>7.82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>9.69</x:v>
-      </x:c>
-      <x:c r="K41" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>13409218</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>500000000</x:v>
       </x:c>
-      <x:c r="F42" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F42" s="0">
+        <x:v>613000</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>9.01</x:v>
+        <x:v>5.26</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>0</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>15.98</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>0</x:v>
+        <x:v>6.13</x:v>
+      </x:c>
+      <x:c r="K42" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>6550000</x:v>
+        <x:v>10366031</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>55000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>100000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>9962550</x:v>
+        <x:v>102614742</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>5.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>0.61</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>1.5</x:v>
+        <x:v>9.41</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>1.52</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>1800452</x:v>
+      </x:c>
+      <x:c r="D44" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E44" s="0">
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F44" s="0">
+        <x:v>17447883</x:v>
+      </x:c>
+      <x:c r="G44" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H44" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="I44" s="0">
+        <x:v>7.83</x:v>
+      </x:c>
+      <x:c r="J44" s="0">
+        <x:v>9.69</x:v>
+      </x:c>
+      <x:c r="K44" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="D44" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="E44" s="0">
-        <x:v>415500000</x:v>
-      </x:c>
-      <x:c r="F44" s="0">
-        <x:v>4769662</x:v>
-      </x:c>
-      <x:c r="G44" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H44" s="0">
-        <x:v>0.27</x:v>
-      </x:c>
-      <x:c r="I44" s="0">
-        <x:v>15.18</x:v>
-      </x:c>
-      <x:c r="J44" s="0">
-        <x:v>15.9</x:v>
-      </x:c>
-      <x:c r="K44" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="C45" s="0">
-        <x:v>6997674</x:v>
+        <x:v>55000</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>40000000</x:v>
+        <x:v>13409218</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>128412350</x:v>
+        <x:v>881400</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>14.64</x:v>
+        <x:v>16.03</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>18.35</x:v>
+        <x:v>16.03</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>15160028</x:v>
+        <x:v>6550000</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>60000000</x:v>
+        <x:v>55000000</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>54496310</x:v>
+        <x:v>9962550</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0.61</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>3.43</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>3.59</x:v>
+        <x:v>1.52</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>2500000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2500000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>415500000</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>950421206</x:v>
+        <x:v>4769662</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>433</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="J47" s="0">
-        <x:v>380.17</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>207649</x:v>
+        <x:v>6997674</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>230000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>15000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>14403966</x:v>
+        <x:v>128412350</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.66</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>1.5</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>59.4</x:v>
+        <x:v>14.52</x:v>
       </x:c>
       <x:c r="J48" s="0">
-        <x:v>69.37</x:v>
+        <x:v>18.35</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="C49" s="0">
-        <x:v>2501710</x:v>
+        <x:v>15160028</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>10000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>450000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>97116052</x:v>
+        <x:v>54496310</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>25.78</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="J49" s="0">
-        <x:v>38.82</x:v>
+        <x:v>3.59</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="C50" s="0">
-        <x:v>59486536</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>85125000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>5000000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2871687459</x:v>
+        <x:v>950421206</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>1.86</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>51.15</x:v>
+        <x:v>430.25</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>48.27</x:v>
+        <x:v>380.17</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>69686718</x:v>
+        <x:v>220399</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>25000000</x:v>
+        <x:v>230000</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2290434265</x:v>
+        <x:v>15186997</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>0</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>2.36</x:v>
+        <x:v>1.59</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>24.52</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>32.87</x:v>
+        <x:v>68.91</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>324474</x:v>
+        <x:v>2501710</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>3000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>40000000</x:v>
+        <x:v>450000000</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>1781383</x:v>
+        <x:v>97116052</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>13.4</x:v>
+        <x:v>25.18</x:v>
       </x:c>
       <x:c r="J52" s="0">
-        <x:v>5.49</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>7999148</x:v>
+        <x:v>59711016</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>15000000</x:v>
+        <x:v>85125000</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>300000000</x:v>
+        <x:v>5000000000</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>168715651</x:v>
+        <x:v>2882965334</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>2.11</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>16.9</x:v>
+        <x:v>50.05</x:v>
       </x:c>
       <x:c r="J53" s="0">
-        <x:v>21.09</x:v>
+        <x:v>48.28</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>201000</x:v>
+        <x:v>69686718</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>21739600</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>350000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>2071755</x:v>
+        <x:v>2290434265</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>0.02</x:v>
+        <x:v>2.36</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>8.5</x:v>
+        <x:v>22.08</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>10.31</x:v>
+        <x:v>32.87</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C55" s="0">
+        <x:v>324474</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>1500000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F55" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>40000000</x:v>
+      </x:c>
+      <x:c r="F55" s="0">
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>8.53</x:v>
+        <x:v>13.81</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>0</x:v>
+        <x:v>5.49</x:v>
+      </x:c>
+      <x:c r="K55" s="0" t="s">
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>1900000</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>10000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>65000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>14177000</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>0.35</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>6.48</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>7.46</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C57" s="0">
+        <x:v>201000</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>26398084</x:v>
+        <x:v>21739600</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F57" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>350000000</x:v>
+      </x:c>
+      <x:c r="F57" s="0">
+        <x:v>2071755</x:v>
       </x:c>
       <x:c r="G57" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>149.8</x:v>
+        <x:v>8.97</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>0</x:v>
+        <x:v>10.31</x:v>
+      </x:c>
+      <x:c r="K57" s="0" t="s">
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C58" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D58" s="0">
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F58" s="0">
-        <x:v>127481195</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>17.59</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="J58" s="0">
-        <x:v>7.13</x:v>
-      </x:c>
-      <x:c r="K58" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>970810</x:v>
+        <x:v>3070328</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>7300000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>225000000</x:v>
+        <x:v>65000000</x:v>
       </x:c>
       <x:c r="F59" s="0">
-        <x:v>28043898</x:v>
+        <x:v>21421330</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.57</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>20.8</x:v>
+        <x:v>6.7</x:v>
       </x:c>
       <x:c r="J59" s="0">
-        <x:v>28.89</x:v>
+        <x:v>6.98</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C60" s="0">
-        <x:v>1001579</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>10000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E60" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F60" s="0">
-        <x:v>15106723</x:v>
+      <x:c r="F60" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G60" s="0">
-        <x:v>2.56</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>7.65</x:v>
+        <x:v>134.9</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>15.08</x:v>
-      </x:c>
-      <x:c r="K60" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D61" s="0">
-        <x:v>40000000</x:v>
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F61" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F61" s="0">
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>0</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>3.97</x:v>
+        <x:v>15.84</x:v>
       </x:c>
       <x:c r="J61" s="0">
-        <x:v>0</x:v>
+        <x:v>7.13</x:v>
+      </x:c>
+      <x:c r="K61" s="0" t="s">
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>2097370</x:v>
+        <x:v>970810</x:v>
       </x:c>
       <x:c r="D62" s="0">
-        <x:v>2000000</x:v>
+        <x:v>7300000</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>40000000</x:v>
+        <x:v>225000000</x:v>
       </x:c>
       <x:c r="F62" s="0">
-        <x:v>48772185</x:v>
+        <x:v>28043898</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>2.78</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>18.1</x:v>
+        <x:v>21.38</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>23.25</x:v>
+        <x:v>28.89</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>29346813</x:v>
+        <x:v>1001579</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>80000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>826937156</x:v>
+        <x:v>15106723</x:v>
       </x:c>
       <x:c r="G63" s="0">
-        <x:v>0</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>1.13</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>41.6</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>28.18</x:v>
+        <x:v>15.08</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="C64" s="0">
-        <x:v>7024156</x:v>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>80000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F64" s="0">
-        <x:v>93719334</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>10.09</x:v>
+        <x:v>4.13</x:v>
       </x:c>
       <x:c r="J64" s="0">
-        <x:v>13.34</x:v>
-      </x:c>
-      <x:c r="K64" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>3500000</x:v>
+        <x:v>2097370</x:v>
       </x:c>
       <x:c r="D65" s="0">
-        <x:v>49400000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F65" s="0">
-        <x:v>137144284</x:v>
+        <x:v>48772185</x:v>
       </x:c>
       <x:c r="G65" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0.71</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>22.78</x:v>
+        <x:v>19.91</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>39.18</x:v>
+        <x:v>23.25</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>3753472</x:v>
+        <x:v>29346813</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>6000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>432000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F66" s="0">
-        <x:v>224929072</x:v>
+        <x:v>826937156</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>0.82</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>57</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J66" s="0">
-        <x:v>59.93</x:v>
+        <x:v>28.18</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>3189049</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D67" s="0">
-        <x:v>4000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>400000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>154328962</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G67" s="0">
-        <x:v>3.74</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>4.13</x:v>
+        <x:v>10.02</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>48.39</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C68" s="0">
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>35000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F68" s="0">
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G68" s="0">
-        <x:v>0.63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>0</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>2.62</x:v>
+        <x:v>20.52</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>0</x:v>
+        <x:v>39.18</x:v>
+      </x:c>
+      <x:c r="K68" s="0" t="s">
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>5350000</x:v>
+        <x:v>3753472</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>10000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>400000000</x:v>
+        <x:v>432000000</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>196494213</x:v>
+        <x:v>224929072</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>14.22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>36.73</x:v>
+        <x:v>59.93</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>21416071</x:v>
+        <x:v>3189049</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>35000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>300000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F70" s="0">
-        <x:v>186756128</x:v>
+        <x:v>154328962</x:v>
       </x:c>
       <x:c r="G70" s="0">
-        <x:v>0</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>5.35</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>6.06</x:v>
+        <x:v>4.23</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>8.72</x:v>
+        <x:v>48.39</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="C71" s="0">
-        <x:v>236122</x:v>
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>1700000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>110000000</x:v>
-      </x:c>
-      <x:c r="F71" s="0">
-        <x:v>14609667</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G71" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>45</x:v>
+        <x:v>2.36</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>61.87</x:v>
-      </x:c>
-      <x:c r="K71" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>1000000</x:v>
+        <x:v>5350000</x:v>
       </x:c>
       <x:c r="D72" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E72" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E72" s="0">
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F72" s="0">
-        <x:v>21055375</x:v>
+        <x:v>196494213</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>15.75</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="J72" s="0">
-        <x:v>21.06</x:v>
+        <x:v>36.73</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C73" s="0">
+        <x:v>21416071</x:v>
       </x:c>
       <x:c r="D73" s="0">
-        <x:v>2000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F73" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F73" s="0">
+        <x:v>186756128</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>0</x:v>
+        <x:v>5.35</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>4.13</x:v>
+        <x:v>6.28</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>0</x:v>
+        <x:v>8.72</x:v>
+      </x:c>
+      <x:c r="K73" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>105404634</x:v>
+        <x:v>236122</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>200000000</x:v>
+        <x:v>1700000</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>110000000</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>1032884452</x:v>
+        <x:v>14609667</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>11.84</x:v>
+        <x:v>40.5</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>9.8</x:v>
+        <x:v>61.87</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C75" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="D75" s="0">
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F75" s="0">
+        <x:v>21055375</x:v>
+      </x:c>
+      <x:c r="G75" s="0">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="H75" s="0">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="I75" s="0">
+        <x:v>15.5</x:v>
+      </x:c>
+      <x:c r="J75" s="0">
+        <x:v>21.06</x:v>
+      </x:c>
+      <x:c r="K75" s="0" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>16445115</x:v>
-      </x:c>
-      <x:c r="D75" s="0">
-        <x:v>25000000</x:v>
-      </x:c>
-      <x:c r="E75" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F75" s="0">
-        <x:v>393919718</x:v>
-      </x:c>
-      <x:c r="G75" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H75" s="0">
-        <x:v>3.29</x:v>
-      </x:c>
-      <x:c r="I75" s="0">
-        <x:v>30.26</x:v>
-      </x:c>
-      <x:c r="J75" s="0">
-        <x:v>23.95</x:v>
-      </x:c>
-      <x:c r="K75" s="0" t="s">
-        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="C76" s="0">
-        <x:v>1110000</x:v>
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D76" s="0">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>1100000000</x:v>
-      </x:c>
-      <x:c r="F76" s="0">
-        <x:v>587039028</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G76" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>433</x:v>
+        <x:v>4.23</x:v>
       </x:c>
       <x:c r="J76" s="0">
-        <x:v>528.86</x:v>
-      </x:c>
-      <x:c r="K76" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>24398659</x:v>
+        <x:v>105404634</x:v>
       </x:c>
       <x:c r="D77" s="0">
-        <x:v>40000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>850000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F77" s="0">
-        <x:v>590270273</x:v>
+        <x:v>1032884452</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>0.94</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>41.6</x:v>
+        <x:v>12.61</x:v>
       </x:c>
       <x:c r="J77" s="0">
-        <x:v>24.19</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>46563878</x:v>
+        <x:v>16445115</x:v>
       </x:c>
       <x:c r="D78" s="0">
-        <x:v>50000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E78" s="0">
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F78" s="0">
-        <x:v>500007798</x:v>
+        <x:v>393919718</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>0.52</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>11.84</x:v>
+        <x:v>27.24</x:v>
       </x:c>
       <x:c r="J78" s="0">
-        <x:v>10.74</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>6611571</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D79" s="0">
-        <x:v>9000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>240000000</x:v>
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F79" s="0">
-        <x:v>39750803</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>0.69</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>5.55</x:v>
+        <x:v>430.25</x:v>
       </x:c>
       <x:c r="J79" s="0">
-        <x:v>6.01</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>2696120</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D80" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>40000000</x:v>
+      </x:c>
+      <x:c r="E80" s="0">
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>67477196</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>1.42</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>14.2</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J80" s="0">
-        <x:v>25.03</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>1000000</x:v>
+        <x:v>46563878</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>30000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>400000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>4455000</x:v>
+        <x:v>500007798</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>3.86</x:v>
+        <x:v>12.61</x:v>
       </x:c>
       <x:c r="J81" s="0">
-        <x:v>4.46</x:v>
+        <x:v>10.74</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>200000</x:v>
+        <x:v>6611571</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>13760000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>300000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F82" s="0">
-        <x:v>2564000</x:v>
+        <x:v>39750803</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>5.37</x:v>
+        <x:v>5.67</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>12.82</x:v>
+        <x:v>6.01</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C83" s="0">
+        <x:v>2696120</x:v>
       </x:c>
       <x:c r="D83" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="E83" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F83" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F83" s="0">
+        <x:v>67477196</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>0</x:v>
+        <x:v>1.42</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>23.4</x:v>
+        <x:v>14.76</x:v>
       </x:c>
       <x:c r="J83" s="0">
-        <x:v>0</x:v>
+        <x:v>25.03</x:v>
+      </x:c>
+      <x:c r="K83" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>5831653</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D84" s="0">
-        <x:v>5000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>500000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>304086107</x:v>
+        <x:v>4455000</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>2.15</x:v>
+        <x:v>4.17</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>52.14</x:v>
+        <x:v>4.46</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>14512000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D85" s="0">
-        <x:v>79451200</x:v>
+        <x:v>13760000</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F85" s="0">
-        <x:v>575005862</x:v>
+        <x:v>2564000</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>1.83</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>37.4</x:v>
+        <x:v>5.43</x:v>
       </x:c>
       <x:c r="J85" s="0">
-        <x:v>39.62</x:v>
+        <x:v>12.82</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C86" s="0">
-        <x:v>5829828</x:v>
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D86" s="0">
-        <x:v>3000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
-      <x:c r="F86" s="0">
-        <x:v>222446644</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G86" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>1.46</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>22.42</x:v>
+        <x:v>24.6</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>38.16</x:v>
-      </x:c>
-      <x:c r="K86" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C87" s="0">
+        <x:v>5831653</x:v>
       </x:c>
       <x:c r="D87" s="0">
-        <x:v>15000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F87" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F87" s="0">
+        <x:v>304086107</x:v>
       </x:c>
       <x:c r="G87" s="0">
-        <x:v>5.49</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>0</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>20.74</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="J87" s="0">
-        <x:v>0</x:v>
+        <x:v>52.14</x:v>
+      </x:c>
+      <x:c r="K87" s="0" t="s">
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>8337681</x:v>
+        <x:v>14512000</x:v>
       </x:c>
       <x:c r="D88" s="0">
-        <x:v>6500000</x:v>
+        <x:v>79451200</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F88" s="0">
-        <x:v>37235183</x:v>
+        <x:v>575005862</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>1.43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>0.33</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>2.78</x:v>
+        <x:v>38.5</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>4.47</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>100000</x:v>
+        <x:v>5829828</x:v>
       </x:c>
       <x:c r="D89" s="0">
-        <x:v>9275000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>950000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F89" s="0">
-        <x:v>3266000</x:v>
+        <x:v>222446644</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>0</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1.46</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>33.04</x:v>
+        <x:v>22.62</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>32.66</x:v>
+        <x:v>38.16</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="C90" s="0">
-        <x:v>1364000</x:v>
+      <x:c r="C90" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D90" s="0">
-        <x:v>23460000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>9000000000</x:v>
-      </x:c>
-      <x:c r="F90" s="0">
-        <x:v>409075556</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>1.7</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>293.5</x:v>
+        <x:v>20.8</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>299.91</x:v>
-      </x:c>
-      <x:c r="K90" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C91" s="0">
+        <x:v>8337681</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>380000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F91" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F91" s="0">
+        <x:v>37235183</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>10</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>19.2</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>0</x:v>
+        <x:v>4.47</x:v>
+      </x:c>
+      <x:c r="K91" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>507440</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D92" s="0">
-        <x:v>2500000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>100000000</x:v>
+        <x:v>950000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>42117724</x:v>
+        <x:v>6502000</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>2.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>244.5</x:v>
+        <x:v>33.88</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>83</x:v>
+        <x:v>32.51</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>2000000</x:v>
+        <x:v>1364000</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>2000000</x:v>
+        <x:v>23460000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>100000000</x:v>
+        <x:v>9000000000</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>81947000</x:v>
+        <x:v>409075556</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>2</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>2</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>30.7</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>40.97</x:v>
+        <x:v>299.91</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="C94" s="0">
-        <x:v>9854768</x:v>
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>10000000</x:v>
+        <x:v>380000000</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F94" s="0">
-        <x:v>233360906</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>0.63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>0.62</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>12.88</x:v>
+        <x:v>19.49</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>23.68</x:v>
-      </x:c>
-      <x:c r="K94" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>324474</x:v>
+        <x:v>507440</x:v>
       </x:c>
       <x:c r="D95" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>30000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F95" s="0">
-        <x:v>1781383</x:v>
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>0</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>13.4</x:v>
+        <x:v>241.8</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>5.49</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E96" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F96" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C96" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D96" s="0">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="E96" s="0">
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F96" s="0">
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>15.18</x:v>
+        <x:v>28.06</x:v>
       </x:c>
       <x:c r="J96" s="0">
-        <x:v>0</x:v>
+        <x:v>40.97</x:v>
+      </x:c>
+      <x:c r="K96" s="0" t="s">
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C97" s="0">
+        <x:v>9854768</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>100000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="F97" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F97" s="0">
+        <x:v>233360906</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>0</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>4.25</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>0</x:v>
+        <x:v>23.68</x:v>
+      </x:c>
+      <x:c r="K97" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>324474</x:v>
+      </x:c>
+      <x:c r="D98" s="0">
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>100000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F98" s="0">
-        <x:v>85838440</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>1</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>6.96</x:v>
+        <x:v>13.81</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>6.6</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="C99" s="0">
-        <x:v>174500000</x:v>
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E99" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F99" s="0">
-        <x:v>694527000</x:v>
+      <x:c r="E99" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>2.31</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>3.98</x:v>
-      </x:c>
-      <x:c r="K99" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="C100" s="0">
-        <x:v>635229</x:v>
-      </x:c>
-      <x:c r="D100" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D100" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F100" s="0">
-        <x:v>11323561</x:v>
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>14.2</x:v>
+        <x:v>4.34</x:v>
       </x:c>
       <x:c r="J100" s="0">
-        <x:v>17.83</x:v>
-      </x:c>
-      <x:c r="K100" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>130000</x:v>
-      </x:c>
-      <x:c r="D101" s="0">
-        <x:v>3500000</x:v>
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E101" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F101" s="0">
-        <x:v>4947800</x:v>
+        <x:v>85838440</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>28.82</x:v>
+        <x:v>6.44</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>38.06</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D102" s="0">
-        <x:v>5000000</x:v>
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="C102" s="0">
+        <x:v>174500000</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F102" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F102" s="0">
+        <x:v>694527000</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>0</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>215.2</x:v>
+        <x:v>2.29</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>0</x:v>
+        <x:v>3.98</x:v>
+      </x:c>
+      <x:c r="K102" s="0" t="s">
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>447761</x:v>
-      </x:c>
-      <x:c r="D103" s="0">
-        <x:v>3000000</x:v>
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>120000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F103" s="0">
-        <x:v>18415143</x:v>
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>27.92</x:v>
+        <x:v>14.76</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>41.13</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>200000</x:v>
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>2000000</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E104" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>4022593</x:v>
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>1.71</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>3.47</x:v>
+        <x:v>28.82</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>20.11</x:v>
+        <x:v>38.06</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="C105" s="0">
-        <x:v>946718</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>20000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F105" s="0">
-        <x:v>37333519</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F105" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>7.55</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>3.59</x:v>
+        <x:v>217.2</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>39.43</x:v>
-      </x:c>
-      <x:c r="K105" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C106" s="0">
+        <x:v>447761</x:v>
+      </x:c>
+      <x:c r="D106" s="0">
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>120000000</x:v>
+      </x:c>
+      <x:c r="F106" s="0">
+        <x:v>18415143</x:v>
       </x:c>
       <x:c r="G106" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>12.99</x:v>
+        <x:v>27.76</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>0</x:v>
+        <x:v>41.13</x:v>
+      </x:c>
+      <x:c r="K106" s="0" t="s">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>3043115</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>50000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F107" s="0">
-        <x:v>49736990</x:v>
+        <x:v>4022593</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>0</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>19.84</x:v>
+        <x:v>3.42</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>16.34</x:v>
+        <x:v>20.11</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>2382736</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>946718</x:v>
+      </x:c>
+      <x:c r="D108" s="0">
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E108" s="0">
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F108" s="0">
-        <x:v>92635231</x:v>
+        <x:v>37333519</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>0</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>45.78</x:v>
+        <x:v>3.24</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>38.88</x:v>
+        <x:v>39.43</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D109" s="0">
-        <x:v>4191000</x:v>
+      <x:c r="D109" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>160000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
         <x:v>13</x:v>
@@ -5130,7 +5148,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>46.12</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>0</x:v>
@@ -5138,142 +5156,139 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>4650000</x:v>
+        <x:v>3043115</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>75000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E110" s="0">
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F110" s="0">
-        <x:v>49978950</x:v>
+        <x:v>49736990</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>7.35</x:v>
+        <x:v>20.26</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>10.75</x:v>
+        <x:v>16.34</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>806343</x:v>
-      </x:c>
-      <x:c r="D111" s="0">
-        <x:v>1862500</x:v>
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>75000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F111" s="0">
-        <x:v>30363861</x:v>
+        <x:v>92635231</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>26.7</x:v>
+        <x:v>41.22</x:v>
       </x:c>
       <x:c r="J111" s="0">
-        <x:v>37.66</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="C112" s="0">
-        <x:v>310000</x:v>
+      <x:c r="C112" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D112" s="0">
-        <x:v>5000000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F112" s="0">
-        <x:v>49980500</x:v>
+        <x:v>160000000</x:v>
+      </x:c>
+      <x:c r="F112" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>7.35</x:v>
+        <x:v>46.46</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>161.23</x:v>
-      </x:c>
-      <x:c r="K112" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C113" s="0">
+        <x:v>4650000</x:v>
+      </x:c>
+      <x:c r="D113" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="E113" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F113" s="0">
+        <x:v>49978950</x:v>
+      </x:c>
+      <x:c r="G113" s="0">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="H113" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I113" s="0">
+        <x:v>7.48</x:v>
+      </x:c>
+      <x:c r="J113" s="0">
+        <x:v>10.75</x:v>
+      </x:c>
+      <x:c r="K113" s="0" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="C113" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="D113" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E113" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F113" s="0">
-        <x:v>31366572</x:v>
-      </x:c>
-      <x:c r="G113" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H113" s="0">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="I113" s="0">
-        <x:v>7.82</x:v>
-      </x:c>
-      <x:c r="J113" s="0">
-        <x:v>15.68</x:v>
-      </x:c>
-      <x:c r="K113" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
@@ -5281,165 +5296,168 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>1250000</x:v>
+        <x:v>806343</x:v>
       </x:c>
       <x:c r="D114" s="0">
-        <x:v>25000000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>250000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F114" s="0">
-        <x:v>11187500</x:v>
+        <x:v>30363861</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>2.08</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>0.05</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>1.58</x:v>
+        <x:v>27.02</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>8.95</x:v>
+        <x:v>37.66</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="B115" s="0" t="s">
+      <x:c r="C115" s="0">
+        <x:v>310000</x:v>
+      </x:c>
+      <x:c r="D115" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E115" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F115" s="0">
+        <x:v>49980500</x:v>
+      </x:c>
+      <x:c r="G115" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H115" s="0">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="I115" s="0">
+        <x:v>7.48</x:v>
+      </x:c>
+      <x:c r="J115" s="0">
+        <x:v>161.23</x:v>
+      </x:c>
+      <x:c r="K115" s="0" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D115" s="0">
-        <x:v>6950000</x:v>
-      </x:c>
-      <x:c r="E115" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F115" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G115" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H115" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I115" s="0">
-        <x:v>2.34</x:v>
-      </x:c>
-      <x:c r="J115" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>12500000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>12500000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>60000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F116" s="0">
-        <x:v>61582393</x:v>
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>1.75</x:v>
+        <x:v>7.83</x:v>
       </x:c>
       <x:c r="J116" s="0">
-        <x:v>4.93</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>2093944</x:v>
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>220000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>8500000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F117" s="0">
-        <x:v>200139168</x:v>
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G117" s="0">
-        <x:v>0</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>99.9</x:v>
+        <x:v>1.58</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>95.58</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>150000000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>3000000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G118" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H118" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>47.24</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>0</x:v>
@@ -5447,69 +5465,69 @@
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>51245979</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>85000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>200000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F119" s="0">
-        <x:v>125342407</x:v>
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G119" s="0">
-        <x:v>2.18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1.31</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>2.4</x:v>
+        <x:v>1.74</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>2.45</x:v>
+        <x:v>4.93</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>1584837</x:v>
+        <x:v>2093944</x:v>
       </x:c>
       <x:c r="D120" s="0">
-        <x:v>2500000</x:v>
+        <x:v>220000000</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>100000000</x:v>
+        <x:v>8500000000</x:v>
       </x:c>
       <x:c r="F120" s="0">
-        <x:v>92450176</x:v>
+        <x:v>200139168</x:v>
       </x:c>
       <x:c r="G120" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>59.65</x:v>
+        <x:v>100.3</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>58.33</x:v>
+        <x:v>95.58</x:v>
       </x:c>
       <x:c r="K120" s="0" t="s">
         <x:v>229</x:v>
@@ -5517,104 +5535,101 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="C121" s="0">
-        <x:v>7999148</x:v>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>11000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F121" s="0">
-        <x:v>168715651</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F121" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>2.11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>16.9</x:v>
+        <x:v>46.58</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>21.09</x:v>
-      </x:c>
-      <x:c r="K121" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>14000000</x:v>
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D122" s="0">
-        <x:v>10000000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E122" s="0">
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>236130680</x:v>
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>0.84</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>0.19</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>3.49</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>16.87</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>1700005</x:v>
+        <x:v>1584837</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>95000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>1425000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F123" s="0">
-        <x:v>20390731</x:v>
+        <x:v>92450176</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>4.28</x:v>
+        <x:v>59.4</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>11.99</x:v>
+        <x:v>58.33</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
         <x:v>231</x:v>
@@ -5622,731 +5637,731 @@
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>6000000</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D124" s="0">
-        <x:v>6000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F124" s="0">
-        <x:v>132286928</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0.16</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>14.3</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="J124" s="0">
-        <x:v>22.05</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>1675000</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>9000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>500000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F125" s="0">
-        <x:v>114158717</x:v>
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G125" s="0">
-        <x:v>7.81</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>6.91</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="J125" s="0">
-        <x:v>68.15</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C126" s="0">
+        <x:v>1700005</x:v>
+      </x:c>
+      <x:c r="D126" s="0">
+        <x:v>95000000</x:v>
+      </x:c>
+      <x:c r="E126" s="0">
+        <x:v>1425000000</x:v>
+      </x:c>
+      <x:c r="F126" s="0">
+        <x:v>20390731</x:v>
+      </x:c>
+      <x:c r="G126" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H126" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="I126" s="0">
+        <x:v>4.11</x:v>
+      </x:c>
+      <x:c r="J126" s="0">
+        <x:v>11.99</x:v>
+      </x:c>
+      <x:c r="K126" s="0" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="C126" s="0">
-        <x:v>1824868</x:v>
-      </x:c>
-      <x:c r="D126" s="0">
-        <x:v>10000000</x:v>
-      </x:c>
-      <x:c r="E126" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F126" s="0">
-        <x:v>64572720</x:v>
-      </x:c>
-      <x:c r="G126" s="0">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="H126" s="0">
-        <x:v>0.68</x:v>
-      </x:c>
-      <x:c r="I126" s="0">
-        <x:v>18.96</x:v>
-      </x:c>
-      <x:c r="J126" s="0">
-        <x:v>35.38</x:v>
-      </x:c>
-      <x:c r="K126" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C127" s="0">
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>50000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F127" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>150000000</x:v>
+      </x:c>
+      <x:c r="F127" s="0">
+        <x:v>132286928</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>5</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>6.36</x:v>
+        <x:v>13.26</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>0</x:v>
+        <x:v>22.05</x:v>
+      </x:c>
+      <x:c r="K127" s="0" t="s">
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1675000</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>1000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>30000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F128" s="0">
-        <x:v>19787700</x:v>
+        <x:v>114158717</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>0.67</x:v>
+        <x:v>7.81</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>6</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>19.79</x:v>
+        <x:v>68.15</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>98551</x:v>
+        <x:v>1824868</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>6500000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>100000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F129" s="0">
-        <x:v>1295684</x:v>
+        <x:v>64572720</x:v>
       </x:c>
       <x:c r="G129" s="0">
-        <x:v>0</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>12.74</x:v>
+        <x:v>17.07</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>13.15</x:v>
+        <x:v>35.38</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="C130" s="0">
-        <x:v>6049315</x:v>
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>15000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F130" s="0">
-        <x:v>66439559</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F130" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>9.81</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>10.98</x:v>
-      </x:c>
-      <x:c r="K130" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>37225000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>12000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>150000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F131" s="0">
-        <x:v>149982056</x:v>
+        <x:v>19787700</x:v>
       </x:c>
       <x:c r="G131" s="0">
-        <x:v>8.99</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>3.45</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>1.5</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>4.03</x:v>
+        <x:v>19.79</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>1000000</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D132" s="0">
-        <x:v>1000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>350000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F132" s="0">
-        <x:v>284578907</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>144.7</x:v>
+        <x:v>12.15</x:v>
       </x:c>
       <x:c r="J132" s="0">
-        <x:v>284.58</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K132" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>600000</x:v>
+        <x:v>6049315</x:v>
       </x:c>
       <x:c r="D133" s="0">
-        <x:v>600000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>25000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F133" s="0">
-        <x:v>22814140</x:v>
+        <x:v>66439559</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4</x:v>
+        <x:v>9.92</x:v>
       </x:c>
       <x:c r="J133" s="0">
-        <x:v>38.02</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>11703083</x:v>
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>16000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>720000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F134" s="0">
-        <x:v>978644023</x:v>
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G134" s="0">
-        <x:v>10.16</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>1.67</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>147.1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>83.62</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>5100000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D135" s="0">
-        <x:v>9000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>200000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F135" s="0">
-        <x:v>90022686</x:v>
+        <x:v>284578907</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>7.6</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>4.31</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>29.64</x:v>
+        <x:v>130.3</x:v>
       </x:c>
       <x:c r="J135" s="0">
-        <x:v>17.65</x:v>
+        <x:v>284.58</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>3228679</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>10000000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>175000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F136" s="0">
-        <x:v>51395842</x:v>
+        <x:v>22814140</x:v>
       </x:c>
       <x:c r="G136" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>6.88</x:v>
+        <x:v>3.91</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>15.92</x:v>
+        <x:v>38.02</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C137" s="0">
+        <x:v>11703083</x:v>
+      </x:c>
+      <x:c r="D137" s="0">
+        <x:v>16000000</x:v>
+      </x:c>
+      <x:c r="E137" s="0">
+        <x:v>720000000</x:v>
+      </x:c>
+      <x:c r="F137" s="0">
+        <x:v>978644023</x:v>
+      </x:c>
+      <x:c r="G137" s="0">
+        <x:v>10.16</x:v>
+      </x:c>
+      <x:c r="H137" s="0">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="I137" s="0">
+        <x:v>132.4</x:v>
+      </x:c>
+      <x:c r="J137" s="0">
+        <x:v>83.62</x:v>
+      </x:c>
+      <x:c r="K137" s="0" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="C137" s="0">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="D137" s="0">
-        <x:v>6000000</x:v>
-      </x:c>
-      <x:c r="E137" s="0">
-        <x:v>240000000</x:v>
-      </x:c>
-      <x:c r="F137" s="0">
-        <x:v>6145450</x:v>
-      </x:c>
-      <x:c r="G137" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H137" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="I137" s="0">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="J137" s="0">
-        <x:v>40.97</x:v>
-      </x:c>
-      <x:c r="K137" s="0" t="s">
-        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="C138" s="0">
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>1000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F138" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F138" s="0">
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>0</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>0</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>9.21</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>0</x:v>
+        <x:v>17.65</x:v>
+      </x:c>
+      <x:c r="K138" s="0" t="s">
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>366107</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D139" s="0">
-        <x:v>1200000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>30000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F139" s="0">
-        <x:v>6010300</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>12.31</x:v>
+        <x:v>6.64</x:v>
       </x:c>
       <x:c r="J139" s="0">
-        <x:v>16.42</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>120000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D140" s="0">
-        <x:v>26398084</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>100000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>3830160</x:v>
+        <x:v>6145450</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>149.8</x:v>
+        <x:v>4.48</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>31.92</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C141" s="0">
-        <x:v>13050000</x:v>
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>13050000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>1305000000</x:v>
-      </x:c>
-      <x:c r="F141" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F141" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G141" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>3.13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>107.4</x:v>
+        <x:v>9.05</x:v>
       </x:c>
       <x:c r="J141" s="0">
-        <x:v>94.36</x:v>
-      </x:c>
-      <x:c r="K141" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>36605658</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>500000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F142" s="0">
-        <x:v>174340918</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>3.66</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>4.07</x:v>
+        <x:v>12.45</x:v>
       </x:c>
       <x:c r="J142" s="0">
-        <x:v>4.76</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>1000000</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>4000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>429817200</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>433</x:v>
+        <x:v>134.9</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>429.82</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C144" s="0">
+        <x:v>13050000</x:v>
+      </x:c>
+      <x:c r="D144" s="0">
+        <x:v>13050000</x:v>
+      </x:c>
+      <x:c r="E144" s="0">
+        <x:v>1305000000</x:v>
+      </x:c>
+      <x:c r="F144" s="0">
+        <x:v>1231340857</x:v>
+      </x:c>
+      <x:c r="G144" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H144" s="0">
+        <x:v>3.13</x:v>
+      </x:c>
+      <x:c r="I144" s="0">
+        <x:v>108.8</x:v>
+      </x:c>
+      <x:c r="J144" s="0">
+        <x:v>94.36</x:v>
+      </x:c>
+      <x:c r="K144" s="0" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C144" s="0">
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="D144" s="0">
-        <x:v>60000000</x:v>
-      </x:c>
-      <x:c r="E144" s="0">
-        <x:v>171000000</x:v>
-      </x:c>
-      <x:c r="F144" s="0">
-        <x:v>791000</x:v>
-      </x:c>
-      <x:c r="G144" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H144" s="0">
-        <x:v>0.05</x:v>
-      </x:c>
-      <x:c r="I144" s="0">
-        <x:v>1.97</x:v>
-      </x:c>
-      <x:c r="J144" s="0">
-        <x:v>2.64</x:v>
-      </x:c>
-      <x:c r="K144" s="0" t="s">
-        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
@@ -6354,153 +6369,156 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>2175097</x:v>
+        <x:v>36605658</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>15000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>175000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F145" s="0">
-        <x:v>17901652</x:v>
+        <x:v>174340918</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>1.45</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>12.2</x:v>
+        <x:v>4.17</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>8.23</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C146" s="0">
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D146" s="0">
-        <x:v>50000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F146" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F146" s="0">
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>2.16</x:v>
+        <x:v>430.25</x:v>
       </x:c>
       <x:c r="J146" s="0">
-        <x:v>0</x:v>
+        <x:v>429.82</x:v>
+      </x:c>
+      <x:c r="K146" s="0" t="s">
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>43000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D147" s="0">
-        <x:v>200000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>5000000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F147" s="0">
-        <x:v>1024885</x:v>
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G147" s="0">
-        <x:v>0.43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>23.8</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="J147" s="0">
-        <x:v>23.83</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>9937037</x:v>
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D148" s="0">
-        <x:v>11000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>50000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F148" s="0">
-        <x:v>50001023</x:v>
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G148" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>0.53</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>1.94</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="J148" s="0">
-        <x:v>5.03</x:v>
+        <x:v>8.23</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D149" s="0">
-        <x:v>5500000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>139000000</x:v>
+        <x:v>152000000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
         <x:v>13</x:v>
@@ -6512,7 +6530,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>1.76</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>0</x:v>
@@ -6520,101 +6538,101 @@
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>13064888</x:v>
+        <x:v>43000</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>30000000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>600000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="F150" s="0">
-        <x:v>268254173</x:v>
+        <x:v>1024885</x:v>
       </x:c>
       <x:c r="G150" s="0">
-        <x:v>0</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>41.6</x:v>
+        <x:v>23.96</x:v>
       </x:c>
       <x:c r="J150" s="0">
-        <x:v>20.53</x:v>
+        <x:v>23.83</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>111673026</x:v>
+        <x:v>9937037</x:v>
       </x:c>
       <x:c r="D151" s="0">
-        <x:v>150000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>500000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F151" s="0">
-        <x:v>500005947</x:v>
+        <x:v>50001023</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>11.84</x:v>
+        <x:v>1.91</x:v>
       </x:c>
       <x:c r="J151" s="0">
-        <x:v>4.48</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="K151" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D152" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="D152" s="0">
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>250000000</x:v>
+        <x:v>139000000</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G152" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H152" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>4</x:v>
+        <x:v>1.84</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>0</x:v>
@@ -6622,104 +6640,104 @@
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C153" s="0">
+        <x:v>13064888</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>19600000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>92000000</x:v>
-      </x:c>
-      <x:c r="F153" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F153" s="0">
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G153" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>4.37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J153" s="0">
-        <x:v>0</x:v>
+        <x:v>20.53</x:v>
+      </x:c>
+      <x:c r="K153" s="0" t="s">
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>1100000</x:v>
+        <x:v>111673026</x:v>
       </x:c>
       <x:c r="D154" s="0">
-        <x:v>2000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>100000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F154" s="0">
-        <x:v>56064346</x:v>
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G154" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>2</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>186.7</x:v>
+        <x:v>12.61</x:v>
       </x:c>
       <x:c r="J154" s="0">
-        <x:v>50.97</x:v>
+        <x:v>4.48</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C155" s="0">
-        <x:v>6598092</x:v>
-      </x:c>
-      <x:c r="D155" s="0">
-        <x:v>11160000</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F155" s="0">
-        <x:v>72091269</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F155" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G155" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>5.91</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>15.18</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="J155" s="0">
-        <x:v>10.93</x:v>
-      </x:c>
-      <x:c r="K155" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
@@ -6727,477 +6745,477 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C156" s="0">
-        <x:v>1590000</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D156" s="0">
-        <x:v>2160000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>35000000</x:v>
-      </x:c>
-      <x:c r="F156" s="0">
-        <x:v>60641600</x:v>
+        <x:v>92000000</x:v>
+      </x:c>
+      <x:c r="F156" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G156" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>0.91</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>32.42</x:v>
+        <x:v>4.21</x:v>
       </x:c>
       <x:c r="J156" s="0">
-        <x:v>38.14</x:v>
-      </x:c>
-      <x:c r="K156" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>1989802</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D157" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F157" s="0">
-        <x:v>78711752</x:v>
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G157" s="0">
-        <x:v>2.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>1.17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>112.7</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="J157" s="0">
-        <x:v>39.56</x:v>
+        <x:v>50.97</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C158" s="0">
+        <x:v>6598092</x:v>
       </x:c>
       <x:c r="D158" s="0">
-        <x:v>1000000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F158" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F158" s="0">
+        <x:v>72091269</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>0</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>470</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="J158" s="0">
-        <x:v>0</x:v>
+        <x:v>10.93</x:v>
+      </x:c>
+      <x:c r="K158" s="0" t="s">
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>300000</x:v>
+        <x:v>1590000</x:v>
       </x:c>
       <x:c r="D159" s="0">
-        <x:v>67500000</x:v>
+        <x:v>2160000</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>326000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="F159" s="0">
-        <x:v>1369300</x:v>
+        <x:v>60641600</x:v>
       </x:c>
       <x:c r="G159" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>4.71</x:v>
+        <x:v>32.74</x:v>
       </x:c>
       <x:c r="J159" s="0">
-        <x:v>4.56</x:v>
+        <x:v>38.14</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>77158759</x:v>
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D160" s="0">
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="E160" s="0">
         <x:v>250000000</x:v>
       </x:c>
-      <x:c r="E160" s="0">
-        <x:v>12000000000</x:v>
-      </x:c>
       <x:c r="F160" s="0">
-        <x:v>1987735371</x:v>
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G160" s="0">
-        <x:v>0</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>0.78</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>34.36</x:v>
+        <x:v>121.4</x:v>
       </x:c>
       <x:c r="J160" s="0">
-        <x:v>25.76</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="K160" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C161" s="0">
-        <x:v>8291656</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D161" s="0">
-        <x:v>11000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F161" s="0">
-        <x:v>126004459</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F161" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>14.63</x:v>
+        <x:v>443.25</x:v>
       </x:c>
       <x:c r="J161" s="0">
-        <x:v>15.2</x:v>
-      </x:c>
-      <x:c r="K161" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>2975773</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D162" s="0">
-        <x:v>6000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>150000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F162" s="0">
-        <x:v>44771095</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G162" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>22.18</x:v>
+        <x:v>4.85</x:v>
       </x:c>
       <x:c r="J162" s="0">
-        <x:v>15.05</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>11039823</x:v>
+        <x:v>77158759</x:v>
       </x:c>
       <x:c r="D163" s="0">
-        <x:v>21600000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>12000000000</x:v>
       </x:c>
       <x:c r="F163" s="0">
-        <x:v>183556428</x:v>
+        <x:v>1987735371</x:v>
       </x:c>
       <x:c r="G163" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>5.11</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>12.14</x:v>
+        <x:v>34.04</x:v>
       </x:c>
       <x:c r="J163" s="0">
-        <x:v>16.63</x:v>
+        <x:v>25.76</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>37920641</x:v>
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D164" s="0">
-        <x:v>195000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F164" s="0">
-        <x:v>432820590</x:v>
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G164" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>15.52</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="J164" s="0">
-        <x:v>11.41</x:v>
+        <x:v>15.2</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>5100000</x:v>
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D165" s="0">
-        <x:v>20000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>700000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F165" s="0">
-        <x:v>155318227</x:v>
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G165" s="0">
-        <x:v>6.81</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>0.93</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>49.38</x:v>
+        <x:v>22.06</x:v>
       </x:c>
       <x:c r="J165" s="0">
-        <x:v>30.45</x:v>
+        <x:v>15.05</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="C166" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="C166" s="0">
+        <x:v>11039823</x:v>
       </x:c>
       <x:c r="D166" s="0">
-        <x:v>300000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>700000000</x:v>
-      </x:c>
-      <x:c r="F166" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1200000000</x:v>
+      </x:c>
+      <x:c r="F166" s="0">
+        <x:v>183556428</x:v>
       </x:c>
       <x:c r="G166" s="0">
-        <x:v>6.67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>0</x:v>
+        <x:v>5.11</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>2.02</x:v>
+        <x:v>12.25</x:v>
       </x:c>
       <x:c r="J166" s="0">
-        <x:v>0</x:v>
+        <x:v>16.63</x:v>
+      </x:c>
+      <x:c r="K166" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>5000000</x:v>
+        <x:v>38590259</x:v>
       </x:c>
       <x:c r="D167" s="0">
-        <x:v>5000000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>50000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F167" s="0">
-        <x:v>39090077</x:v>
+        <x:v>442806603</x:v>
       </x:c>
       <x:c r="G167" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>0.21</x:v>
+        <x:v>1.98</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>9.49</x:v>
+        <x:v>15.95</x:v>
       </x:c>
       <x:c r="J167" s="0">
-        <x:v>7.82</x:v>
+        <x:v>11.47</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>905991</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D168" s="0">
-        <x:v>21000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>500000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F168" s="0">
-        <x:v>17447317</x:v>
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G168" s="0">
-        <x:v>3</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>14.85</x:v>
+        <x:v>51.75</x:v>
       </x:c>
       <x:c r="J168" s="0">
-        <x:v>19.26</x:v>
+        <x:v>30.45</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C169" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D169" s="0">
-        <x:v>11700000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>200000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G169" s="0">
-        <x:v>0</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H169" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>32.38</x:v>
+        <x:v>2.13</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>0</x:v>
@@ -7205,941 +7223,1043 @@
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="C170" s="0">
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="D170" s="0">
-        <x:v>1000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F170" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F170" s="0">
+        <x:v>39090077</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>0</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>470</x:v>
+        <x:v>9.41</x:v>
       </x:c>
       <x:c r="J170" s="0">
-        <x:v>0</x:v>
+        <x:v>7.82</x:v>
+      </x:c>
+      <x:c r="K170" s="0" t="s">
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>53584</x:v>
+        <x:v>905991</x:v>
       </x:c>
       <x:c r="D171" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>640000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F171" s="0">
-        <x:v>8271098</x:v>
+        <x:v>17447317</x:v>
       </x:c>
       <x:c r="G171" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>242</x:v>
+        <x:v>14.91</x:v>
       </x:c>
       <x:c r="J171" s="0">
-        <x:v>154.36</x:v>
+        <x:v>19.26</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="C172" s="0">
-        <x:v>7550000</x:v>
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D172" s="0">
-        <x:v>30000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F172" s="0">
-        <x:v>111777791</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F172" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>10.37</x:v>
+        <x:v>32.06</x:v>
       </x:c>
       <x:c r="J172" s="0">
-        <x:v>14.81</x:v>
-      </x:c>
-      <x:c r="K172" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="C173" s="0">
-        <x:v>2097716</x:v>
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D173" s="0">
-        <x:v>10112561</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>120000000</x:v>
-      </x:c>
-      <x:c r="F173" s="0">
-        <x:v>28985167</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F173" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G173" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>1.02</x:v>
+        <x:v>443.25</x:v>
       </x:c>
       <x:c r="J173" s="0">
-        <x:v>13.82</x:v>
-      </x:c>
-      <x:c r="K173" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:11">
       <x:c r="A174" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>5185302</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D174" s="0">
-        <x:v>57000000</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>513000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F174" s="0">
-        <x:v>37061183</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G174" s="0">
-        <x:v>5.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>5.33</x:v>
+        <x:v>240.7</x:v>
       </x:c>
       <x:c r="J174" s="0">
-        <x:v>7.15</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K174" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>669111</x:v>
+        <x:v>7550000</x:v>
       </x:c>
       <x:c r="D175" s="0">
-        <x:v>1000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>260000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F175" s="0">
-        <x:v>151220429</x:v>
+        <x:v>111777791</x:v>
       </x:c>
       <x:c r="G175" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>748.5</x:v>
+        <x:v>9.34</x:v>
       </x:c>
       <x:c r="J175" s="0">
-        <x:v>226</x:v>
+        <x:v>14.81</x:v>
       </x:c>
       <x:c r="K175" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:11">
       <x:c r="A176" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>38840</x:v>
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D176" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>270000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F176" s="0">
-        <x:v>9431791</x:v>
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G176" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>470</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="J176" s="0">
-        <x:v>242.84</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="K176" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:11">
       <x:c r="A177" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>2250000</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D177" s="0">
-        <x:v>20000000</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>300000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F177" s="0">
-        <x:v>31750000</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G177" s="0">
-        <x:v>4.98</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>10.37</x:v>
+        <x:v>5.23</x:v>
       </x:c>
       <x:c r="J177" s="0">
-        <x:v>14.11</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K177" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:11">
       <x:c r="A178" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>1500000</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D178" s="0">
-        <x:v>10112561</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E178" s="0">
-        <x:v>175000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F178" s="0">
-        <x:v>21870885</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G178" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H178" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>1.02</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="J178" s="0">
-        <x:v>14.58</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K178" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:11">
       <x:c r="A179" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>1656401</x:v>
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D179" s="0">
-        <x:v>8299326</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E179" s="0">
-        <x:v>600000000</x:v>
+        <x:v>270000000</x:v>
       </x:c>
       <x:c r="F179" s="0">
-        <x:v>229213803</x:v>
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G179" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H179" s="0">
-        <x:v>1.74</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>138.8</x:v>
+        <x:v>443.25</x:v>
       </x:c>
       <x:c r="J179" s="0">
-        <x:v>138.38</x:v>
+        <x:v>242.84</x:v>
       </x:c>
       <x:c r="K179" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:11">
       <x:c r="A180" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="C180" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="C180" s="0">
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D180" s="0">
-        <x:v>2500000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E180" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F180" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F180" s="0">
+        <x:v>31750000</x:v>
       </x:c>
       <x:c r="G180" s="0">
-        <x:v>2.7</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="H180" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>244.5</x:v>
+        <x:v>9.34</x:v>
       </x:c>
       <x:c r="J180" s="0">
-        <x:v>0</x:v>
+        <x:v>14.11</x:v>
+      </x:c>
+      <x:c r="K180" s="0" t="s">
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:11">
       <x:c r="A181" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>845945</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D181" s="0">
-        <x:v>15000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E181" s="0">
-        <x:v>250000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F181" s="0">
-        <x:v>10058606</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G181" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H181" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>2.78</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="J181" s="0">
-        <x:v>11.89</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K181" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:11">
       <x:c r="A182" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>21446</x:v>
+        <x:v>1656401</x:v>
       </x:c>
       <x:c r="D182" s="0">
-        <x:v>1000000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E182" s="0">
-        <x:v>200000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F182" s="0">
-        <x:v>2015907</x:v>
+        <x:v>229213803</x:v>
       </x:c>
       <x:c r="G182" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H182" s="0">
-        <x:v>0.03</x:v>
+        <x:v>1.74</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>38.92</x:v>
+        <x:v>145.9</x:v>
       </x:c>
       <x:c r="J182" s="0">
-        <x:v>94</x:v>
+        <x:v>138.38</x:v>
       </x:c>
       <x:c r="K182" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:11">
       <x:c r="A183" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="C183" s="0">
-        <x:v>1164369</x:v>
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D183" s="0">
-        <x:v>4250000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E183" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F183" s="0">
-        <x:v>8459528</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F183" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G183" s="0">
-        <x:v>5</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H183" s="0">
-        <x:v>1.37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>6.36</x:v>
+        <x:v>241.8</x:v>
       </x:c>
       <x:c r="J183" s="0">
-        <x:v>7.27</x:v>
-      </x:c>
-      <x:c r="K183" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:11">
       <x:c r="A184" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C184" s="0">
+        <x:v>845945</x:v>
+      </x:c>
+      <x:c r="D184" s="0">
         <x:v>15000000</x:v>
       </x:c>
-      <x:c r="D184" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
       <x:c r="E184" s="0">
-        <x:v>600000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F184" s="0">
-        <x:v>23990000</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G184" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H184" s="0">
-        <x:v>0.22</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>2.03</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="J184" s="0">
-        <x:v>1.6</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K184" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:11">
       <x:c r="A185" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>6397124</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D185" s="0">
-        <x:v>35300000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E185" s="0">
-        <x:v>1046645000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F185" s="0">
-        <x:v>122892213</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G185" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H185" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>3.4</x:v>
+        <x:v>39.22</x:v>
       </x:c>
       <x:c r="J185" s="0">
-        <x:v>19.21</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K185" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:11">
       <x:c r="A186" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>17495257</x:v>
+        <x:v>1164369</x:v>
       </x:c>
       <x:c r="D186" s="0">
-        <x:v>17500000</x:v>
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E186" s="0">
-        <x:v>525000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F186" s="0">
-        <x:v>409385433</x:v>
+        <x:v>8459528</x:v>
       </x:c>
       <x:c r="G186" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H186" s="0">
-        <x:v>5</x:v>
+        <x:v>1.37</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>15.75</x:v>
+        <x:v>6.37</x:v>
       </x:c>
       <x:c r="J186" s="0">
-        <x:v>23.4</x:v>
+        <x:v>7.27</x:v>
       </x:c>
       <x:c r="K186" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:11">
       <x:c r="A187" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>9350000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="D187" s="0">
-        <x:v>14710247</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E187" s="0">
-        <x:v>150000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F187" s="0">
-        <x:v>69547091</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G187" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H187" s="0">
-        <x:v>1.1</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I187" s="0">
-        <x:v>1.71</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="J187" s="0">
-        <x:v>7.44</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K187" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:11">
       <x:c r="A188" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D188" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>6397124</x:v>
+      </x:c>
+      <x:c r="D188" s="0">
+        <x:v>35300000</x:v>
       </x:c>
       <x:c r="E188" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1046645000</x:v>
       </x:c>
       <x:c r="F188" s="0">
-        <x:v>75911475</x:v>
+        <x:v>122892213</x:v>
       </x:c>
       <x:c r="G188" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H188" s="0">
-        <x:v>0.37</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I188" s="0">
-        <x:v>22.42</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="J188" s="0">
-        <x:v>51.7</x:v>
+        <x:v>19.21</x:v>
       </x:c>
       <x:c r="K188" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:11">
       <x:c r="A189" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>500000</x:v>
+        <x:v>17495257</x:v>
       </x:c>
       <x:c r="D189" s="0">
-        <x:v>2000000</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E189" s="0">
-        <x:v>60000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F189" s="0">
-        <x:v>13401783</x:v>
+        <x:v>409385433</x:v>
       </x:c>
       <x:c r="G189" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H189" s="0">
-        <x:v>0.08</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I189" s="0">
-        <x:v>2.13</x:v>
+        <x:v>15.5</x:v>
       </x:c>
       <x:c r="J189" s="0">
-        <x:v>26.8</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="K189" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:11">
       <x:c r="A190" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C190" s="0">
-        <x:v>725000</x:v>
+        <x:v>9350000</x:v>
       </x:c>
       <x:c r="D190" s="0">
-        <x:v>10000000</x:v>
+        <x:v>14710247</x:v>
       </x:c>
       <x:c r="E190" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F190" s="0">
-        <x:v>48539975</x:v>
+        <x:v>69547091</x:v>
       </x:c>
       <x:c r="G190" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H190" s="0">
-        <x:v>0.2</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I190" s="0">
-        <x:v>33.04</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="J190" s="0">
-        <x:v>66.95</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="K190" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:11">
       <x:c r="A191" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C191" s="0">
-        <x:v>1060056</x:v>
-      </x:c>
-      <x:c r="D191" s="0">
-        <x:v>7000000</x:v>
+        <x:v>1468255</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E191" s="0">
-        <x:v>250000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F191" s="0">
-        <x:v>60762934</x:v>
+        <x:v>75911475</x:v>
       </x:c>
       <x:c r="G191" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H191" s="0">
-        <x:v>0.44</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="I191" s="0">
-        <x:v>215.2</x:v>
+        <x:v>22.62</x:v>
       </x:c>
       <x:c r="J191" s="0">
-        <x:v>57.32</x:v>
+        <x:v>51.7</x:v>
       </x:c>
       <x:c r="K191" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:11">
       <x:c r="A192" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="C192" s="0">
-        <x:v>132750000</x:v>
-      </x:c>
-      <x:c r="D192" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="D192" s="0">
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E192" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F192" s="0">
-        <x:v>565141750</x:v>
+        <x:v>13401783</x:v>
       </x:c>
       <x:c r="G192" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H192" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I192" s="0">
-        <x:v>2.31</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="J192" s="0">
-        <x:v>4.26</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="K192" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:11">
       <x:c r="A193" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C193" s="0">
-        <x:v>373000</x:v>
+        <x:v>725000</x:v>
       </x:c>
       <x:c r="D193" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E193" s="0">
-        <x:v>75000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F193" s="0">
-        <x:v>23786370</x:v>
+        <x:v>48539975</x:v>
       </x:c>
       <x:c r="G193" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H193" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I193" s="0">
-        <x:v>5.43</x:v>
+        <x:v>33.88</x:v>
       </x:c>
       <x:c r="J193" s="0">
-        <x:v>63.77</x:v>
+        <x:v>66.95</x:v>
       </x:c>
       <x:c r="K193" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:11">
       <x:c r="A194" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C194" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1060056</x:v>
       </x:c>
       <x:c r="D194" s="0">
-        <x:v>10000000</x:v>
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="E194" s="0">
-        <x:v>140000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F194" s="0">
-        <x:v>133271568</x:v>
+        <x:v>60762934</x:v>
       </x:c>
       <x:c r="G194" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H194" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="I194" s="0">
-        <x:v>10.03</x:v>
+        <x:v>217.2</x:v>
       </x:c>
       <x:c r="J194" s="0">
-        <x:v>13.33</x:v>
+        <x:v>57.32</x:v>
       </x:c>
       <x:c r="K194" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:11">
       <x:c r="A195" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C195" s="0">
-        <x:v>66142950</x:v>
-      </x:c>
-      <x:c r="D195" s="0">
-        <x:v>105000000</x:v>
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E195" s="0">
-        <x:v>650000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F195" s="0">
-        <x:v>384952260</x:v>
+        <x:v>565141750</x:v>
       </x:c>
       <x:c r="G195" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H195" s="0">
-        <x:v>2.71</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I195" s="0">
-        <x:v>4.34</x:v>
+        <x:v>2.29</x:v>
       </x:c>
       <x:c r="J195" s="0">
-        <x:v>5.82</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="K195" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:11">
       <x:c r="A196" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C196" s="0">
+        <x:v>373000</x:v>
+      </x:c>
+      <x:c r="D196" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E196" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F196" s="0">
+        <x:v>23786370</x:v>
+      </x:c>
+      <x:c r="G196" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H196" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I196" s="0">
+        <x:v>5.56</x:v>
+      </x:c>
+      <x:c r="J196" s="0">
+        <x:v>63.77</x:v>
+      </x:c>
+      <x:c r="K196" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:11">
+      <x:c r="A197" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="C197" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="D197" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E197" s="0">
+        <x:v>140000000</x:v>
+      </x:c>
+      <x:c r="F197" s="0">
+        <x:v>133271568</x:v>
+      </x:c>
+      <x:c r="G197" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H197" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I197" s="0">
+        <x:v>9.03</x:v>
+      </x:c>
+      <x:c r="J197" s="0">
+        <x:v>13.33</x:v>
+      </x:c>
+      <x:c r="K197" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:11">
+      <x:c r="A198" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="B196" s="0" t="s">
+      <x:c r="C198" s="0">
+        <x:v>66142950</x:v>
+      </x:c>
+      <x:c r="D198" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="E198" s="0">
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F198" s="0">
+        <x:v>384952260</x:v>
+      </x:c>
+      <x:c r="G198" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H198" s="0">
+        <x:v>2.71</x:v>
+      </x:c>
+      <x:c r="I198" s="0">
+        <x:v>4.23</x:v>
+      </x:c>
+      <x:c r="J198" s="0">
+        <x:v>5.82</x:v>
+      </x:c>
+      <x:c r="K198" s="0" t="s">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="C196" s="0">
+    </x:row>
+    <x:row r="199" spans="1:11">
+      <x:c r="A199" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="C199" s="0">
         <x:v>3081843</x:v>
       </x:c>
-      <x:c r="D196" s="0">
+      <x:c r="D199" s="0">
         <x:v>5000000</x:v>
       </x:c>
-      <x:c r="E196" s="0">
+      <x:c r="E199" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F196" s="0">
+      <x:c r="F199" s="0">
         <x:v>43986444</x:v>
       </x:c>
-      <x:c r="G196" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H196" s="0">
+      <x:c r="G199" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H199" s="0">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="I196" s="0">
-        <x:v>5.07</x:v>
-      </x:c>
-      <x:c r="J196" s="0">
+      <x:c r="I199" s="0">
+        <x:v>5.1</x:v>
+      </x:c>
+      <x:c r="J199" s="0">
         <x:v>14.27</x:v>
       </x:c>
-      <x:c r="K196" s="0" t="s">
-        <x:v>288</x:v>
+      <x:c r="K199" s="0" t="s">
+        <x:v>290</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -49,18 +49,36 @@
     <x:t>Son İşlem Tarihi</x:t>
   </x:si>
   <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>NTHOL</x:t>
   </x:si>
   <x:si>
     <x:t>23.09.2026</x:t>
   </x:si>
   <x:si>
-    <x:t/>
+    <x:t>BLCYT</x:t>
   </x:si>
   <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
     <x:t>CGCAM</x:t>
   </x:si>
   <x:si>
@@ -400,9 +418,6 @@
     <x:t>27.01.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>24.07.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>23.01.2026</x:t>
   </x:si>
   <x:si>
@@ -769,9 +784,6 @@
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>30.09.2025</x:t>
   </x:si>
   <x:si>
@@ -830,9 +842,6 @@
   </x:si>
   <x:si>
     <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.12.2025</x:t>
   </x:si>
   <x:si>
     <x:t>MHRGY</x:t>
@@ -1426,7 +1435,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K207"/>
+  <x:dimension ref="A1:K212"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:11">
@@ -1475,22 +1484,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>25000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>1200000000</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>5</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="H2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>38.24</x:v>
+        <x:v>4.45</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1507,22 +1516,22 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>10000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>50000000</x:v>
+        <x:v>315000000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>6.29</x:v>
+        <x:v>101.6</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>0</x:v>
@@ -1533,60 +1542,63 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>6000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>84000000</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1200000000</x:v>
+      </x:c>
+      <x:c r="F4" s="0">
+        <x:v>15630999</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>3.57</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>23.62</x:v>
+        <x:v>36.86</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>0</x:v>
+        <x:v>39.08</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>50000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>200000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>5.58</x:v>
+        <x:v>1.79</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1594,37 +1606,34 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>70000</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>30000000</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>2241140</x:v>
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>35.96</x:v>
+        <x:v>6.12</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>32.02</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -1632,28 +1641,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>33000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>100000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>7</x:v>
+        <x:v>10.01</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>0</x:v>
@@ -1664,16 +1673,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>50000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>13</x:v>
@@ -1685,7 +1694,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>34.96</x:v>
+        <x:v>15.91</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>0</x:v>
@@ -1696,101 +1705,101 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>1950000</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>125000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F9" s="0">
-        <x:v>14457300</x:v>
+        <x:v>84000000</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.78</x:v>
+        <x:v>3.57</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>6.74</x:v>
+        <x:v>22.24</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>7.41</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>2712539</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>5000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F10" s="0">
+        <x:v>14582610</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.92</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>0</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>56.9</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>0</x:v>
+        <x:v>5.38</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="C11" s="0">
-        <x:v>157000</x:v>
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>15000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>624470</x:v>
+        <x:v>4266108</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>3.86</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>3.98</x:v>
+        <x:v>32.82</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -1798,34 +1807,31 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>46500000</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>500000000</x:v>
+        <x:v>33000000</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F12" s="0">
-        <x:v>90814500</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>11.11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>1.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>2.34</x:v>
+        <x:v>6.61</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>1.95</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1833,34 +1839,34 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>2000000</x:v>
+        <x:v>292129</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>21000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>100000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>8120000</x:v>
+        <x:v>10093057</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>3.47</x:v>
+        <x:v>31.6</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>4.06</x:v>
+        <x:v>34.55</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
@@ -1868,139 +1874,136 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>595000</x:v>
+        <x:v>2775000</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>10000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>100000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>5009900</x:v>
+        <x:v>20438550</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>0.07</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>8.68</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>8.42</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>40000</x:v>
+      <x:c r="C15" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>4000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F15" s="0">
-        <x:v>992800</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>23.86</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>24.82</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>375298</x:v>
+        <x:v>400150</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>12000000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>600000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>13716692</x:v>
+        <x:v>1526926</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0.07</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>38.56</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>36.55</x:v>
+        <x:v>3.82</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>1000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>4200000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>45000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>8865394</x:v>
+        <x:v>214078500</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0</x:v>
+        <x:v>11.11</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>2.38</x:v>
+        <x:v>2.22</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>8.8</x:v>
+        <x:v>2.33</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>8.87</x:v>
+        <x:v>2.14</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
@@ -2008,34 +2011,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>6000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>50000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>5948224</x:v>
+        <x:v>8120000</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>5.5</x:v>
+        <x:v>3.13</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>5.95</x:v>
+        <x:v>4.06</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -2043,34 +2046,34 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>2095179</x:v>
+        <x:v>1170000</x:v>
       </x:c>
       <x:c r="D19" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E19" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="E19" s="0">
-        <x:v>700000000</x:v>
-      </x:c>
       <x:c r="F19" s="0">
-        <x:v>10933313</x:v>
+        <x:v>9983650</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>5.22</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>5.22</x:v>
+        <x:v>8.53</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -2078,31 +2081,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>5000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F20" s="0">
+        <x:v>992800</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>38.48</x:v>
+        <x:v>22.44</x:v>
       </x:c>
       <x:c r="J20" s="0">
-        <x:v>0</x:v>
+        <x:v>24.82</x:v>
+      </x:c>
+      <x:c r="K20" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -2110,34 +2116,34 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>210000</x:v>
+        <x:v>375298</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>10000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>21924000</x:v>
+        <x:v>13716692</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>84.6</x:v>
+        <x:v>38.28</x:v>
       </x:c>
       <x:c r="J21" s="0">
-        <x:v>104.4</x:v>
+        <x:v>36.55</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -2148,31 +2154,31 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>3000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>60000000</x:v>
+        <x:v>4200000</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>200000000</x:v>
+        <x:v>45000000</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>7177500</x:v>
+        <x:v>8865394</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>0.08</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>2.49</x:v>
+        <x:v>8.46</x:v>
       </x:c>
       <x:c r="J22" s="0">
-        <x:v>2.39</x:v>
+        <x:v>8.87</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -2183,31 +2189,31 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>2591614</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D23" s="0">
+        <x:v>6000000</x:v>
+      </x:c>
+      <x:c r="E23" s="0">
         <x:v>50000000</x:v>
       </x:c>
-      <x:c r="E23" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
       <x:c r="F23" s="0">
-        <x:v>104806039</x:v>
+        <x:v>5948224</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>44.2</x:v>
+        <x:v>5.36</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>40.44</x:v>
+        <x:v>5.95</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -2218,31 +2224,31 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>23412270</x:v>
+        <x:v>2095179</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>180000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>700000000</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>292660856</x:v>
+        <x:v>10933313</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>13.03</x:v>
+        <x:v>4.97</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>12.5</x:v>
+        <x:v>5.22</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -2253,31 +2259,31 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>176000</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>25000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>4034608</x:v>
+        <x:v>938880</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>4.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>22.76</x:v>
+        <x:v>37.12</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>22.92</x:v>
+        <x:v>39.12</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -2288,31 +2294,31 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>2360000</x:v>
+        <x:v>210000</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>50000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>200000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>5003983</x:v>
+        <x:v>21924000</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>0.39</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>1.95</x:v>
+        <x:v>93.05</x:v>
       </x:c>
       <x:c r="J26" s="0">
-        <x:v>2.12</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -2320,101 +2326,104 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>3600000</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>9260000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>1200000000</x:v>
-      </x:c>
-      <x:c r="F27" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F27" s="0">
+        <x:v>8671500</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>10</x:v>
+        <x:v>1.54</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>0</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>94.4</x:v>
+        <x:v>2.44</x:v>
       </x:c>
       <x:c r="J27" s="0">
-        <x:v>0</x:v>
+        <x:v>2.41</x:v>
+      </x:c>
+      <x:c r="K27" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="C28" s="0">
-        <x:v>492277</x:v>
+        <x:v>2621614</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2500000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>225000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>34896577</x:v>
+        <x:v>106123939</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>76.6</x:v>
+        <x:v>44.24</x:v>
       </x:c>
       <x:c r="J28" s="0">
-        <x:v>70.89</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>300000</x:v>
+        <x:v>23412270</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>39725600</x:v>
+        <x:v>180000000</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>11018400</x:v>
+        <x:v>292660856</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>38.78</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>36.73</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -2422,1827 +2431,1830 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>1747427</x:v>
+        <x:v>276000</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>12000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>1750000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>266091792</x:v>
+        <x:v>6330908</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0</x:v>
+        <x:v>4.84</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>0.66</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>121.5</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>152.28</x:v>
+        <x:v>22.94</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>105000</x:v>
+        <x:v>2360000</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>300000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>30022828</x:v>
+        <x:v>5003983</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>275</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="J31" s="0">
-        <x:v>285.93</x:v>
+        <x:v>2.12</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>522511</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2850000</x:v>
+        <x:v>9260000</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F32" s="0">
-        <x:v>15590102</x:v>
+        <x:v>1200000000</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2.41</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0.44</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>30.84</x:v>
+        <x:v>88.55</x:v>
       </x:c>
       <x:c r="J32" s="0">
-        <x:v>29.84</x:v>
-      </x:c>
-      <x:c r="K32" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C33" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>612277</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>20000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>2500000000</x:v>
-      </x:c>
-      <x:c r="F33" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>225000000</x:v>
+      </x:c>
+      <x:c r="F33" s="0">
+        <x:v>44160577</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>54.5</x:v>
+        <x:v>74.3</x:v>
       </x:c>
       <x:c r="J33" s="0">
-        <x:v>0</x:v>
+        <x:v>72.13</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>10000000</x:v>
+        <x:v>39725600</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F34" s="0">
+        <x:v>14866400</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>6.89</x:v>
+        <x:v>37.52</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>0</x:v>
+        <x:v>37.17</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>12450000</x:v>
+        <x:v>1747427</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>96033600</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>650000000</x:v>
+        <x:v>1750000000</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>60880500</x:v>
+        <x:v>266091792</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>1.31</x:v>
+        <x:v>133.6</x:v>
       </x:c>
       <x:c r="J35" s="0">
-        <x:v>4.89</x:v>
+        <x:v>152.28</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>479103</x:v>
+        <x:v>109925</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>36000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>250000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>2606320</x:v>
+        <x:v>31377203</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>5.66</x:v>
+        <x:v>268.75</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>5.44</x:v>
+        <x:v>285.44</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>915789</x:v>
+        <x:v>556084</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>15000000</x:v>
+        <x:v>2850000</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>150000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>7785618</x:v>
+        <x:v>16629858</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>3</x:v>
+        <x:v>2.41</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.47</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>7.85</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>8.5</x:v>
+        <x:v>29.91</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>3700000</x:v>
+        <x:v>375000</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>13500000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>400000000</x:v>
+        <x:v>2500000000</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>61627000</x:v>
+        <x:v>20259375</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>1.85</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>16.26</x:v>
+        <x:v>54.55</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>16.66</x:v>
+        <x:v>54.03</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>20746859</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>30000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>210000000</x:v>
-      </x:c>
-      <x:c r="F39" s="0">
-        <x:v>145013995</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>3.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>5.16</x:v>
+        <x:v>6.93</x:v>
       </x:c>
       <x:c r="J39" s="0">
-        <x:v>6.99</x:v>
-      </x:c>
-      <x:c r="K39" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>11397816</x:v>
+        <x:v>12450000</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>15000000</x:v>
+        <x:v>96033600</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>650000000</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>269900283</x:v>
+        <x:v>60880500</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>10.44</x:v>
+        <x:v>1.18</x:v>
       </x:c>
       <x:c r="J40" s="0">
-        <x:v>23.68</x:v>
+        <x:v>4.89</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>4000000</x:v>
+        <x:v>479103</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>50000000</x:v>
+        <x:v>36000000</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>500000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>21195000</x:v>
+        <x:v>2606320</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.05</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>4.15</x:v>
+        <x:v>5.68</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>5.3</x:v>
+        <x:v>5.44</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>2300000</x:v>
+        <x:v>915789</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>12000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>12000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>1739216</x:v>
+        <x:v>7785618</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>3.83</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>10.6</x:v>
+        <x:v>7.41</x:v>
       </x:c>
       <x:c r="J42" s="0">
-        <x:v>0.76</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>4790000</x:v>
+        <x:v>5700000</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>12000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>12000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>7029498</x:v>
+        <x:v>92827000</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>7.98</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>3.73</x:v>
+        <x:v>16.21</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>1.47</x:v>
+        <x:v>16.29</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>4850000</x:v>
+        <x:v>20746859</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>12000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>12000000</x:v>
+        <x:v>210000000</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>3543837</x:v>
+        <x:v>145013995</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>8.08</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>8.32</x:v>
+        <x:v>5.16</x:v>
       </x:c>
       <x:c r="J44" s="0">
-        <x:v>0.73</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>111250</x:v>
+        <x:v>11397816</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>2000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>250000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>6994999</x:v>
+        <x:v>269900283</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>59.45</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="J45" s="0">
-        <x:v>62.88</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>30000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="D46" s="0">
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="E46" s="0">
         <x:v>500000000</x:v>
       </x:c>
-      <x:c r="E46" s="0">
-        <x:v>750000000</x:v>
-      </x:c>
       <x:c r="F46" s="0">
-        <x:v>36200000</x:v>
+        <x:v>21195000</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.99</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J46" s="0">
-        <x:v>1.21</x:v>
+        <x:v>5.3</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>2300000</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>150000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>33000000</x:v>
-      </x:c>
-      <x:c r="F47" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12000000</x:v>
+      </x:c>
+      <x:c r="F47" s="0">
+        <x:v>1739216</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>0</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>91.25</x:v>
+        <x:v>9.54</x:v>
       </x:c>
       <x:c r="J47" s="0">
-        <x:v>0</x:v>
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="K47" s="0" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>100000</x:v>
+        <x:v>4790000</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>50000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>500000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>613000</x:v>
+        <x:v>7029498</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>0.01</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>4.03</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="J48" s="0">
-        <x:v>6.13</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>10366031</x:v>
+        <x:v>4850000</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>25000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>240000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>102614742</x:v>
+        <x:v>3543837</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>0.43</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>9.47</x:v>
+        <x:v>9.15</x:v>
       </x:c>
       <x:c r="J49" s="0">
-        <x:v>9.9</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>1800452</x:v>
+        <x:v>111250</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>15000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>150000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>17447883</x:v>
+        <x:v>6994999</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>7.85</x:v>
+        <x:v>58.6</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>9.69</x:v>
+        <x:v>62.88</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>55000</x:v>
+        <x:v>30352652</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>13409218</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>500000000</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>881400</x:v>
+        <x:v>36549125</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>9.01</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>15.8</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>16.03</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C52" s="0">
-        <x:v>6550000</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>55000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F52" s="0">
-        <x:v>9962550</x:v>
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>5.09</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>0.61</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>1.5</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J52" s="0">
-        <x:v>1.52</x:v>
-      </x:c>
-      <x:c r="K52" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>300000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>25000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>415500000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>4769662</x:v>
+        <x:v>613000</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>0</x:v>
+        <x:v>5.26</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>16.01</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="J53" s="0">
-        <x:v>15.9</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>6997674</x:v>
+        <x:v>10366031</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>40000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>128412350</x:v>
+        <x:v>102614742</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>13.92</x:v>
+        <x:v>9.47</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>18.35</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>15160028</x:v>
+        <x:v>1800452</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>60000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>250000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>54496310</x:v>
+        <x:v>17447883</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>0.86</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>3.85</x:v>
+        <x:v>7.41</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>3.59</x:v>
+        <x:v>9.69</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>2500000</x:v>
+        <x:v>92745</x:v>
       </x:c>
       <x:c r="D56" s="0">
-        <x:v>2500000</x:v>
+        <x:v>13409218</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>950421206</x:v>
+        <x:v>1475411</x:v>
       </x:c>
       <x:c r="G56" s="0">
-        <x:v>0</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>433.75</x:v>
+        <x:v>14.79</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>380.17</x:v>
+        <x:v>15.91</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>220399</x:v>
+        <x:v>8550000</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>230000</x:v>
+        <x:v>55000000</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>15000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F57" s="0">
-        <x:v>15186997</x:v>
+        <x:v>12994550</x:v>
       </x:c>
       <x:c r="G57" s="0">
-        <x:v>1.66</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>1.59</x:v>
+        <x:v>0.79</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>60.1</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>68.91</x:v>
+        <x:v>1.52</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>2501710</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D58" s="0">
-        <x:v>10000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>450000000</x:v>
+        <x:v>415500000</x:v>
       </x:c>
       <x:c r="F58" s="0">
-        <x:v>97116052</x:v>
+        <x:v>4769662</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>25.32</x:v>
+        <x:v>15.83</x:v>
       </x:c>
       <x:c r="J58" s="0">
-        <x:v>38.82</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>59711016</x:v>
+        <x:v>6997674</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>85125000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>5000000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F59" s="0">
-        <x:v>2882965334</x:v>
+        <x:v>128412350</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>1.86</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>50.15</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="J59" s="0">
-        <x:v>48.28</x:v>
+        <x:v>18.35</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>69686718</x:v>
+        <x:v>15160028</x:v>
       </x:c>
       <x:c r="D60" s="0">
-        <x:v>25000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F60" s="0">
-        <x:v>2290434265</x:v>
+        <x:v>54496310</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>2.36</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>19.88</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="J60" s="0">
-        <x:v>32.87</x:v>
+        <x:v>3.59</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>100000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="D61" s="0">
-        <x:v>3000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>40000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F61" s="0">
-        <x:v>1365000</x:v>
+        <x:v>950421206</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>14.07</x:v>
+        <x:v>422.75</x:v>
       </x:c>
       <x:c r="J61" s="0">
-        <x:v>13.65</x:v>
+        <x:v>380.17</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>7999148</x:v>
+        <x:v>220399</x:v>
       </x:c>
       <x:c r="D62" s="0">
+        <x:v>230000</x:v>
+      </x:c>
+      <x:c r="E62" s="0">
         <x:v>15000000</x:v>
       </x:c>
-      <x:c r="E62" s="0">
-        <x:v>300000000</x:v>
-      </x:c>
       <x:c r="F62" s="0">
-        <x:v>168715651</x:v>
+        <x:v>15186997</x:v>
       </x:c>
       <x:c r="G62" s="0">
-        <x:v>0</x:v>
+        <x:v>1.66</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>2.11</x:v>
+        <x:v>1.59</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>17.02</x:v>
+        <x:v>54.1</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>21.09</x:v>
+        <x:v>68.91</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>201000</x:v>
+        <x:v>2501710</x:v>
       </x:c>
       <x:c r="D63" s="0">
-        <x:v>21739600</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>350000000</x:v>
+        <x:v>450000000</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>2071755</x:v>
+        <x:v>97116052</x:v>
       </x:c>
       <x:c r="G63" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>8.91</x:v>
+        <x:v>26.6</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>10.31</x:v>
+        <x:v>38.82</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C64" s="0">
+        <x:v>59711016</x:v>
       </x:c>
       <x:c r="D64" s="0">
-        <x:v>1500000000</x:v>
+        <x:v>85125000</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>1500000000</x:v>
-      </x:c>
-      <x:c r="F64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>5000000000</x:v>
+      </x:c>
+      <x:c r="F64" s="0">
+        <x:v>2882965334</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>8.52</x:v>
+        <x:v>48.4</x:v>
       </x:c>
       <x:c r="J64" s="0">
-        <x:v>0</x:v>
+        <x:v>48.28</x:v>
+      </x:c>
+      <x:c r="K64" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>3070328</x:v>
+        <x:v>69686718</x:v>
       </x:c>
       <x:c r="D65" s="0">
-        <x:v>10000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>65000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F65" s="0">
-        <x:v>21421330</x:v>
+        <x:v>2290434265</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0.57</x:v>
+        <x:v>2.36</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>6.8</x:v>
+        <x:v>17.9</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>6.98</x:v>
+        <x:v>32.87</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C66" s="0">
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="D66" s="0">
-        <x:v>26398084</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F66" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>40000000</x:v>
+      </x:c>
+      <x:c r="F66" s="0">
+        <x:v>1365000</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>121.5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J66" s="0">
-        <x:v>0</x:v>
+        <x:v>13.65</x:v>
+      </x:c>
+      <x:c r="K66" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>17879000</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>7999148</x:v>
+      </x:c>
+      <x:c r="D67" s="0">
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>127481195</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>0.82</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>14.26</x:v>
+        <x:v>16.45</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>7.13</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>970810</x:v>
+        <x:v>201000</x:v>
       </x:c>
       <x:c r="D68" s="0">
-        <x:v>7300000</x:v>
+        <x:v>21739600</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>225000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F68" s="0">
-        <x:v>28043898</x:v>
+        <x:v>2071755</x:v>
       </x:c>
       <x:c r="G68" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>21.12</x:v>
+        <x:v>8.55</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>28.89</x:v>
+        <x:v>10.31</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C69" s="0">
-        <x:v>1001579</x:v>
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D69" s="0">
-        <x:v>10000000</x:v>
+        <x:v>1500000000</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F69" s="0">
-        <x:v>15106723</x:v>
+        <x:v>1500000000</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G69" s="0">
-        <x:v>2.56</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>7.75</x:v>
+        <x:v>8.35</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>15.08</x:v>
-      </x:c>
-      <x:c r="K69" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C70" s="0">
+        <x:v>3070328</x:v>
       </x:c>
       <x:c r="D70" s="0">
-        <x:v>40000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F70" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>65000000</x:v>
+      </x:c>
+      <x:c r="F70" s="0">
+        <x:v>21421330</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>0</x:v>
+        <x:v>0.57</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>4.19</x:v>
+        <x:v>6.49</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>0</x:v>
+        <x:v>6.98</x:v>
+      </x:c>
+      <x:c r="K70" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C71" s="0">
-        <x:v>2097370</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D71" s="0">
-        <x:v>2000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="F71" s="0">
-        <x:v>48772185</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>2.78</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>21.9</x:v>
+        <x:v>133.6</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>23.25</x:v>
-      </x:c>
-      <x:c r="K71" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>29346813</x:v>
-      </x:c>
-      <x:c r="D72" s="0">
-        <x:v>80000000</x:v>
+        <x:v>17879000</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E72" s="0">
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F72" s="0">
-        <x:v>826937156</x:v>
+        <x:v>127481195</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>1.13</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>44.2</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="J72" s="0">
-        <x:v>28.18</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>7024156</x:v>
+        <x:v>970810</x:v>
       </x:c>
       <x:c r="D73" s="0">
-        <x:v>80000000</x:v>
+        <x:v>7300000</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>225000000</x:v>
       </x:c>
       <x:c r="F73" s="0">
-        <x:v>93719334</x:v>
+        <x:v>28043898</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>9.96</x:v>
+        <x:v>20.6</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>13.34</x:v>
+        <x:v>28.89</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>3500000</x:v>
+        <x:v>1001579</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>49400000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>137144284</x:v>
+        <x:v>15106723</x:v>
       </x:c>
       <x:c r="G74" s="0">
-        <x:v>10</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>22.56</x:v>
+        <x:v>7.35</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>39.18</x:v>
+        <x:v>15.08</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>3753472</x:v>
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D75" s="0">
-        <x:v>6000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>432000000</x:v>
-      </x:c>
-      <x:c r="F75" s="0">
-        <x:v>224929072</x:v>
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>55</x:v>
+        <x:v>4.06</x:v>
       </x:c>
       <x:c r="J75" s="0">
-        <x:v>59.93</x:v>
-      </x:c>
-      <x:c r="K75" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>3189049</x:v>
+        <x:v>2099706</x:v>
       </x:c>
       <x:c r="D76" s="0">
-        <x:v>4000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>400000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F76" s="0">
-        <x:v>154328962</x:v>
+        <x:v>48823343</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>3.74</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>0.6</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>4.16</x:v>
+        <x:v>23.06</x:v>
       </x:c>
       <x:c r="J76" s="0">
-        <x:v>48.39</x:v>
+        <x:v>23.25</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C77" s="0">
+        <x:v>29346813</x:v>
       </x:c>
       <x:c r="D77" s="0">
-        <x:v>35000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>150000000</x:v>
-      </x:c>
-      <x:c r="F77" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F77" s="0">
+        <x:v>826937156</x:v>
       </x:c>
       <x:c r="G77" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>0</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>2.37</x:v>
+        <x:v>44.24</x:v>
       </x:c>
       <x:c r="J77" s="0">
-        <x:v>0</x:v>
+        <x:v>28.18</x:v>
+      </x:c>
+      <x:c r="K77" s="0" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>5450000</x:v>
+        <x:v>7024156</x:v>
       </x:c>
       <x:c r="D78" s="0">
-        <x:v>10000000</x:v>
+        <x:v>80000000</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>400000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F78" s="0">
-        <x:v>197774213</x:v>
+        <x:v>93719334</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>0.66</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>11.52</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="J78" s="0">
-        <x:v>36.29</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>21416071</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="D79" s="0">
-        <x:v>35000000</x:v>
+        <x:v>49400000</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>300000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F79" s="0">
-        <x:v>186756128</x:v>
+        <x:v>137144284</x:v>
       </x:c>
       <x:c r="G79" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>5.35</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>6.1</x:v>
+        <x:v>24.8</x:v>
       </x:c>
       <x:c r="J79" s="0">
-        <x:v>8.72</x:v>
+        <x:v>39.18</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>236122</x:v>
+        <x:v>3753472</x:v>
       </x:c>
       <x:c r="D80" s="0">
-        <x:v>1700000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>110000000</x:v>
+        <x:v>432000000</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>14609667</x:v>
+        <x:v>224929072</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>36.46</x:v>
+        <x:v>52.6</x:v>
       </x:c>
       <x:c r="J80" s="0">
-        <x:v>61.87</x:v>
+        <x:v>59.93</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>1000000</x:v>
+        <x:v>3189049</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>17500000</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>4000000</x:v>
+      </x:c>
+      <x:c r="E81" s="0">
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>21055375</x:v>
+        <x:v>154328962</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>0.29</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>15.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J81" s="0">
-        <x:v>21.06</x:v>
+        <x:v>48.39</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D82" s="0">
-        <x:v>2000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>200000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G82" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H82" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>4.16</x:v>
+        <x:v>2.28</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>0</x:v>
@@ -4250,996 +4262,999 @@
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>105404634</x:v>
+        <x:v>5550000</x:v>
       </x:c>
       <x:c r="D83" s="0">
-        <x:v>200000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F83" s="0">
-        <x:v>1032884452</x:v>
+        <x:v>198926213</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>13.03</x:v>
+        <x:v>10.37</x:v>
       </x:c>
       <x:c r="J83" s="0">
-        <x:v>9.8</x:v>
+        <x:v>35.84</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>16445115</x:v>
+        <x:v>21579841</x:v>
       </x:c>
       <x:c r="D84" s="0">
-        <x:v>25000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>500000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>393919718</x:v>
+        <x:v>187755700</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>3.29</x:v>
+        <x:v>5.39</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>24.52</x:v>
+        <x:v>5.61</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>23.95</x:v>
+        <x:v>8.7</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>1110000</x:v>
+        <x:v>236122</x:v>
       </x:c>
       <x:c r="D85" s="0">
-        <x:v>2000000</x:v>
+        <x:v>1700000</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>1100000000</x:v>
+        <x:v>110000000</x:v>
       </x:c>
       <x:c r="F85" s="0">
-        <x:v>587039028</x:v>
+        <x:v>14609667</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>433.75</x:v>
+        <x:v>32.82</x:v>
       </x:c>
       <x:c r="J85" s="0">
-        <x:v>528.86</x:v>
+        <x:v>61.87</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>24398659</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D86" s="0">
-        <x:v>40000000</x:v>
-      </x:c>
-      <x:c r="E86" s="0">
-        <x:v>850000000</x:v>
+        <x:v>17500000</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F86" s="0">
-        <x:v>590270273</x:v>
+        <x:v>21055375</x:v>
       </x:c>
       <x:c r="G86" s="0">
-        <x:v>0</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>44.2</x:v>
+        <x:v>15.43</x:v>
       </x:c>
       <x:c r="J86" s="0">
-        <x:v>24.19</x:v>
+        <x:v>21.06</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="C87" s="0">
-        <x:v>46563878</x:v>
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D87" s="0">
-        <x:v>50000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F87" s="0">
-        <x:v>500007798</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>13.03</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J87" s="0">
-        <x:v>10.74</x:v>
-      </x:c>
-      <x:c r="K87" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>6611571</x:v>
+        <x:v>105404634</x:v>
       </x:c>
       <x:c r="D88" s="0">
-        <x:v>9000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>240000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F88" s="0">
-        <x:v>39750803</x:v>
+        <x:v>1032884452</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>0.69</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>5.66</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="J88" s="0">
-        <x:v>6.01</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>2796120</x:v>
+        <x:v>16445115</x:v>
       </x:c>
       <x:c r="D89" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="E89" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="E89" s="0">
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F89" s="0">
-        <x:v>68939196</x:v>
+        <x:v>393919718</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>1.47</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>15.2</x:v>
+        <x:v>22.08</x:v>
       </x:c>
       <x:c r="J89" s="0">
-        <x:v>24.66</x:v>
+        <x:v>23.95</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1110000</x:v>
       </x:c>
       <x:c r="D90" s="0">
-        <x:v>30000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>400000000</x:v>
+        <x:v>1100000000</x:v>
       </x:c>
       <x:c r="F90" s="0">
-        <x:v>4455000</x:v>
+        <x:v>587039028</x:v>
       </x:c>
       <x:c r="G90" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>4.11</x:v>
+        <x:v>422.75</x:v>
       </x:c>
       <x:c r="J90" s="0">
-        <x:v>4.46</x:v>
+        <x:v>528.86</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>200000</x:v>
+        <x:v>24398659</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>13760000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>300000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F91" s="0">
-        <x:v>2564000</x:v>
+        <x:v>590270273</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>5.16</x:v>
+        <x:v>44.24</x:v>
       </x:c>
       <x:c r="J91" s="0">
-        <x:v>12.82</x:v>
+        <x:v>24.19</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C92" s="0">
+        <x:v>46563878</x:v>
       </x:c>
       <x:c r="D92" s="0">
-        <x:v>30000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F92" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F92" s="0">
+        <x:v>500007798</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>25.72</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>0</x:v>
+        <x:v>10.74</x:v>
+      </x:c>
+      <x:c r="K92" s="0" t="s">
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>5831653</x:v>
+        <x:v>6611571</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>5000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>500000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>304086107</x:v>
+        <x:v>39750803</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>2.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0.83</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>2.07</x:v>
+        <x:v>5.68</x:v>
       </x:c>
       <x:c r="J93" s="0">
-        <x:v>52.14</x:v>
+        <x:v>6.01</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>14512000</x:v>
+        <x:v>2816120</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>79451200</x:v>
-      </x:c>
-      <x:c r="E94" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F94" s="0">
-        <x:v>575005862</x:v>
+        <x:v>69240896</x:v>
       </x:c>
       <x:c r="G94" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>1.83</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>38.78</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="J94" s="0">
-        <x:v>39.62</x:v>
+        <x:v>24.59</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>5829828</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D95" s="0">
-        <x:v>3000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>300000000</x:v>
+        <x:v>400000000</x:v>
       </x:c>
       <x:c r="F95" s="0">
-        <x:v>222446644</x:v>
+        <x:v>4455000</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>3.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>1.46</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>22.9</x:v>
+        <x:v>4.08</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>38.16</x:v>
+        <x:v>4.46</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D96" s="0">
-        <x:v>15000000</x:v>
+        <x:v>13760000</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>600000000</x:v>
-      </x:c>
-      <x:c r="F96" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F96" s="0">
+        <x:v>2564000</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>5.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>0</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>20.64</x:v>
+        <x:v>5.16</x:v>
       </x:c>
       <x:c r="J96" s="0">
-        <x:v>0</x:v>
+        <x:v>12.82</x:v>
+      </x:c>
+      <x:c r="K96" s="0" t="s">
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C97" s="0">
-        <x:v>8337681</x:v>
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>6500000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F97" s="0">
-        <x:v>37235183</x:v>
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>1.43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>2.76</x:v>
+        <x:v>24.42</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>4.47</x:v>
-      </x:c>
-      <x:c r="K97" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>400000</x:v>
+        <x:v>5831653</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>9275000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>950000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F98" s="0">
-        <x:v>13352000</x:v>
+        <x:v>304086107</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>0</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>0.11</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>33.76</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>33.38</x:v>
+        <x:v>52.14</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>1364000</x:v>
+        <x:v>14512000</x:v>
       </x:c>
       <x:c r="D99" s="0">
-        <x:v>23460000</x:v>
+        <x:v>79451200</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>9000000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F99" s="0">
-        <x:v>409075556</x:v>
+        <x:v>575005862</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>1.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>298.5</x:v>
+        <x:v>37.52</x:v>
       </x:c>
       <x:c r="J99" s="0">
-        <x:v>299.91</x:v>
+        <x:v>39.62</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="C100" s="0">
+        <x:v>5829828</x:v>
       </x:c>
       <x:c r="D100" s="0">
-        <x:v>380000000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F100" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>300000000</x:v>
+      </x:c>
+      <x:c r="F100" s="0">
+        <x:v>222446644</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>10</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>0</x:v>
+        <x:v>1.46</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>19.9</x:v>
+        <x:v>22.56</x:v>
       </x:c>
       <x:c r="J100" s="0">
-        <x:v>0</x:v>
+        <x:v>38.16</x:v>
+      </x:c>
+      <x:c r="K100" s="0" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="C101" s="0">
-        <x:v>507440</x:v>
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>2500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F101" s="0">
-        <x:v>42117724</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>2.67</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>254.75</x:v>
+        <x:v>20.08</x:v>
       </x:c>
       <x:c r="J101" s="0">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K101" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>2000000</x:v>
+        <x:v>8337681</x:v>
       </x:c>
       <x:c r="D102" s="0">
-        <x:v>2000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E102" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F102" s="0">
-        <x:v>81947000</x:v>
+        <x:v>37235183</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>2</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>2</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>27.78</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J102" s="0">
-        <x:v>40.97</x:v>
+        <x:v>4.47</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>9854768</x:v>
+        <x:v>400000</x:v>
       </x:c>
       <x:c r="D103" s="0">
-        <x:v>10000000</x:v>
+        <x:v>9275000</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>250000000</x:v>
+        <x:v>950000000</x:v>
       </x:c>
       <x:c r="F103" s="0">
-        <x:v>233360906</x:v>
+        <x:v>13352000</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>0.62</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>10.44</x:v>
+        <x:v>32.98</x:v>
       </x:c>
       <x:c r="J103" s="0">
-        <x:v>23.68</x:v>
+        <x:v>33.38</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>324474</x:v>
+        <x:v>1364000</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>5000000</x:v>
+        <x:v>23460000</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>30000000</x:v>
+        <x:v>9000000000</x:v>
       </x:c>
       <x:c r="F104" s="0">
-        <x:v>1781383</x:v>
+        <x:v>409075556</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>0</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>14.07</x:v>
+        <x:v>288.5</x:v>
       </x:c>
       <x:c r="J104" s="0">
-        <x:v>5.49</x:v>
+        <x:v>299.91</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E105" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F105" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C105" s="0">
+        <x:v>450000</x:v>
+      </x:c>
+      <x:c r="D105" s="0">
+        <x:v>380000000</x:v>
+      </x:c>
+      <x:c r="E105" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F105" s="0">
+        <x:v>8968500</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>16.01</x:v>
+        <x:v>19.58</x:v>
       </x:c>
       <x:c r="J105" s="0">
-        <x:v>0</x:v>
+        <x:v>19.93</x:v>
+      </x:c>
+      <x:c r="K105" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C106" s="0">
+        <x:v>507440</x:v>
       </x:c>
       <x:c r="D106" s="0">
-        <x:v>100000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>7000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F106" s="0">
+        <x:v>42117724</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>0.02</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0</x:v>
+        <x:v>0.54</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>4.48</x:v>
+        <x:v>237.7</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K106" s="0" t="s">
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>13000000</x:v>
-      </x:c>
-      <x:c r="D107" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D107" s="0">
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E107" s="0">
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F107" s="0">
-        <x:v>85838440</x:v>
+        <x:v>81947000</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>6.42</x:v>
+        <x:v>27.02</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>6.6</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>174500000</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>9854768</x:v>
+      </x:c>
+      <x:c r="D108" s="0">
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F108" s="0">
-        <x:v>694527000</x:v>
+        <x:v>233360906</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>0</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>2.26</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="J108" s="0">
-        <x:v>3.98</x:v>
+        <x:v>23.68</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>635229</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>324474</x:v>
+      </x:c>
+      <x:c r="D109" s="0">
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>100000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F109" s="0">
-        <x:v>11323561</x:v>
+        <x:v>1781383</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>15.2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J109" s="0">
-        <x:v>17.83</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="C110" s="0">
-        <x:v>130000</x:v>
-      </x:c>
-      <x:c r="D110" s="0">
-        <x:v>3500000</x:v>
-      </x:c>
-      <x:c r="E110" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F110" s="0">
-        <x:v>4947800</x:v>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E110" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F110" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>28.62</x:v>
+        <x:v>15.83</x:v>
       </x:c>
       <x:c r="J110" s="0">
-        <x:v>38.06</x:v>
-      </x:c>
-      <x:c r="K110" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D111" s="0">
-        <x:v>5000000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>600000000</x:v>
+        <x:v>7000000</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>0</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="H111" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>216.8</x:v>
+        <x:v>4.41</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>0</x:v>
@@ -5247,448 +5262,448 @@
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>447761</x:v>
-      </x:c>
-      <x:c r="D112" s="0">
-        <x:v>3000000</x:v>
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>120000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F112" s="0">
-        <x:v>18415143</x:v>
+        <x:v>85838440</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>0.86</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>27.56</x:v>
+        <x:v>6.39</x:v>
       </x:c>
       <x:c r="J112" s="0">
-        <x:v>41.13</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="K112" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="D113" s="0">
-        <x:v>2000000</x:v>
+        <x:v>174500000</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F113" s="0">
-        <x:v>4022593</x:v>
+        <x:v>694527000</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>1.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>3.33</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="J113" s="0">
-        <x:v>20.11</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="K113" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>946718</x:v>
-      </x:c>
-      <x:c r="D114" s="0">
-        <x:v>20000000</x:v>
+        <x:v>635229</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F114" s="0">
-        <x:v>37333519</x:v>
+        <x:v>11323561</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>7.55</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>3.56</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="J114" s="0">
-        <x:v>39.43</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="C115" s="0">
+        <x:v>130000</x:v>
+      </x:c>
+      <x:c r="D115" s="0">
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E115" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F115" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F115" s="0">
+        <x:v>4947800</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>0</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>0</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>10.57</x:v>
+        <x:v>27.44</x:v>
       </x:c>
       <x:c r="J115" s="0">
-        <x:v>0</x:v>
+        <x:v>38.06</x:v>
+      </x:c>
+      <x:c r="K115" s="0" t="s">
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="C116" s="0">
-        <x:v>3043115</x:v>
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>50000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>1000000000</x:v>
-      </x:c>
-      <x:c r="F116" s="0">
-        <x:v>49736990</x:v>
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="F116" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G116" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>20.24</x:v>
+        <x:v>204.3</x:v>
       </x:c>
       <x:c r="J116" s="0">
-        <x:v>16.34</x:v>
-      </x:c>
-      <x:c r="K116" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>2382736</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>447761</x:v>
+      </x:c>
+      <x:c r="D117" s="0">
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>500000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F117" s="0">
-        <x:v>92635231</x:v>
+        <x:v>18415143</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>37.1</x:v>
+        <x:v>26.3</x:v>
       </x:c>
       <x:c r="J117" s="0">
-        <x:v>38.88</x:v>
+        <x:v>41.13</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C118" s="0">
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>4191000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>160000000</x:v>
-      </x:c>
-      <x:c r="F118" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F118" s="0">
+        <x:v>4022593</x:v>
       </x:c>
       <x:c r="G118" s="0">
-        <x:v>0</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>0</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>45.88</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="J118" s="0">
-        <x:v>0</x:v>
+        <x:v>20.11</x:v>
+      </x:c>
+      <x:c r="K118" s="0" t="s">
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>4650000</x:v>
+        <x:v>946718</x:v>
       </x:c>
       <x:c r="D119" s="0">
-        <x:v>75000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F119" s="0">
-        <x:v>49978950</x:v>
+        <x:v>37333519</x:v>
       </x:c>
       <x:c r="G119" s="0">
-        <x:v>1.67</x:v>
+        <x:v>7.55</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>6.74</x:v>
+        <x:v>3.57</x:v>
       </x:c>
       <x:c r="J119" s="0">
-        <x:v>10.75</x:v>
+        <x:v>39.43</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="C120" s="0">
-        <x:v>806343</x:v>
-      </x:c>
-      <x:c r="D120" s="0">
-        <x:v>1862500</x:v>
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>75000000</x:v>
-      </x:c>
-      <x:c r="F120" s="0">
-        <x:v>30363861</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F120" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>2.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>27.08</x:v>
+        <x:v>10.01</x:v>
       </x:c>
       <x:c r="J120" s="0">
-        <x:v>37.66</x:v>
-      </x:c>
-      <x:c r="K120" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>310000</x:v>
+        <x:v>3043115</x:v>
       </x:c>
       <x:c r="D121" s="0">
-        <x:v>5000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E121" s="0">
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>49980500</x:v>
+        <x:v>49736990</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>6.74</x:v>
+        <x:v>20.08</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>161.23</x:v>
+        <x:v>16.34</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C122" s="0">
+        <x:v>2382736</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E122" s="0">
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F122" s="0">
+        <x:v>92635231</x:v>
+      </x:c>
+      <x:c r="G122" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H122" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I122" s="0">
+        <x:v>33.42</x:v>
+      </x:c>
+      <x:c r="J122" s="0">
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="K122" s="0" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="C122" s="0">
-        <x:v>2000000</x:v>
-      </x:c>
-      <x:c r="D122" s="0">
-        <x:v>5000000</x:v>
-      </x:c>
-      <x:c r="E122" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F122" s="0">
-        <x:v>31366572</x:v>
-      </x:c>
-      <x:c r="G122" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H122" s="0">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="I122" s="0">
-        <x:v>7.85</x:v>
-      </x:c>
-      <x:c r="J122" s="0">
-        <x:v>15.68</x:v>
-      </x:c>
-      <x:c r="K122" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="C123" s="0">
-        <x:v>1250000</x:v>
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D123" s="0">
-        <x:v>25000000</x:v>
+        <x:v>4191000</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F123" s="0">
-        <x:v>11187500</x:v>
+        <x:v>160000000</x:v>
+      </x:c>
+      <x:c r="F123" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>2.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>1.53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J123" s="0">
-        <x:v>8.95</x:v>
-      </x:c>
-      <x:c r="K123" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="C124" s="0">
+        <x:v>4650000</x:v>
+      </x:c>
+      <x:c r="D124" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="E124" s="0">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="F124" s="0">
+        <x:v>49978950</x:v>
+      </x:c>
+      <x:c r="G124" s="0">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="H124" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I124" s="0">
+        <x:v>6.75</x:v>
+      </x:c>
+      <x:c r="J124" s="0">
+        <x:v>10.75</x:v>
+      </x:c>
+      <x:c r="K124" s="0" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D124" s="0">
-        <x:v>6950000</x:v>
-      </x:c>
-      <x:c r="E124" s="0">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="F124" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G124" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H124" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I124" s="0">
-        <x:v>2.23</x:v>
-      </x:c>
-      <x:c r="J124" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
@@ -5699,1069 +5714,1069 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>12500000</x:v>
+        <x:v>806343</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>12500000</x:v>
+        <x:v>1862500</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>60000000</x:v>
+        <x:v>75000000</x:v>
       </x:c>
       <x:c r="F125" s="0">
-        <x:v>61582393</x:v>
+        <x:v>30363861</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>1.25</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>1.7</x:v>
+        <x:v>26.12</x:v>
       </x:c>
       <x:c r="J125" s="0">
-        <x:v>4.93</x:v>
+        <x:v>37.66</x:v>
       </x:c>
       <x:c r="K125" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>2093944</x:v>
+        <x:v>310000</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>220000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>8500000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F126" s="0">
-        <x:v>200139168</x:v>
+        <x:v>49980500</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>100.8</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="J126" s="0">
-        <x:v>95.58</x:v>
+        <x:v>161.23</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C127" s="0">
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>150000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>3000000000</x:v>
-      </x:c>
-      <x:c r="F127" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F127" s="0">
+        <x:v>31366572</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>46.06</x:v>
+        <x:v>7.41</x:v>
       </x:c>
       <x:c r="J127" s="0">
-        <x:v>0</x:v>
+        <x:v>15.68</x:v>
+      </x:c>
+      <x:c r="K127" s="0" t="s">
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>51245979</x:v>
+        <x:v>1250000</x:v>
       </x:c>
       <x:c r="D128" s="0">
-        <x:v>85000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>200000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F128" s="0">
-        <x:v>125342407</x:v>
+        <x:v>11187500</x:v>
       </x:c>
       <x:c r="G128" s="0">
-        <x:v>2.18</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>1.31</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>2.49</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="J128" s="0">
-        <x:v>2.45</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="C129" s="0">
-        <x:v>1584837</x:v>
+      <x:c r="C129" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D129" s="0">
-        <x:v>2500000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F129" s="0">
-        <x:v>92450176</x:v>
+        <x:v>125000000</x:v>
+      </x:c>
+      <x:c r="F129" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G129" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>59.45</x:v>
+        <x:v>2.01</x:v>
       </x:c>
       <x:c r="J129" s="0">
-        <x:v>58.33</x:v>
-      </x:c>
-      <x:c r="K129" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>7999148</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="D130" s="0">
-        <x:v>11000000</x:v>
+        <x:v>12500000</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>200000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F130" s="0">
-        <x:v>168715651</x:v>
+        <x:v>61582393</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>2.11</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>17.02</x:v>
+        <x:v>1.61</x:v>
       </x:c>
       <x:c r="J130" s="0">
-        <x:v>21.09</x:v>
+        <x:v>4.93</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>234</x:v>
-      </x:c>
       <x:c r="C131" s="0">
-        <x:v>14000000</x:v>
+        <x:v>2093944</x:v>
       </x:c>
       <x:c r="D131" s="0">
-        <x:v>10000000</x:v>
+        <x:v>220000000</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>200000000</x:v>
+        <x:v>8500000000</x:v>
       </x:c>
       <x:c r="F131" s="0">
-        <x:v>236130680</x:v>
+        <x:v>200139168</x:v>
       </x:c>
       <x:c r="G131" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>0.19</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>3.54</x:v>
+        <x:v>99.45</x:v>
       </x:c>
       <x:c r="J131" s="0">
-        <x:v>16.87</x:v>
+        <x:v>95.58</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C132" s="0">
-        <x:v>1700005</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D132" s="0">
-        <x:v>95000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>1425000000</x:v>
-      </x:c>
-      <x:c r="F132" s="0">
-        <x:v>20390731</x:v>
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="F132" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>4.03</x:v>
+        <x:v>45.2</x:v>
       </x:c>
       <x:c r="J132" s="0">
-        <x:v>11.99</x:v>
-      </x:c>
-      <x:c r="K132" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>6000000</x:v>
+        <x:v>51245979</x:v>
       </x:c>
       <x:c r="D133" s="0">
-        <x:v>6000000</x:v>
+        <x:v>85000000</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F133" s="0">
-        <x:v>132286928</x:v>
+        <x:v>125342407</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>0.94</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>0.16</x:v>
+        <x:v>1.31</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>14.46</x:v>
+        <x:v>2.44</x:v>
       </x:c>
       <x:c r="J133" s="0">
-        <x:v>22.05</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>1675000</x:v>
+        <x:v>1584837</x:v>
       </x:c>
       <x:c r="D134" s="0">
-        <x:v>9000000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>500000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F134" s="0">
-        <x:v>114158717</x:v>
+        <x:v>92450176</x:v>
       </x:c>
       <x:c r="G134" s="0">
-        <x:v>7.81</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>7.93</x:v>
+        <x:v>58.6</x:v>
       </x:c>
       <x:c r="J134" s="0">
-        <x:v>68.15</x:v>
+        <x:v>58.33</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>1824868</x:v>
+        <x:v>7999148</x:v>
       </x:c>
       <x:c r="D135" s="0">
-        <x:v>10000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E135" s="0">
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F135" s="0">
-        <x:v>64572720</x:v>
+        <x:v>168715651</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>3.73</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>0.68</x:v>
+        <x:v>2.11</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>15.37</x:v>
+        <x:v>16.45</x:v>
       </x:c>
       <x:c r="J135" s="0">
-        <x:v>35.38</x:v>
+        <x:v>21.09</x:v>
       </x:c>
       <x:c r="K135" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="C136" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C136" s="0">
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="D136" s="0">
-        <x:v>50000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F136" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F136" s="0">
+        <x:v>236130680</x:v>
       </x:c>
       <x:c r="G136" s="0">
-        <x:v>5</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>0</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>6.25</x:v>
+        <x:v>3.51</x:v>
       </x:c>
       <x:c r="J136" s="0">
-        <x:v>0</x:v>
+        <x:v>16.87</x:v>
+      </x:c>
+      <x:c r="K136" s="0" t="s">
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1700005</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>1000000</x:v>
+        <x:v>95000000</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>30000000</x:v>
+        <x:v>1425000000</x:v>
       </x:c>
       <x:c r="F137" s="0">
-        <x:v>19787700</x:v>
+        <x:v>20390731</x:v>
       </x:c>
       <x:c r="G137" s="0">
-        <x:v>0.67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>4.86</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="J137" s="0">
-        <x:v>19.79</x:v>
+        <x:v>11.99</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>98551</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="D138" s="0">
-        <x:v>6500000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>100000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F138" s="0">
-        <x:v>1295684</x:v>
+        <x:v>132286928</x:v>
       </x:c>
       <x:c r="G138" s="0">
-        <x:v>0</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>13.36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>13.15</x:v>
+        <x:v>22.05</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>6049315</x:v>
+        <x:v>1675000</x:v>
       </x:c>
       <x:c r="D139" s="0">
-        <x:v>15000000</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>150000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F139" s="0">
-        <x:v>66439559</x:v>
+        <x:v>114158717</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>0</x:v>
+        <x:v>7.81</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>0.92</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>9.88</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="J139" s="0">
-        <x:v>10.98</x:v>
+        <x:v>68.15</x:v>
       </x:c>
       <x:c r="K139" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>37225000</x:v>
+        <x:v>1824868</x:v>
       </x:c>
       <x:c r="D140" s="0">
-        <x:v>12000000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>149982056</x:v>
+        <x:v>64572720</x:v>
       </x:c>
       <x:c r="G140" s="0">
-        <x:v>8.99</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>3.45</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>1.5</x:v>
+        <x:v>13.84</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>4.03</x:v>
+        <x:v>35.38</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="C141" s="0">
-        <x:v>1000000</x:v>
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D141" s="0">
-        <x:v>1000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>350000000</x:v>
-      </x:c>
-      <x:c r="F141" s="0">
-        <x:v>284578907</x:v>
+        <x:v>500000000</x:v>
+      </x:c>
+      <x:c r="F141" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G141" s="0">
-        <x:v>0.8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>117.3</x:v>
+        <x:v>6.02</x:v>
       </x:c>
       <x:c r="J141" s="0">
-        <x:v>284.58</x:v>
-      </x:c>
-      <x:c r="K141" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>600000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D142" s="0">
-        <x:v>600000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>25000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F142" s="0">
-        <x:v>22814140</x:v>
+        <x:v>19787700</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>0</x:v>
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>3.86</x:v>
+        <x:v>4.71</x:v>
       </x:c>
       <x:c r="J142" s="0">
-        <x:v>38.02</x:v>
+        <x:v>19.79</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>11703083</x:v>
+        <x:v>98551</x:v>
       </x:c>
       <x:c r="D143" s="0">
-        <x:v>16000000</x:v>
+        <x:v>6500000</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>720000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F143" s="0">
-        <x:v>978644023</x:v>
+        <x:v>1295684</x:v>
       </x:c>
       <x:c r="G143" s="0">
-        <x:v>10.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>1.67</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>119.2</x:v>
+        <x:v>14.69</x:v>
       </x:c>
       <x:c r="J143" s="0">
-        <x:v>83.62</x:v>
+        <x:v>13.15</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>5100000</x:v>
+        <x:v>6049315</x:v>
       </x:c>
       <x:c r="D144" s="0">
-        <x:v>9000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>200000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F144" s="0">
-        <x:v>90022686</x:v>
+        <x:v>66439559</x:v>
       </x:c>
       <x:c r="G144" s="0">
-        <x:v>7.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>4.31</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>30.84</x:v>
+        <x:v>10.01</x:v>
       </x:c>
       <x:c r="J144" s="0">
-        <x:v>17.65</x:v>
+        <x:v>10.98</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>3228679</x:v>
+        <x:v>37225000</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>10000000</x:v>
+        <x:v>12000000</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>175000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F145" s="0">
-        <x:v>51395842</x:v>
+        <x:v>149982056</x:v>
       </x:c>
       <x:c r="G145" s="0">
-        <x:v>0.9</x:v>
+        <x:v>8.99</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>0.29</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>6.89</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="J145" s="0">
-        <x:v>15.92</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>150000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D146" s="0">
-        <x:v>6000000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>240000000</x:v>
+        <x:v>350000000</x:v>
       </x:c>
       <x:c r="F146" s="0">
-        <x:v>6145450</x:v>
+        <x:v>284578907</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>0</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>4.46</x:v>
+        <x:v>105.6</x:v>
       </x:c>
       <x:c r="J146" s="0">
-        <x:v>40.97</x:v>
+        <x:v>284.58</x:v>
       </x:c>
       <x:c r="K146" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C147" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="D147" s="0">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="E147" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="F147" s="0">
+        <x:v>22814140</x:v>
+      </x:c>
+      <x:c r="G147" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H147" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="I147" s="0">
+        <x:v>3.56</x:v>
+      </x:c>
+      <x:c r="J147" s="0">
+        <x:v>38.02</x:v>
+      </x:c>
+      <x:c r="K147" s="0" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D147" s="0">
-        <x:v>1000000</x:v>
-      </x:c>
-      <x:c r="E147" s="0">
-        <x:v>28000000</x:v>
-      </x:c>
-      <x:c r="F147" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G147" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H147" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I147" s="0">
-        <x:v>9.33</x:v>
-      </x:c>
-      <x:c r="J147" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>366107</x:v>
+        <x:v>11703083</x:v>
       </x:c>
       <x:c r="D148" s="0">
-        <x:v>1200000</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>30000000</x:v>
+        <x:v>720000000</x:v>
       </x:c>
       <x:c r="F148" s="0">
-        <x:v>6010300</x:v>
+        <x:v>978644023</x:v>
       </x:c>
       <x:c r="G148" s="0">
-        <x:v>0</x:v>
+        <x:v>10.16</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>0.33</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>13</x:v>
+        <x:v>107.3</x:v>
       </x:c>
       <x:c r="J148" s="0">
-        <x:v>16.42</x:v>
+        <x:v>83.62</x:v>
       </x:c>
       <x:c r="K148" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>120000</x:v>
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D149" s="0">
-        <x:v>26398084</x:v>
+        <x:v>9000000</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>100000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F149" s="0">
-        <x:v>3830160</x:v>
+        <x:v>90022686</x:v>
       </x:c>
       <x:c r="G149" s="0">
-        <x:v>0</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>0.05</x:v>
+        <x:v>4.31</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>121.5</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="J149" s="0">
-        <x:v>31.92</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="K149" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>13050000</x:v>
+        <x:v>3228679</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>13050000</x:v>
+        <x:v>10000000</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>1305000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F150" s="0">
-        <x:v>1231340857</x:v>
+        <x:v>51395842</x:v>
       </x:c>
       <x:c r="G150" s="0">
-        <x:v>3</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>3.13</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>109.2</x:v>
+        <x:v>6.93</x:v>
       </x:c>
       <x:c r="J150" s="0">
-        <x:v>94.36</x:v>
+        <x:v>15.92</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>36605658</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D151" s="0">
-        <x:v>100000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>500000000</x:v>
+        <x:v>240000000</x:v>
       </x:c>
       <x:c r="F151" s="0">
-        <x:v>174340918</x:v>
+        <x:v>6145450</x:v>
       </x:c>
       <x:c r="G151" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>3.66</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>4.09</x:v>
+        <x:v>4.24</x:v>
       </x:c>
       <x:c r="J151" s="0">
-        <x:v>4.76</x:v>
+        <x:v>40.97</x:v>
       </x:c>
       <x:c r="K151" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C152" s="0">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D152" s="0">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="D152" s="0">
-        <x:v>4000000</x:v>
-      </x:c>
       <x:c r="E152" s="0">
-        <x:v>2000000000</x:v>
-      </x:c>
-      <x:c r="F152" s="0">
-        <x:v>429817200</x:v>
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="F152" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>433.75</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="J152" s="0">
-        <x:v>429.82</x:v>
-      </x:c>
-      <x:c r="K152" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>300000</x:v>
+        <x:v>366107</x:v>
       </x:c>
       <x:c r="D153" s="0">
-        <x:v>60000000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>171000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="F153" s="0">
-        <x:v>791000</x:v>
+        <x:v>6010300</x:v>
       </x:c>
       <x:c r="G153" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>1.9</x:v>
+        <x:v>12.75</x:v>
       </x:c>
       <x:c r="J153" s="0">
-        <x:v>2.64</x:v>
+        <x:v>16.42</x:v>
       </x:c>
       <x:c r="K153" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>2175097</x:v>
+        <x:v>120000</x:v>
       </x:c>
       <x:c r="D154" s="0">
-        <x:v>15000000</x:v>
+        <x:v>26398084</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>175000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F154" s="0">
-        <x:v>17901652</x:v>
+        <x:v>3830160</x:v>
       </x:c>
       <x:c r="G154" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>12.25</x:v>
+        <x:v>133.6</x:v>
       </x:c>
       <x:c r="J154" s="0">
-        <x:v>8.23</x:v>
+        <x:v>31.92</x:v>
       </x:c>
       <x:c r="K154" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C155" s="0">
+        <x:v>13050000</x:v>
+      </x:c>
+      <x:c r="D155" s="0">
+        <x:v>13050000</x:v>
+      </x:c>
+      <x:c r="E155" s="0">
+        <x:v>1305000000</x:v>
+      </x:c>
+      <x:c r="F155" s="0">
+        <x:v>1231340857</x:v>
+      </x:c>
+      <x:c r="G155" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H155" s="0">
+        <x:v>3.13</x:v>
+      </x:c>
+      <x:c r="I155" s="0">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="J155" s="0">
+        <x:v>94.36</x:v>
+      </x:c>
+      <x:c r="K155" s="0" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C155" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D155" s="0">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="E155" s="0">
-        <x:v>152000000</x:v>
-      </x:c>
-      <x:c r="F155" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G155" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H155" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I155" s="0">
-        <x:v>2.12</x:v>
-      </x:c>
-      <x:c r="J155" s="0">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
@@ -6769,404 +6784,404 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>43000</x:v>
+        <x:v>36605658</x:v>
       </x:c>
       <x:c r="D156" s="0">
-        <x:v>200000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>5000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F156" s="0">
-        <x:v>1024885</x:v>
+        <x:v>174340918</x:v>
       </x:c>
       <x:c r="G156" s="0">
-        <x:v>0.43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>0.09</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>23.8</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="J156" s="0">
-        <x:v>23.83</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>9937037</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D157" s="0">
-        <x:v>11000000</x:v>
+        <x:v>4000000</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>50000000</x:v>
+        <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F157" s="0">
-        <x:v>50001023</x:v>
+        <x:v>429817200</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>0.53</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>1.86</x:v>
+        <x:v>422.75</x:v>
       </x:c>
       <x:c r="J157" s="0">
-        <x:v>5.03</x:v>
+        <x:v>429.82</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C158" s="0">
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D158" s="0">
-        <x:v>5500000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>139000000</x:v>
-      </x:c>
-      <x:c r="F158" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>171000000</x:v>
+      </x:c>
+      <x:c r="F158" s="0">
+        <x:v>791000</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>1.79</x:v>
+        <x:v>1.88</x:v>
       </x:c>
       <x:c r="J158" s="0">
-        <x:v>0</x:v>
+        <x:v>2.64</x:v>
+      </x:c>
+      <x:c r="K158" s="0" t="s">
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>13064888</x:v>
+        <x:v>2175097</x:v>
       </x:c>
       <x:c r="D159" s="0">
-        <x:v>30000000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>600000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F159" s="0">
-        <x:v>268254173</x:v>
+        <x:v>17901652</x:v>
       </x:c>
       <x:c r="G159" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>0.5</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>44.2</x:v>
+        <x:v>12.06</x:v>
       </x:c>
       <x:c r="J159" s="0">
-        <x:v>20.53</x:v>
+        <x:v>8.23</x:v>
       </x:c>
       <x:c r="K159" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C160" s="0">
-        <x:v>111673026</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D160" s="0">
-        <x:v>150000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="F160" s="0">
-        <x:v>500005947</x:v>
+        <x:v>152000000</x:v>
+      </x:c>
+      <x:c r="F160" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G160" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>1.24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>13.03</x:v>
+        <x:v>1.98</x:v>
       </x:c>
       <x:c r="J160" s="0">
-        <x:v>4.48</x:v>
-      </x:c>
-      <x:c r="K160" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D161" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C161" s="0">
+        <x:v>83000</x:v>
+      </x:c>
+      <x:c r="D161" s="0">
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>250000000</x:v>
-      </x:c>
-      <x:c r="F161" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>5000000</x:v>
+      </x:c>
+      <x:c r="F161" s="0">
+        <x:v>2006086</x:v>
       </x:c>
       <x:c r="G161" s="0">
-        <x:v>0</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>0</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>3.48</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J161" s="0">
-        <x:v>0</x:v>
+        <x:v>24.17</x:v>
+      </x:c>
+      <x:c r="K161" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C162" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C162" s="0">
+        <x:v>9937037</x:v>
       </x:c>
       <x:c r="D162" s="0">
-        <x:v>19600000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>92000000</x:v>
-      </x:c>
-      <x:c r="F162" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>50000000</x:v>
+      </x:c>
+      <x:c r="F162" s="0">
+        <x:v>50001023</x:v>
       </x:c>
       <x:c r="G162" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>0</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>4.05</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="J162" s="0">
-        <x:v>0</x:v>
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="K162" s="0" t="s">
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C163" s="0">
-        <x:v>1100000</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D163" s="0">
-        <x:v>2000000</x:v>
+        <x:v>5500000</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F163" s="0">
-        <x:v>56064346</x:v>
+        <x:v>139000000</x:v>
+      </x:c>
+      <x:c r="F163" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G163" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>192</x:v>
+        <x:v>1.64</x:v>
       </x:c>
       <x:c r="J163" s="0">
-        <x:v>50.97</x:v>
-      </x:c>
-      <x:c r="K163" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>6598092</x:v>
+        <x:v>13064888</x:v>
       </x:c>
       <x:c r="D164" s="0">
-        <x:v>11160000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>125000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F164" s="0">
-        <x:v>72091269</x:v>
+        <x:v>268254173</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>5.91</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>16.01</x:v>
+        <x:v>44.24</x:v>
       </x:c>
       <x:c r="J164" s="0">
-        <x:v>10.93</x:v>
+        <x:v>20.53</x:v>
       </x:c>
       <x:c r="K164" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>1590000</x:v>
+        <x:v>111673026</x:v>
       </x:c>
       <x:c r="D165" s="0">
-        <x:v>2160000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>35000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F165" s="0">
-        <x:v>60641600</x:v>
+        <x:v>500005947</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>0.91</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>35.96</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="J165" s="0">
-        <x:v>38.14</x:v>
+        <x:v>4.48</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C166" s="0">
-        <x:v>1989802</x:v>
-      </x:c>
-      <x:c r="D166" s="0">
-        <x:v>5000000</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E166" s="0">
         <x:v>250000000</x:v>
       </x:c>
-      <x:c r="F166" s="0">
-        <x:v>78711752</x:v>
+      <x:c r="F166" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G166" s="0">
-        <x:v>2.94</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>1.17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>128.8</x:v>
+        <x:v>3.36</x:v>
       </x:c>
       <x:c r="J166" s="0">
-        <x:v>39.56</x:v>
-      </x:c>
-      <x:c r="K166" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D167" s="0">
-        <x:v>1000000</x:v>
+        <x:v>19600000</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>270000000</x:v>
+        <x:v>92000000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="G167" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H167" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>423.25</x:v>
+        <x:v>3.95</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>0</x:v>
@@ -7174,1390 +7189,1562 @@
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>300000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="D168" s="0">
-        <x:v>67500000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>326000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F168" s="0">
-        <x:v>1369300</x:v>
+        <x:v>56064346</x:v>
       </x:c>
       <x:c r="G168" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>0.04</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>4.66</x:v>
+        <x:v>172.8</x:v>
       </x:c>
       <x:c r="J168" s="0">
-        <x:v>4.56</x:v>
+        <x:v>50.97</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>77658759</x:v>
+        <x:v>6598092</x:v>
       </x:c>
       <x:c r="D169" s="0">
-        <x:v>250000000</x:v>
+        <x:v>11160000</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>12000000000</x:v>
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="F169" s="0">
-        <x:v>2004847371</x:v>
+        <x:v>72091269</x:v>
       </x:c>
       <x:c r="G169" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>0.78</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>34.44</x:v>
+        <x:v>15.83</x:v>
       </x:c>
       <x:c r="J169" s="0">
-        <x:v>25.82</x:v>
+        <x:v>10.93</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>8291656</x:v>
+        <x:v>1590000</x:v>
       </x:c>
       <x:c r="D170" s="0">
-        <x:v>11000000</x:v>
+        <x:v>2160000</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>200000000</x:v>
+        <x:v>35000000</x:v>
       </x:c>
       <x:c r="F170" s="0">
-        <x:v>126004459</x:v>
+        <x:v>60641600</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>14.86</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J170" s="0">
-        <x:v>15.2</x:v>
+        <x:v>38.14</x:v>
       </x:c>
       <x:c r="K170" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>2975773</x:v>
+        <x:v>1989802</x:v>
       </x:c>
       <x:c r="D171" s="0">
-        <x:v>6000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>150000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F171" s="0">
-        <x:v>44771095</x:v>
+        <x:v>78711752</x:v>
       </x:c>
       <x:c r="G171" s="0">
-        <x:v>0</x:v>
+        <x:v>2.94</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>0.3</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>22.18</x:v>
+        <x:v>123.4</x:v>
       </x:c>
       <x:c r="J171" s="0">
-        <x:v>15.05</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="C172" s="0">
-        <x:v>11039823</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D172" s="0">
-        <x:v>21600000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>1200000000</x:v>
-      </x:c>
-      <x:c r="F172" s="0">
-        <x:v>183556428</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F172" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G172" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>5.11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>12.11</x:v>
+        <x:v>406.75</x:v>
       </x:c>
       <x:c r="J172" s="0">
-        <x:v>16.63</x:v>
-      </x:c>
-      <x:c r="K172" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>38590259</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="D173" s="0">
-        <x:v>195000000</x:v>
+        <x:v>67500000</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>2500000000</x:v>
+        <x:v>326000000</x:v>
       </x:c>
       <x:c r="F173" s="0">
-        <x:v>442806603</x:v>
+        <x:v>1369300</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>1.98</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>15.76</x:v>
+        <x:v>4.22</x:v>
       </x:c>
       <x:c r="J173" s="0">
-        <x:v>11.47</x:v>
+        <x:v>4.56</x:v>
       </x:c>
       <x:c r="K173" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:11">
       <x:c r="A174" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>5100000</x:v>
+        <x:v>77658759</x:v>
       </x:c>
       <x:c r="D174" s="0">
-        <x:v>20000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>700000000</x:v>
+        <x:v>12000000000</x:v>
       </x:c>
       <x:c r="F174" s="0">
-        <x:v>155318227</x:v>
+        <x:v>2004847371</x:v>
       </x:c>
       <x:c r="G174" s="0">
-        <x:v>6.81</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>0.93</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>56.9</x:v>
+        <x:v>33.78</x:v>
       </x:c>
       <x:c r="J174" s="0">
-        <x:v>30.45</x:v>
+        <x:v>25.82</x:v>
       </x:c>
       <x:c r="K174" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="C175" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C175" s="0">
+        <x:v>8291656</x:v>
       </x:c>
       <x:c r="D175" s="0">
-        <x:v>300000000</x:v>
+        <x:v>11000000</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>700000000</x:v>
-      </x:c>
-      <x:c r="F175" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F175" s="0">
+        <x:v>126004459</x:v>
       </x:c>
       <x:c r="G175" s="0">
-        <x:v>6.67</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>0</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>2.34</x:v>
+        <x:v>14.87</x:v>
       </x:c>
       <x:c r="J175" s="0">
-        <x:v>0</x:v>
+        <x:v>15.2</x:v>
+      </x:c>
+      <x:c r="K175" s="0" t="s">
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:11">
       <x:c r="A176" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>5000000</x:v>
+        <x:v>2975773</x:v>
       </x:c>
       <x:c r="D176" s="0">
-        <x:v>5000000</x:v>
+        <x:v>6000000</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>50000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F176" s="0">
-        <x:v>39090077</x:v>
+        <x:v>44771095</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>9.47</x:v>
+        <x:v>21.22</x:v>
       </x:c>
       <x:c r="J176" s="0">
-        <x:v>7.82</x:v>
+        <x:v>15.05</x:v>
       </x:c>
       <x:c r="K176" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:11">
       <x:c r="A177" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>905991</x:v>
+        <x:v>11039823</x:v>
       </x:c>
       <x:c r="D177" s="0">
-        <x:v>21000000</x:v>
+        <x:v>21600000</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>500000000</x:v>
+        <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F177" s="0">
-        <x:v>17447317</x:v>
+        <x:v>183556428</x:v>
       </x:c>
       <x:c r="G177" s="0">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>0.13</x:v>
+        <x:v>5.11</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>14.9</x:v>
+        <x:v>11.69</x:v>
       </x:c>
       <x:c r="J177" s="0">
-        <x:v>19.26</x:v>
+        <x:v>16.63</x:v>
       </x:c>
       <x:c r="K177" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:11">
       <x:c r="A178" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="C178" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C178" s="0">
+        <x:v>38590259</x:v>
       </x:c>
       <x:c r="D178" s="0">
-        <x:v>11700000</x:v>
+        <x:v>195000000</x:v>
       </x:c>
       <x:c r="E178" s="0">
-        <x:v>200000000</x:v>
-      </x:c>
-      <x:c r="F178" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>2500000000</x:v>
+      </x:c>
+      <x:c r="F178" s="0">
+        <x:v>442806603</x:v>
       </x:c>
       <x:c r="G178" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H178" s="0">
-        <x:v>0</x:v>
+        <x:v>1.98</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>31.76</x:v>
+        <x:v>15.65</x:v>
       </x:c>
       <x:c r="J178" s="0">
-        <x:v>0</x:v>
+        <x:v>11.47</x:v>
+      </x:c>
+      <x:c r="K178" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:11">
       <x:c r="A179" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="C179" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C179" s="0">
+        <x:v>5100000</x:v>
       </x:c>
       <x:c r="D179" s="0">
-        <x:v>1000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E179" s="0">
-        <x:v>270000000</x:v>
-      </x:c>
-      <x:c r="F179" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F179" s="0">
+        <x:v>155318227</x:v>
       </x:c>
       <x:c r="G179" s="0">
-        <x:v>0</x:v>
+        <x:v>6.81</x:v>
       </x:c>
       <x:c r="H179" s="0">
-        <x:v>0</x:v>
+        <x:v>0.93</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>423.25</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J179" s="0">
-        <x:v>0</x:v>
+        <x:v>30.45</x:v>
+      </x:c>
+      <x:c r="K179" s="0" t="s">
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:11">
       <x:c r="A180" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="C180" s="0">
-        <x:v>53584</x:v>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D180" s="0">
-        <x:v>1630000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E180" s="0">
-        <x:v>640000000</x:v>
-      </x:c>
-      <x:c r="F180" s="0">
-        <x:v>8271098</x:v>
+        <x:v>700000000</x:v>
+      </x:c>
+      <x:c r="F180" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G180" s="0">
-        <x:v>0</x:v>
+        <x:v>6.67</x:v>
       </x:c>
       <x:c r="H180" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>239.1</x:v>
+        <x:v>2.33</x:v>
       </x:c>
       <x:c r="J180" s="0">
-        <x:v>154.36</x:v>
-      </x:c>
-      <x:c r="K180" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:11">
       <x:c r="A181" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>7550000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="D181" s="0">
-        <x:v>30000000</x:v>
+        <x:v>5000000</x:v>
       </x:c>
       <x:c r="E181" s="0">
-        <x:v>500000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="F181" s="0">
-        <x:v>111777791</x:v>
+        <x:v>39090077</x:v>
       </x:c>
       <x:c r="G181" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H181" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>8.41</x:v>
+        <x:v>9.47</x:v>
       </x:c>
       <x:c r="J181" s="0">
-        <x:v>14.81</x:v>
+        <x:v>7.82</x:v>
       </x:c>
       <x:c r="K181" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:11">
       <x:c r="A182" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>2097716</x:v>
+        <x:v>905991</x:v>
       </x:c>
       <x:c r="D182" s="0">
-        <x:v>10112561</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="E182" s="0">
-        <x:v>120000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F182" s="0">
-        <x:v>28985167</x:v>
+        <x:v>17447317</x:v>
       </x:c>
       <x:c r="G182" s="0">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H182" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>1.01</x:v>
+        <x:v>14.37</x:v>
       </x:c>
       <x:c r="J182" s="0">
-        <x:v>13.82</x:v>
+        <x:v>19.26</x:v>
       </x:c>
       <x:c r="K182" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:11">
       <x:c r="A183" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="C183" s="0">
-        <x:v>5185302</x:v>
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D183" s="0">
-        <x:v>57000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="E183" s="0">
-        <x:v>513000000</x:v>
-      </x:c>
-      <x:c r="F183" s="0">
-        <x:v>37061183</x:v>
+        <x:v>200000000</x:v>
+      </x:c>
+      <x:c r="F183" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G183" s="0">
-        <x:v>5.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H183" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>5.22</x:v>
+        <x:v>30.36</x:v>
       </x:c>
       <x:c r="J183" s="0">
-        <x:v>7.15</x:v>
-      </x:c>
-      <x:c r="K183" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:11">
       <x:c r="A184" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="C184" s="0">
-        <x:v>669111</x:v>
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D184" s="0">
         <x:v>1000000</x:v>
       </x:c>
       <x:c r="E184" s="0">
-        <x:v>260000000</x:v>
-      </x:c>
-      <x:c r="F184" s="0">
-        <x:v>151220429</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F184" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G184" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H184" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>744</x:v>
+        <x:v>406.75</x:v>
       </x:c>
       <x:c r="J184" s="0">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="K184" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:11">
       <x:c r="A185" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>38840</x:v>
+        <x:v>53584</x:v>
       </x:c>
       <x:c r="D185" s="0">
-        <x:v>1000000</x:v>
+        <x:v>1630000000</x:v>
       </x:c>
       <x:c r="E185" s="0">
-        <x:v>270000000</x:v>
+        <x:v>640000000</x:v>
       </x:c>
       <x:c r="F185" s="0">
-        <x:v>9431791</x:v>
+        <x:v>8271098</x:v>
       </x:c>
       <x:c r="G185" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H185" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>423.25</x:v>
+        <x:v>231.4</x:v>
       </x:c>
       <x:c r="J185" s="0">
-        <x:v>242.84</x:v>
+        <x:v>154.36</x:v>
       </x:c>
       <x:c r="K185" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:11">
       <x:c r="A186" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>2250000</x:v>
+        <x:v>7550000</x:v>
       </x:c>
       <x:c r="D186" s="0">
-        <x:v>20000000</x:v>
+        <x:v>30000000</x:v>
       </x:c>
       <x:c r="E186" s="0">
-        <x:v>300000000</x:v>
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="F186" s="0">
-        <x:v>31750000</x:v>
+        <x:v>111777791</x:v>
       </x:c>
       <x:c r="G186" s="0">
-        <x:v>4.98</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H186" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>8.41</x:v>
+        <x:v>8.57</x:v>
       </x:c>
       <x:c r="J186" s="0">
-        <x:v>14.11</x:v>
+        <x:v>14.81</x:v>
       </x:c>
       <x:c r="K186" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:11">
       <x:c r="A187" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>1500000</x:v>
+        <x:v>2097716</x:v>
       </x:c>
       <x:c r="D187" s="0">
         <x:v>10112561</x:v>
       </x:c>
       <x:c r="E187" s="0">
-        <x:v>175000000</x:v>
+        <x:v>120000000</x:v>
       </x:c>
       <x:c r="F187" s="0">
-        <x:v>21870885</x:v>
+        <x:v>28985167</x:v>
       </x:c>
       <x:c r="G187" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H187" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I187" s="0">
-        <x:v>1.01</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="J187" s="0">
-        <x:v>14.58</x:v>
+        <x:v>13.82</x:v>
       </x:c>
       <x:c r="K187" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:11">
       <x:c r="A188" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>1656401</x:v>
+        <x:v>5185302</x:v>
       </x:c>
       <x:c r="D188" s="0">
-        <x:v>8299326</x:v>
+        <x:v>57000000</x:v>
       </x:c>
       <x:c r="E188" s="0">
-        <x:v>600000000</x:v>
+        <x:v>513000000</x:v>
       </x:c>
       <x:c r="F188" s="0">
-        <x:v>229213803</x:v>
+        <x:v>37061183</x:v>
       </x:c>
       <x:c r="G188" s="0">
-        <x:v>0</x:v>
+        <x:v>5.7</x:v>
       </x:c>
       <x:c r="H188" s="0">
-        <x:v>1.74</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="I188" s="0">
-        <x:v>143.5</x:v>
+        <x:v>4.97</x:v>
       </x:c>
       <x:c r="J188" s="0">
-        <x:v>138.38</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="K188" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:11">
       <x:c r="A189" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>17990900</x:v>
+        <x:v>669111</x:v>
       </x:c>
       <x:c r="D189" s="0">
-        <x:v>18200000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E189" s="0">
-        <x:v>850000000</x:v>
+        <x:v>260000000</x:v>
       </x:c>
       <x:c r="F189" s="0">
-        <x:v>773698614</x:v>
+        <x:v>151220429</x:v>
       </x:c>
       <x:c r="G189" s="0">
-        <x:v>3.64</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H189" s="0">
-        <x:v>3.6</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I189" s="0">
-        <x:v>38.24</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="J189" s="0">
-        <x:v>43</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K189" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:11">
       <x:c r="A190" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="C190" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="C190" s="0">
+        <x:v>38840</x:v>
       </x:c>
       <x:c r="D190" s="0">
-        <x:v>2500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E190" s="0">
-        <x:v>100000000</x:v>
-      </x:c>
-      <x:c r="F190" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>270000000</x:v>
+      </x:c>
+      <x:c r="F190" s="0">
+        <x:v>9431791</x:v>
       </x:c>
       <x:c r="G190" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H190" s="0">
-        <x:v>0</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="I190" s="0">
-        <x:v>254.75</x:v>
+        <x:v>406.75</x:v>
       </x:c>
       <x:c r="J190" s="0">
-        <x:v>0</x:v>
+        <x:v>242.84</x:v>
+      </x:c>
+      <x:c r="K190" s="0" t="s">
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:11">
       <x:c r="A191" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C191" s="0">
-        <x:v>845945</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="D191" s="0">
-        <x:v>15000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="E191" s="0">
-        <x:v>250000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F191" s="0">
-        <x:v>10058606</x:v>
+        <x:v>31750000</x:v>
       </x:c>
       <x:c r="G191" s="0">
-        <x:v>0</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="H191" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I191" s="0">
-        <x:v>2.76</x:v>
+        <x:v>8.57</x:v>
       </x:c>
       <x:c r="J191" s="0">
-        <x:v>11.89</x:v>
+        <x:v>14.11</x:v>
       </x:c>
       <x:c r="K191" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:11">
       <x:c r="A192" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C192" s="0">
-        <x:v>21446</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="D192" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10112561</x:v>
       </x:c>
       <x:c r="E192" s="0">
-        <x:v>200000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F192" s="0">
-        <x:v>2015907</x:v>
+        <x:v>21870885</x:v>
       </x:c>
       <x:c r="G192" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H192" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="I192" s="0">
-        <x:v>38.48</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="J192" s="0">
-        <x:v>94</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="K192" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>317</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:11">
       <x:c r="A193" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C193" s="0">
-        <x:v>1284369</x:v>
+        <x:v>1656401</x:v>
       </x:c>
       <x:c r="D193" s="0">
-        <x:v>4250000</x:v>
+        <x:v>8299326</x:v>
       </x:c>
       <x:c r="E193" s="0">
-        <x:v>40000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F193" s="0">
-        <x:v>9208528</x:v>
+        <x:v>229213803</x:v>
       </x:c>
       <x:c r="G193" s="0">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H193" s="0">
-        <x:v>1.51</x:v>
+        <x:v>1.74</x:v>
       </x:c>
       <x:c r="I193" s="0">
-        <x:v>6.28</x:v>
+        <x:v>139.8</x:v>
       </x:c>
       <x:c r="J193" s="0">
-        <x:v>7.17</x:v>
+        <x:v>138.38</x:v>
       </x:c>
       <x:c r="K193" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:11">
       <x:c r="A194" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C194" s="0">
-        <x:v>15000000</x:v>
+        <x:v>17990900</x:v>
       </x:c>
       <x:c r="D194" s="0">
-        <x:v>300000000</x:v>
+        <x:v>18200000</x:v>
       </x:c>
       <x:c r="E194" s="0">
-        <x:v>600000000</x:v>
+        <x:v>850000000</x:v>
       </x:c>
       <x:c r="F194" s="0">
-        <x:v>23990000</x:v>
+        <x:v>773698614</x:v>
       </x:c>
       <x:c r="G194" s="0">
-        <x:v>0</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="H194" s="0">
-        <x:v>0.22</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="I194" s="0">
-        <x:v>1.88</x:v>
+        <x:v>36.86</x:v>
       </x:c>
       <x:c r="J194" s="0">
-        <x:v>1.6</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K194" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:11">
       <x:c r="A195" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="C195" s="0">
-        <x:v>6397124</x:v>
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D195" s="0">
-        <x:v>35300000</x:v>
+        <x:v>2500000</x:v>
       </x:c>
       <x:c r="E195" s="0">
-        <x:v>1046645000</x:v>
-      </x:c>
-      <x:c r="F195" s="0">
-        <x:v>122892213</x:v>
+        <x:v>100000000</x:v>
+      </x:c>
+      <x:c r="F195" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G195" s="0">
-        <x:v>0</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H195" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I195" s="0">
-        <x:v>3.35</x:v>
+        <x:v>237.7</x:v>
       </x:c>
       <x:c r="J195" s="0">
-        <x:v>19.21</x:v>
-      </x:c>
-      <x:c r="K195" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:11">
       <x:c r="A196" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C196" s="0">
-        <x:v>17495257</x:v>
+        <x:v>845945</x:v>
       </x:c>
       <x:c r="D196" s="0">
-        <x:v>17500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E196" s="0">
-        <x:v>525000000</x:v>
+        <x:v>250000000</x:v>
       </x:c>
       <x:c r="F196" s="0">
-        <x:v>409385433</x:v>
+        <x:v>10058606</x:v>
       </x:c>
       <x:c r="G196" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H196" s="0">
-        <x:v>5</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I196" s="0">
-        <x:v>15.8</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J196" s="0">
-        <x:v>23.4</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="K196" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:11">
       <x:c r="A197" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C197" s="0">
-        <x:v>9350000</x:v>
+        <x:v>21446</x:v>
       </x:c>
       <x:c r="D197" s="0">
-        <x:v>14710247</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="E197" s="0">
-        <x:v>150000000</x:v>
+        <x:v>200000000</x:v>
       </x:c>
       <x:c r="F197" s="0">
-        <x:v>69547091</x:v>
+        <x:v>2015907</x:v>
       </x:c>
       <x:c r="G197" s="0">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H197" s="0">
-        <x:v>1.1</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="I197" s="0">
-        <x:v>1.66</x:v>
+        <x:v>37.12</x:v>
       </x:c>
       <x:c r="J197" s="0">
-        <x:v>7.44</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K197" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:11">
       <x:c r="A198" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C198" s="0">
-        <x:v>1468255</x:v>
-      </x:c>
-      <x:c r="D198" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>1284369</x:v>
+      </x:c>
+      <x:c r="D198" s="0">
+        <x:v>4250000</x:v>
       </x:c>
       <x:c r="E198" s="0">
-        <x:v>100000000</x:v>
+        <x:v>40000000</x:v>
       </x:c>
       <x:c r="F198" s="0">
-        <x:v>75911475</x:v>
+        <x:v>9208528</x:v>
       </x:c>
       <x:c r="G198" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H198" s="0">
-        <x:v>0.37</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="I198" s="0">
-        <x:v>22.9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J198" s="0">
-        <x:v>51.7</x:v>
+        <x:v>7.17</x:v>
       </x:c>
       <x:c r="K198" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:11">
       <x:c r="A199" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C199" s="0">
-        <x:v>500000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="D199" s="0">
-        <x:v>2000000</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="E199" s="0">
-        <x:v>60000000</x:v>
+        <x:v>600000000</x:v>
       </x:c>
       <x:c r="F199" s="0">
-        <x:v>13401783</x:v>
+        <x:v>23990000</x:v>
       </x:c>
       <x:c r="G199" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H199" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I199" s="0">
-        <x:v>1.95</x:v>
+        <x:v>1.89</x:v>
       </x:c>
       <x:c r="J199" s="0">
-        <x:v>26.8</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="K199" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:11">
       <x:c r="A200" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="C200" s="0">
-        <x:v>725000</x:v>
+        <x:v>6397124</x:v>
       </x:c>
       <x:c r="D200" s="0">
-        <x:v>10000000</x:v>
+        <x:v>35300000</x:v>
       </x:c>
       <x:c r="E200" s="0">
-        <x:v>1000000000</x:v>
+        <x:v>1046645000</x:v>
       </x:c>
       <x:c r="F200" s="0">
-        <x:v>48539975</x:v>
+        <x:v>122892213</x:v>
       </x:c>
       <x:c r="G200" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H200" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="I200" s="0">
-        <x:v>33.76</x:v>
+        <x:v>3.33</x:v>
       </x:c>
       <x:c r="J200" s="0">
-        <x:v>66.95</x:v>
+        <x:v>19.21</x:v>
       </x:c>
       <x:c r="K200" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:11">
       <x:c r="A201" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C201" s="0">
-        <x:v>681000</x:v>
+        <x:v>17495257</x:v>
       </x:c>
       <x:c r="D201" s="0">
-        <x:v>3469200</x:v>
+        <x:v>17500000</x:v>
       </x:c>
       <x:c r="E201" s="0">
-        <x:v>175000000</x:v>
+        <x:v>525000000</x:v>
       </x:c>
       <x:c r="F201" s="0">
-        <x:v>26542774</x:v>
+        <x:v>409385433</x:v>
       </x:c>
       <x:c r="G201" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H201" s="0">
-        <x:v>0.49</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I201" s="0">
-        <x:v>35.98</x:v>
+        <x:v>15.43</x:v>
       </x:c>
       <x:c r="J201" s="0">
-        <x:v>38.98</x:v>
+        <x:v>23.4</x:v>
       </x:c>
       <x:c r="K201" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:11">
       <x:c r="A202" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C202" s="0">
-        <x:v>1060056</x:v>
+        <x:v>9350000</x:v>
       </x:c>
       <x:c r="D202" s="0">
-        <x:v>7000000</x:v>
+        <x:v>14710247</x:v>
       </x:c>
       <x:c r="E202" s="0">
-        <x:v>250000000</x:v>
+        <x:v>150000000</x:v>
       </x:c>
       <x:c r="F202" s="0">
-        <x:v>60762934</x:v>
+        <x:v>69547091</x:v>
       </x:c>
       <x:c r="G202" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H202" s="0">
-        <x:v>0.44</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I202" s="0">
-        <x:v>216.8</x:v>
+        <x:v>1.59</x:v>
       </x:c>
       <x:c r="J202" s="0">
-        <x:v>57.32</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="K202" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:11">
       <x:c r="A203" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C203" s="0">
-        <x:v>132750000</x:v>
+        <x:v>1468255</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E203" s="0">
-        <x:v>2000000000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F203" s="0">
-        <x:v>565141750</x:v>
+        <x:v>75911475</x:v>
       </x:c>
       <x:c r="G203" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H203" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="I203" s="0">
-        <x:v>2.26</x:v>
+        <x:v>22.56</x:v>
       </x:c>
       <x:c r="J203" s="0">
-        <x:v>4.26</x:v>
+        <x:v>51.7</x:v>
       </x:c>
       <x:c r="K203" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:11">
       <x:c r="A204" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C204" s="0">
-        <x:v>373000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="D204" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="E204" s="0">
-        <x:v>75000000</x:v>
+        <x:v>60000000</x:v>
       </x:c>
       <x:c r="F204" s="0">
-        <x:v>23786370</x:v>
+        <x:v>13401783</x:v>
       </x:c>
       <x:c r="G204" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H204" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I204" s="0">
-        <x:v>5.44</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="J204" s="0">
-        <x:v>63.77</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="K204" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:11">
       <x:c r="A205" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C205" s="0">
-        <x:v>10000000</x:v>
+        <x:v>725000</x:v>
       </x:c>
       <x:c r="D205" s="0">
         <x:v>10000000</x:v>
       </x:c>
       <x:c r="E205" s="0">
-        <x:v>140000000</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F205" s="0">
-        <x:v>133271568</x:v>
+        <x:v>48539975</x:v>
       </x:c>
       <x:c r="G205" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H205" s="0">
-        <x:v>0.67</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I205" s="0">
-        <x:v>9.12</x:v>
+        <x:v>32.98</x:v>
       </x:c>
       <x:c r="J205" s="0">
-        <x:v>13.33</x:v>
+        <x:v>66.95</x:v>
       </x:c>
       <x:c r="K205" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:11">
       <x:c r="A206" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C206" s="0">
-        <x:v>66142950</x:v>
+        <x:v>761000</x:v>
       </x:c>
       <x:c r="D206" s="0">
-        <x:v>105000000</x:v>
+        <x:v>3469200</x:v>
       </x:c>
       <x:c r="E206" s="0">
-        <x:v>650000000</x:v>
+        <x:v>175000000</x:v>
       </x:c>
       <x:c r="F206" s="0">
-        <x:v>384952260</x:v>
+        <x:v>29441174</x:v>
       </x:c>
       <x:c r="G206" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H206" s="0">
-        <x:v>2.71</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="I206" s="0">
-        <x:v>4.15</x:v>
+        <x:v>35.3</x:v>
       </x:c>
       <x:c r="J206" s="0">
-        <x:v>5.82</x:v>
+        <x:v>38.69</x:v>
       </x:c>
       <x:c r="K206" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:11">
       <x:c r="A207" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="C207" s="0">
+        <x:v>1060056</x:v>
+      </x:c>
+      <x:c r="D207" s="0">
+        <x:v>7000000</x:v>
+      </x:c>
+      <x:c r="E207" s="0">
+        <x:v>250000000</x:v>
+      </x:c>
+      <x:c r="F207" s="0">
+        <x:v>60762934</x:v>
+      </x:c>
+      <x:c r="G207" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H207" s="0">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I207" s="0">
+        <x:v>204.3</x:v>
+      </x:c>
+      <x:c r="J207" s="0">
+        <x:v>57.32</x:v>
+      </x:c>
+      <x:c r="K207" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:11">
+      <x:c r="A208" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="C208" s="0">
+        <x:v>132750000</x:v>
+      </x:c>
+      <x:c r="D208" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E208" s="0">
+        <x:v>2000000000</x:v>
+      </x:c>
+      <x:c r="F208" s="0">
+        <x:v>565141750</x:v>
+      </x:c>
+      <x:c r="G208" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H208" s="0">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="I208" s="0">
+        <x:v>2.11</x:v>
+      </x:c>
+      <x:c r="J208" s="0">
+        <x:v>4.26</x:v>
+      </x:c>
+      <x:c r="K208" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:11">
+      <x:c r="A209" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="C209" s="0">
+        <x:v>373000</x:v>
+      </x:c>
+      <x:c r="D209" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="E209" s="0">
+        <x:v>75000000</x:v>
+      </x:c>
+      <x:c r="F209" s="0">
+        <x:v>23786370</x:v>
+      </x:c>
+      <x:c r="G209" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H209" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="I209" s="0">
+        <x:v>4.9</x:v>
+      </x:c>
+      <x:c r="J209" s="0">
+        <x:v>63.77</x:v>
+      </x:c>
+      <x:c r="K209" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:11">
+      <x:c r="A210" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="C210" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="D210" s="0">
+        <x:v>10000000</x:v>
+      </x:c>
+      <x:c r="E210" s="0">
+        <x:v>140000000</x:v>
+      </x:c>
+      <x:c r="F210" s="0">
+        <x:v>133271568</x:v>
+      </x:c>
+      <x:c r="G210" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H210" s="0">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I210" s="0">
+        <x:v>9.43</x:v>
+      </x:c>
+      <x:c r="J210" s="0">
+        <x:v>13.33</x:v>
+      </x:c>
+      <x:c r="K210" s="0" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="B207" s="0" t="s">
+    </x:row>
+    <x:row r="211" spans="1:11">
+      <x:c r="A211" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="C207" s="0">
+      <x:c r="C211" s="0">
+        <x:v>66142950</x:v>
+      </x:c>
+      <x:c r="D211" s="0">
+        <x:v>105000000</x:v>
+      </x:c>
+      <x:c r="E211" s="0">
+        <x:v>650000000</x:v>
+      </x:c>
+      <x:c r="F211" s="0">
+        <x:v>384952260</x:v>
+      </x:c>
+      <x:c r="G211" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H211" s="0">
+        <x:v>2.71</x:v>
+      </x:c>
+      <x:c r="I211" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J211" s="0">
+        <x:v>5.82</x:v>
+      </x:c>
+      <x:c r="K211" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:11">
+      <x:c r="A212" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="C212" s="0">
         <x:v>3081843</x:v>
       </x:c>
-      <x:c r="D207" s="0">
+      <x:c r="D212" s="0">
         <x:v>5000000</x:v>
       </x:c>
-      <x:c r="E207" s="0">
+      <x:c r="E212" s="0">
         <x:v>100000000</x:v>
       </x:c>
-      <x:c r="F207" s="0">
+      <x:c r="F212" s="0">
         <x:v>43986444</x:v>
       </x:c>
-      <x:c r="G207" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H207" s="0">
+      <x:c r="G212" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H212" s="0">
         <x:v>0.66</x:v>
       </x:c>
-      <x:c r="I207" s="0">
-        <x:v>4.95</x:v>
-      </x:c>
-      <x:c r="J207" s="0">
+      <x:c r="I212" s="0">
+        <x:v>4.84</x:v>
+      </x:c>
+      <x:c r="J212" s="0">
         <x:v>14.27</x:v>
       </x:c>
-      <x:c r="K207" s="0" t="s">
-        <x:v>296</x:v>
+      <x:c r="K212" s="0" t="s">
+        <x:v>299</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -73,18 +73,18 @@
     <x:t>ULUUN</x:t>
   </x:si>
   <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUICK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
     <x:t>07.10.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUICK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
     <x:t>SVGYO</x:t>
   </x:si>
   <x:si>
@@ -1112,6 +1112,9 @@
   </x:si>
   <x:si>
     <x:t>29.08.2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>PSGYO</x:t>
@@ -1619,7 +1622,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>12.91</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1651,7 +1654,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>30.46</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>32.34</x:v>
@@ -1686,7 +1689,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>47.7</x:v>
+        <x:v>52.45</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1700,7 +1703,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>3400630</x:v>
+        <x:v>5648081</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>75000000</x:v>
@@ -1709,33 +1712,33 @@
         <x:v>525000000</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>22727179</x:v>
+        <x:v>37908802</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>0.45</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>6.98</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="J5" s="0">
-        <x:v>6.68</x:v>
+        <x:v>6.71</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>2425000</x:v>
+        <x:v>3120684</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>30000000</x:v>
@@ -1744,27 +1747,27 @@
         <x:v>210000000</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>17158250</x:v>
+        <x:v>22296364</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>7.76</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>7.99</x:v>
+        <x:v>7.92</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>7.08</x:v>
+        <x:v>7.14</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>16</x:v>
@@ -1788,7 +1791,7 @@
         <x:v>0.31</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>49.08</x:v>
+        <x:v>49.48</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>47.54</x:v>
@@ -1799,7 +1802,7 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>16</x:v>
@@ -1823,13 +1826,13 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>4.14</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>4.21</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -1858,13 +1861,13 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>3.34</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>3.38</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1893,7 +1896,7 @@
         <x:v>0.34</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>51.85</x:v>
+        <x:v>53.8</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>52.68</x:v>
@@ -1928,13 +1931,13 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>99.2</x:v>
+        <x:v>109.1</x:v>
       </x:c>
       <x:c r="J11" s="0">
         <x:v>85.19</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -1963,7 +1966,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.72</x:v>
+        <x:v>21.2</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>19.3</x:v>
@@ -1998,7 +2001,7 @@
         <x:v>4.2</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>7.25</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>7.05</x:v>
@@ -2015,7 +2018,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>425944</x:v>
+        <x:v>490875</x:v>
       </x:c>
       <x:c r="D14" s="0">
         <x:v>7000000</x:v>
@@ -2024,22 +2027,22 @@
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>7011108</x:v>
+        <x:v>8097404</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>16.72</x:v>
+        <x:v>16.74</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>16.46</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -2068,13 +2071,13 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>8.88</x:v>
+        <x:v>8.79</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>8.64</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -2085,7 +2088,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>265485</x:v>
+        <x:v>350031</x:v>
       </x:c>
       <x:c r="D16" s="0">
         <x:v>4000000</x:v>
@@ -2094,22 +2097,22 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>7144755</x:v>
+        <x:v>9595743</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>1.46</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>29.42</x:v>
+        <x:v>30.26</x:v>
       </x:c>
       <x:c r="J16" s="0">
-        <x:v>26.91</x:v>
+        <x:v>27.41</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -2138,7 +2141,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>13.66</x:v>
+        <x:v>14.24</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>10.38</x:v>
@@ -2155,7 +2158,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>335996</x:v>
+        <x:v>355996</x:v>
       </x:c>
       <x:c r="D18" s="0">
         <x:v>15000000</x:v>
@@ -2164,22 +2167,22 @@
         <x:v>110000000</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1789677</x:v>
+        <x:v>1899277</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>3.74</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>5.5</x:v>
+        <x:v>5.51</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>5.33</x:v>
+        <x:v>5.34</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -2208,13 +2211,13 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>3.29</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>3.34</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -2243,7 +2246,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>1.06</x:v>
+        <x:v>1.09</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>1.03</x:v>
@@ -2278,7 +2281,7 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>11.46</x:v>
+        <x:v>11.75</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>12.59</x:v>
@@ -2313,7 +2316,7 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>8.33</x:v>
+        <x:v>8.24</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>8.51</x:v>
@@ -2330,7 +2333,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>215000</x:v>
+        <x:v>220000</x:v>
       </x:c>
       <x:c r="D23" s="0">
         <x:v>5000000</x:v>
@@ -2339,7 +2342,7 @@
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>14218390</x:v>
+        <x:v>14541640</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>1.55</x:v>
@@ -2348,13 +2351,13 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>66.13</x:v>
+        <x:v>66.1</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -2365,7 +2368,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>1881188</x:v>
+        <x:v>2081188</x:v>
       </x:c>
       <x:c r="D24" s="0">
         <x:v>20000000</x:v>
@@ -2374,22 +2377,22 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>9152511</x:v>
+        <x:v>10072011</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>1.78</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0.17</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>4.62</x:v>
+        <x:v>5.08</x:v>
       </x:c>
       <x:c r="J24" s="0">
-        <x:v>4.87</x:v>
+        <x:v>4.84</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -2400,7 +2403,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>341000</x:v>
+        <x:v>706000</x:v>
       </x:c>
       <x:c r="D25" s="0">
         <x:v>28481914</x:v>
@@ -2409,22 +2412,22 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>2774376</x:v>
+        <x:v>5599476</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>4.55</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>7.78</x:v>
+        <x:v>8.05</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>8.14</x:v>
+        <x:v>7.93</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -2453,7 +2456,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>74.2</x:v>
+        <x:v>81.6</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>72.97</x:v>
@@ -2488,7 +2491,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>50.05</x:v>
+        <x:v>47.44</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>0</x:v>
@@ -2520,13 +2523,13 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>4.27</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>4.32</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
@@ -2537,7 +2540,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>5409436</x:v>
+        <x:v>5529436</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>11848341</x:v>
@@ -2546,22 +2549,22 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>49955603</x:v>
+        <x:v>50966603</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>1.69</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.77</x:v>
+        <x:v>0.79</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>8.46</x:v>
+        <x:v>8.64</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>9.23</x:v>
+        <x:v>9.22</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
@@ -2590,7 +2593,7 @@
         <x:v>1.13</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>7.57</x:v>
+        <x:v>7.76</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>7.82</x:v>
@@ -2625,7 +2628,7 @@
         <x:v>2.7</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>7.25</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>6.81</x:v>
@@ -2660,7 +2663,7 @@
         <x:v>0.51</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>1.6</x:v>
+        <x:v>1.62</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>1.59</x:v>
@@ -2677,7 +2680,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>275229</x:v>
+        <x:v>305229</x:v>
       </x:c>
       <x:c r="D33" s="0">
         <x:v>2000000</x:v>
@@ -2686,22 +2689,22 @@
         <x:v>40000000</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>3112058</x:v>
+        <x:v>3452978</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2.38</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>11.36</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>11.31</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
@@ -2712,7 +2715,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>5318015</x:v>
+        <x:v>6194766</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>15000000</x:v>
@@ -2721,22 +2724,22 @@
         <x:v>50000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>11357225</x:v>
+        <x:v>13192265</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>0.69</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.18</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>2.14</x:v>
+        <x:v>2.13</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
@@ -2765,13 +2768,13 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>29.98</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>29.29</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -2800,7 +2803,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>72.75</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>74.13</x:v>
@@ -2835,7 +2838,7 @@
         <x:v>0.61</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>50.3</x:v>
+        <x:v>51.5</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>57.9</x:v>
@@ -2870,7 +2873,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>38.92</x:v>
+        <x:v>38.98</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2902,7 +2905,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>125.9</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>115.6</x:v>
@@ -2937,13 +2940,13 @@
         <x:v>0.42</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>3.06</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>3.12</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
@@ -2954,7 +2957,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>1853000</x:v>
+        <x:v>2136000</x:v>
       </x:c>
       <x:c r="D41" s="0">
         <x:v>5000000</x:v>
@@ -2963,22 +2966,22 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>223145353</x:v>
+        <x:v>254855503</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>1.48</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>121.5</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="J41" s="0">
-        <x:v>120.42</x:v>
+        <x:v>119.31</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
@@ -3007,7 +3010,7 @@
         <x:v>0.34</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>36.94</x:v>
+        <x:v>36.6</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>37.34</x:v>
@@ -3077,7 +3080,7 @@
         <x:v>2.7</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>7.25</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.81</x:v>
@@ -3094,7 +3097,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>23944766</x:v>
+        <x:v>24896406</x:v>
       </x:c>
       <x:c r="D45" s="0">
         <x:v>50000000</x:v>
@@ -3103,22 +3106,22 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>136190413</x:v>
+        <x:v>141706118</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>4.63</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>2.22</x:v>
+        <x:v>2.31</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>5.8</x:v>
+        <x:v>5.88</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>5.69</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
@@ -3147,7 +3150,7 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>9.58</x:v>
+        <x:v>9.77</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>9.96</x:v>
@@ -3182,7 +3185,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>18.73</x:v>
+        <x:v>19.7</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>20.88</x:v>
@@ -3217,13 +3220,13 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>14.01</x:v>
+        <x:v>13.93</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>13.84</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
@@ -3252,7 +3255,7 @@
         <x:v>0.37</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>32.7</x:v>
+        <x:v>32.2</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>34.56</x:v>
@@ -3287,7 +3290,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>6.82</x:v>
+        <x:v>6.92</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>7.25</x:v>
@@ -3322,7 +3325,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>30.46</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>32.34</x:v>
@@ -3357,7 +3360,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>3.51</x:v>
@@ -3392,13 +3395,13 @@
         <x:v>3.78</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>1.99</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>2.14</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
@@ -3433,7 +3436,7 @@
         <x:v>8.33</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
@@ -3444,7 +3447,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>3689298</x:v>
+        <x:v>3839798</x:v>
       </x:c>
       <x:c r="D55" s="0">
         <x:v>12000000</x:v>
@@ -3453,22 +3456,22 @@
         <x:v>600000000</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>138512360</x:v>
+        <x:v>144083118</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2.16</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>0.66</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>37.26</x:v>
+        <x:v>38.04</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>37.54</x:v>
+        <x:v>37.52</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
@@ -3497,7 +3500,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>3.84</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>3.78</x:v>
@@ -3514,7 +3517,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>165000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="D57" s="0">
         <x:v>5000000</x:v>
@@ -3523,22 +3526,22 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F57" s="0">
-        <x:v>7525285</x:v>
+        <x:v>9105535</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>45.36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>45.61</x:v>
+        <x:v>45.53</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
@@ -3567,7 +3570,7 @@
         <x:v>0.24</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>22.5</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>24.37</x:v>
@@ -3602,7 +3605,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>4.25</x:v>
+        <x:v>4.67</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>6.94</x:v>
@@ -3637,7 +3640,7 @@
         <x:v>2.38</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>7.92</x:v>
+        <x:v>8.01</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>8.87</x:v>
@@ -3672,7 +3675,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>5</x:v>
+        <x:v>5.04</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>5.95</x:v>
@@ -3707,7 +3710,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>34.5</x:v>
+        <x:v>35.44</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>37.41</x:v>
@@ -3742,13 +3745,13 @@
         <x:v>4.22</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>124.2</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>86.07</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
@@ -3759,7 +3762,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>8520576</x:v>
+        <x:v>9780787</x:v>
       </x:c>
       <x:c r="D64" s="0">
         <x:v>100000000</x:v>
@@ -3768,22 +3771,22 @@
         <x:v>700000000</x:v>
       </x:c>
       <x:c r="F64" s="0">
-        <x:v>42873561</x:v>
+        <x:v>49180917</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0.43</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
@@ -3794,7 +3797,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>24301435</x:v>
+        <x:v>27555966</x:v>
       </x:c>
       <x:c r="D65" s="0">
         <x:v>60000000</x:v>
@@ -3803,22 +3806,22 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F65" s="0">
-        <x:v>59665231</x:v>
+        <x:v>67384313</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>1.54</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0.62</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>2.4</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>2.46</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
@@ -3864,7 +3867,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>116174</x:v>
+        <x:v>121130</x:v>
       </x:c>
       <x:c r="D67" s="0">
         <x:v>9260000</x:v>
@@ -3873,7 +3876,7 @@
         <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>11359357</x:v>
+        <x:v>11864869</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>10</x:v>
@@ -3882,13 +3885,13 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>102.1</x:v>
+        <x:v>101.6</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>97.78</x:v>
+        <x:v>97.95</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
@@ -3899,7 +3902,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>856204</x:v>
+        <x:v>1276630</x:v>
       </x:c>
       <x:c r="D68" s="0">
         <x:v>2500000</x:v>
@@ -3908,22 +3911,22 @@
         <x:v>225000000</x:v>
       </x:c>
       <x:c r="F68" s="0">
-        <x:v>61745274</x:v>
+        <x:v>93067011</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>0.74</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>72.6</x:v>
+        <x:v>73.5</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>72.12</x:v>
+        <x:v>72.9</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
@@ -3934,7 +3937,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>6972564</x:v>
+        <x:v>7537299</x:v>
       </x:c>
       <x:c r="D69" s="0">
         <x:v>50000000</x:v>
@@ -3943,22 +3946,22 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>295390414</x:v>
+        <x:v>322502212</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>1.92</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>48.02</x:v>
+        <x:v>48.38</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>42.36</x:v>
+        <x:v>42.79</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
@@ -3969,7 +3972,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>46035847</x:v>
+        <x:v>46260161</x:v>
       </x:c>
       <x:c r="D70" s="0">
         <x:v>180000000</x:v>
@@ -3978,7 +3981,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F70" s="0">
-        <x:v>592056574</x:v>
+        <x:v>595217159</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2</x:v>
@@ -3987,13 +3990,13 @@
         <x:v>0.51</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>14.15</x:v>
+        <x:v>14.28</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>12.86</x:v>
+        <x:v>12.87</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
@@ -4004,7 +4007,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>1814552</x:v>
+        <x:v>1914552</x:v>
       </x:c>
       <x:c r="D71" s="0">
         <x:v>25000000</x:v>
@@ -4013,22 +4016,22 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F71" s="0">
-        <x:v>42596745</x:v>
+        <x:v>44957845</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>4.84</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0.35</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>23.72</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>23.48</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
@@ -4057,13 +4060,13 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>37.24</x:v>
+        <x:v>37.7</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>37.46</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
@@ -4092,7 +4095,7 @@
         <x:v>1.42</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>127.8</x:v>
+        <x:v>129.5</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>137.41</x:v>
@@ -4109,7 +4112,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>110740</x:v>
+        <x:v>113000</x:v>
       </x:c>
       <x:c r="D74" s="0">
         <x:v>1000000</x:v>
@@ -4118,7 +4121,7 @@
         <x:v>300000000</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>31594890</x:v>
+        <x:v>32196680</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>0.98</x:v>
@@ -4127,13 +4130,13 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>274.5</x:v>
+        <x:v>280.5</x:v>
       </x:c>
       <x:c r="J74" s="0">
-        <x:v>285.31</x:v>
+        <x:v>284.93</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
@@ -4144,7 +4147,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>975029</x:v>
+        <x:v>1033649</x:v>
       </x:c>
       <x:c r="D75" s="0">
         <x:v>2850000</x:v>
@@ -4153,22 +4156,22 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F75" s="0">
-        <x:v>29677673</x:v>
+        <x:v>31466228</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2.41</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0.87</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>30.6</x:v>
+        <x:v>30.4</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>30.44</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
@@ -4197,7 +4200,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>52.4</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>53.69</x:v>
@@ -4232,7 +4235,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>8.7</x:v>
+        <x:v>9.02</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>0</x:v>
@@ -4264,7 +4267,7 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>1.38</x:v>
+        <x:v>1.49</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.89</x:v>
@@ -4281,7 +4284,7 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>1285319</x:v>
+        <x:v>1365338</x:v>
       </x:c>
       <x:c r="D79" s="0">
         <x:v>36000000</x:v>
@@ -4290,22 +4293,22 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F79" s="0">
-        <x:v>6947586</x:v>
+        <x:v>7376488</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>3.75</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>5.41</x:v>
+        <x:v>5.53</x:v>
       </x:c>
       <x:c r="J79" s="0">
-        <x:v>5.41</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
@@ -4334,7 +4337,7 @@
         <x:v>0.32</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>7.23</x:v>
+        <x:v>7.34</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>7.98</x:v>
@@ -4351,7 +4354,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>6329227</x:v>
+        <x:v>6384227</x:v>
       </x:c>
       <x:c r="D81" s="0">
         <x:v>13500000</x:v>
@@ -4360,22 +4363,22 @@
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>102521068</x:v>
+        <x:v>103421418</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>3.16</x:v>
+        <x:v>3.19</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>16.41</x:v>
+        <x:v>17.65</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>16.2</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
@@ -4404,7 +4407,7 @@
         <x:v>3.86</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>5</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>6.91</x:v>
@@ -4439,7 +4442,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>5.62</x:v>
+        <x:v>6.18</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>23.68</x:v>
@@ -4474,13 +4477,13 @@
         <x:v>1.07</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>4.03</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>3.72</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
@@ -4509,7 +4512,7 @@
         <x:v>3.83</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>9.41</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>0.76</x:v>
@@ -4579,7 +4582,7 @@
         <x:v>8.08</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>10.5</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0.73</x:v>
@@ -4614,13 +4617,13 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.9</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>60.51</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
@@ -4649,7 +4652,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.98</x:v>
+        <x:v>1.03</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>1.14</x:v>
@@ -4684,7 +4687,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>118.6</x:v>
+        <x:v>119.5</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>0</x:v>
@@ -4716,7 +4719,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>3.3</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>6.13</x:v>
@@ -4733,7 +4736,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>11196031</x:v>
+        <x:v>12590031</x:v>
       </x:c>
       <x:c r="D92" s="0">
         <x:v>25000000</x:v>
@@ -4742,22 +4745,22 @@
         <x:v>240000000</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>110381015</x:v>
+        <x:v>123385085</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>1.04</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>0.46</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>9.3</x:v>
+        <x:v>9.54</x:v>
       </x:c>
       <x:c r="J92" s="0">
-        <x:v>9.86</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
@@ -4786,7 +4789,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>7.23</x:v>
+        <x:v>7.34</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>9.69</x:v>
@@ -4821,7 +4824,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>15.61</x:v>
+        <x:v>14.72</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>15.28</x:v>
@@ -4856,7 +4859,7 @@
         <x:v>1.07</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>1.43</x:v>
+        <x:v>1.49</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>1.51</x:v>
@@ -4891,7 +4894,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>16.17</x:v>
+        <x:v>16.14</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>15.9</x:v>
@@ -4908,7 +4911,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>10092017</x:v>
+        <x:v>11514033</x:v>
       </x:c>
       <x:c r="D97" s="0">
         <x:v>40000000</x:v>
@@ -4917,22 +4920,22 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F97" s="0">
-        <x:v>174648368</x:v>
+        <x:v>199305477</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>4.81</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>1.21</x:v>
+        <x:v>1.38</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>17.97</x:v>
+        <x:v>19.42</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>17.31</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
@@ -4961,7 +4964,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>3.41</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>3.59</x:v>
@@ -4996,7 +4999,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>401</x:v>
+        <x:v>402.75</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>380.17</x:v>
@@ -5031,7 +5034,7 @@
         <x:v>1.59</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>57.5</x:v>
+        <x:v>57.45</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>68.91</x:v>
@@ -5066,7 +5069,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>23.8</x:v>
+        <x:v>26.18</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>38.82</x:v>
@@ -5101,13 +5104,13 @@
         <x:v>2.4</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>42.24</x:v>
+        <x:v>43.9</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>47.51</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
@@ -5136,7 +5139,7 @@
         <x:v>2.36</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>7.96</x:v>
+        <x:v>8.61</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>32.87</x:v>
@@ -5171,7 +5174,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>14</x:v>
+        <x:v>14.03</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>13.65</x:v>
@@ -5206,7 +5209,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>15.58</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>21.09</x:v>
@@ -5223,7 +5226,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>1423000</x:v>
+        <x:v>1618000</x:v>
       </x:c>
       <x:c r="D106" s="0">
         <x:v>21739600</x:v>
@@ -5232,22 +5235,22 @@
         <x:v>350000000</x:v>
       </x:c>
       <x:c r="F106" s="0">
-        <x:v>11563775</x:v>
+        <x:v>13007224</x:v>
       </x:c>
       <x:c r="G106" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>7.57</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>8.13</x:v>
+        <x:v>8.04</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
@@ -5276,7 +5279,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>8.78</x:v>
+        <x:v>8.9</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5308,7 +5311,7 @@
         <x:v>0.57</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>7.65</x:v>
+        <x:v>7.67</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>6.98</x:v>
@@ -5343,7 +5346,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>127.8</x:v>
+        <x:v>129.5</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>0</x:v>
@@ -5375,7 +5378,7 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>15.34</x:v>
+        <x:v>16.87</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>7.61</x:v>
@@ -5410,7 +5413,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>19.87</x:v>
+        <x:v>20.24</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>28.89</x:v>
@@ -5445,7 +5448,7 @@
         <x:v>1.62</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>8.05</x:v>
+        <x:v>8.11</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>9.52</x:v>
@@ -5480,7 +5483,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>4.15</x:v>
+        <x:v>4.12</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>0</x:v>
@@ -5512,7 +5515,7 @@
         <x:v>2.79</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>21.06</x:v>
+        <x:v>21.02</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>23.25</x:v>
@@ -5547,7 +5550,7 @@
         <x:v>1.13</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>48.02</x:v>
+        <x:v>48.38</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>28.18</x:v>
@@ -5582,7 +5585,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>9.3</x:v>
+        <x:v>9.24</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>13.34</x:v>
@@ -5617,7 +5620,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>28.72</x:v>
+        <x:v>27.4</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>39.18</x:v>
@@ -5652,7 +5655,7 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>59.93</x:v>
@@ -5687,7 +5690,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>3.61</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>48.39</x:v>
@@ -5722,7 +5725,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>1.93</x:v>
+        <x:v>2.08</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5754,7 +5757,7 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>8.37</x:v>
+        <x:v>8.85</x:v>
       </x:c>
       <x:c r="J121" s="0">
         <x:v>26.19</x:v>
@@ -5771,7 +5774,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>29146645</x:v>
+        <x:v>29346645</x:v>
       </x:c>
       <x:c r="D122" s="0">
         <x:v>35000000</x:v>
@@ -5780,22 +5783,22 @@
         <x:v>300000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>229749719</x:v>
+        <x:v>230894719</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>16.25</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>7.29</x:v>
+        <x:v>7.34</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>5.82</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>7.88</x:v>
+        <x:v>7.87</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
@@ -5824,7 +5827,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>29.98</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>61.87</x:v>
@@ -5859,7 +5862,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>13.99</x:v>
+        <x:v>14.34</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>21.06</x:v>
@@ -5894,7 +5897,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>3.61</x:v>
+        <x:v>3.73</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>0</x:v>
@@ -5926,7 +5929,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>14.15</x:v>
+        <x:v>14.28</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>9.8</x:v>
@@ -5961,7 +5964,7 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>14.8</x:v>
+        <x:v>16.28</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>23.95</x:v>
@@ -5996,7 +5999,7 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>401</x:v>
+        <x:v>402.75</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>528.86</x:v>
@@ -6031,7 +6034,7 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>48.02</x:v>
+        <x:v>48.38</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>24.19</x:v>
@@ -6066,7 +6069,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>14.15</x:v>
+        <x:v>14.28</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>10.74</x:v>
@@ -6101,7 +6104,7 @@
         <x:v>0.69</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>5.41</x:v>
+        <x:v>5.53</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>6.01</x:v>
@@ -6136,7 +6139,7 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>10.69</x:v>
+        <x:v>11.03</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>20.61</x:v>
@@ -6171,7 +6174,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.07</x:v>
+        <x:v>4.34</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>4.46</x:v>
@@ -6206,7 +6209,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>5</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>12.82</x:v>
@@ -6241,7 +6244,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>0</x:v>
@@ -6273,7 +6276,7 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>1.74</x:v>
+        <x:v>1.91</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>52.14</x:v>
@@ -6308,7 +6311,7 @@
         <x:v>1.83</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>37.24</x:v>
+        <x:v>37.7</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>39.62</x:v>
@@ -6325,7 +6328,7 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>5899828</x:v>
+        <x:v>5999828</x:v>
       </x:c>
       <x:c r="D138" s="0">
         <x:v>3000000</x:v>
@@ -6334,22 +6337,22 @@
         <x:v>300000000</x:v>
       </x:c>
       <x:c r="F138" s="0">
-        <x:v>223937644</x:v>
+        <x:v>226137644</x:v>
       </x:c>
       <x:c r="G138" s="0">
         <x:v>3.75</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>1.47</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="J138" s="0">
-        <x:v>37.96</x:v>
+        <x:v>37.69</x:v>
       </x:c>
       <x:c r="K138" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:11">
@@ -6378,7 +6381,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>18.01</x:v>
+        <x:v>18.39</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>0</x:v>
@@ -6392,7 +6395,7 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>14837681</x:v>
+        <x:v>15837681</x:v>
       </x:c>
       <x:c r="D140" s="0">
         <x:v>6500000</x:v>
@@ -6401,22 +6404,22 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F140" s="0">
-        <x:v>53535183</x:v>
+        <x:v>56135183</x:v>
       </x:c>
       <x:c r="G140" s="0">
-        <x:v>1.43</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>2.63</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J140" s="0">
-        <x:v>3.61</x:v>
+        <x:v>3.54</x:v>
       </x:c>
       <x:c r="K140" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:11">
@@ -6445,7 +6448,7 @@
         <x:v>0.37</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>29.3</x:v>
+        <x:v>29.62</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>30.83</x:v>
@@ -6480,7 +6483,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>284.25</x:v>
+        <x:v>287.5</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>299.91</x:v>
@@ -6515,7 +6518,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>19.61</x:v>
+        <x:v>19.85</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>19.3</x:v>
@@ -6550,7 +6553,7 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>243.5</x:v>
+        <x:v>236.1</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>83</x:v>
@@ -6585,7 +6588,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>23.52</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="J145" s="0">
         <x:v>40.97</x:v>
@@ -6620,7 +6623,7 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>5.62</x:v>
+        <x:v>6.18</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>23.68</x:v>
@@ -6655,7 +6658,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>14</x:v>
+        <x:v>14.03</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>5.49</x:v>
@@ -6690,7 +6693,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>16.17</x:v>
+        <x:v>16.14</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>0</x:v>
@@ -6722,7 +6725,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>4.36</x:v>
+        <x:v>4.42</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>0</x:v>
@@ -6754,7 +6757,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>1.88</x:v>
+        <x:v>1.93</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>3.98</x:v>
@@ -6789,7 +6792,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>5.61</x:v>
+        <x:v>5.64</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>6.6</x:v>
@@ -6824,7 +6827,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>10.69</x:v>
+        <x:v>11.03</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>17.83</x:v>
@@ -6859,7 +6862,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>24.58</x:v>
+        <x:v>24.4</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>38.06</x:v>
@@ -6894,7 +6897,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>207.4</x:v>
+        <x:v>213.8</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>0</x:v>
@@ -6926,7 +6929,7 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>25.8</x:v>
+        <x:v>26.9</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>41.13</x:v>
@@ -6961,7 +6964,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>2.92</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>20.11</x:v>
@@ -6996,7 +6999,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>39.43</x:v>
@@ -7031,7 +7034,7 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>18.37</x:v>
+        <x:v>18.66</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>16.34</x:v>
@@ -7066,7 +7069,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>9.55</x:v>
+        <x:v>9.72</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>0</x:v>
@@ -7098,7 +7101,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>39.02</x:v>
+        <x:v>39.16</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>0</x:v>
@@ -7130,7 +7133,7 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>14.28</x:v>
+        <x:v>12.86</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>38.88</x:v>
@@ -7165,7 +7168,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>4.25</x:v>
+        <x:v>4.67</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>10.75</x:v>
@@ -7200,7 +7203,7 @@
         <x:v>2.16</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>28.3</x:v>
+        <x:v>29.88</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>37.66</x:v>
@@ -7235,7 +7238,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>1.49</x:v>
+        <x:v>1.63</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>0</x:v>
@@ -7267,7 +7270,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.23</x:v>
+        <x:v>7.34</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>15.68</x:v>
@@ -7302,7 +7305,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>1.33</x:v>
+        <x:v>1.37</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>4.02</x:v>
@@ -7337,7 +7340,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>4.25</x:v>
+        <x:v>4.67</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>161.23</x:v>
@@ -7372,7 +7375,7 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>1.63</x:v>
+        <x:v>1.73</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>4.93</x:v>
@@ -7407,7 +7410,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>100.2</x:v>
+        <x:v>98.55</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>95.58</x:v>
@@ -7442,7 +7445,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>43.92</x:v>
+        <x:v>43.88</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>0</x:v>
@@ -7474,7 +7477,7 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>2.4</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>2.45</x:v>
@@ -7509,7 +7512,7 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.9</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>58.33</x:v>
@@ -7544,7 +7547,7 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>15.58</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="J173" s="0">
         <x:v>21.09</x:v>
@@ -7579,7 +7582,7 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>3.75</x:v>
+        <x:v>3.81</x:v>
       </x:c>
       <x:c r="J174" s="0">
         <x:v>16.87</x:v>
@@ -7614,7 +7617,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>3.3</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="J175" s="0">
         <x:v>11.99</x:v>
@@ -7649,7 +7652,7 @@
         <x:v>0.68</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>12.12</x:v>
+        <x:v>13.33</x:v>
       </x:c>
       <x:c r="J176" s="0">
         <x:v>35.38</x:v>
@@ -7684,7 +7687,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>5.38</x:v>
+        <x:v>5.45</x:v>
       </x:c>
       <x:c r="J177" s="0">
         <x:v>0</x:v>
@@ -7716,7 +7719,7 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>4.12</x:v>
+        <x:v>4.53</x:v>
       </x:c>
       <x:c r="J178" s="0">
         <x:v>19.79</x:v>
@@ -7751,7 +7754,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>10.47</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="J179" s="0">
         <x:v>13.15</x:v>
@@ -7786,7 +7789,7 @@
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>1.43</x:v>
+        <x:v>1.49</x:v>
       </x:c>
       <x:c r="J180" s="0">
         <x:v>4.03</x:v>
@@ -7821,7 +7824,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="J181" s="0">
         <x:v>38.02</x:v>
@@ -7856,7 +7859,7 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>30.6</x:v>
+        <x:v>30.4</x:v>
       </x:c>
       <x:c r="J182" s="0">
         <x:v>17.65</x:v>
@@ -7891,7 +7894,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>8.76</x:v>
+        <x:v>9.57</x:v>
       </x:c>
       <x:c r="J183" s="0">
         <x:v>68.15</x:v>
@@ -7926,7 +7929,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>9.58</x:v>
+        <x:v>9.77</x:v>
       </x:c>
       <x:c r="J184" s="0">
         <x:v>10.98</x:v>
@@ -7961,7 +7964,7 @@
         <x:v>0.16</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>16.98</x:v>
+        <x:v>17.83</x:v>
       </x:c>
       <x:c r="J185" s="0">
         <x:v>22.05</x:v>
@@ -7996,7 +7999,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>121.5</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="J186" s="0">
         <x:v>284.58</x:v>
@@ -8031,7 +8034,7 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I187" s="0">
-        <x:v>41.7</x:v>
+        <x:v>37.54</x:v>
       </x:c>
       <x:c r="J187" s="0">
         <x:v>83.62</x:v>
@@ -8066,7 +8069,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I188" s="0">
-        <x:v>8.88</x:v>
+        <x:v>8.79</x:v>
       </x:c>
       <x:c r="J188" s="0">
         <x:v>0</x:v>
@@ -8098,7 +8101,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I189" s="0">
-        <x:v>13.27</x:v>
+        <x:v>13.66</x:v>
       </x:c>
       <x:c r="J189" s="0">
         <x:v>16.42</x:v>
@@ -8133,7 +8136,7 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I190" s="0">
-        <x:v>3.95</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="J190" s="0">
         <x:v>40.97</x:v>
@@ -8168,7 +8171,7 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I191" s="0">
-        <x:v>8.7</x:v>
+        <x:v>9.02</x:v>
       </x:c>
       <x:c r="J191" s="0">
         <x:v>15.92</x:v>
@@ -8203,7 +8206,7 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I192" s="0">
-        <x:v>108.3</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J192" s="0">
         <x:v>94.36</x:v>
@@ -8238,13 +8241,13 @@
         <x:v>5.26</x:v>
       </x:c>
       <x:c r="I193" s="0">
-        <x:v>4.26</x:v>
+        <x:v>4.32</x:v>
       </x:c>
       <x:c r="J193" s="0">
         <x:v>4.64</x:v>
       </x:c>
       <x:c r="K193" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:11">
@@ -8273,7 +8276,7 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I194" s="0">
-        <x:v>401</x:v>
+        <x:v>402.75</x:v>
       </x:c>
       <x:c r="J194" s="0">
         <x:v>429.82</x:v>
@@ -8308,7 +8311,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I195" s="0">
-        <x:v>1.94</x:v>
+        <x:v>2.01</x:v>
       </x:c>
       <x:c r="J195" s="0">
         <x:v>2.64</x:v>
@@ -8343,7 +8346,7 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I196" s="0">
-        <x:v>11.54</x:v>
+        <x:v>11.72</x:v>
       </x:c>
       <x:c r="J196" s="0">
         <x:v>8.23</x:v>
@@ -8378,7 +8381,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I197" s="0">
-        <x:v>2.37</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="J197" s="0">
         <x:v>0</x:v>
@@ -8410,7 +8413,7 @@
         <x:v>0.23</x:v>
       </x:c>
       <x:c r="I198" s="0">
-        <x:v>21.92</x:v>
+        <x:v>22.7</x:v>
       </x:c>
       <x:c r="J198" s="0">
         <x:v>23.66</x:v>
@@ -8445,7 +8448,7 @@
         <x:v>0.53</x:v>
       </x:c>
       <x:c r="I199" s="0">
-        <x:v>1.75</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="J199" s="0">
         <x:v>5.03</x:v>
@@ -8480,7 +8483,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I200" s="0">
-        <x:v>1.7</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="J200" s="0">
         <x:v>0</x:v>
@@ -8544,7 +8547,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I202" s="0">
-        <x:v>4.11</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="J202" s="0">
         <x:v>0</x:v>
@@ -8576,7 +8579,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I203" s="0">
-        <x:v>147</x:v>
+        <x:v>146.1</x:v>
       </x:c>
       <x:c r="J203" s="0">
         <x:v>50.97</x:v>
@@ -8611,7 +8614,7 @@
         <x:v>5.91</x:v>
       </x:c>
       <x:c r="I204" s="0">
-        <x:v>16.17</x:v>
+        <x:v>16.14</x:v>
       </x:c>
       <x:c r="J204" s="0">
         <x:v>10.93</x:v>
@@ -8646,7 +8649,7 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I205" s="0">
-        <x:v>32.7</x:v>
+        <x:v>32.2</x:v>
       </x:c>
       <x:c r="J205" s="0">
         <x:v>38.14</x:v>
@@ -8681,7 +8684,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I206" s="0">
-        <x:v>519.5</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="J206" s="0">
         <x:v>0</x:v>
@@ -8713,7 +8716,7 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I207" s="0">
-        <x:v>33.66</x:v>
+        <x:v>33.9</x:v>
       </x:c>
       <x:c r="J207" s="0">
         <x:v>25.82</x:v>
@@ -8748,7 +8751,7 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I208" s="0">
-        <x:v>4.41</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="J208" s="0">
         <x:v>4.56</x:v>
@@ -8783,7 +8786,7 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I209" s="0">
-        <x:v>127.8</x:v>
+        <x:v>129.5</x:v>
       </x:c>
       <x:c r="J209" s="0">
         <x:v>31.92</x:v>
@@ -8818,7 +8821,7 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I210" s="0">
-        <x:v>12.12</x:v>
+        <x:v>12.52</x:v>
       </x:c>
       <x:c r="J210" s="0">
         <x:v>15.2</x:v>
@@ -8853,7 +8856,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I211" s="0">
-        <x:v>48.02</x:v>
+        <x:v>48.38</x:v>
       </x:c>
       <x:c r="J211" s="0">
         <x:v>20.53</x:v>
@@ -8888,7 +8891,7 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I212" s="0">
-        <x:v>14.15</x:v>
+        <x:v>14.28</x:v>
       </x:c>
       <x:c r="J212" s="0">
         <x:v>4.48</x:v>
@@ -8923,7 +8926,7 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I213" s="0">
-        <x:v>123.8</x:v>
+        <x:v>123.3</x:v>
       </x:c>
       <x:c r="J213" s="0">
         <x:v>39.56</x:v>
@@ -8958,7 +8961,7 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I214" s="0">
-        <x:v>19.38</x:v>
+        <x:v>19.93</x:v>
       </x:c>
       <x:c r="J214" s="0">
         <x:v>15.05</x:v>
@@ -8975,7 +8978,7 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="C215" s="0">
-        <x:v>11323189</x:v>
+        <x:v>11348189</x:v>
       </x:c>
       <x:c r="D215" s="0">
         <x:v>21600000</x:v>
@@ -8984,22 +8987,22 @@
         <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F215" s="0">
-        <x:v>186810680</x:v>
+        <x:v>187078430</x:v>
       </x:c>
       <x:c r="G215" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H215" s="0">
-        <x:v>5.24</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="I215" s="0">
-        <x:v>10.79</x:v>
+        <x:v>11.13</x:v>
       </x:c>
       <x:c r="J215" s="0">
-        <x:v>16.5</x:v>
+        <x:v>16.49</x:v>
       </x:c>
       <x:c r="K215" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:11">
@@ -9028,7 +9031,7 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I216" s="0">
-        <x:v>45.36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J216" s="0">
         <x:v>30.45</x:v>
@@ -9063,7 +9066,7 @@
         <x:v>1.98</x:v>
       </x:c>
       <x:c r="I217" s="0">
-        <x:v>17.55</x:v>
+        <x:v>17.33</x:v>
       </x:c>
       <x:c r="J217" s="0">
         <x:v>11.47</x:v>
@@ -9098,7 +9101,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I218" s="0">
-        <x:v>1.99</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J218" s="0">
         <x:v>0</x:v>
@@ -9130,7 +9133,7 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I219" s="0">
-        <x:v>9.3</x:v>
+        <x:v>9.54</x:v>
       </x:c>
       <x:c r="J219" s="0">
         <x:v>7.82</x:v>
@@ -9165,7 +9168,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I220" s="0">
-        <x:v>13.24</x:v>
+        <x:v>13.34</x:v>
       </x:c>
       <x:c r="J220" s="0">
         <x:v>18.44</x:v>
@@ -9200,7 +9203,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I221" s="0">
-        <x:v>27.26</x:v>
+        <x:v>28.06</x:v>
       </x:c>
       <x:c r="J221" s="0">
         <x:v>0</x:v>
@@ -9232,7 +9235,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I222" s="0">
-        <x:v>519.5</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="J222" s="0">
         <x:v>0</x:v>
@@ -9264,7 +9267,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I223" s="0">
-        <x:v>229.5</x:v>
+        <x:v>230.6</x:v>
       </x:c>
       <x:c r="J223" s="0">
         <x:v>154.36</x:v>
@@ -9299,7 +9302,7 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I224" s="0">
-        <x:v>5.5</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="J224" s="0">
         <x:v>14.81</x:v>
@@ -9334,7 +9337,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I225" s="0">
-        <x:v>0.99</x:v>
+        <x:v>1.01</x:v>
       </x:c>
       <x:c r="J225" s="0">
         <x:v>13.82</x:v>
@@ -9369,7 +9372,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I226" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="J226" s="0">
         <x:v>7.15</x:v>
@@ -9404,7 +9407,7 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I227" s="0">
-        <x:v>519.5</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="J227" s="0">
         <x:v>242.84</x:v>
@@ -9439,7 +9442,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I228" s="0">
-        <x:v>728.5</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="J228" s="0">
         <x:v>226</x:v>
@@ -9474,7 +9477,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I229" s="0">
-        <x:v>5.5</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="J229" s="0">
         <x:v>14.11</x:v>
@@ -9509,7 +9512,7 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I230" s="0">
-        <x:v>0.99</x:v>
+        <x:v>1.01</x:v>
       </x:c>
       <x:c r="J230" s="0">
         <x:v>14.58</x:v>
@@ -9544,7 +9547,7 @@
         <x:v>1.74</x:v>
       </x:c>
       <x:c r="I231" s="0">
-        <x:v>146.5</x:v>
+        <x:v>142.5</x:v>
       </x:c>
       <x:c r="J231" s="0">
         <x:v>138.38</x:v>
@@ -9579,7 +9582,7 @@
         <x:v>3.6</x:v>
       </x:c>
       <x:c r="I232" s="0">
-        <x:v>36.94</x:v>
+        <x:v>36.6</x:v>
       </x:c>
       <x:c r="J232" s="0">
         <x:v>43</x:v>
@@ -9614,7 +9617,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I233" s="0">
-        <x:v>243.5</x:v>
+        <x:v>236.1</x:v>
       </x:c>
       <x:c r="J233" s="0">
         <x:v>0</x:v>
@@ -9646,7 +9649,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I234" s="0">
-        <x:v>2.63</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="J234" s="0">
         <x:v>11.89</x:v>
@@ -9681,7 +9684,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I235" s="0">
-        <x:v>34.5</x:v>
+        <x:v>35.44</x:v>
       </x:c>
       <x:c r="J235" s="0">
         <x:v>94</x:v>
@@ -9698,7 +9701,7 @@
         <x:v>365</x:v>
       </x:c>
       <x:c r="C236" s="0">
-        <x:v>2565919</x:v>
+        <x:v>2791213</x:v>
       </x:c>
       <x:c r="D236" s="0">
         <x:v>4250000</x:v>
@@ -9707,30 +9710,30 @@
         <x:v>40000000</x:v>
       </x:c>
       <x:c r="F236" s="0">
-        <x:v>17221295</x:v>
+        <x:v>18742029</x:v>
       </x:c>
       <x:c r="G236" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H236" s="0">
-        <x:v>3.02</x:v>
+        <x:v>3.28</x:v>
       </x:c>
       <x:c r="I236" s="0">
-        <x:v>6.75</x:v>
+        <x:v>6.89</x:v>
       </x:c>
       <x:c r="J236" s="0">
         <x:v>6.71</x:v>
       </x:c>
       <x:c r="K236" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="237" spans="1:11">
       <x:c r="A237" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C237" s="0">
         <x:v>15000000</x:v>
@@ -9751,21 +9754,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I237" s="0">
-        <x:v>1.72</x:v>
+        <x:v>1.73</x:v>
       </x:c>
       <x:c r="J237" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K237" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>369</x:v>
       </x:c>
     </x:row>
     <x:row r="238" spans="1:11">
       <x:c r="A238" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C238" s="0">
         <x:v>6397124</x:v>
@@ -9786,13 +9789,13 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I238" s="0">
-        <x:v>3.05</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="J238" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K238" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>372</x:v>
       </x:c>
     </x:row>
     <x:row r="239" spans="1:11">
@@ -9800,7 +9803,7 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C239" s="0">
         <x:v>17495257</x:v>
@@ -9821,21 +9824,21 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I239" s="0">
-        <x:v>13.99</x:v>
+        <x:v>14.34</x:v>
       </x:c>
       <x:c r="J239" s="0">
         <x:v>23.4</x:v>
       </x:c>
       <x:c r="K239" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="240" spans="1:11">
       <x:c r="A240" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C240" s="0">
         <x:v>9350000</x:v>
@@ -9856,13 +9859,13 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I240" s="0">
-        <x:v>2.1</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="J240" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K240" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
     </x:row>
     <x:row r="241" spans="1:11">
@@ -9870,7 +9873,7 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C241" s="0">
         <x:v>1468255</x:v>
@@ -9891,13 +9894,13 @@
         <x:v>0.37</x:v>
       </x:c>
       <x:c r="I241" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="J241" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K241" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>379</x:v>
       </x:c>
     </x:row>
     <x:row r="242" spans="1:11">
@@ -9905,7 +9908,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C242" s="0">
         <x:v>500000</x:v>
@@ -9940,7 +9943,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C243" s="0">
         <x:v>725000</x:v>
@@ -9961,21 +9964,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I243" s="0">
-        <x:v>29.3</x:v>
+        <x:v>29.62</x:v>
       </x:c>
       <x:c r="J243" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K243" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="244" spans="1:11">
       <x:c r="A244" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="C244" s="0">
         <x:v>841000</x:v>
@@ -9996,7 +9999,7 @@
         <x:v>0.61</x:v>
       </x:c>
       <x:c r="I244" s="0">
-        <x:v>35.3</x:v>
+        <x:v>35.48</x:v>
       </x:c>
       <x:c r="J244" s="0">
         <x:v>38.43</x:v>
@@ -10010,7 +10013,7 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C245" s="0">
         <x:v>1060056</x:v>
@@ -10031,13 +10034,13 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I245" s="0">
-        <x:v>207.4</x:v>
+        <x:v>213.8</x:v>
       </x:c>
       <x:c r="J245" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K245" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="246" spans="1:11">
@@ -10045,7 +10048,7 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C246" s="0">
         <x:v>132750000</x:v>
@@ -10066,7 +10069,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I246" s="0">
-        <x:v>1.88</x:v>
+        <x:v>1.93</x:v>
       </x:c>
       <x:c r="J246" s="0">
         <x:v>4.26</x:v>
@@ -10077,10 +10080,10 @@
     </x:row>
     <x:row r="247" spans="1:11">
       <x:c r="A247" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="C247" s="0">
         <x:v>373000</x:v>
@@ -10101,21 +10104,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I247" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="J247" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K247" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="248" spans="1:11">
       <x:c r="A248" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="C248" s="0">
         <x:v>10000000</x:v>
@@ -10136,13 +10139,13 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I248" s="0">
-        <x:v>7.9</x:v>
+        <x:v>7.13</x:v>
       </x:c>
       <x:c r="J248" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K248" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>393</x:v>
       </x:c>
     </x:row>
     <x:row r="249" spans="1:11">
@@ -10150,7 +10153,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C249" s="0">
         <x:v>66142950</x:v>
@@ -10171,21 +10174,21 @@
         <x:v>2.71</x:v>
       </x:c>
       <x:c r="I249" s="0">
-        <x:v>4.03</x:v>
+        <x:v>3.66</x:v>
       </x:c>
       <x:c r="J249" s="0">
         <x:v>5.82</x:v>
       </x:c>
       <x:c r="K249" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>395</x:v>
       </x:c>
     </x:row>
     <x:row r="250" spans="1:11">
       <x:c r="A250" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C250" s="0">
         <x:v>3935266</x:v>
@@ -10206,7 +10209,7 @@
         <x:v>0.84</x:v>
       </x:c>
       <x:c r="I250" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.95</x:v>
       </x:c>
       <x:c r="J250" s="0">
         <x:v>12.25</x:v>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -73,6 +73,9 @@
     <x:t>ULUUN</x:t>
   </x:si>
   <x:si>
+    <x:t>09.10.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>SOKE</x:t>
   </x:si>
   <x:si>
@@ -82,15 +85,15 @@
     <x:t>GENTS</x:t>
   </x:si>
   <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.10.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>07.10.2026</x:t>
   </x:si>
   <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.10.2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>KPEKS</x:t>
   </x:si>
   <x:si>
@@ -169,6 +172,9 @@
     <x:t>DERHL</x:t>
   </x:si>
   <x:si>
+    <x:t>12.10.2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>FADE</x:t>
   </x:si>
   <x:si>
@@ -1112,9 +1118,6 @@
   </x:si>
   <x:si>
     <x:t>29.08.2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.10.2026</x:t>
   </x:si>
   <x:si>
     <x:t>PSGYO</x:t>
@@ -1622,7 +1625,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>13.9</x:v>
+        <x:v>13.19</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1654,7 +1657,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>31</x:v>
+        <x:v>28.52</x:v>
       </x:c>
       <x:c r="J3" s="0">
         <x:v>32.34</x:v>
@@ -1689,7 +1692,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>52.45</x:v>
+        <x:v>47.22</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>0</x:v>
@@ -1703,7 +1706,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>5648081</x:v>
+        <x:v>7515157</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>75000000</x:v>
@@ -1712,33 +1715,33 @@
         <x:v>525000000</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>37908802</x:v>
+        <x:v>50852956</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>0.75</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>6.9</x:v>
+        <x:v>6.79</x:v>
       </x:c>
       <x:c r="J5" s="0">
-        <x:v>6.71</x:v>
+        <x:v>6.77</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>3120684</x:v>
+        <x:v>4075368</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>30000000</x:v>
@@ -1747,27 +1750,27 @@
         <x:v>210000000</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>22296364</x:v>
+        <x:v>29902272</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>7.76</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>0.81</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>7.92</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>7.14</x:v>
+        <x:v>7.34</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>16</x:v>
@@ -1791,7 +1794,7 @@
         <x:v>0.31</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>49.48</x:v>
+        <x:v>46.92</x:v>
       </x:c>
       <x:c r="J7" s="0">
         <x:v>47.54</x:v>
@@ -1802,13 +1805,13 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>379775</x:v>
+        <x:v>729775</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>15000000</x:v>
@@ -1817,22 +1820,22 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1599078</x:v>
+        <x:v>3076078</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>4.16</x:v>
+        <x:v>3.97</x:v>
       </x:c>
       <x:c r="J8" s="0">
-        <x:v>4.21</x:v>
+        <x:v>4.22</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -1861,18 +1864,18 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>3.2</x:v>
+        <x:v>2.92</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>3.38</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>24</x:v>
@@ -1896,7 +1899,7 @@
         <x:v>0.34</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>53.8</x:v>
+        <x:v>52.6</x:v>
       </x:c>
       <x:c r="J10" s="0">
         <x:v>52.68</x:v>
@@ -1907,13 +1910,13 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>87500</x:v>
+        <x:v>92500</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>1000000</x:v>
@@ -1922,7 +1925,7 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>7453925</x:v>
+        <x:v>7986425</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>1.33</x:v>
@@ -1931,21 +1934,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>109.1</x:v>
+        <x:v>104.8</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>85.19</x:v>
+        <x:v>86.34</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>46969</x:v>
@@ -1966,7 +1969,7 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>21.2</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="J12" s="0">
         <x:v>19.3</x:v>
@@ -1977,10 +1980,10 @@
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>10509612</x:v>
@@ -2001,24 +2004,24 @@
         <x:v>4.2</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>7.37</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="J13" s="0">
         <x:v>7.05</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>490875</x:v>
+        <x:v>715375</x:v>
       </x:c>
       <x:c r="D14" s="0">
         <x:v>7000000</x:v>
@@ -2027,30 +2030,30 @@
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>8097404</x:v>
+        <x:v>12019419</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>16.74</x:v>
+        <x:v>18.41</x:v>
       </x:c>
       <x:c r="J14" s="0">
-        <x:v>16.5</x:v>
+        <x:v>16.8</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>24843</x:v>
@@ -2071,21 +2074,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>8.79</x:v>
+        <x:v>8.76</x:v>
       </x:c>
       <x:c r="J15" s="0">
         <x:v>8.64</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>350031</x:v>
@@ -2106,7 +2109,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>30.26</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>27.41</x:v>
@@ -2117,10 +2120,10 @@
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>2920000</x:v>
@@ -2141,7 +2144,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>14.24</x:v>
+        <x:v>12.82</x:v>
       </x:c>
       <x:c r="J17" s="0">
         <x:v>10.38</x:v>
@@ -2152,13 +2155,13 @@
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>355996</x:v>
+        <x:v>423777</x:v>
       </x:c>
       <x:c r="D18" s="0">
         <x:v>15000000</x:v>
@@ -2167,30 +2170,30 @@
         <x:v>110000000</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1899277</x:v>
+        <x:v>2271666</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>3.74</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>5.51</x:v>
+        <x:v>5.53</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>5.34</x:v>
+        <x:v>5.36</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>300000</x:v>
@@ -2211,21 +2214,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="J19" s="0">
         <x:v>3.34</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>25000000</x:v>
@@ -2246,21 +2249,21 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>1.09</x:v>
+        <x:v>1.08</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>4360372</x:v>
@@ -2281,7 +2284,7 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>11.75</x:v>
+        <x:v>11.34</x:v>
       </x:c>
       <x:c r="J21" s="0">
         <x:v>12.59</x:v>
@@ -2292,10 +2295,10 @@
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>4690808</x:v>
@@ -2316,7 +2319,7 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>8.24</x:v>
+        <x:v>8.04</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>8.51</x:v>
@@ -2327,13 +2330,13 @@
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>220000</x:v>
+        <x:v>225000</x:v>
       </x:c>
       <x:c r="D23" s="0">
         <x:v>5000000</x:v>
@@ -2342,7 +2345,7 @@
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>14541640</x:v>
+        <x:v>14881140</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>1.55</x:v>
@@ -2351,24 +2354,24 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="J23" s="0">
-        <x:v>66.1</x:v>
+        <x:v>66.14</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>2081188</x:v>
+        <x:v>2281188</x:v>
       </x:c>
       <x:c r="D24" s="0">
         <x:v>20000000</x:v>
@@ -2377,30 +2380,30 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>10072011</x:v>
+        <x:v>11038011</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>1.78</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>0.19</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>5.08</x:v>
+        <x:v>4.83</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>4.84</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>706000</x:v>
@@ -2421,7 +2424,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>8.05</x:v>
+        <x:v>7.58</x:v>
       </x:c>
       <x:c r="J25" s="0">
         <x:v>7.93</x:v>
@@ -2432,10 +2435,10 @@
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>781528</x:v>
@@ -2456,7 +2459,7 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>81.6</x:v>
+        <x:v>79.35</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>72.97</x:v>
@@ -2467,10 +2470,10 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
@@ -2491,7 +2494,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>47.44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>0</x:v>
@@ -2499,10 +2502,10 @@
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>2100000</x:v>
@@ -2523,24 +2526,24 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>4.25</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>4.32</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="C29" s="0">
-        <x:v>5529436</x:v>
+        <x:v>5625098</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>11848341</x:v>
@@ -2549,30 +2552,30 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>50966603</x:v>
+        <x:v>51798726</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>1.69</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.79</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.67</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>9.22</x:v>
+        <x:v>9.21</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>2175000</x:v>
@@ -2593,7 +2596,7 @@
         <x:v>1.13</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>7.76</x:v>
+        <x:v>7.66</x:v>
       </x:c>
       <x:c r="J30" s="0">
         <x:v>7.82</x:v>
@@ -2604,10 +2607,10 @@
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>6754888</x:v>
@@ -2628,24 +2631,24 @@
         <x:v>2.7</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>7.37</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>6.81</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="C32" s="0">
-        <x:v>5050000</x:v>
+        <x:v>6200000</x:v>
       </x:c>
       <x:c r="D32" s="0">
         <x:v>50000000</x:v>
@@ -2654,30 +2657,30 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>8046650</x:v>
+        <x:v>9873650</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>5.05</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>0.51</x:v>
+        <x:v>0.63</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>1.62</x:v>
+        <x:v>1.57</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>1.59</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>305229</x:v>
@@ -2698,7 +2701,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>11.89</x:v>
+        <x:v>11.41</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>11.31</x:v>
@@ -2709,13 +2712,13 @@
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>6194766</x:v>
+        <x:v>6578258</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>15000000</x:v>
@@ -2724,30 +2727,30 @@
         <x:v>50000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>13192265</x:v>
+        <x:v>14033263</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>0.69</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>0.29</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>2.21</x:v>
+        <x:v>2.18</x:v>
       </x:c>
       <x:c r="J34" s="0">
         <x:v>2.13</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
       <x:c r="A35" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>225000</x:v>
@@ -2768,21 +2771,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>30.2</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>29.29</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
       <x:c r="A36" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>60000</x:v>
@@ -2803,21 +2806,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>75</x:v>
+        <x:v>72.05</x:v>
       </x:c>
       <x:c r="J36" s="0">
         <x:v>74.13</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
       <x:c r="A37" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>756586</x:v>
@@ -2838,7 +2841,7 @@
         <x:v>0.61</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>51.5</x:v>
+        <x:v>46.36</x:v>
       </x:c>
       <x:c r="J37" s="0">
         <x:v>57.9</x:v>
@@ -2849,10 +2852,10 @@
     </x:row>
     <x:row r="38" spans="1:11">
       <x:c r="A38" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>13</x:v>
@@ -2873,7 +2876,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>38.98</x:v>
+        <x:v>39.94</x:v>
       </x:c>
       <x:c r="J38" s="0">
         <x:v>0</x:v>
@@ -2881,10 +2884,10 @@
     </x:row>
     <x:row r="39" spans="1:11">
       <x:c r="A39" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>99139</x:v>
@@ -2905,7 +2908,7 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>123</x:v>
+        <x:v>110.7</x:v>
       </x:c>
       <x:c r="J39" s="0">
         <x:v>115.6</x:v>
@@ -2916,10 +2919,10 @@
     </x:row>
     <x:row r="40" spans="1:11">
       <x:c r="A40" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>11235500</x:v>
@@ -2940,21 +2943,21 @@
         <x:v>0.42</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>3.2</x:v>
+        <x:v>3.21</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>3.12</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
       <x:c r="A41" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>2136000</x:v>
@@ -2975,7 +2978,7 @@
         <x:v>1.71</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>122</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>119.31</x:v>
@@ -2986,10 +2989,10 @@
     </x:row>
     <x:row r="42" spans="1:11">
       <x:c r="A42" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>1718790</x:v>
@@ -3010,24 +3013,24 @@
         <x:v>0.34</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>36.6</x:v>
+        <x:v>36.18</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>37.34</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>10487306</x:v>
+        <x:v>11570610</x:v>
       </x:c>
       <x:c r="D43" s="0">
         <x:v>100000000</x:v>
@@ -3036,30 +3039,30 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>18667335</x:v>
+        <x:v>20524118</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>1.05</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>1.72</x:v>
+        <x:v>1.69</x:v>
       </x:c>
       <x:c r="J43" s="0">
-        <x:v>1.78</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>6754888</x:v>
@@ -3080,24 +3083,24 @@
         <x:v>2.7</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>7.37</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>6.81</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="C45" s="0">
-        <x:v>24896406</x:v>
+        <x:v>25080276</x:v>
       </x:c>
       <x:c r="D45" s="0">
         <x:v>50000000</x:v>
@@ -3106,30 +3109,30 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>141706118</x:v>
+        <x:v>142789664</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>4.63</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>2.31</x:v>
+        <x:v>2.32</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>5.88</x:v>
+        <x:v>5.79</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>5.69</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>1145127</x:v>
@@ -3150,21 +3153,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>9.77</x:v>
+        <x:v>9.49</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>9.96</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>607144</x:v>
@@ -3185,7 +3188,7 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>19.7</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>20.88</x:v>
@@ -3196,10 +3199,10 @@
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>2040033</x:v>
@@ -3220,21 +3223,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>13.93</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>13.84</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>655000</x:v>
@@ -3255,7 +3258,7 @@
         <x:v>0.37</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>32.2</x:v>
+        <x:v>31.94</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>34.56</x:v>
@@ -3266,10 +3269,10 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>2352721</x:v>
@@ -3290,7 +3293,7 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>6.92</x:v>
+        <x:v>6.72</x:v>
       </x:c>
       <x:c r="J50" s="0">
         <x:v>7.25</x:v>
@@ -3304,7 +3307,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>845965</x:v>
@@ -3325,7 +3328,7 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>31</x:v>
+        <x:v>28.52</x:v>
       </x:c>
       <x:c r="J51" s="0">
         <x:v>32.34</x:v>
@@ -3336,13 +3339,13 @@
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>1292475</x:v>
+        <x:v>1421075</x:v>
       </x:c>
       <x:c r="D52" s="0">
         <x:v>1500000</x:v>
@@ -3351,30 +3354,30 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>4542131</x:v>
+        <x:v>4993486</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>0.38</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>3.55</x:v>
+        <x:v>3.49</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>3.51</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>170000000</x:v>
@@ -3395,24 +3398,24 @@
         <x:v>3.78</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>2</x:v>
+        <x:v>1.98</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>2.14</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="C54" s="0">
-        <x:v>3489169</x:v>
+        <x:v>4139169</x:v>
       </x:c>
       <x:c r="D54" s="0">
         <x:v>10000000</x:v>
@@ -3421,33 +3424,33 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>29056160</x:v>
+        <x:v>34500160</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>1.15</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.48</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>8.28</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>8.33</x:v>
+        <x:v>8.34</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>3839798</x:v>
+        <x:v>4377298</x:v>
       </x:c>
       <x:c r="D55" s="0">
         <x:v>12000000</x:v>
@@ -3456,30 +3459,30 @@
         <x:v>600000000</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>144083118</x:v>
+        <x:v>164059683</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2.16</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>0.69</x:v>
+        <x:v>0.79</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>38.04</x:v>
+        <x:v>36.54</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>37.52</x:v>
+        <x:v>37.48</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C56" s="0">
         <x:v>2700000</x:v>
@@ -3500,24 +3503,24 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="J56" s="0">
         <x:v>3.78</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>200000</x:v>
+        <x:v>265000</x:v>
       </x:c>
       <x:c r="D57" s="0">
         <x:v>5000000</x:v>
@@ -3526,30 +3529,30 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F57" s="0">
-        <x:v>9105535</x:v>
+        <x:v>12044900</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>43</x:v>
+        <x:v>42.68</x:v>
       </x:c>
       <x:c r="J57" s="0">
-        <x:v>45.53</x:v>
+        <x:v>45.45</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C58" s="0">
         <x:v>612000</x:v>
@@ -3570,7 +3573,7 @@
         <x:v>0.24</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>22.26</x:v>
+        <x:v>21.78</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>24.37</x:v>
@@ -3581,10 +3584,10 @@
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C59" s="0">
         <x:v>4875000</x:v>
@@ -3605,21 +3608,21 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>4.67</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>6.94</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>1000000</x:v>
@@ -3640,21 +3643,21 @@
         <x:v>2.38</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>8.01</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>8.87</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>1000000</x:v>
@@ -3675,24 +3678,24 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>5.04</x:v>
+        <x:v>4.98</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>5.95</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="C62" s="0">
-        <x:v>72000</x:v>
+        <x:v>90000</x:v>
       </x:c>
       <x:c r="D62" s="0">
         <x:v>5000000</x:v>
@@ -3701,30 +3704,30 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F62" s="0">
-        <x:v>2693320</x:v>
+        <x:v>3329080</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>6.43</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>35.44</x:v>
+        <x:v>37.68</x:v>
       </x:c>
       <x:c r="J62" s="0">
-        <x:v>37.41</x:v>
+        <x:v>36.99</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C63" s="0">
         <x:v>7596643</x:v>
@@ -3745,24 +3748,24 @@
         <x:v>4.22</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>119</x:v>
+        <x:v>108.9</x:v>
       </x:c>
       <x:c r="J63" s="0">
         <x:v>86.07</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>9780787</x:v>
+        <x:v>11159780</x:v>
       </x:c>
       <x:c r="D64" s="0">
         <x:v>100000000</x:v>
@@ -3771,33 +3774,33 @@
         <x:v>700000000</x:v>
       </x:c>
       <x:c r="F64" s="0">
-        <x:v>49180917</x:v>
+        <x:v>56086914</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0.56</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>4.92</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>27555966</x:v>
+        <x:v>29555966</x:v>
       </x:c>
       <x:c r="D65" s="0">
         <x:v>60000000</x:v>
@@ -3806,30 +3809,30 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F65" s="0">
-        <x:v>67384313</x:v>
+        <x:v>72254313</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>1.54</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>2.46</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>2.45</x:v>
+        <x:v>2.44</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C66" s="0">
         <x:v>5510000</x:v>
@@ -3850,7 +3853,7 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>1.79</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="J66" s="0">
         <x:v>2.04</x:v>
@@ -3861,13 +3864,13 @@
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="C67" s="0">
-        <x:v>121130</x:v>
+        <x:v>141130</x:v>
       </x:c>
       <x:c r="D67" s="0">
         <x:v>9260000</x:v>
@@ -3876,30 +3879,30 @@
         <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>11864869</x:v>
+        <x:v>13923869</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>101.6</x:v>
+        <x:v>98.65</x:v>
       </x:c>
       <x:c r="J67" s="0">
-        <x:v>97.95</x:v>
+        <x:v>98.66</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C68" s="0">
         <x:v>1276630</x:v>
@@ -3920,7 +3923,7 @@
         <x:v>0.38</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>73.5</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J68" s="0">
         <x:v>72.9</x:v>
@@ -3931,13 +3934,13 @@
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>7537299</x:v>
+        <x:v>7612299</x:v>
       </x:c>
       <x:c r="D69" s="0">
         <x:v>50000000</x:v>
@@ -3946,7 +3949,7 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>322502212</x:v>
+        <x:v>326132212</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>1.92</x:v>
@@ -3955,24 +3958,24 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>48.38</x:v>
+        <x:v>48.7</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>42.79</x:v>
+        <x:v>42.84</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>46260161</x:v>
+        <x:v>46360161</x:v>
       </x:c>
       <x:c r="D70" s="0">
         <x:v>180000000</x:v>
@@ -3981,33 +3984,33 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F70" s="0">
-        <x:v>595217159</x:v>
+        <x:v>596644159</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>0.51</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>14.28</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="J70" s="0">
         <x:v>12.87</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>1914552</x:v>
+        <x:v>2014552</x:v>
       </x:c>
       <x:c r="D71" s="0">
         <x:v>25000000</x:v>
@@ -4016,30 +4019,30 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F71" s="0">
-        <x:v>44957845</x:v>
+        <x:v>47347645</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>4.84</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>0.37</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>24.1</x:v>
+        <x:v>23.52</x:v>
       </x:c>
       <x:c r="J71" s="0">
-        <x:v>23.48</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>2393628</x:v>
@@ -4060,21 +4063,21 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>37.7</x:v>
+        <x:v>37.58</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>37.46</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C73" s="0">
         <x:v>3740344</x:v>
@@ -4095,7 +4098,7 @@
         <x:v>1.42</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>129.5</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J73" s="0">
         <x:v>137.41</x:v>
@@ -4106,10 +4109,10 @@
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C74" s="0">
         <x:v>113000</x:v>
@@ -4130,7 +4133,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>280.5</x:v>
+        <x:v>280.25</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>284.93</x:v>
@@ -4141,13 +4144,13 @@
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>1033649</x:v>
+        <x:v>1077640</x:v>
       </x:c>
       <x:c r="D75" s="0">
         <x:v>2850000</x:v>
@@ -4156,30 +4159,30 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F75" s="0">
-        <x:v>31466228</x:v>
+        <x:v>32815871</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2.41</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>0.87</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>30.4</x:v>
+        <x:v>30.22</x:v>
       </x:c>
       <x:c r="J75" s="0">
-        <x:v>30.44</x:v>
+        <x:v>30.45</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C76" s="0">
         <x:v>1214000</x:v>
@@ -4200,21 +4203,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>52.3</x:v>
+        <x:v>51.85</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>53.69</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>13</x:v>
@@ -4235,7 +4238,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>9.02</x:v>
+        <x:v>9.06</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>0</x:v>
@@ -4243,10 +4246,10 @@
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C78" s="0">
         <x:v>12450000</x:v>
@@ -4267,21 +4270,21 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>1.49</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>4.89</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>1365338</x:v>
@@ -4302,7 +4305,7 @@
         <x:v>0.14</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>5.53</x:v>
+        <x:v>5.42</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>5.4</x:v>
@@ -4313,10 +4316,10 @@
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C80" s="0">
         <x:v>1577544</x:v>
@@ -4337,24 +4340,24 @@
         <x:v>0.32</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>7.34</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>7.98</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>6384227</x:v>
+        <x:v>6394227</x:v>
       </x:c>
       <x:c r="D81" s="0">
         <x:v>13500000</x:v>
@@ -4363,30 +4366,30 @@
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>103421418</x:v>
+        <x:v>103589868</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>17.65</x:v>
+        <x:v>16.88</x:v>
       </x:c>
       <x:c r="J81" s="0">
         <x:v>16.2</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C82" s="0">
         <x:v>21607359</x:v>
@@ -4407,21 +4410,21 @@
         <x:v>3.86</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>5.13</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="J82" s="0">
         <x:v>6.91</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>11397816</x:v>
@@ -4442,24 +4445,24 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>6.18</x:v>
+        <x:v>6.43</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>23.68</x:v>
       </x:c>
       <x:c r="K83" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>26224596</x:v>
+        <x:v>30224596</x:v>
       </x:c>
       <x:c r="D84" s="0">
         <x:v>50000000</x:v>
@@ -4468,30 +4471,30 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>97662691</x:v>
+        <x:v>113362691</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>12.28</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>1.07</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J84" s="0">
-        <x:v>3.72</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>2300000</x:v>
@@ -4512,21 +4515,21 @@
         <x:v>3.83</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>9.8</x:v>
+        <x:v>9.65</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>0.76</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>4790000</x:v>
@@ -4547,21 +4550,21 @@
         <x:v>7.98</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>4.39</x:v>
+        <x:v>4.29</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>1.47</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>4850000</x:v>
@@ -4582,21 +4585,21 @@
         <x:v>8.08</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>11.5</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>0.73</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>165166</x:v>
@@ -4617,21 +4620,21 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>54.9</x:v>
+        <x:v>54.1</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>60.51</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>37446277</x:v>
@@ -4652,21 +4655,21 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>1.03</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>1.14</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>13</x:v>
@@ -4687,7 +4690,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>119.5</x:v>
+        <x:v>130.8</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>0</x:v>
@@ -4695,10 +4698,10 @@
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>100000</x:v>
@@ -4719,21 +4722,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>3.41</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>6.13</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>12590031</x:v>
@@ -4754,7 +4757,7 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>9.54</x:v>
+        <x:v>9.42</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>9.8</x:v>
@@ -4765,10 +4768,10 @@
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>1800452</x:v>
@@ -4789,21 +4792,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>7.34</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>9.69</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>187494</x:v>
@@ -4824,21 +4827,21 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>14.72</x:v>
+        <x:v>14.94</x:v>
       </x:c>
       <x:c r="J94" s="0">
         <x:v>15.28</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C95" s="0">
         <x:v>11550000</x:v>
@@ -4859,21 +4862,21 @@
         <x:v>1.07</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>1.49</x:v>
+        <x:v>1.53</x:v>
       </x:c>
       <x:c r="J95" s="0">
         <x:v>1.51</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>300000</x:v>
@@ -4894,24 +4897,24 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>16.14</x:v>
+        <x:v>16.06</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>15.9</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>11514033</x:v>
+        <x:v>13403606</x:v>
       </x:c>
       <x:c r="D97" s="0">
         <x:v>40000000</x:v>
@@ -4920,30 +4923,30 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F97" s="0">
-        <x:v>199305477</x:v>
+        <x:v>235253610</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>4.81</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>1.38</x:v>
+        <x:v>1.61</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>19.42</x:v>
+        <x:v>20.28</x:v>
       </x:c>
       <x:c r="J97" s="0">
-        <x:v>17.31</x:v>
+        <x:v>17.55</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C98" s="0">
         <x:v>15160028</x:v>
@@ -4964,21 +4967,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>3.4</x:v>
+        <x:v>3.32</x:v>
       </x:c>
       <x:c r="J98" s="0">
         <x:v>3.59</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>2500000</x:v>
@@ -4999,21 +5002,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>402.75</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>380.17</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>220399</x:v>
@@ -5034,21 +5037,21 @@
         <x:v>1.59</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>57.45</x:v>
+        <x:v>51.75</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>68.91</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C101" s="0">
         <x:v>2501710</x:v>
@@ -5069,21 +5072,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>26.18</x:v>
+        <x:v>25.7</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>38.82</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>76701016</x:v>
@@ -5104,21 +5107,21 @@
         <x:v>2.4</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>43.9</x:v>
+        <x:v>43.48</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>47.51</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>69686718</x:v>
@@ -5139,21 +5142,21 @@
         <x:v>2.36</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>8.61</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>32.87</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>100000</x:v>
@@ -5174,21 +5177,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>14.03</x:v>
+        <x:v>14.14</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>13.65</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>7999148</x:v>
@@ -5209,24 +5212,24 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.19</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>21.09</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>1618000</x:v>
+        <x:v>1690000</x:v>
       </x:c>
       <x:c r="D106" s="0">
         <x:v>21739600</x:v>
@@ -5235,30 +5238,30 @@
         <x:v>350000000</x:v>
       </x:c>
       <x:c r="F106" s="0">
-        <x:v>13007224</x:v>
+        <x:v>13557684</x:v>
       </x:c>
       <x:c r="G106" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>7.69</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="J106" s="0">
-        <x:v>8.04</x:v>
+        <x:v>8.02</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>13</x:v>
@@ -5279,7 +5282,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>8.9</x:v>
+        <x:v>8.86</x:v>
       </x:c>
       <x:c r="J107" s="0">
         <x:v>0</x:v>
@@ -5287,10 +5290,10 @@
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C108" s="0">
         <x:v>3070328</x:v>
@@ -5311,21 +5314,21 @@
         <x:v>0.57</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>7.67</x:v>
+        <x:v>7.73</x:v>
       </x:c>
       <x:c r="J108" s="0">
         <x:v>6.98</x:v>
       </x:c>
       <x:c r="K108" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>13</x:v>
@@ -5346,7 +5349,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>129.5</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>0</x:v>
@@ -5354,10 +5357,10 @@
     </x:row>
     <x:row r="110" spans="1:11">
       <x:c r="A110" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C110" s="0">
         <x:v>13879000</x:v>
@@ -5378,21 +5381,21 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>16.87</x:v>
+        <x:v>17.5</x:v>
       </x:c>
       <x:c r="J110" s="0">
         <x:v>7.61</x:v>
       </x:c>
       <x:c r="K110" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:11">
       <x:c r="A111" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C111" s="0">
         <x:v>970810</x:v>
@@ -5413,21 +5416,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>20.24</x:v>
+        <x:v>19.92</x:v>
       </x:c>
       <x:c r="J111" s="0">
         <x:v>28.89</x:v>
       </x:c>
       <x:c r="K111" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:11">
       <x:c r="A112" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C112" s="0">
         <x:v>6307105</x:v>
@@ -5448,7 +5451,7 @@
         <x:v>1.62</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>8.11</x:v>
+        <x:v>8.06</x:v>
       </x:c>
       <x:c r="J112" s="0">
         <x:v>9.52</x:v>
@@ -5459,10 +5462,10 @@
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>13</x:v>
@@ -5483,7 +5486,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>4.12</x:v>
+        <x:v>4.15</x:v>
       </x:c>
       <x:c r="J113" s="0">
         <x:v>0</x:v>
@@ -5491,10 +5494,10 @@
     </x:row>
     <x:row r="114" spans="1:11">
       <x:c r="A114" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C114" s="0">
         <x:v>2099706</x:v>
@@ -5515,21 +5518,21 @@
         <x:v>2.79</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>21.02</x:v>
+        <x:v>20.48</x:v>
       </x:c>
       <x:c r="J114" s="0">
         <x:v>23.25</x:v>
       </x:c>
       <x:c r="K114" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:11">
       <x:c r="A115" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C115" s="0">
         <x:v>29346813</x:v>
@@ -5550,21 +5553,21 @@
         <x:v>1.13</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>48.38</x:v>
+        <x:v>48.7</x:v>
       </x:c>
       <x:c r="J115" s="0">
         <x:v>28.18</x:v>
       </x:c>
       <x:c r="K115" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:11">
       <x:c r="A116" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C116" s="0">
         <x:v>7024156</x:v>
@@ -5585,21 +5588,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>9.24</x:v>
+        <x:v>9.09</x:v>
       </x:c>
       <x:c r="J116" s="0">
         <x:v>13.34</x:v>
       </x:c>
       <x:c r="K116" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:11">
       <x:c r="A117" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C117" s="0">
         <x:v>3500000</x:v>
@@ -5620,21 +5623,21 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>27.4</x:v>
+        <x:v>26.3</x:v>
       </x:c>
       <x:c r="J117" s="0">
         <x:v>39.18</x:v>
       </x:c>
       <x:c r="K117" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:11">
       <x:c r="A118" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C118" s="0">
         <x:v>3753472</x:v>
@@ -5655,21 +5658,21 @@
         <x:v>0.82</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="J118" s="0">
         <x:v>59.93</x:v>
       </x:c>
       <x:c r="K118" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:11">
       <x:c r="A119" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C119" s="0">
         <x:v>3189049</x:v>
@@ -5690,21 +5693,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>3.73</x:v>
+        <x:v>3.57</x:v>
       </x:c>
       <x:c r="J119" s="0">
         <x:v>48.39</x:v>
       </x:c>
       <x:c r="K119" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:11">
       <x:c r="A120" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>13</x:v>
@@ -5725,7 +5728,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>2.08</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="J120" s="0">
         <x:v>0</x:v>
@@ -5733,13 +5736,13 @@
     </x:row>
     <x:row r="121" spans="1:11">
       <x:c r="A121" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>8500000</x:v>
+        <x:v>9500000</x:v>
       </x:c>
       <x:c r="D121" s="0">
         <x:v>10000000</x:v>
@@ -5748,33 +5751,33 @@
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F121" s="0">
-        <x:v>222622213</x:v>
+        <x:v>231080213</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>1.21</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>1.03</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>8.85</x:v>
+        <x:v>8.58</x:v>
       </x:c>
       <x:c r="J121" s="0">
-        <x:v>26.19</x:v>
+        <x:v>24.32</x:v>
       </x:c>
       <x:c r="K121" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:11">
       <x:c r="A122" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>29346645</x:v>
+        <x:v>29846645</x:v>
       </x:c>
       <x:c r="D122" s="0">
         <x:v>35000000</x:v>
@@ -5783,30 +5786,30 @@
         <x:v>300000000</x:v>
       </x:c>
       <x:c r="F122" s="0">
-        <x:v>230894719</x:v>
+        <x:v>233769719</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>16.25</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>7.34</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>5.55</x:v>
+        <x:v>5.46</x:v>
       </x:c>
       <x:c r="J122" s="0">
-        <x:v>7.87</x:v>
+        <x:v>7.83</x:v>
       </x:c>
       <x:c r="K122" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:11">
       <x:c r="A123" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C123" s="0">
         <x:v>236122</x:v>
@@ -5827,21 +5830,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>30.2</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="J123" s="0">
         <x:v>61.87</x:v>
       </x:c>
       <x:c r="K123" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:11">
       <x:c r="A124" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C124" s="0">
         <x:v>1000000</x:v>
@@ -5862,21 +5865,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>14.34</x:v>
+        <x:v>13.87</x:v>
       </x:c>
       <x:c r="J124" s="0">
         <x:v>21.06</x:v>
       </x:c>
       <x:c r="K124" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:11">
       <x:c r="A125" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>13</x:v>
@@ -5897,7 +5900,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>3.73</x:v>
+        <x:v>3.57</x:v>
       </x:c>
       <x:c r="J125" s="0">
         <x:v>0</x:v>
@@ -5905,10 +5908,10 @@
     </x:row>
     <x:row r="126" spans="1:11">
       <x:c r="A126" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C126" s="0">
         <x:v>105404634</x:v>
@@ -5929,21 +5932,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>14.28</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="J126" s="0">
         <x:v>9.8</x:v>
       </x:c>
       <x:c r="K126" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:11">
       <x:c r="A127" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C127" s="0">
         <x:v>16445115</x:v>
@@ -5964,21 +5967,21 @@
         <x:v>3.29</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>16.28</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="J127" s="0">
         <x:v>23.95</x:v>
       </x:c>
       <x:c r="K127" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:11">
       <x:c r="A128" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C128" s="0">
         <x:v>1110000</x:v>
@@ -5999,21 +6002,21 @@
         <x:v>0.09</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>402.75</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="J128" s="0">
         <x:v>528.86</x:v>
       </x:c>
       <x:c r="K128" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:11">
       <x:c r="A129" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C129" s="0">
         <x:v>24398659</x:v>
@@ -6034,21 +6037,21 @@
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>48.38</x:v>
+        <x:v>48.7</x:v>
       </x:c>
       <x:c r="J129" s="0">
         <x:v>24.19</x:v>
       </x:c>
       <x:c r="K129" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:11">
       <x:c r="A130" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C130" s="0">
         <x:v>46563878</x:v>
@@ -6069,21 +6072,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>14.28</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="J130" s="0">
         <x:v>10.74</x:v>
       </x:c>
       <x:c r="K130" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:11">
       <x:c r="A131" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C131" s="0">
         <x:v>6611571</x:v>
@@ -6104,21 +6107,21 @@
         <x:v>0.69</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>5.53</x:v>
+        <x:v>5.42</x:v>
       </x:c>
       <x:c r="J131" s="0">
         <x:v>6.01</x:v>
       </x:c>
       <x:c r="K131" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:11">
       <x:c r="A132" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C132" s="0">
         <x:v>4096132</x:v>
@@ -6139,7 +6142,7 @@
         <x:v>2.15</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>11.03</x:v>
+        <x:v>10.68</x:v>
       </x:c>
       <x:c r="J132" s="0">
         <x:v>20.61</x:v>
@@ -6150,10 +6153,10 @@
     </x:row>
     <x:row r="133" spans="1:11">
       <x:c r="A133" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C133" s="0">
         <x:v>1000000</x:v>
@@ -6174,21 +6177,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>4.34</x:v>
+        <x:v>4.21</x:v>
       </x:c>
       <x:c r="J133" s="0">
         <x:v>4.46</x:v>
       </x:c>
       <x:c r="K133" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:11">
       <x:c r="A134" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C134" s="0">
         <x:v>200000</x:v>
@@ -6209,21 +6212,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>5.13</x:v>
+        <x:v>5.09</x:v>
       </x:c>
       <x:c r="J134" s="0">
         <x:v>12.82</x:v>
       </x:c>
       <x:c r="K134" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:11">
       <x:c r="A135" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>13</x:v>
@@ -6244,7 +6247,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="J135" s="0">
         <x:v>0</x:v>
@@ -6252,10 +6255,10 @@
     </x:row>
     <x:row r="136" spans="1:11">
       <x:c r="A136" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C136" s="0">
         <x:v>5831653</x:v>
@@ -6276,21 +6279,21 @@
         <x:v>0.83</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>1.91</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="J136" s="0">
         <x:v>52.14</x:v>
       </x:c>
       <x:c r="K136" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:11">
       <x:c r="A137" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C137" s="0">
         <x:v>14512000</x:v>
@@ -6311,21 +6314,21 @@
         <x:v>1.83</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>37.7</x:v>
+        <x:v>37.58</x:v>
       </x:c>
       <x:c r="J137" s="0">
         <x:v>39.62</x:v>
       </x:c>
       <x:c r="K137" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:11">
       <x:c r="A138" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C138" s="0">
         <x:v>5999828</x:v>
@@ -6346,7 +6349,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="J138" s="0">
         <x:v>37.69</x:v>
@@ -6357,10 +6360,10 @@
     </x:row>
     <x:row r="139" spans="1:11">
       <x:c r="A139" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>13</x:v>
@@ -6381,7 +6384,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>18.39</x:v>
+        <x:v>17.31</x:v>
       </x:c>
       <x:c r="J139" s="0">
         <x:v>0</x:v>
@@ -6389,10 +6392,10 @@
     </x:row>
     <x:row r="140" spans="1:11">
       <x:c r="A140" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C140" s="0">
         <x:v>15837681</x:v>
@@ -6413,7 +6416,7 @@
         <x:v>0.63</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.61</x:v>
       </x:c>
       <x:c r="J140" s="0">
         <x:v>3.54</x:v>
@@ -6424,10 +6427,10 @@
     </x:row>
     <x:row r="141" spans="1:11">
       <x:c r="A141" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="C141" s="0">
         <x:v>1350000</x:v>
@@ -6448,21 +6451,21 @@
         <x:v>0.37</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>29.62</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="J141" s="0">
         <x:v>30.83</x:v>
       </x:c>
       <x:c r="K141" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:11">
       <x:c r="A142" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>1364000</x:v>
@@ -6483,21 +6486,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>287.5</x:v>
+        <x:v>285.75</x:v>
       </x:c>
       <x:c r="J142" s="0">
         <x:v>299.91</x:v>
       </x:c>
       <x:c r="K142" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:11">
       <x:c r="A143" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C143" s="0">
         <x:v>1240500</x:v>
@@ -6518,21 +6521,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>19.85</x:v>
+        <x:v>19.73</x:v>
       </x:c>
       <x:c r="J143" s="0">
         <x:v>19.3</x:v>
       </x:c>
       <x:c r="K143" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:11">
       <x:c r="A144" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C144" s="0">
         <x:v>507440</x:v>
@@ -6553,21 +6556,21 @@
         <x:v>0.54</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>236.1</x:v>
+        <x:v>233.5</x:v>
       </x:c>
       <x:c r="J144" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K144" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:11">
       <x:c r="A145" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C145" s="0">
         <x:v>2000000</x:v>
@@ -6594,15 +6597,15 @@
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K145" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:11">
       <x:c r="A146" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C146" s="0">
         <x:v>9854768</x:v>
@@ -6623,21 +6626,21 @@
         <x:v>0.62</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>6.18</x:v>
+        <x:v>6.43</x:v>
       </x:c>
       <x:c r="J146" s="0">
         <x:v>23.68</x:v>
       </x:c>
       <x:c r="K146" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:11">
       <x:c r="A147" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C147" s="0">
         <x:v>324474</x:v>
@@ -6658,21 +6661,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>14.03</x:v>
+        <x:v>14.14</x:v>
       </x:c>
       <x:c r="J147" s="0">
         <x:v>5.49</x:v>
       </x:c>
       <x:c r="K147" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:11">
       <x:c r="A148" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>13</x:v>
@@ -6693,7 +6696,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>16.14</x:v>
+        <x:v>16.06</x:v>
       </x:c>
       <x:c r="J148" s="0">
         <x:v>0</x:v>
@@ -6701,10 +6704,10 @@
     </x:row>
     <x:row r="149" spans="1:11">
       <x:c r="A149" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>13</x:v>
@@ -6725,7 +6728,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>4.42</x:v>
+        <x:v>4.36</x:v>
       </x:c>
       <x:c r="J149" s="0">
         <x:v>0</x:v>
@@ -6733,10 +6736,10 @@
     </x:row>
     <x:row r="150" spans="1:11">
       <x:c r="A150" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C150" s="0">
         <x:v>174500000</x:v>
@@ -6757,21 +6760,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>1.93</x:v>
+        <x:v>1.87</x:v>
       </x:c>
       <x:c r="J150" s="0">
         <x:v>3.98</x:v>
       </x:c>
       <x:c r="K150" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:11">
       <x:c r="A151" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>246</x:v>
       </x:c>
       <x:c r="C151" s="0">
         <x:v>13000000</x:v>
@@ -6792,21 +6795,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>5.64</x:v>
+        <x:v>5.54</x:v>
       </x:c>
       <x:c r="J151" s="0">
         <x:v>6.6</x:v>
       </x:c>
       <x:c r="K151" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:11">
       <x:c r="A152" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C152" s="0">
         <x:v>635229</x:v>
@@ -6827,21 +6830,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>11.03</x:v>
+        <x:v>10.68</x:v>
       </x:c>
       <x:c r="J152" s="0">
         <x:v>17.83</x:v>
       </x:c>
       <x:c r="K152" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:11">
       <x:c r="A153" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C153" s="0">
         <x:v>130000</x:v>
@@ -6862,21 +6865,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>24.4</x:v>
+        <x:v>25.66</x:v>
       </x:c>
       <x:c r="J153" s="0">
         <x:v>38.06</x:v>
       </x:c>
       <x:c r="K153" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:11">
       <x:c r="A154" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>13</x:v>
@@ -6897,7 +6900,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>213.8</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="J154" s="0">
         <x:v>0</x:v>
@@ -6905,10 +6908,10 @@
     </x:row>
     <x:row r="155" spans="1:11">
       <x:c r="A155" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C155" s="0">
         <x:v>447761</x:v>
@@ -6929,21 +6932,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>26.9</x:v>
+        <x:v>26.22</x:v>
       </x:c>
       <x:c r="J155" s="0">
         <x:v>41.13</x:v>
       </x:c>
       <x:c r="K155" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:11">
       <x:c r="A156" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C156" s="0">
         <x:v>200000</x:v>
@@ -6964,21 +6967,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>3.03</x:v>
+        <x:v>2.92</x:v>
       </x:c>
       <x:c r="J156" s="0">
         <x:v>20.11</x:v>
       </x:c>
       <x:c r="K156" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:11">
       <x:c r="A157" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C157" s="0">
         <x:v>946718</x:v>
@@ -6999,21 +7002,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>3.64</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="J157" s="0">
         <x:v>39.43</x:v>
       </x:c>
       <x:c r="K157" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:11">
       <x:c r="A158" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C158" s="0">
         <x:v>3043115</x:v>
@@ -7034,21 +7037,21 @@
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>18.66</x:v>
+        <x:v>18.63</x:v>
       </x:c>
       <x:c r="J158" s="0">
         <x:v>16.34</x:v>
       </x:c>
       <x:c r="K158" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:11">
       <x:c r="A159" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>266</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>13</x:v>
@@ -7069,7 +7072,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>9.72</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="J159" s="0">
         <x:v>0</x:v>
@@ -7077,10 +7080,10 @@
     </x:row>
     <x:row r="160" spans="1:11">
       <x:c r="A160" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
         <x:v>13</x:v>
@@ -7101,7 +7104,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>39.16</x:v>
+        <x:v>38.2</x:v>
       </x:c>
       <x:c r="J160" s="0">
         <x:v>0</x:v>
@@ -7109,10 +7112,10 @@
     </x:row>
     <x:row r="161" spans="1:11">
       <x:c r="A161" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C161" s="0">
         <x:v>2382736</x:v>
@@ -7133,21 +7136,21 @@
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>12.86</x:v>
+        <x:v>12.75</x:v>
       </x:c>
       <x:c r="J161" s="0">
         <x:v>38.88</x:v>
       </x:c>
       <x:c r="K161" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:11">
       <x:c r="A162" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C162" s="0">
         <x:v>4650000</x:v>
@@ -7168,21 +7171,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>4.67</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="J162" s="0">
         <x:v>10.75</x:v>
       </x:c>
       <x:c r="K162" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:11">
       <x:c r="A163" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C163" s="0">
         <x:v>806343</x:v>
@@ -7203,21 +7206,21 @@
         <x:v>2.16</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>29.88</x:v>
+        <x:v>28.98</x:v>
       </x:c>
       <x:c r="J163" s="0">
         <x:v>37.66</x:v>
       </x:c>
       <x:c r="K163" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:11">
       <x:c r="A164" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>276</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
         <x:v>13</x:v>
@@ -7238,7 +7241,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>1.63</x:v>
+        <x:v>1.47</x:v>
       </x:c>
       <x:c r="J164" s="0">
         <x:v>0</x:v>
@@ -7246,10 +7249,10 @@
     </x:row>
     <x:row r="165" spans="1:11">
       <x:c r="A165" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C165" s="0">
         <x:v>2000000</x:v>
@@ -7270,21 +7273,21 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>7.34</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="J165" s="0">
         <x:v>15.68</x:v>
       </x:c>
       <x:c r="K165" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:11">
       <x:c r="A166" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C166" s="0">
         <x:v>3587613</x:v>
@@ -7305,7 +7308,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>1.37</x:v>
+        <x:v>1.35</x:v>
       </x:c>
       <x:c r="J166" s="0">
         <x:v>4.02</x:v>
@@ -7316,10 +7319,10 @@
     </x:row>
     <x:row r="167" spans="1:11">
       <x:c r="A167" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C167" s="0">
         <x:v>310000</x:v>
@@ -7340,21 +7343,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>4.67</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="J167" s="0">
         <x:v>161.23</x:v>
       </x:c>
       <x:c r="K167" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:11">
       <x:c r="A168" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C168" s="0">
         <x:v>12500000</x:v>
@@ -7375,21 +7378,21 @@
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>1.73</x:v>
+        <x:v>1.78</x:v>
       </x:c>
       <x:c r="J168" s="0">
         <x:v>4.93</x:v>
       </x:c>
       <x:c r="K168" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:11">
       <x:c r="A169" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C169" s="0">
         <x:v>2093944</x:v>
@@ -7410,21 +7413,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>98.55</x:v>
+        <x:v>97.25</x:v>
       </x:c>
       <x:c r="J169" s="0">
         <x:v>95.58</x:v>
       </x:c>
       <x:c r="K169" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:11">
       <x:c r="A170" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C170" s="0" t="s">
         <x:v>13</x:v>
@@ -7445,7 +7448,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>43.88</x:v>
+        <x:v>44.04</x:v>
       </x:c>
       <x:c r="J170" s="0">
         <x:v>0</x:v>
@@ -7453,10 +7456,10 @@
     </x:row>
     <x:row r="171" spans="1:11">
       <x:c r="A171" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C171" s="0">
         <x:v>51245979</x:v>
@@ -7477,21 +7480,21 @@
         <x:v>1.31</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>2.46</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="J171" s="0">
         <x:v>2.45</x:v>
       </x:c>
       <x:c r="K171" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:11">
       <x:c r="A172" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C172" s="0">
         <x:v>1584837</x:v>
@@ -7512,21 +7515,21 @@
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>54.9</x:v>
+        <x:v>54.1</x:v>
       </x:c>
       <x:c r="J172" s="0">
         <x:v>58.33</x:v>
       </x:c>
       <x:c r="K172" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:11">
       <x:c r="A173" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C173" s="0">
         <x:v>7999148</x:v>
@@ -7547,21 +7550,21 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.19</x:v>
       </x:c>
       <x:c r="J173" s="0">
         <x:v>21.09</x:v>
       </x:c>
       <x:c r="K173" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:11">
       <x:c r="A174" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C174" s="0">
         <x:v>14000000</x:v>
@@ -7582,21 +7585,21 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>3.81</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="J174" s="0">
         <x:v>16.87</x:v>
       </x:c>
       <x:c r="K174" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:11">
       <x:c r="A175" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C175" s="0">
         <x:v>1700005</x:v>
@@ -7617,21 +7620,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>3.41</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="J175" s="0">
         <x:v>11.99</x:v>
       </x:c>
       <x:c r="K175" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:11">
       <x:c r="A176" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C176" s="0">
         <x:v>1824868</x:v>
@@ -7652,21 +7655,21 @@
         <x:v>0.68</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>13.33</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="J176" s="0">
         <x:v>35.38</x:v>
       </x:c>
       <x:c r="K176" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:11">
       <x:c r="A177" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C177" s="0" t="s">
         <x:v>13</x:v>
@@ -7687,7 +7690,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>5.45</x:v>
+        <x:v>5.36</x:v>
       </x:c>
       <x:c r="J177" s="0">
         <x:v>0</x:v>
@@ -7695,10 +7698,10 @@
     </x:row>
     <x:row r="178" spans="1:11">
       <x:c r="A178" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
         <x:v>291</x:v>
-      </x:c>
-      <x:c r="B178" s="0" t="s">
-        <x:v>289</x:v>
       </x:c>
       <x:c r="C178" s="0">
         <x:v>1000000</x:v>
@@ -7719,21 +7722,21 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>4.53</x:v>
+        <x:v>4.52</x:v>
       </x:c>
       <x:c r="J178" s="0">
         <x:v>19.79</x:v>
       </x:c>
       <x:c r="K178" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:11">
       <x:c r="A179" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C179" s="0">
         <x:v>98551</x:v>
@@ -7760,15 +7763,15 @@
         <x:v>13.15</x:v>
       </x:c>
       <x:c r="K179" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:11">
       <x:c r="A180" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C180" s="0">
         <x:v>37225000</x:v>
@@ -7789,21 +7792,21 @@
         <x:v>3.45</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>1.49</x:v>
+        <x:v>1.53</x:v>
       </x:c>
       <x:c r="J180" s="0">
         <x:v>4.03</x:v>
       </x:c>
       <x:c r="K180" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:11">
       <x:c r="A181" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C181" s="0">
         <x:v>600000</x:v>
@@ -7824,21 +7827,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>3.55</x:v>
+        <x:v>3.49</x:v>
       </x:c>
       <x:c r="J181" s="0">
         <x:v>38.02</x:v>
       </x:c>
       <x:c r="K181" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:11">
       <x:c r="A182" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C182" s="0">
         <x:v>5100000</x:v>
@@ -7859,21 +7862,21 @@
         <x:v>4.31</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>30.4</x:v>
+        <x:v>30.22</x:v>
       </x:c>
       <x:c r="J182" s="0">
         <x:v>17.65</x:v>
       </x:c>
       <x:c r="K182" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:11">
       <x:c r="A183" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C183" s="0">
         <x:v>1675000</x:v>
@@ -7894,21 +7897,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>9.57</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="J183" s="0">
         <x:v>68.15</x:v>
       </x:c>
       <x:c r="K183" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>299</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:11">
       <x:c r="A184" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C184" s="0">
         <x:v>6049315</x:v>
@@ -7929,21 +7932,21 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>9.77</x:v>
+        <x:v>9.49</x:v>
       </x:c>
       <x:c r="J184" s="0">
         <x:v>10.98</x:v>
       </x:c>
       <x:c r="K184" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:11">
       <x:c r="A185" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C185" s="0">
         <x:v>6000000</x:v>
@@ -7964,21 +7967,21 @@
         <x:v>0.16</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>17.83</x:v>
+        <x:v>16.95</x:v>
       </x:c>
       <x:c r="J185" s="0">
         <x:v>22.05</x:v>
       </x:c>
       <x:c r="K185" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:11">
       <x:c r="A186" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C186" s="0">
         <x:v>1000000</x:v>
@@ -7999,21 +8002,21 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>122</x:v>
+        <x:v>109.8</x:v>
       </x:c>
       <x:c r="J186" s="0">
         <x:v>284.58</x:v>
       </x:c>
       <x:c r="K186" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:11">
       <x:c r="A187" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C187" s="0">
         <x:v>11703083</x:v>
@@ -8034,21 +8037,21 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I187" s="0">
-        <x:v>37.54</x:v>
+        <x:v>33.8</x:v>
       </x:c>
       <x:c r="J187" s="0">
         <x:v>83.62</x:v>
       </x:c>
       <x:c r="K187" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:11">
       <x:c r="A188" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C188" s="0" t="s">
         <x:v>13</x:v>
@@ -8069,7 +8072,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I188" s="0">
-        <x:v>8.79</x:v>
+        <x:v>8.76</x:v>
       </x:c>
       <x:c r="J188" s="0">
         <x:v>0</x:v>
@@ -8077,10 +8080,10 @@
     </x:row>
     <x:row r="189" spans="1:11">
       <x:c r="A189" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C189" s="0">
         <x:v>366107</x:v>
@@ -8101,21 +8104,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I189" s="0">
-        <x:v>13.66</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="J189" s="0">
         <x:v>16.42</x:v>
       </x:c>
       <x:c r="K189" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:11">
       <x:c r="A190" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
         <x:v>306</x:v>
-      </x:c>
-      <x:c r="B190" s="0" t="s">
-        <x:v>304</x:v>
       </x:c>
       <x:c r="C190" s="0">
         <x:v>150000</x:v>
@@ -8136,21 +8139,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I190" s="0">
-        <x:v>4.04</x:v>
+        <x:v>3.93</x:v>
       </x:c>
       <x:c r="J190" s="0">
         <x:v>40.97</x:v>
       </x:c>
       <x:c r="K190" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:11">
       <x:c r="A191" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C191" s="0">
         <x:v>3228679</x:v>
@@ -8171,21 +8174,21 @@
         <x:v>0.29</x:v>
       </x:c>
       <x:c r="I191" s="0">
-        <x:v>9.02</x:v>
+        <x:v>9.06</x:v>
       </x:c>
       <x:c r="J191" s="0">
         <x:v>15.92</x:v>
       </x:c>
       <x:c r="K191" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:11">
       <x:c r="A192" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C192" s="0">
         <x:v>13050000</x:v>
@@ -8206,21 +8209,21 @@
         <x:v>3.13</x:v>
       </x:c>
       <x:c r="I192" s="0">
-        <x:v>109</x:v>
+        <x:v>110.1</x:v>
       </x:c>
       <x:c r="J192" s="0">
         <x:v>94.36</x:v>
       </x:c>
       <x:c r="K192" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:11">
       <x:c r="A193" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
         <x:v>311</x:v>
-      </x:c>
-      <x:c r="B193" s="0" t="s">
-        <x:v>309</x:v>
       </x:c>
       <x:c r="C193" s="0">
         <x:v>52605658</x:v>
@@ -8241,21 +8244,21 @@
         <x:v>5.26</x:v>
       </x:c>
       <x:c r="I193" s="0">
-        <x:v>4.32</x:v>
+        <x:v>4.29</x:v>
       </x:c>
       <x:c r="J193" s="0">
         <x:v>4.64</x:v>
       </x:c>
       <x:c r="K193" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:11">
       <x:c r="A194" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C194" s="0">
         <x:v>1000000</x:v>
@@ -8276,21 +8279,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I194" s="0">
-        <x:v>402.75</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="J194" s="0">
         <x:v>429.82</x:v>
       </x:c>
       <x:c r="K194" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:11">
       <x:c r="A195" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C195" s="0">
         <x:v>300000</x:v>
@@ -8311,21 +8314,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I195" s="0">
-        <x:v>2.01</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="J195" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="K195" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:11">
       <x:c r="A196" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C196" s="0">
         <x:v>2175097</x:v>
@@ -8346,21 +8349,21 @@
         <x:v>1.45</x:v>
       </x:c>
       <x:c r="I196" s="0">
-        <x:v>11.72</x:v>
+        <x:v>11.47</x:v>
       </x:c>
       <x:c r="J196" s="0">
         <x:v>8.23</x:v>
       </x:c>
       <x:c r="K196" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:11">
       <x:c r="A197" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C197" s="0" t="s">
         <x:v>13</x:v>
@@ -8381,7 +8384,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I197" s="0">
-        <x:v>2.6</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="J197" s="0">
         <x:v>0</x:v>
@@ -8389,10 +8392,10 @@
     </x:row>
     <x:row r="198" spans="1:11">
       <x:c r="A198" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C198" s="0">
         <x:v>106000</x:v>
@@ -8413,21 +8416,21 @@
         <x:v>0.23</x:v>
       </x:c>
       <x:c r="I198" s="0">
-        <x:v>22.7</x:v>
+        <x:v>21.7</x:v>
       </x:c>
       <x:c r="J198" s="0">
         <x:v>23.66</x:v>
       </x:c>
       <x:c r="K198" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:11">
       <x:c r="A199" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C199" s="0">
         <x:v>9937037</x:v>
@@ -8448,21 +8451,21 @@
         <x:v>0.53</x:v>
       </x:c>
       <x:c r="I199" s="0">
-        <x:v>1.8</x:v>
+        <x:v>1.98</x:v>
       </x:c>
       <x:c r="J199" s="0">
         <x:v>5.03</x:v>
       </x:c>
       <x:c r="K199" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:11">
       <x:c r="A200" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C200" s="0" t="s">
         <x:v>13</x:v>
@@ -8483,7 +8486,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I200" s="0">
-        <x:v>1.76</x:v>
+        <x:v>1.69</x:v>
       </x:c>
       <x:c r="J200" s="0">
         <x:v>0</x:v>
@@ -8491,10 +8494,10 @@
     </x:row>
     <x:row r="201" spans="1:11">
       <x:c r="A201" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C201" s="0" t="s">
         <x:v>13</x:v>
@@ -8515,7 +8518,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I201" s="0">
-        <x:v>3.01</x:v>
+        <x:v>2.87</x:v>
       </x:c>
       <x:c r="J201" s="0">
         <x:v>0</x:v>
@@ -8523,10 +8526,10 @@
     </x:row>
     <x:row r="202" spans="1:11">
       <x:c r="A202" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C202" s="0" t="s">
         <x:v>13</x:v>
@@ -8547,7 +8550,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I202" s="0">
-        <x:v>4.52</x:v>
+        <x:v>4.37</x:v>
       </x:c>
       <x:c r="J202" s="0">
         <x:v>0</x:v>
@@ -8555,10 +8558,10 @@
     </x:row>
     <x:row r="203" spans="1:11">
       <x:c r="A203" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C203" s="0">
         <x:v>1100000</x:v>
@@ -8579,21 +8582,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I203" s="0">
-        <x:v>146.1</x:v>
+        <x:v>152.9</x:v>
       </x:c>
       <x:c r="J203" s="0">
         <x:v>50.97</x:v>
       </x:c>
       <x:c r="K203" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:11">
       <x:c r="A204" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C204" s="0">
         <x:v>6598092</x:v>
@@ -8614,21 +8617,21 @@
         <x:v>5.91</x:v>
       </x:c>
       <x:c r="I204" s="0">
-        <x:v>16.14</x:v>
+        <x:v>16.06</x:v>
       </x:c>
       <x:c r="J204" s="0">
         <x:v>10.93</x:v>
       </x:c>
       <x:c r="K204" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:11">
       <x:c r="A205" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C205" s="0">
         <x:v>1590000</x:v>
@@ -8649,21 +8652,21 @@
         <x:v>0.91</x:v>
       </x:c>
       <x:c r="I205" s="0">
-        <x:v>32.2</x:v>
+        <x:v>31.94</x:v>
       </x:c>
       <x:c r="J205" s="0">
         <x:v>38.14</x:v>
       </x:c>
       <x:c r="K205" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:11">
       <x:c r="A206" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C206" s="0" t="s">
         <x:v>13</x:v>
@@ -8684,7 +8687,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I206" s="0">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="J206" s="0">
         <x:v>0</x:v>
@@ -8692,10 +8695,10 @@
     </x:row>
     <x:row r="207" spans="1:11">
       <x:c r="A207" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C207" s="0">
         <x:v>77658759</x:v>
@@ -8716,21 +8719,21 @@
         <x:v>0.78</x:v>
       </x:c>
       <x:c r="I207" s="0">
-        <x:v>33.9</x:v>
+        <x:v>34.44</x:v>
       </x:c>
       <x:c r="J207" s="0">
         <x:v>25.82</x:v>
       </x:c>
       <x:c r="K207" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:11">
       <x:c r="A208" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C208" s="0">
         <x:v>300000</x:v>
@@ -8751,21 +8754,21 @@
         <x:v>0.04</x:v>
       </x:c>
       <x:c r="I208" s="0">
-        <x:v>4.63</x:v>
+        <x:v>4.36</x:v>
       </x:c>
       <x:c r="J208" s="0">
         <x:v>4.56</x:v>
       </x:c>
       <x:c r="K208" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:11">
       <x:c r="A209" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C209" s="0">
         <x:v>120000</x:v>
@@ -8786,21 +8789,21 @@
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="I209" s="0">
-        <x:v>129.5</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J209" s="0">
         <x:v>31.92</x:v>
       </x:c>
       <x:c r="K209" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:11">
       <x:c r="A210" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C210" s="0">
         <x:v>8291656</x:v>
@@ -8821,21 +8824,21 @@
         <x:v>1.9</x:v>
       </x:c>
       <x:c r="I210" s="0">
-        <x:v>12.52</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="J210" s="0">
         <x:v>15.2</x:v>
       </x:c>
       <x:c r="K210" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:11">
       <x:c r="A211" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C211" s="0">
         <x:v>13064888</x:v>
@@ -8856,21 +8859,21 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I211" s="0">
-        <x:v>48.38</x:v>
+        <x:v>48.7</x:v>
       </x:c>
       <x:c r="J211" s="0">
         <x:v>20.53</x:v>
       </x:c>
       <x:c r="K211" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:11">
       <x:c r="A212" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C212" s="0">
         <x:v>111673026</x:v>
@@ -8891,21 +8894,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I212" s="0">
-        <x:v>14.28</x:v>
+        <x:v>14.6</x:v>
       </x:c>
       <x:c r="J212" s="0">
         <x:v>4.48</x:v>
       </x:c>
       <x:c r="K212" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:11">
       <x:c r="A213" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C213" s="0">
         <x:v>1989802</x:v>
@@ -8926,21 +8929,21 @@
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="I213" s="0">
-        <x:v>123.3</x:v>
+        <x:v>123.9</x:v>
       </x:c>
       <x:c r="J213" s="0">
         <x:v>39.56</x:v>
       </x:c>
       <x:c r="K213" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:11">
       <x:c r="A214" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C214" s="0">
         <x:v>2975773</x:v>
@@ -8961,24 +8964,24 @@
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="I214" s="0">
-        <x:v>19.93</x:v>
+        <x:v>18.88</x:v>
       </x:c>
       <x:c r="J214" s="0">
         <x:v>15.05</x:v>
       </x:c>
       <x:c r="K214" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:11">
       <x:c r="A215" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C215" s="0">
-        <x:v>11348189</x:v>
+        <x:v>11378189</x:v>
       </x:c>
       <x:c r="D215" s="0">
         <x:v>21600000</x:v>
@@ -8987,30 +8990,30 @@
         <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F215" s="0">
-        <x:v>187078430</x:v>
+        <x:v>187411130</x:v>
       </x:c>
       <x:c r="G215" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H215" s="0">
-        <x:v>5.25</x:v>
+        <x:v>5.27</x:v>
       </x:c>
       <x:c r="I215" s="0">
-        <x:v>11.13</x:v>
+        <x:v>10.9</x:v>
       </x:c>
       <x:c r="J215" s="0">
-        <x:v>16.49</x:v>
+        <x:v>16.47</x:v>
       </x:c>
       <x:c r="K215" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:11">
       <x:c r="A216" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C216" s="0">
         <x:v>5100000</x:v>
@@ -9031,21 +9034,21 @@
         <x:v>0.93</x:v>
       </x:c>
       <x:c r="I216" s="0">
-        <x:v>43</x:v>
+        <x:v>42.68</x:v>
       </x:c>
       <x:c r="J216" s="0">
         <x:v>30.45</x:v>
       </x:c>
       <x:c r="K216" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:11">
       <x:c r="A217" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B217" s="0" t="s">
-        <x:v>335</x:v>
       </x:c>
       <x:c r="C217" s="0">
         <x:v>38590259</x:v>
@@ -9066,21 +9069,21 @@
         <x:v>1.98</x:v>
       </x:c>
       <x:c r="I217" s="0">
-        <x:v>17.33</x:v>
+        <x:v>17.78</x:v>
       </x:c>
       <x:c r="J217" s="0">
         <x:v>11.47</x:v>
       </x:c>
       <x:c r="K217" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:11">
       <x:c r="A218" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C218" s="0" t="s">
         <x:v>13</x:v>
@@ -9101,7 +9104,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I218" s="0">
-        <x:v>2</x:v>
+        <x:v>1.98</x:v>
       </x:c>
       <x:c r="J218" s="0">
         <x:v>0</x:v>
@@ -9109,10 +9112,10 @@
     </x:row>
     <x:row r="219" spans="1:11">
       <x:c r="A219" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C219" s="0">
         <x:v>5000000</x:v>
@@ -9133,21 +9136,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I219" s="0">
-        <x:v>9.54</x:v>
+        <x:v>9.42</x:v>
       </x:c>
       <x:c r="J219" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K219" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:11">
       <x:c r="A220" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C220" s="0">
         <x:v>1053786</x:v>
@@ -9168,21 +9171,21 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="I220" s="0">
-        <x:v>13.34</x:v>
+        <x:v>13.13</x:v>
       </x:c>
       <x:c r="J220" s="0">
         <x:v>18.44</x:v>
       </x:c>
       <x:c r="K220" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:11">
       <x:c r="A221" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="C221" s="0" t="s">
         <x:v>13</x:v>
@@ -9203,7 +9206,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I221" s="0">
-        <x:v>28.06</x:v>
+        <x:v>27.22</x:v>
       </x:c>
       <x:c r="J221" s="0">
         <x:v>0</x:v>
@@ -9211,10 +9214,10 @@
     </x:row>
     <x:row r="222" spans="1:11">
       <x:c r="A222" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C222" s="0" t="s">
         <x:v>13</x:v>
@@ -9235,7 +9238,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I222" s="0">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="J222" s="0">
         <x:v>0</x:v>
@@ -9243,10 +9246,10 @@
     </x:row>
     <x:row r="223" spans="1:11">
       <x:c r="A223" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C223" s="0">
         <x:v>53584</x:v>
@@ -9267,21 +9270,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I223" s="0">
-        <x:v>230.6</x:v>
+        <x:v>231.2</x:v>
       </x:c>
       <x:c r="J223" s="0">
         <x:v>154.36</x:v>
       </x:c>
       <x:c r="K223" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:11">
       <x:c r="A224" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C224" s="0">
         <x:v>7550000</x:v>
@@ -9302,21 +9305,21 @@
         <x:v>0.33</x:v>
       </x:c>
       <x:c r="I224" s="0">
-        <x:v>6.05</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="J224" s="0">
         <x:v>14.81</x:v>
       </x:c>
       <x:c r="K224" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>352</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:11">
       <x:c r="A225" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="C225" s="0">
         <x:v>2097716</x:v>
@@ -9337,21 +9340,21 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I225" s="0">
-        <x:v>1.01</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="J225" s="0">
         <x:v>13.82</x:v>
       </x:c>
       <x:c r="K225" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:11">
       <x:c r="A226" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C226" s="0">
         <x:v>5185302</x:v>
@@ -9372,21 +9375,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I226" s="0">
-        <x:v>4.92</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="J226" s="0">
         <x:v>7.15</x:v>
       </x:c>
       <x:c r="K226" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:11">
       <x:c r="A227" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C227" s="0">
         <x:v>38840</x:v>
@@ -9407,21 +9410,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I227" s="0">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="J227" s="0">
         <x:v>242.84</x:v>
       </x:c>
       <x:c r="K227" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="228" spans="1:11">
       <x:c r="A228" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C228" s="0">
         <x:v>669111</x:v>
@@ -9442,21 +9445,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I228" s="0">
-        <x:v>731</x:v>
+        <x:v>732.5</x:v>
       </x:c>
       <x:c r="J228" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="K228" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="229" spans="1:11">
       <x:c r="A229" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C229" s="0">
         <x:v>2250000</x:v>
@@ -9477,21 +9480,21 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I229" s="0">
-        <x:v>6.05</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="J229" s="0">
         <x:v>14.11</x:v>
       </x:c>
       <x:c r="K229" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>359</x:v>
       </x:c>
     </x:row>
     <x:row r="230" spans="1:11">
       <x:c r="A230" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="C230" s="0">
         <x:v>1500000</x:v>
@@ -9512,21 +9515,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I230" s="0">
-        <x:v>1.01</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="J230" s="0">
         <x:v>14.58</x:v>
       </x:c>
       <x:c r="K230" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>359</x:v>
       </x:c>
     </x:row>
     <x:row r="231" spans="1:11">
       <x:c r="A231" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C231" s="0">
         <x:v>1656401</x:v>
@@ -9547,21 +9550,21 @@
         <x:v>1.74</x:v>
       </x:c>
       <x:c r="I231" s="0">
-        <x:v>142.5</x:v>
+        <x:v>141.1</x:v>
       </x:c>
       <x:c r="J231" s="0">
         <x:v>138.38</x:v>
       </x:c>
       <x:c r="K231" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="232" spans="1:11">
       <x:c r="A232" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C232" s="0">
         <x:v>17990900</x:v>
@@ -9582,21 +9585,21 @@
         <x:v>3.6</x:v>
       </x:c>
       <x:c r="I232" s="0">
-        <x:v>36.6</x:v>
+        <x:v>36.18</x:v>
       </x:c>
       <x:c r="J232" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="K232" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="233" spans="1:11">
       <x:c r="A233" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C233" s="0" t="s">
         <x:v>13</x:v>
@@ -9617,7 +9620,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I233" s="0">
-        <x:v>236.1</x:v>
+        <x:v>233.5</x:v>
       </x:c>
       <x:c r="J233" s="0">
         <x:v>0</x:v>
@@ -9625,10 +9628,10 @@
     </x:row>
     <x:row r="234" spans="1:11">
       <x:c r="A234" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C234" s="0">
         <x:v>845945</x:v>
@@ -9649,21 +9652,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I234" s="0">
-        <x:v>2.59</x:v>
+        <x:v>2.61</x:v>
       </x:c>
       <x:c r="J234" s="0">
         <x:v>11.89</x:v>
       </x:c>
       <x:c r="K234" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="235" spans="1:11">
       <x:c r="A235" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C235" s="0">
         <x:v>21446</x:v>
@@ -9684,24 +9687,24 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I235" s="0">
-        <x:v>35.44</x:v>
+        <x:v>37.68</x:v>
       </x:c>
       <x:c r="J235" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="K235" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="236" spans="1:11">
       <x:c r="A236" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C236" s="0">
-        <x:v>2791213</x:v>
+        <x:v>2894228</x:v>
       </x:c>
       <x:c r="D236" s="0">
         <x:v>4250000</x:v>
@@ -9710,30 +9713,30 @@
         <x:v>40000000</x:v>
       </x:c>
       <x:c r="F236" s="0">
-        <x:v>18742029</x:v>
+        <x:v>19437381</x:v>
       </x:c>
       <x:c r="G236" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H236" s="0">
-        <x:v>3.28</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="I236" s="0">
-        <x:v>6.89</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="J236" s="0">
-        <x:v>6.71</x:v>
+        <x:v>6.72</x:v>
       </x:c>
       <x:c r="K236" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="237" spans="1:11">
       <x:c r="A237" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C237" s="0">
         <x:v>15000000</x:v>
@@ -9754,21 +9757,21 @@
         <x:v>0.22</x:v>
       </x:c>
       <x:c r="I237" s="0">
-        <x:v>1.73</x:v>
+        <x:v>1.74</x:v>
       </x:c>
       <x:c r="J237" s="0">
         <x:v>1.6</x:v>
       </x:c>
       <x:c r="K237" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="238" spans="1:11">
       <x:c r="A238" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C238" s="0">
         <x:v>6397124</x:v>
@@ -9789,21 +9792,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I238" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3.02</x:v>
       </x:c>
       <x:c r="J238" s="0">
         <x:v>19.21</x:v>
       </x:c>
       <x:c r="K238" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>373</x:v>
       </x:c>
     </x:row>
     <x:row r="239" spans="1:11">
       <x:c r="A239" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="C239" s="0">
         <x:v>17495257</x:v>
@@ -9824,21 +9827,21 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I239" s="0">
-        <x:v>14.34</x:v>
+        <x:v>13.87</x:v>
       </x:c>
       <x:c r="J239" s="0">
         <x:v>23.4</x:v>
       </x:c>
       <x:c r="K239" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="240" spans="1:11">
       <x:c r="A240" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C240" s="0">
         <x:v>9350000</x:v>
@@ -9859,21 +9862,21 @@
         <x:v>1.1</x:v>
       </x:c>
       <x:c r="I240" s="0">
-        <x:v>2.25</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="J240" s="0">
         <x:v>7.44</x:v>
       </x:c>
       <x:c r="K240" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
     </x:row>
     <x:row r="241" spans="1:11">
       <x:c r="A241" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C241" s="0">
         <x:v>1468255</x:v>
@@ -9894,21 +9897,21 @@
         <x:v>0.37</x:v>
       </x:c>
       <x:c r="I241" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="J241" s="0">
         <x:v>51.7</x:v>
       </x:c>
       <x:c r="K241" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="242" spans="1:11">
       <x:c r="A242" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C242" s="0">
         <x:v>500000</x:v>
@@ -9929,21 +9932,21 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="I242" s="0">
-        <x:v>1.79</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="J242" s="0">
         <x:v>26.8</x:v>
       </x:c>
       <x:c r="K242" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="243" spans="1:11">
       <x:c r="A243" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C243" s="0">
         <x:v>725000</x:v>
@@ -9964,21 +9967,21 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="I243" s="0">
-        <x:v>29.62</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="J243" s="0">
         <x:v>66.95</x:v>
       </x:c>
       <x:c r="K243" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
     </x:row>
     <x:row r="244" spans="1:11">
       <x:c r="A244" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C244" s="0">
         <x:v>841000</x:v>
@@ -9999,21 +10002,21 @@
         <x:v>0.61</x:v>
       </x:c>
       <x:c r="I244" s="0">
-        <x:v>35.48</x:v>
+        <x:v>33.88</x:v>
       </x:c>
       <x:c r="J244" s="0">
         <x:v>38.43</x:v>
       </x:c>
       <x:c r="K244" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="245" spans="1:11">
       <x:c r="A245" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="C245" s="0">
         <x:v>1060056</x:v>
@@ -10034,21 +10037,21 @@
         <x:v>0.44</x:v>
       </x:c>
       <x:c r="I245" s="0">
-        <x:v>213.8</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="J245" s="0">
         <x:v>57.32</x:v>
       </x:c>
       <x:c r="K245" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>387</x:v>
       </x:c>
     </x:row>
     <x:row r="246" spans="1:11">
       <x:c r="A246" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C246" s="0">
         <x:v>132750000</x:v>
@@ -10069,21 +10072,21 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I246" s="0">
-        <x:v>1.93</x:v>
+        <x:v>1.87</x:v>
       </x:c>
       <x:c r="J246" s="0">
         <x:v>4.26</x:v>
       </x:c>
       <x:c r="K246" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="247" spans="1:11">
       <x:c r="A247" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C247" s="0">
         <x:v>373000</x:v>
@@ -10104,21 +10107,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I247" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="J247" s="0">
         <x:v>63.77</x:v>
       </x:c>
       <x:c r="K247" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="248" spans="1:11">
       <x:c r="A248" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C248" s="0">
         <x:v>10000000</x:v>
@@ -10139,21 +10142,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I248" s="0">
-        <x:v>7.13</x:v>
+        <x:v>6.96</x:v>
       </x:c>
       <x:c r="J248" s="0">
         <x:v>13.33</x:v>
       </x:c>
       <x:c r="K248" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="249" spans="1:11">
       <x:c r="A249" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C249" s="0">
         <x:v>66142950</x:v>
@@ -10174,21 +10177,21 @@
         <x:v>2.71</x:v>
       </x:c>
       <x:c r="I249" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="J249" s="0">
         <x:v>5.82</x:v>
       </x:c>
       <x:c r="K249" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>396</x:v>
       </x:c>
     </x:row>
     <x:row r="250" spans="1:11">
       <x:c r="A250" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C250" s="0">
         <x:v>3935266</x:v>
@@ -10209,13 +10212,13 @@
         <x:v>0.84</x:v>
       </x:c>
       <x:c r="I250" s="0">
-        <x:v>4.95</x:v>
+        <x:v>4.86</x:v>
       </x:c>
       <x:c r="J250" s="0">
         <x:v>12.25</x:v>
       </x:c>
       <x:c r="K250" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
+++ b/app/borsa/geri-alim-programlari/data/geri-alim.xlsx
@@ -64,154 +64,157 @@
     <x:t>08.10.2026</x:t>
   </x:si>
   <x:si>
+    <x:t>EKDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARCL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUICK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KPEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZERGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.10.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.09.2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
     <x:t>12.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARCL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUICK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KPEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09.10.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZERGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24.09.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
   </x:si>
   <x:si>
     <x:t>NTHOL</x:t>
@@ -1628,7 +1631,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>3.15</x:v>
+        <x:v>2.84</x:v>
       </x:c>
       <x:c r="J2" s="0">
         <x:v>0</x:v>
@@ -1642,7 +1645,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>1575000</x:v>
+        <x:v>2838735</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>100000000</x:v>
@@ -1651,30 +1654,30 @@
         <x:v>1400000000</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>20774250</x:v>
+        <x:v>37392365</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>2.65</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>12.92</x:v>
+        <x:v>12.12</x:v>
       </x:c>
       <x:c r="J3" s="0">
-        <x:v>13.19</x:v>
+        <x:v>13.17</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="A4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>845965</x:v>
@@ -1695,21 +1698,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>28.1</x:v>
+        <x:v>26.98</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>32.34</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>13</x:v>
@@ -1730,7 +1733,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>42.5</x:v>
+        <x:v>41.98</x:v>
       </x:c>
       <x:c r="J5" s="0">
         <x:v>0</x:v>
@@ -1738,13 +1741,13 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>9142937</x:v>
+        <x:v>10760741</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>75000000</x:v>
@@ -1753,33 +1756,33 @@
         <x:v>525000000</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>61951204</x:v>
+        <x:v>72818957</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1.22</x:v>
+        <x:v>1.43</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>6.67</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="J6" s="0">
-        <x:v>6.78</x:v>
+        <x:v>6.77</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>5094966</x:v>
+        <x:v>5837077</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>30000000</x:v>
@@ -1788,30 +1791,30 @@
         <x:v>210000000</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>37952298</x:v>
+        <x:v>43769118</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>7.76</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1.32</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>7.67</x:v>
+        <x:v>7.47</x:v>
       </x:c>
       <x:c r="J7" s="0">
-        <x:v>7.45</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>1494874</x:v>
@@ -1832,24 +1835,24 @@
         <x:v>0.31</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>45.2</x:v>
+        <x:v>42.66</x:v>
       </x:c>
       <x:c r="J8" s="0">
         <x:v>47.54</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>919377</x:v>
+        <x:v>1130908</x:v>
       </x:c>
       <x:c r="D9" s="0">
         <x:v>15000000</x:v>
@@ -1858,33 +1861,33 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>3840174</x:v>
+        <x:v>4677837</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>3.95</x:v>
+        <x:v>3.81</x:v>
       </x:c>
       <x:c r="J9" s="0">
-        <x:v>4.18</x:v>
+        <x:v>4.14</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="C10" s="0">
-        <x:v>4250000</x:v>
+        <x:v>5250000</x:v>
       </x:c>
       <x:c r="D10" s="0">
         <x:v>37500000</x:v>
@@ -1893,33 +1896,33 @@
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>13914407</x:v>
+        <x:v>16703407</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>3.46</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>0.39</x:v>
+        <x:v>0.48</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="J10" s="0">
-        <x:v>3.27</x:v>
+        <x:v>3.18</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>515569</x:v>
+        <x:v>575569</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>10000000</x:v>
@@ -1928,33 +1931,33 @@
         <x:v>750000000</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>27181747</x:v>
+        <x:v>30289747</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>7.99</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>0.41</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>53.6</x:v>
+        <x:v>50.1</x:v>
       </x:c>
       <x:c r="J11" s="0">
-        <x:v>52.72</x:v>
+        <x:v>52.63</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="C12" s="0">
-        <x:v>122500</x:v>
+        <x:v>142948</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>1000000</x:v>
@@ -1963,33 +1966,33 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>11131925</x:v>
+        <x:v>13255654</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>1.33</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>114</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J12" s="0">
-        <x:v>90.87</x:v>
+        <x:v>92.73</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:11">
       <x:c r="A13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>46969</x:v>
+        <x:v>55669</x:v>
       </x:c>
       <x:c r="D13" s="0">
         <x:v>7500000</x:v>
@@ -1998,30 +2001,30 @@
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>906648</x:v>
+        <x:v>1080247</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>21.98</x:v>
+        <x:v>19.79</x:v>
       </x:c>
       <x:c r="J13" s="0">
-        <x:v>19.3</x:v>
+        <x:v>19.4</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:11">
       <x:c r="A14" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>10509612</x:v>
@@ -2042,24 +2045,24 @@
         <x:v>4.2</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>7.1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J14" s="0">
         <x:v>7.05</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:11">
       <x:c r="A15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>1103206</x:v>
+        <x:v>1278206</x:v>
       </x:c>
       <x:c r="D15" s="0">
         <x:v>7000000</x:v>
@@ -2068,30 +2071,30 @@
         <x:v>150000000</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>18717260</x:v>
+        <x:v>21984510</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>3.5</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>0.55</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>18</x:v>
+        <x:v>17.88</x:v>
       </x:c>
       <x:c r="J15" s="0">
-        <x:v>16.97</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:11">
       <x:c r="A16" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>24843</x:v>
@@ -2112,24 +2115,24 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>9.1</x:v>
+        <x:v>8.95</x:v>
       </x:c>
       <x:c r="J16" s="0">
         <x:v>8.64</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:11">
       <x:c r="A17" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>409345</x:v>
+        <x:v>559345</x:v>
       </x:c>
       <x:c r="D17" s="0">
         <x:v>4000000</x:v>
@@ -2138,33 +2141,33 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>11398296</x:v>
+        <x:v>15895296</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>1.46</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>30.48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J17" s="0">
-        <x:v>27.85</x:v>
+        <x:v>28.42</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:11">
       <x:c r="A18" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>2920000</x:v>
+        <x:v>3038000</x:v>
       </x:c>
       <x:c r="D18" s="0">
         <x:v>50000000</x:v>
@@ -2173,7 +2176,7 @@
         <x:v>600000000</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>30314660</x:v>
+        <x:v>31676380</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>1.71</x:v>
@@ -2182,24 +2185,24 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>11.54</x:v>
+        <x:v>11.01</x:v>
       </x:c>
       <x:c r="J18" s="0">
-        <x:v>10.38</x:v>
+        <x:v>10.43</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:11">
       <x:c r="A19" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>550488</x:v>
+        <x:v>670488</x:v>
       </x:c>
       <x:c r="D19" s="0">
         <x:v>15000000</x:v>
@@ -2208,30 +2211,30 @@
         <x:v>110000000</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>2962494</x:v>
+        <x:v>3615894</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>3.74</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.17</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>5.35</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="J19" s="0">
-        <x:v>5.38</x:v>
+        <x:v>5.39</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11">
       <x:c r="A20" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>300000</x:v>
@@ -2252,21 +2255,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>3.15</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="J20" s="0">
         <x:v>3.34</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:11">
       <x:c r="A21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>25000000</x:v>
@@ -2293,15 +2296,15 @@
         <x:v>1.03</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:11">
       <x:c r="A22" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>4360372</x:v>
@@ -2322,21 +2325,21 @@
         <x:v>0.64</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>11.32</x:v>
+        <x:v>11.18</x:v>
       </x:c>
       <x:c r="J22" s="0">
         <x:v>12.59</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:11">
       <x:c r="A23" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>4690808</x:v>
@@ -2357,21 +2360,21 @@
         <x:v>1.88</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>7.89</x:v>
+        <x:v>7.63</x:v>
       </x:c>
       <x:c r="J23" s="0">
         <x:v>8.51</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:11">
       <x:c r="A24" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>225000</x:v>
@@ -2392,24 +2395,24 @@
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>64.2</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J24" s="0">
         <x:v>66.14</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:11">
       <x:c r="A25" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>2799551</x:v>
+        <x:v>4299551</x:v>
       </x:c>
       <x:c r="D25" s="0">
         <x:v>20000000</x:v>
@@ -2418,30 +2421,30 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>13552021</x:v>
+        <x:v>20689021</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>1.78</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>4.69</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="J25" s="0">
-        <x:v>4.84</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:11">
       <x:c r="A26" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>706000</x:v>
@@ -2462,7 +2465,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>7.29</x:v>
+        <x:v>7.33</x:v>
       </x:c>
       <x:c r="J26" s="0">
         <x:v>7.93</x:v>
@@ -2473,10 +2476,10 @@
     </x:row>
     <x:row r="27" spans="1:11">
       <x:c r="A27" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>781528</x:v>
@@ -2497,21 +2500,21 @@
         <x:v>0.13</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>73.65</x:v>
+        <x:v>71.9</x:v>
       </x:c>
       <x:c r="J27" s="0">
         <x:v>72.97</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:11">
       <x:c r="A28" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
@@ -2532,7 +2535,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>38.7</x:v>
+        <x:v>41.5</x:v>
       </x:c>
       <x:c r="J28" s="0">
         <x:v>0</x:v>
@@ -2540,13 +2543,13 @@
     </x:row>
     <x:row r="29" spans="1:11">
       <x:c r="A29" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="C29" s="0">
-        <x:v>2100000</x:v>
+        <x:v>2353000</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>100000000</x:v>
@@ -2555,33 +2558,33 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>9077000</x:v>
+        <x:v>10106204</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>7.17</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.17</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>4.04</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="J29" s="0">
-        <x:v>4.32</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:11">
       <x:c r="A30" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>6525098</x:v>
+        <x:v>6695098</x:v>
       </x:c>
       <x:c r="D30" s="0">
         <x:v>11848341</x:v>
@@ -2590,30 +2593,30 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>59814026</x:v>
+        <x:v>61277826</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>1.69</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>0.93</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>8.46</x:v>
+        <x:v>8.29</x:v>
       </x:c>
       <x:c r="J30" s="0">
-        <x:v>9.17</x:v>
+        <x:v>9.15</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:11">
       <x:c r="A31" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>2175000</x:v>
@@ -2634,21 +2637,21 @@
         <x:v>1.13</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>7.51</x:v>
+        <x:v>7.22</x:v>
       </x:c>
       <x:c r="J31" s="0">
         <x:v>7.82</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:11">
       <x:c r="A32" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>6754888</x:v>
@@ -2669,24 +2672,24 @@
         <x:v>2.7</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>7.1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J32" s="0">
         <x:v>6.81</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:11">
       <x:c r="A33" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>6200000</x:v>
+        <x:v>6950000</x:v>
       </x:c>
       <x:c r="D33" s="0">
         <x:v>50000000</x:v>
@@ -2695,33 +2698,33 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>9873650</x:v>
+        <x:v>11043650</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>5.05</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>1.57</x:v>
+        <x:v>1.53</x:v>
       </x:c>
       <x:c r="J33" s="0">
         <x:v>1.59</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:11">
       <x:c r="A34" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>305229</x:v>
+        <x:v>340229</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>2000000</x:v>
@@ -2730,22 +2733,22 @@
         <x:v>40000000</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>3452978</x:v>
+        <x:v>3851103</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2.38</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>11.47</x:v>
+        <x:v>11.03</x:v>
       </x:c>
       <x:c r="J34" s="0">
-        <x:v>11.31</x:v>
+        <x:v>11.32</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:11">
@@ -2753,10 +2756,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>7228258</x:v>
+        <x:v>7576338</x:v>
       </x:c>
       <x:c r="D35" s="0">
         <x:v>15000000</x:v>
@@ -2765,22 +2768,22 @@
         <x:v>50000000</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>15456113</x:v>
+        <x:v>16211098</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>0.69</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>2.17</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="J35" s="0">
         <x:v>2.14</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:11">
@@ -2788,10 +2791,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>281000</x:v>
+        <x:v>288000</x:v>
       </x:c>
       <x:c r="D36" s="0">
         <x:v>10000000</x:v>
@@ -2800,22 +2803,22 @@
         <x:v>350000000</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>8233740</x:v>
+        <x:v>8431140</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>7.58</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>28.12</x:v>
+        <x:v>27.5</x:v>
       </x:c>
       <x:c r="J36" s="0">
-        <x:v>29.3</x:v>
+        <x:v>29.27</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:11">
@@ -2823,10 +2826,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>60000</x:v>
+        <x:v>85000</x:v>
       </x:c>
       <x:c r="D37" s="0">
         <x:v>750000</x:v>
@@ -2835,22 +2838,22 @@
         <x:v>50000000</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>4447548</x:v>
+        <x:v>6135048</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0</x:v>
+        <x:v>0.48</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>69.8</x:v>
+        <x:v>69.9</x:v>
       </x:c>
       <x:c r="J37" s="0">
-        <x:v>74.13</x:v>
+        <x:v>72.18</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:11">
@@ -2861,7 +2864,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>756586</x:v>
+        <x:v>856586</x:v>
       </x:c>
       <x:c r="D38" s="0">
         <x:v>8800000</x:v>
@@ -2870,22 +2873,22 @@
         <x:v>750000000</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>43805634</x:v>
+        <x:v>47979634</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>7.04</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>0.61</x:v>
+        <x:v>0.69</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>41.74</x:v>
+        <x:v>38.46</x:v>
       </x:c>
       <x:c r="J38" s="0">
-        <x:v>57.9</x:v>
+        <x:v>56.01</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:11">
@@ -2895,8 +2898,8 @@
       <x:c r="B39" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C39" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="C39" s="0">
+        <x:v>175107</x:v>
       </x:c>
       <x:c r="D39" s="0">
         <x:v>11400000</x:v>
@@ -2904,20 +2907,23 @@
       <x:c r="E39" s="0">
         <x:v>750000000</x:v>
       </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>13</x:v>
+      <x:c r="F39" s="0">
+        <x:v>7627661</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0</x:v>
+        <x:v>4.74</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>0</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>39.78</x:v>
+        <x:v>39.36</x:v>
       </x:c>
       <x:c r="J39" s="0">
-        <x:v>0</x:v>
+        <x:v>43.56</x:v>
+      </x:c>
+      <x:c r="K39" s="0" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:11">
@@ -2946,13 +2952,13 @@
         <x:v>0.66</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>99.65</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J40" s="0">
         <x:v>115.6</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:11">
@@ -2981,13 +2987,13 @@
         <x:v>0.42</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>3.06</x:v>
+        <x:v>2.9</x:v>
       </x:c>
       <x:c r="J41" s="0">
         <x:v>3.12</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:11">
@@ -3016,21 +3022,21 @@
         <x:v>1.85</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>98.85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J42" s="0">
         <x:v>118.61</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:11">
       <x:c r="A43" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>1718790</x:v>
@@ -3051,21 +3057,21 @@
         <x:v>0.34</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>35.86</x:v>
+        <x:v>35.7</x:v>
       </x:c>
       <x:c r="J43" s="0">
         <x:v>37.34</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:11">
       <x:c r="A44" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>11570610</x:v>
@@ -3086,21 +3092,21 @@
         <x:v>1.16</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>1.68</x:v>
+        <x:v>1.61</x:v>
       </x:c>
       <x:c r="J44" s="0">
         <x:v>1.77</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:11">
       <x:c r="A45" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>6754888</x:v>
@@ -3121,24 +3127,24 @@
         <x:v>2.7</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>7.1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J45" s="0">
         <x:v>6.81</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:11">
       <x:c r="A46" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>25564224</x:v>
+        <x:v>26368842</x:v>
       </x:c>
       <x:c r="D46" s="0">
         <x:v>50000000</x:v>
@@ -3147,30 +3153,30 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>145626083</x:v>
+        <x:v>150267925</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>4.63</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>2.37</x:v>
+        <x:v>2.44</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>5.85</x:v>
+        <x:v>5.86</x:v>
       </x:c>
       <x:c r="J46" s="0">
         <x:v>5.7</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:11">
       <x:c r="A47" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>1145127</x:v>
@@ -3191,21 +3197,21 @@
         <x:v>0.17</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>9.53</x:v>
+        <x:v>9.31</x:v>
       </x:c>
       <x:c r="J47" s="0">
         <x:v>9.96</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:11">
       <x:c r="A48" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>607144</x:v>
@@ -3226,21 +3232,21 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>19.12</x:v>
+        <x:v>18.22</x:v>
       </x:c>
       <x:c r="J48" s="0">
         <x:v>20.88</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:11">
       <x:c r="A49" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>4540033</x:v>
@@ -3261,7 +3267,7 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>13.2</x:v>
+        <x:v>12.76</x:v>
       </x:c>
       <x:c r="J49" s="0">
         <x:v>13.54</x:v>
@@ -3272,13 +3278,13 @@
     </x:row>
     <x:row r="50" spans="1:11">
       <x:c r="A50" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>655000</x:v>
+        <x:v>799954</x:v>
       </x:c>
       <x:c r="D50" s="0">
         <x:v>1000000</x:v>
@@ -3287,33 +3293,33 @@
         <x:v>30000000</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>22636359</x:v>
+        <x:v>27199643</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>0.57</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>0.37</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>32.2</x:v>
+        <x:v>31.58</x:v>
       </x:c>
       <x:c r="J50" s="0">
-        <x:v>34.56</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:11">
       <x:c r="A51" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="C51" s="0">
-        <x:v>2572721</x:v>
+        <x:v>2662283</x:v>
       </x:c>
       <x:c r="D51" s="0">
         <x:v>33000000</x:v>
@@ -3322,30 +3328,30 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>18578878</x:v>
+        <x:v>19180645</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>0.78</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>6.79</x:v>
+        <x:v>6.72</x:v>
       </x:c>
       <x:c r="J51" s="0">
-        <x:v>7.22</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:11">
       <x:c r="A52" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C52" s="0">
         <x:v>845965</x:v>
@@ -3366,21 +3372,21 @@
         <x:v>0.26</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>28.1</x:v>
+        <x:v>26.98</x:v>
       </x:c>
       <x:c r="J52" s="0">
         <x:v>32.34</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:11">
       <x:c r="A53" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C53" s="0">
         <x:v>1421075</x:v>
@@ -3401,24 +3407,24 @@
         <x:v>0.36</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.63</x:v>
       </x:c>
       <x:c r="J53" s="0">
         <x:v>3.51</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:11">
       <x:c r="A54" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="C54" s="0">
-        <x:v>173000000</x:v>
+        <x:v>180000000</x:v>
       </x:c>
       <x:c r="D54" s="0">
         <x:v>500000000</x:v>
@@ -3427,33 +3433,33 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>369454954</x:v>
+        <x:v>383377954</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>11.11</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>3.84</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>1.97</x:v>
+        <x:v>1.94</x:v>
       </x:c>
       <x:c r="J54" s="0">
-        <x:v>2.14</x:v>
+        <x:v>2.13</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:11">
       <x:c r="A55" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>5049169</x:v>
+        <x:v>5699169</x:v>
       </x:c>
       <x:c r="D55" s="0">
         <x:v>10000000</x:v>
@@ -3462,33 +3468,33 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>41814460</x:v>
+        <x:v>46957460</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>1.15</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>0.58</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>7.88</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="J55" s="0">
-        <x:v>8.28</x:v>
+        <x:v>8.24</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:11">
       <x:c r="A56" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>4377298</x:v>
+        <x:v>6104298</x:v>
       </x:c>
       <x:c r="D56" s="0">
         <x:v>12000000</x:v>
@@ -3497,30 +3503,30 @@
         <x:v>600000000</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>164059683</x:v>
+        <x:v>227091729</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2.16</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>0.79</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>36.24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J56" s="0">
-        <x:v>37.48</x:v>
+        <x:v>37.2</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:11">
       <x:c r="A57" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C57" s="0">
         <x:v>2700000</x:v>
@@ -3541,21 +3547,21 @@
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>3.18</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="J57" s="0">
         <x:v>3.78</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:11">
       <x:c r="A58" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C58" s="0">
         <x:v>310000</x:v>
@@ -3576,21 +3582,21 @@
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>42.66</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="J58" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:11">
       <x:c r="A59" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C59" s="0">
         <x:v>612000</x:v>
@@ -3611,21 +3617,21 @@
         <x:v>0.24</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>21.02</x:v>
+        <x:v>19.99</x:v>
       </x:c>
       <x:c r="J59" s="0">
         <x:v>24.37</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:11">
       <x:c r="A60" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C60" s="0">
         <x:v>4875000</x:v>
@@ -3646,21 +3652,21 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>5.24</x:v>
+        <x:v>5.05</x:v>
       </x:c>
       <x:c r="J60" s="0">
         <x:v>6.94</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:11">
       <x:c r="A61" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C61" s="0">
         <x:v>1000000</x:v>
@@ -3681,21 +3687,21 @@
         <x:v>2.38</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>7.6</x:v>
+        <x:v>7.59</x:v>
       </x:c>
       <x:c r="J61" s="0">
         <x:v>8.87</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:11">
       <x:c r="A62" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="C62" s="0">
         <x:v>1000000</x:v>
@@ -3716,24 +3722,24 @@
         <x:v>1.67</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>4.85</x:v>
+        <x:v>4.75</x:v>
       </x:c>
       <x:c r="J62" s="0">
         <x:v>5.95</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:11">
       <x:c r="A63" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>1189000</x:v>
+        <x:v>2154200</x:v>
       </x:c>
       <x:c r="D63" s="0">
         <x:v>5000000</x:v>
@@ -3742,30 +3748,30 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>44695440</x:v>
+        <x:v>84085252</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>6.43</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>1.53</x:v>
+        <x:v>2.77</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>41.22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J63" s="0">
-        <x:v>37.59</x:v>
+        <x:v>39.03</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:11">
       <x:c r="A64" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C64" s="0">
         <x:v>7959116</x:v>
@@ -3786,24 +3792,24 @@
         <x:v>4.42</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>98.05</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J64" s="0">
         <x:v>87.3</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:11">
       <x:c r="A65" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>12056995</x:v>
+        <x:v>12830453</x:v>
       </x:c>
       <x:c r="D65" s="0">
         <x:v>100000000</x:v>
@@ -3812,33 +3818,33 @@
         <x:v>700000000</x:v>
       </x:c>
       <x:c r="F65" s="0">
-        <x:v>60520054</x:v>
+        <x:v>64286794</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>4.87</x:v>
+        <x:v>4.84</x:v>
       </x:c>
       <x:c r="J65" s="0">
-        <x:v>5.02</x:v>
+        <x:v>5.01</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:11">
       <x:c r="A66" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>31738996</x:v>
+        <x:v>35438996</x:v>
       </x:c>
       <x:c r="D66" s="0">
         <x:v>60000000</x:v>
@@ -3847,13 +3853,13 @@
         <x:v>200000000</x:v>
       </x:c>
       <x:c r="F66" s="0">
-        <x:v>77599906</x:v>
+        <x:v>86567406</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>1.54</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>0.81</x:v>
+        <x:v>0.91</x:v>
       </x:c>
       <x:c r="I66" s="0">
         <x:v>2.49</x:v>
@@ -3862,15 +3868,15 @@
         <x:v>2.44</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:11">
       <x:c r="A67" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="C67" s="0">
         <x:v>5510000</x:v>
@@ -3891,24 +3897,24 @@
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>1.72</x:v>
+        <x:v>1.65</x:v>
       </x:c>
       <x:c r="J67" s="0">
         <x:v>2.04</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:11">
       <x:c r="A68" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>174883</x:v>
+        <x:v>233130</x:v>
       </x:c>
       <x:c r="D68" s="0">
         <x:v>9260000</x:v>
@@ -3917,33 +3923,33 @@
         <x:v>1200000000</x:v>
       </x:c>
       <x:c r="F68" s="0">
-        <x:v>17241958</x:v>
+        <x:v>22923836</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>0.19</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>98.75</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J68" s="0">
-        <x:v>98.59</x:v>
+        <x:v>98.33</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:11">
       <x:c r="A69" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>1276630</x:v>
+        <x:v>1541630</x:v>
       </x:c>
       <x:c r="D69" s="0">
         <x:v>2500000</x:v>
@@ -3952,33 +3958,33 @@
         <x:v>225000000</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>93067011</x:v>
+        <x:v>111230111</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>0.74</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>0.38</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>67.75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J69" s="0">
-        <x:v>72.9</x:v>
+        <x:v>72.15</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:11">
       <x:c r="A70" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>7757299</x:v>
+        <x:v>8684003</x:v>
       </x:c>
       <x:c r="D70" s="0">
         <x:v>50000000</x:v>
@@ -3987,30 +3993,30 @@
         <x:v>2000000000</x:v>
       </x:c>
       <x:c r="F70" s="0">
-        <x:v>333154562</x:v>
+        <x:v>377730878</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>1.92</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.33</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>47.68</x:v>
+        <x:v>47.16</x:v>
       </x:c>
       <x:c r="J70" s="0">
-        <x:v>42.95</x:v>
+        <x:v>43.5</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:11">
       <x:c r="A71" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C71" s="0">
         <x:v>46360161</x:v>
@@ -4031,21 +4037,21 @@
         <x:v>0.52</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>14.46</x:v>
+        <x:v>14.04</x:v>
       </x:c>
       <x:c r="J71" s="0">
         <x:v>12.87</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:11">
       <x:c r="A72" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C72" s="0">
         <x:v>2114552</x:v>
@@ -4066,24 +4072,24 @@
         <x:v>0.41</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>23.5</x:v>
+        <x:v>22.92</x:v>
       </x:c>
       <x:c r="J72" s="0">
         <x:v>23.52</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:11">
       <x:c r="A73" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>2643000</x:v>
+        <x:v>2893000</x:v>
       </x:c>
       <x:c r="D73" s="0">
         <x:v>39725600</x:v>
@@ -4092,30 +4098,30 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F73" s="0">
-        <x:v>99043038</x:v>
+        <x:v>108415538</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>0.33</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>37.5</x:v>
+        <x:v>36.94</x:v>
       </x:c>
       <x:c r="J73" s="0">
-        <x:v>37.47</x:v>
+        <x:v>37.48</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:11">
       <x:c r="A74" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C74" s="0">
         <x:v>4740344</x:v>
@@ -4136,21 +4142,21 @@
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>128.5</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J74" s="0">
         <x:v>136.69</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:11">
       <x:c r="A75" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C75" s="0">
         <x:v>113000</x:v>
@@ -4171,7 +4177,7 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>288</x:v>
+        <x:v>287.25</x:v>
       </x:c>
       <x:c r="J75" s="0">
         <x:v>284.93</x:v>
@@ -4182,13 +4188,13 @@
     </x:row>
     <x:row r="76" spans="1:11">
       <x:c r="A76" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="C76" s="0">
-        <x:v>1181190</x:v>
+        <x:v>1231554</x:v>
       </x:c>
       <x:c r="D76" s="0">
         <x:v>2850000</x:v>
@@ -4197,30 +4203,30 @@
         <x:v>100000000</x:v>
       </x:c>
       <x:c r="F76" s="0">
-        <x:v>35947431</x:v>
+        <x:v>37479000</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>2.41</x:v>
+        <x:v>4.22</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>1</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>30.44</x:v>
+        <x:v>30.54</x:v>
       </x:c>
       <x:c r="J76" s="0">
         <x:v>30.43</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:11">
       <x:c r="A77" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>1214000</x:v>
@@ -4241,21 +4247,21 @@
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>52.25</x:v>
+        <x:v>52.5</x:v>
       </x:c>
       <x:c r="J77" s="0">
         <x:v>53.69</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:11">
       <x:c r="A78" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>13</x:v>
@@ -4276,7 +4282,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>9.25</x:v>
+        <x:v>8.63</x:v>
       </x:c>
       <x:c r="J78" s="0">
         <x:v>0</x:v>
@@ -4284,10 +4290,10 @@
     </x:row>
     <x:row r="79" spans="1:11">
       <x:c r="A79" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C79" s="0">
         <x:v>12450000</x:v>
@@ -4308,24 +4314,24 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>1.27</x:v>
+        <x:v>1.23</x:v>
       </x:c>
       <x:c r="J79" s="0">
         <x:v>4.89</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:11">
       <x:c r="A80" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>1499929</x:v>
+        <x:v>1519929</x:v>
       </x:c>
       <x:c r="D80" s="0">
         <x:v>36000000</x:v>
@@ -4334,7 +4340,7 @@
         <x:v>250000000</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>8104625</x:v>
+        <x:v>8211625</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>3.75</x:v>
@@ -4343,21 +4349,21 @@
         <x:v>0.16</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>5.42</x:v>
+        <x:v>5.28</x:v>
       </x:c>
       <x:c r="J80" s="0">
         <x:v>5.4</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:11">
       <x:c r="A81" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C81" s="0">
         <x:v>1577544</x:v>
@@ -4384,18 +4390,18 @@
         <x:v>7.98</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:11">
       <x:c r="A82" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>6533823</x:v>
+        <x:v>6618823</x:v>
       </x:c>
       <x:c r="D82" s="0">
         <x:v>13500000</x:v>
@@ -4404,30 +4410,30 @@
         <x:v>400000000</x:v>
       </x:c>
       <x:c r="F82" s="0">
-        <x:v>105984916</x:v>
+        <x:v>107411641</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>6.75</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>3.27</x:v>
+        <x:v>3.31</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>16.37</x:v>
+        <x:v>15.61</x:v>
       </x:c>
       <x:c r="J82" s="0">
-        <x:v>16.22</x:v>
+        <x:v>16.23</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:11">
       <x:c r="A83" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="C83" s="0">
         <x:v>21607359</x:v>
@@ -4448,7 +4454,7 @@
         <x:v>3.86</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>5.06</x:v>
+        <x:v>4.96</x:v>
       </x:c>
       <x:c r="J83" s="0">
         <x:v>6.91</x:v>
@@ -4459,10 +4465,10 @@
     </x:row>
     <x:row r="84" spans="1:11">
       <x:c r="A84" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C84" s="0">
         <x:v>11397816</x:v>
@@ -4483,21 +4489,21 @@
         <x:v>0.71</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>6</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="J84" s="0">
         <x:v>23.68</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:11">
       <x:c r="A85" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C85" s="0">
         <x:v>30224596</x:v>
@@ -4518,21 +4524,21 @@
         <x:v>1.24</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>3.76</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="J85" s="0">
         <x:v>3.75</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:11">
       <x:c r="A86" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C86" s="0">
         <x:v>2300000</x:v>
@@ -4553,21 +4559,21 @@
         <x:v>3.83</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>9.15</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="J86" s="0">
         <x:v>0.76</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:11">
       <x:c r="A87" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C87" s="0">
         <x:v>4790000</x:v>
@@ -4588,21 +4594,21 @@
         <x:v>7.98</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>3.97</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="J87" s="0">
         <x:v>1.47</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:11">
       <x:c r="A88" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C88" s="0">
         <x:v>4850000</x:v>
@@ -4623,21 +4629,21 @@
         <x:v>8.08</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>12.96</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="J88" s="0">
         <x:v>0.73</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:11">
       <x:c r="A89" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C89" s="0">
         <x:v>165166</x:v>
@@ -4658,21 +4664,21 @@
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>53.65</x:v>
+        <x:v>54.3</x:v>
       </x:c>
       <x:c r="J89" s="0">
         <x:v>60.51</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:11">
       <x:c r="A90" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C90" s="0">
         <x:v>37446277</x:v>
@@ -4693,21 +4699,21 @@
         <x:v>0.19</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>1.04</x:v>
+        <x:v>1.03</x:v>
       </x:c>
       <x:c r="J90" s="0">
         <x:v>1.14</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:11">
       <x:c r="A91" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>13</x:v>
@@ -4728,7 +4734,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>127.8</x:v>
+        <x:v>127.6</x:v>
       </x:c>
       <x:c r="J91" s="0">
         <x:v>0</x:v>
@@ -4736,10 +4742,10 @@
     </x:row>
     <x:row r="92" spans="1:11">
       <x:c r="A92" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="C92" s="0">
         <x:v>100000</x:v>
@@ -4760,21 +4766,21 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>3.26</x:v>
+        <x:v>3.11</x:v>
       </x:c>
       <x:c r="J92" s="0">
         <x:v>6.13</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:11">
       <x:c r="A93" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C93" s="0">
         <x:v>13920031</x:v>
@@ -4795,21 +4801,21 @@
         <x:v>0.58</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>9.43</x:v>
+        <x:v>9.4</x:v>
       </x:c>
       <x:c r="J93" s="0">
         <x:v>9.77</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:11">
       <x:c r="A94" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C94" s="0">
         <x:v>1800452</x:v>
@@ -4836,18 +4842,18 @@
         <x:v>9.69</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:11">
       <x:c r="A95" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>187494</x:v>
+        <x:v>237494</x:v>
       </x:c>
       <x:c r="D95" s="0">
         <x:v>13409218</x:v>
@@ -4856,30 +4862,30 @@
         <x:v>500000000</x:v>
       </x:c>
       <x:c r="F95" s="0">
-        <x:v>2865527</x:v>
+        <x:v>3565277</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>9.01</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>14.57</x:v>
+        <x:v>13.75</x:v>
       </x:c>
       <x:c r="J95" s="0">
-        <x:v>15.28</x:v>
+        <x:v>15.01</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:11">
       <x:c r="A96" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="C96" s="0">
         <x:v>11550000</x:v>
@@ -4900,7 +4906,7 @@
         <x:v>1.07</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>1.5</x:v>
+        <x:v>1.51</x:v>
       </x:c>
       <x:c r="J96" s="0">
         <x:v>1.51</x:v>
@@ -4911,10 +4917,10 @@
     </x:row>
     <x:row r="97" spans="1:11">
       <x:c r="A97" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C97" s="0">
         <x:v>300000</x:v>
@@ -4935,24 +4941,24 @@
         <x:v>0.27</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>16.05</x:v>
+        <x:v>15.41</x:v>
       </x:c>
       <x:c r="J97" s="0">
         <x:v>15.9</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:11">
       <x:c r="A98" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>16716406</x:v>
+        <x:v>22597643</x:v>
       </x:c>
       <x:c r="D98" s="0">
         <x:v>40000000</x:v>
@@ -4961,30 +4967,30 @@
         <x:v>1000000000</x:v>
       </x:c>
       <x:c r="F98" s="0">
-        <x:v>302765161</x:v>
+        <x:v>417908019</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>4.81</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>2.01</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>18.3</x:v>
+        <x:v>16.57</x:v>
       </x:c>
       <x:c r="J98" s="0">
-        <x:v>18.11</x:v>
+        <x:v>18.49</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:11">
       <x:c r="A99" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C99" s="0">
         <x:v>15160028</x:v>
@@ -5005,21 +5011,21 @@
         <x:v>0.86</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.18</x:v>
       </x:c>
       <x:c r="J99" s="0">
         <x:v>3.59</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:11">
       <x:c r="A100" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C100" s="0">
         <x:v>2500000</x:v>
@@ -5040,21 +5046,21 @@
         <x:v>0.21</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>411.25</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="J100" s="0">
         <x:v>380.17</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:11">
       <x:c r="A101" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="C101" s="0">
         <x:v>220399</x:v>
@@ -5075,21 +5081,21 @@
         <x:v>1.59</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>51.65</x:v>
+        <x:v>51.45</x:v>
       </x:c>
       <x:c r="J101" s="0">
         <x:v>68.91</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:11">
       <x:c r="A102" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C102" s="0">
         <x:v>2501710</x:v>
@@ -5110,21 +5116,21 @@
         <x:v>0.67</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>26.82</x:v>
+        <x:v>28.64</x:v>
       </x:c>
       <x:c r="J102" s="0">
         <x:v>38.82</x:v>
       </x:c>
       <x:c r="K102" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:11">
       <x:c r="A103" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C103" s="0">
         <x:v>76701016</x:v>
@@ -5145,21 +5151,21 @@
         <x:v>2.4</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>44.56</x:v>
+        <x:v>42.64</x:v>
       </x:c>
       <x:c r="J103" s="0">
         <x:v>47.51</x:v>
       </x:c>
       <x:c r="K103" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:11">
       <x:c r="A104" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C104" s="0">
         <x:v>69686718</x:v>
@@ -5180,21 +5186,21 @@
         <x:v>2.36</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>7.56</x:v>
+        <x:v>7.4</x:v>
       </x:c>
       <x:c r="J104" s="0">
         <x:v>32.87</x:v>
       </x:c>
       <x:c r="K104" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:11">
       <x:c r="A105" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C105" s="0">
         <x:v>100000</x:v>
@@ -5215,21 +5221,21 @@
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>14.29</x:v>
+        <x:v>14.48</x:v>
       </x:c>
       <x:c r="J105" s="0">
         <x:v>13.65</x:v>
       </x:c>
       <x:c r="K105" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:11">
       <x:c r="A106" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C106" s="0">
         <x:v>7999148</x:v>
@@ -5250,24 +5256,24 @@
         <x:v>2.11</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>15.14</x:v>
+        <x:v>14.51</x:v>
       </x:c>
       <x:c r="J106" s="0">
         <x:v>21.09</x:v>
       </x:c>
       <x:c r="K106" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:11">
       <x:c r="A107" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>1690000</x:v>
+        <x:v>1889006</x:v>
       </x:c>
       <x:c r="D107" s="0">
         <x:v>21739600</x:v>
@@ -5276,30 +5282,30 @@
         <x:v>350000000</x:v>
       </x:c>
       <x:c r="F107" s="0">
-        <x:v>13557684</x:v>
+        <x:v>15033163</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0.17</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>7.46</x:v>
+        <x:v>7.34</x:v>
       </x:c>
       <x:c r="J107" s="0">
-        <x:v>8.02</x:v>
+        <x:v>7.96</x:v>
       </x:c>
       <x:c r="K107" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:11">
       <x:c r="A108" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>13</x:v>
@@ -5328,10 +5334,10 @@
     </x:row>
     <x:row r="109" spans="1:11">
       <x:c r="A109" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C109" s="0">
         <x:v>3070328</x:v>
@@ -5352,21 +5358,21 @@
         <x:v>0.57</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>7.88</x:v>
+        <x:v>7.71</x:v>
       </x:c>
       <x:c r="J109" s="0">
         <x:v>6.98</x:v>
       </x:c>
       <x:c r="K109" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x